--- a/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="43">
   <si>
     <t>sector</t>
   </si>
@@ -169,6 +169,8 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -229,7 +231,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -250,6 +252,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -553,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.42578125" customWidth="1"/>
@@ -589,1405 +597,1405 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="C2" s="2">
         <v>2021</v>
       </c>
       <c r="D2" s="3">
-        <v>2688475.9724428668</v>
+        <v>496312.33844584553</v>
       </c>
       <c r="E2" s="3">
-        <v>22918.622383440001</v>
+        <v>6058.6276942799996</v>
       </c>
       <c r="F2" s="4">
-        <v>1.411209606183382E-2</v>
+        <v>1.149126975828702E-3</v>
       </c>
       <c r="G2" s="4">
-        <v>6.7540592802753808E-4</v>
+        <v>4.3326889923906344E-3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2022</v>
+      <c r="A3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2023</v>
       </c>
       <c r="D3" s="3">
-        <v>2237559.59010129</v>
+        <v>481190.63450056087</v>
       </c>
       <c r="E3" s="3">
-        <v>28962.7912646</v>
+        <v>5659.2905294400007</v>
       </c>
       <c r="F3" s="4">
-        <v>0.18094518011478611</v>
+        <v>2.7642536319032169E-4</v>
       </c>
       <c r="G3" s="4">
-        <v>2.339677504868966E-4</v>
+        <v>2.609783923120391E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="C4" s="2">
         <v>2022</v>
       </c>
       <c r="D4" s="3">
-        <v>2199098.9702055152</v>
+        <v>463554.2380744408</v>
       </c>
       <c r="E4" s="3">
-        <v>27186.587841839999</v>
+        <v>6405.1162323599992</v>
       </c>
       <c r="F4" s="4">
-        <v>1.428164445640567E-2</v>
+        <v>1.36542870460566E-3</v>
       </c>
       <c r="G4" s="4">
-        <v>1.063284111568874E-3</v>
+        <v>1.06191448730258E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="C5" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D5" s="3">
-        <v>2136662.9096641121</v>
+        <v>463215.01884109463</v>
       </c>
       <c r="E5" s="3">
-        <v>34419.6404244</v>
+        <v>6600.4823040000001</v>
       </c>
       <c r="F5" s="4">
-        <v>1.2450489874850871E-3</v>
+        <v>1.0184783005820781E-3</v>
       </c>
       <c r="G5" s="4">
-        <v>2.6914455891389468E-4</v>
+        <v>1.1952508372333631E-3</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="C6" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D6" s="3">
-        <v>2110825.0242093089</v>
+        <v>624490.81179662514</v>
       </c>
       <c r="E6" s="3">
-        <v>36820.330575920001</v>
+        <v>23490.718752000001</v>
       </c>
       <c r="F6" s="4">
-        <v>1.1388913987487259E-2</v>
+        <v>1.927088927244758E-3</v>
       </c>
       <c r="G6" s="4">
-        <v>1.346627653376551E-3</v>
+        <v>1.8760825696850091E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="C7" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D7" s="3">
-        <v>2060147.693651289</v>
+        <v>615005.46689121344</v>
       </c>
       <c r="E7" s="3">
-        <v>24111.565200000001</v>
+        <v>18304.5266156</v>
       </c>
       <c r="F7" s="4">
-        <v>1.6816288641435851E-2</v>
+        <v>2.0544865338363899E-3</v>
       </c>
       <c r="G7" s="4">
-        <v>4.7603910840263489E-4</v>
+        <v>2.397692315221963E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="C8" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D8" s="3">
-        <v>1963532.5336935241</v>
+        <v>557880.96074185451</v>
       </c>
       <c r="E8" s="3">
-        <v>38266.632667600003</v>
+        <v>17673.58753398</v>
       </c>
       <c r="F8" s="4">
-        <v>0.1254843771395045</v>
+        <v>1.2639185721094849E-3</v>
       </c>
       <c r="G8" s="4">
-        <v>3.2594779133939081E-4</v>
+        <v>7.224852054202324E-4</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="C9" s="2">
         <v>2022</v>
       </c>
       <c r="D9" s="3">
-        <v>1501058.080583167</v>
+        <v>528936.59684355662</v>
       </c>
       <c r="E9" s="3">
-        <v>10016.90090194</v>
+        <v>14840.029964359999</v>
       </c>
       <c r="F9" s="4">
-        <v>4.8543989239808157E-3</v>
+        <v>3.348617336982791E-3</v>
       </c>
       <c r="G9" s="4">
-        <v>2.722411311338672E-3</v>
+        <v>9.7700369843055682E-4</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="C10" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D10" s="3">
-        <v>1438073.2884498299</v>
+        <v>480752.63075950177</v>
       </c>
       <c r="E10" s="3">
-        <v>33002.728752000003</v>
+        <v>13713.99982974</v>
       </c>
       <c r="F10" s="4">
-        <v>1.2530342781881009E-2</v>
+        <v>1.8909555433829729E-4</v>
       </c>
       <c r="G10" s="4">
-        <v>4.7058508757579111E-4</v>
+        <v>1.421912259449817E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="C11" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D11" s="3">
-        <v>1291276.529800517</v>
+        <v>430680.74778667098</v>
       </c>
       <c r="E11" s="3">
-        <v>12420.628572240001</v>
+        <v>9650.7308639999992</v>
       </c>
       <c r="F11" s="4">
-        <v>9.5505969516812179E-3</v>
+        <v>3.2382873836611008E-4</v>
       </c>
       <c r="G11" s="4">
-        <v>7.1947529628030547E-3</v>
+        <v>1.307147425181787E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="C12" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D12" s="3">
-        <v>1235191.2922385989</v>
+        <v>344818.33344279532</v>
       </c>
       <c r="E12" s="3">
-        <v>17766.839759999999</v>
+        <v>7766.5175531200011</v>
       </c>
       <c r="F12" s="4">
-        <v>9.3958949512133153E-4</v>
+        <v>5.6879237956854514E-4</v>
       </c>
       <c r="G12" s="4">
-        <v>8.8262764857625984E-4</v>
+        <v>9.2862762115340628E-4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D13" s="3">
-        <v>1202957.7138338401</v>
+        <v>310794.74797233898</v>
       </c>
       <c r="E13" s="3">
-        <v>13409.25543712</v>
+        <v>8210.8821614400003</v>
       </c>
       <c r="F13" s="4">
-        <v>1.2431315547808089E-3</v>
+        <v>1.515288413031857E-4</v>
       </c>
       <c r="G13" s="4">
-        <v>1.4794270549193711E-3</v>
+        <v>1.134724744407487E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="C14" s="2">
         <v>2024</v>
       </c>
       <c r="D14" s="3">
-        <v>1079590.799601601</v>
+        <v>615324.90182869229</v>
       </c>
       <c r="E14" s="3">
-        <v>29824.255583999999</v>
+        <v>12188.037840000001</v>
       </c>
       <c r="F14" s="4">
-        <v>1.7700063980245699E-2</v>
+        <v>3.5563801629943082E-3</v>
       </c>
       <c r="G14" s="4">
-        <v>1.8406361575525849E-2</v>
+        <v>2.3262126662383252E-3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="C15" s="2">
         <v>2023</v>
       </c>
       <c r="D15" s="3">
-        <v>917032.53729645221</v>
+        <v>463470.71898289572</v>
       </c>
       <c r="E15" s="3">
-        <v>21948.7441788</v>
+        <v>9380.3853557600014</v>
       </c>
       <c r="F15" s="4">
-        <v>5.1385668600091312E-2</v>
+        <v>2.4821681068467739E-3</v>
       </c>
       <c r="G15" s="4">
-        <v>1.045825844659099E-3</v>
+        <v>1.7821392198706289E-3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="C16" s="2">
         <v>2022</v>
       </c>
       <c r="D16" s="3">
-        <v>802566.08061441511</v>
+        <v>441905.15975913568</v>
       </c>
       <c r="E16" s="3">
-        <v>12046.641059559999</v>
+        <v>8680.9984719799995</v>
       </c>
       <c r="F16" s="4">
-        <v>1.264319260007594E-2</v>
+        <v>5.3628300774693723E-2</v>
       </c>
       <c r="G16" s="4">
-        <v>9.2646432850616075E-4</v>
+        <v>1.9809359137092151E-3</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="C17" s="2">
         <v>2021</v>
       </c>
       <c r="D17" s="3">
-        <v>774599.50938466226</v>
+        <v>396416.47748978873</v>
       </c>
       <c r="E17" s="3">
-        <v>31768.917493320001</v>
+        <v>10615.43888874</v>
       </c>
       <c r="F17" s="4">
-        <v>4.5024994770462897E-3</v>
+        <v>5.7122249315871114E-3</v>
       </c>
       <c r="G17" s="4">
-        <v>6.1504127372638605E-4</v>
+        <v>1.223257961926933E-3</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="C18" s="2">
         <v>2024</v>
       </c>
       <c r="D18" s="3">
-        <v>702640.28510284843</v>
+        <v>333902.21266145178</v>
       </c>
       <c r="E18" s="3">
-        <v>24692.815392</v>
+        <v>6590.0541599999997</v>
       </c>
       <c r="F18" s="4">
-        <v>1.2473785395074479E-2</v>
+        <v>3.968817154607421E-3</v>
       </c>
       <c r="G18" s="4">
-        <v>1.210844187888221E-3</v>
+        <v>1.4273582237145071E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="C19" s="2">
         <v>2023</v>
       </c>
       <c r="D19" s="3">
-        <v>648523.59030139784</v>
+        <v>289865.32010952412</v>
       </c>
       <c r="E19" s="3">
-        <v>20365.73930736</v>
+        <v>5130.8202951200001</v>
       </c>
       <c r="F19" s="4">
-        <v>2.3285205202868371E-2</v>
+        <v>7.1409024001186736E-3</v>
       </c>
       <c r="G19" s="4">
-        <v>1.5783067550306741E-3</v>
+        <v>1.6292149323472839E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="C20" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D20" s="3">
-        <v>624490.81179662514</v>
+        <v>259818.50988372459</v>
       </c>
       <c r="E20" s="3">
-        <v>23490.718752000001</v>
+        <v>45922.658233419999</v>
       </c>
       <c r="F20" s="4">
-        <v>1.927088927244758E-3</v>
+        <v>4.0433840100499702E-5</v>
       </c>
       <c r="G20" s="4">
-        <v>1.8760825696850091E-3</v>
+        <v>1.5232724169502069E-4</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="C21" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D21" s="3">
-        <v>615324.90182869229</v>
+        <v>234189.89306239539</v>
       </c>
       <c r="E21" s="3">
-        <v>12188.037840000001</v>
+        <v>4733.3383234200001</v>
       </c>
       <c r="F21" s="4">
-        <v>3.5563801629943082E-3</v>
+        <v>6.6356632156617178E-4</v>
       </c>
       <c r="G21" s="4">
-        <v>2.3262126662383252E-3</v>
+        <v>3.1476572520248271E-3</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="C22" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D22" s="3">
-        <v>615005.46689121344</v>
+        <v>702640.28510284843</v>
       </c>
       <c r="E22" s="3">
-        <v>18304.5266156</v>
+        <v>24692.815392</v>
       </c>
       <c r="F22" s="4">
-        <v>2.0544865338363899E-3</v>
+        <v>1.2473785395074479E-2</v>
       </c>
       <c r="G22" s="4">
-        <v>2.397692315221963E-3</v>
+        <v>1.210844187888221E-3</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="C23" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D23" s="3">
-        <v>589836.07301855378</v>
+        <v>648523.59030139784</v>
       </c>
       <c r="E23" s="3">
-        <v>3459.2387039999999</v>
+        <v>20365.73930736</v>
       </c>
       <c r="F23" s="4">
-        <v>2.6129124854981389E-3</v>
+        <v>2.3285205202868371E-2</v>
       </c>
       <c r="G23" s="4">
-        <v>2.2962786554205951E-3</v>
+        <v>1.5783067550306741E-3</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="C24" s="2">
         <v>2022</v>
       </c>
       <c r="D24" s="3">
-        <v>585427.26654459862</v>
+        <v>525586.90611574077</v>
       </c>
       <c r="E24" s="3">
-        <v>4854.6591208600003</v>
+        <v>57596.7124071</v>
       </c>
       <c r="F24" s="4">
-        <v>3.7612999688359748E-4</v>
+        <v>6.9328647193893768E-4</v>
       </c>
       <c r="G24" s="4">
-        <v>2.0756040556386131E-3</v>
+        <v>1.2640594598421069E-2</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="C25" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D25" s="3">
-        <v>575669.32501484314</v>
+        <v>489831.22166003252</v>
       </c>
       <c r="E25" s="3">
-        <v>4774.9529707199999</v>
+        <v>28233.8392518</v>
       </c>
       <c r="F25" s="4">
-        <v>2.8738600116371028E-4</v>
+        <v>1.7629362658082969E-3</v>
       </c>
       <c r="G25" s="4">
-        <v>1.316480132589062E-3</v>
+        <v>1.091290811894655E-3</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="C26" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D26" s="3">
-        <v>557880.96074185451</v>
+        <v>1079590.799601601</v>
       </c>
       <c r="E26" s="3">
-        <v>17673.58753398</v>
+        <v>29824.255583999999</v>
       </c>
       <c r="F26" s="4">
-        <v>1.2639185721094849E-3</v>
+        <v>1.7700063980245699E-2</v>
       </c>
       <c r="G26" s="4">
-        <v>7.224852054202324E-4</v>
+        <v>1.8406361575525849E-2</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="C27" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D27" s="3">
-        <v>532258.74860418728</v>
+        <v>917032.53729645221</v>
       </c>
       <c r="E27" s="3">
-        <v>5998.8555937799993</v>
+        <v>21948.7441788</v>
       </c>
       <c r="F27" s="4">
-        <v>3.3561812091085249E-3</v>
+        <v>5.1385668600091312E-2</v>
       </c>
       <c r="G27" s="4">
-        <v>1.7434020366891251E-3</v>
+        <v>1.045825844659099E-3</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="C28" s="2">
         <v>2022</v>
       </c>
       <c r="D28" s="3">
-        <v>528936.59684355662</v>
+        <v>802566.08061441511</v>
       </c>
       <c r="E28" s="3">
-        <v>14840.029964359999</v>
+        <v>12046.641059559999</v>
       </c>
       <c r="F28" s="4">
-        <v>3.348617336982791E-3</v>
+        <v>1.264319260007594E-2</v>
       </c>
       <c r="G28" s="4">
-        <v>9.7700369843055682E-4</v>
+        <v>9.2646432850616075E-4</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="C29" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D29" s="3">
-        <v>525586.90611574077</v>
+        <v>774599.50938466226</v>
       </c>
       <c r="E29" s="3">
-        <v>57596.7124071</v>
+        <v>31768.917493320001</v>
       </c>
       <c r="F29" s="4">
-        <v>6.9328647193893768E-4</v>
+        <v>4.5024994770462897E-3</v>
       </c>
       <c r="G29" s="4">
-        <v>1.2640594598421069E-2</v>
+        <v>6.1504127372638605E-4</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="C30" s="2">
         <v>2021</v>
       </c>
       <c r="D30" s="3">
-        <v>496312.33844584553</v>
+        <v>2688475.9724428668</v>
       </c>
       <c r="E30" s="3">
-        <v>6058.6276942799996</v>
+        <v>22918.622383440001</v>
       </c>
       <c r="F30" s="4">
-        <v>1.149126975828702E-3</v>
+        <v>1.411209606183382E-2</v>
       </c>
       <c r="G30" s="4">
-        <v>4.3326889923906344E-3</v>
+        <v>6.7540592802753808E-4</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="C31" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D31" s="3">
-        <v>489831.22166003252</v>
+        <v>2199098.9702055152</v>
       </c>
       <c r="E31" s="3">
-        <v>28233.8392518</v>
+        <v>27186.587841839999</v>
       </c>
       <c r="F31" s="4">
-        <v>1.7629362658082969E-3</v>
+        <v>1.428164445640567E-2</v>
       </c>
       <c r="G31" s="4">
-        <v>1.091290811894655E-3</v>
+        <v>1.063284111568874E-3</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="5">
+      <c r="A32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="2">
         <v>2023</v>
       </c>
       <c r="D32" s="3">
-        <v>481190.63450056087</v>
+        <v>2110825.0242093089</v>
       </c>
       <c r="E32" s="3">
-        <v>5659.2905294400007</v>
+        <v>36820.330575920001</v>
       </c>
       <c r="F32" s="4">
-        <v>2.7642536319032169E-4</v>
+        <v>1.1388913987487259E-2</v>
       </c>
       <c r="G32" s="4">
-        <v>2.609783923120391E-3</v>
+        <v>1.346627653376551E-3</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="C33" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D33" s="3">
-        <v>480752.63075950177</v>
+        <v>2060147.693651289</v>
       </c>
       <c r="E33" s="3">
-        <v>13713.99982974</v>
+        <v>24111.565200000001</v>
       </c>
       <c r="F33" s="4">
-        <v>1.8909555433829729E-4</v>
+        <v>1.6816288641435851E-2</v>
       </c>
       <c r="G33" s="4">
-        <v>1.421912259449817E-2</v>
+        <v>4.7603910840263489E-4</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>38</v>
+        <v>21</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="C34" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D34" s="3">
-        <v>463554.2380744408</v>
+        <v>589836.07301855378</v>
       </c>
       <c r="E34" s="3">
-        <v>6405.1162323599992</v>
+        <v>3459.2387039999999</v>
       </c>
       <c r="F34" s="4">
-        <v>1.36542870460566E-3</v>
+        <v>2.6129124854981389E-3</v>
       </c>
       <c r="G34" s="4">
-        <v>1.06191448730258E-3</v>
+        <v>2.2962786554205951E-3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="C35" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D35" s="3">
-        <v>463470.71898289572</v>
+        <v>585427.26654459862</v>
       </c>
       <c r="E35" s="3">
-        <v>9380.3853557600014</v>
+        <v>4854.6591208600003</v>
       </c>
       <c r="F35" s="4">
-        <v>2.4821681068467739E-3</v>
+        <v>3.7612999688359748E-4</v>
       </c>
       <c r="G35" s="4">
-        <v>1.7821392198706289E-3</v>
+        <v>2.0756040556386131E-3</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>38</v>
+        <v>21</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="C36" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D36" s="3">
-        <v>463215.01884109463</v>
+        <v>575669.32501484314</v>
       </c>
       <c r="E36" s="3">
-        <v>6600.4823040000001</v>
+        <v>4774.9529707199999</v>
       </c>
       <c r="F36" s="4">
-        <v>1.0184783005820781E-3</v>
+        <v>2.8738600116371028E-4</v>
       </c>
       <c r="G36" s="4">
-        <v>1.1952508372333631E-3</v>
+        <v>1.316480132589062E-3</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="C37" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D37" s="3">
-        <v>441905.15975913568</v>
+        <v>532258.74860418728</v>
       </c>
       <c r="E37" s="3">
-        <v>8680.9984719799995</v>
+        <v>5998.8555937799993</v>
       </c>
       <c r="F37" s="4">
-        <v>5.3628300774693723E-2</v>
+        <v>3.3561812091085249E-3</v>
       </c>
       <c r="G37" s="4">
-        <v>1.9809359137092151E-3</v>
+        <v>1.7434020366891251E-3</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="C38" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D38" s="3">
-        <v>430680.74778667098</v>
+        <v>327266.01547195681</v>
       </c>
       <c r="E38" s="3">
-        <v>9650.7308639999992</v>
+        <v>2736.7203125999999</v>
       </c>
       <c r="F38" s="4">
-        <v>3.2382873836611008E-4</v>
+        <v>6.5575458761258591E-4</v>
       </c>
       <c r="G38" s="4">
-        <v>1.307147425181787E-3</v>
+        <v>9.6186040198574876E-4</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="C39" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D39" s="3">
-        <v>396416.47748978873</v>
+        <v>323997.44760210218</v>
       </c>
       <c r="E39" s="3">
-        <v>10615.43888874</v>
+        <v>2594.2840083999999</v>
       </c>
       <c r="F39" s="4">
-        <v>5.7122249315871114E-3</v>
+        <v>4.4144095106468531E-4</v>
       </c>
       <c r="G39" s="4">
-        <v>1.223257961926933E-3</v>
+        <v>4.2813564143465432E-3</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="C40" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D40" s="3">
-        <v>391236.03926557873</v>
+        <v>321762.90970591619</v>
       </c>
       <c r="E40" s="3">
-        <v>9174.7777388399991</v>
+        <v>2793.945984</v>
       </c>
       <c r="F40" s="4">
-        <v>7.2720955318134649E-3</v>
+        <v>3.0877619142976242E-4</v>
       </c>
       <c r="G40" s="4">
-        <v>4.0538663342816288E-4</v>
+        <v>1.0062327675981299E-3</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="C41" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D41" s="3">
-        <v>344818.33344279532</v>
+        <v>297602.00445720641</v>
       </c>
       <c r="E41" s="3">
-        <v>7766.5175531200011</v>
+        <v>3256.4356082999998</v>
       </c>
       <c r="F41" s="4">
-        <v>5.6879237956854514E-4</v>
+        <v>3.8592436982227681E-4</v>
       </c>
       <c r="G41" s="4">
-        <v>9.2862762115340628E-4</v>
+        <v>2.369477916386043E-3</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="C42" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D42" s="3">
-        <v>333902.21266145178</v>
+        <v>391236.03926557873</v>
       </c>
       <c r="E42" s="3">
-        <v>6590.0541599999997</v>
+        <v>9174.7777388399991</v>
       </c>
       <c r="F42" s="4">
-        <v>3.968817154607421E-3</v>
+        <v>7.2720955318134649E-3</v>
       </c>
       <c r="G42" s="4">
-        <v>1.4273582237145071E-3</v>
+        <v>4.0538663342816288E-4</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="C43" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D43" s="3">
-        <v>332033.64455055603</v>
+        <v>331000.25434189721</v>
       </c>
       <c r="E43" s="3">
-        <v>1720.9347523199999</v>
+        <v>7502.6813292799998</v>
       </c>
       <c r="F43" s="4">
-        <v>5.4438237053266124E-4</v>
+        <v>1.753601618218082E-3</v>
       </c>
       <c r="G43" s="4">
-        <v>1.095196036606934E-3</v>
+        <v>3.3407912051630981E-4</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="8" t="s">
         <v>18</v>
       </c>
       <c r="C44" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D44" s="3">
-        <v>331000.25434189721</v>
+        <v>315114.80271184049</v>
       </c>
       <c r="E44" s="3">
-        <v>7502.6813292799998</v>
+        <v>3780.5631839999992</v>
       </c>
       <c r="F44" s="4">
-        <v>1.753601618218082E-3</v>
+        <v>1.04121883656369E-2</v>
       </c>
       <c r="G44" s="4">
-        <v>3.3407912051630981E-4</v>
+        <v>1.4970467955548929E-3</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="C45" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D45" s="3">
-        <v>327266.01547195681</v>
+        <v>311812.99097068148</v>
       </c>
       <c r="E45" s="3">
-        <v>2736.7203125999999</v>
+        <v>3403.6800820799999</v>
       </c>
       <c r="F45" s="4">
-        <v>6.5575458761258591E-4</v>
+        <v>7.8396110552474759E-4</v>
       </c>
       <c r="G45" s="4">
-        <v>9.6186040198574876E-4</v>
+        <v>1.35821810761219E-3</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="C46" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D46" s="3">
-        <v>323997.44760210218</v>
+        <v>1501058.080583167</v>
       </c>
       <c r="E46" s="3">
-        <v>2594.2840083999999</v>
+        <v>10016.90090194</v>
       </c>
       <c r="F46" s="4">
-        <v>4.4144095106468531E-4</v>
+        <v>4.8543989239808157E-3</v>
       </c>
       <c r="G46" s="4">
-        <v>4.2813564143465432E-3</v>
+        <v>2.722411311338672E-3</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="C47" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D47" s="3">
-        <v>321762.90970591619</v>
+        <v>1291276.529800517</v>
       </c>
       <c r="E47" s="3">
-        <v>2793.945984</v>
+        <v>12420.628572240001</v>
       </c>
       <c r="F47" s="4">
-        <v>3.0877619142976242E-4</v>
+        <v>9.5505969516812179E-3</v>
       </c>
       <c r="G47" s="4">
-        <v>1.0062327675981299E-3</v>
+        <v>7.1947529628030547E-3</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="C48" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D48" s="3">
-        <v>320449.11322310509</v>
+        <v>1235191.2922385989</v>
       </c>
       <c r="E48" s="3">
-        <v>3164.1185242800002</v>
+        <v>17766.839759999999</v>
       </c>
       <c r="F48" s="4">
-        <v>6.7699852441129374E-3</v>
+        <v>9.3958949512133153E-4</v>
       </c>
       <c r="G48" s="4">
-        <v>2.6803313639870169E-3</v>
+        <v>8.8262764857625984E-4</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="C49" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D49" s="3">
-        <v>315114.80271184049</v>
+        <v>1202957.7138338401</v>
       </c>
       <c r="E49" s="3">
-        <v>3780.5631839999992</v>
+        <v>13409.25543712</v>
       </c>
       <c r="F49" s="4">
-        <v>1.04121883656369E-2</v>
+        <v>1.2431315547808089E-3</v>
       </c>
       <c r="G49" s="4">
-        <v>1.4970467955548929E-3</v>
+        <v>1.4794270549193711E-3</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="C50" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D50" s="3">
-        <v>311812.99097068148</v>
+        <v>2237559.59010129</v>
       </c>
       <c r="E50" s="3">
-        <v>3403.6800820799999</v>
+        <v>28962.7912646</v>
       </c>
       <c r="F50" s="4">
-        <v>7.8396110552474759E-4</v>
+        <v>0.18094518011478611</v>
       </c>
       <c r="G50" s="4">
-        <v>1.35821810761219E-3</v>
+        <v>2.339677504868966E-4</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>34</v>
+        <v>13</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="C51" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D51" s="3">
-        <v>310794.74797233898</v>
+        <v>2136662.9096641121</v>
       </c>
       <c r="E51" s="3">
-        <v>8210.8821614400003</v>
+        <v>34419.6404244</v>
       </c>
       <c r="F51" s="4">
-        <v>1.515288413031857E-4</v>
+        <v>1.2450489874850871E-3</v>
       </c>
       <c r="G51" s="4">
-        <v>1.134724744407487E-2</v>
+        <v>2.6914455891389468E-4</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="C52" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D52" s="3">
-        <v>297602.00445720641</v>
+        <v>1963532.5336935241</v>
       </c>
       <c r="E52" s="3">
-        <v>3256.4356082999998</v>
+        <v>38266.632667600003</v>
       </c>
       <c r="F52" s="4">
-        <v>3.8592436982227681E-4</v>
+        <v>0.1254843771395045</v>
       </c>
       <c r="G52" s="4">
-        <v>2.369477916386043E-3</v>
+        <v>3.2594779133939081E-4</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="C53" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D53" s="3">
-        <v>289865.32010952412</v>
+        <v>1438073.2884498299</v>
       </c>
       <c r="E53" s="3">
-        <v>5130.8202951200001</v>
+        <v>33002.728752000003</v>
       </c>
       <c r="F53" s="4">
-        <v>7.1409024001186736E-3</v>
+        <v>1.2530342781881009E-2</v>
       </c>
       <c r="G53" s="4">
-        <v>1.6292149323472839E-3</v>
+        <v>4.7058508757579111E-4</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="C54" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D54" s="3">
-        <v>269939.47590449912</v>
+        <v>97959.145876195587</v>
       </c>
       <c r="E54" s="3">
-        <v>2592.956784</v>
+        <v>683.65838265999992</v>
       </c>
       <c r="F54" s="4">
-        <v>1.8052595511364291E-3</v>
+        <v>5.6993377084615887E-5</v>
       </c>
       <c r="G54" s="4">
-        <v>8.4950123873718997E-4</v>
+        <v>2.003412193486057E-3</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="C55" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D55" s="3">
-        <v>262055.5197426404</v>
+        <v>95591.120637130909</v>
       </c>
       <c r="E55" s="3">
-        <v>1735.1564722600001</v>
+        <v>1766.41918304</v>
       </c>
       <c r="F55" s="4">
-        <v>3.0591654094954831E-3</v>
+        <v>1.0827214844375309E-3</v>
       </c>
       <c r="G55" s="4">
-        <v>7.4264450532327117E-4</v>
+        <v>1.157616504413661E-3</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>30</v>
+        <v>11</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="C56" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D56" s="3">
-        <v>259818.50988372459</v>
+        <v>82867.321381128873</v>
       </c>
       <c r="E56" s="3">
-        <v>45922.658233419999</v>
+        <v>2276.6300928000001</v>
       </c>
       <c r="F56" s="4">
-        <v>4.0433840100499702E-5</v>
+        <v>2.6907058899788261E-3</v>
       </c>
       <c r="G56" s="4">
-        <v>1.5232724169502069E-4</v>
+        <v>8.8722397476340717E-4</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="C57" s="2">
         <v>2021</v>
       </c>
       <c r="D57" s="3">
-        <v>234189.89306239539</v>
+        <v>320449.11322310509</v>
       </c>
       <c r="E57" s="3">
-        <v>4733.3383234200001</v>
+        <v>3164.1185242800002</v>
       </c>
       <c r="F57" s="4">
-        <v>6.6356632156617178E-4</v>
+        <v>6.7699852441129374E-3</v>
       </c>
       <c r="G57" s="4">
-        <v>3.1476572520248271E-3</v>
+        <v>2.6803313639870169E-3</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="C58" s="2">
         <v>2024</v>
       </c>
       <c r="D58" s="3">
-        <v>208604.95707132079</v>
+        <v>269939.47590449912</v>
       </c>
       <c r="E58" s="3">
-        <v>1402.2910079999999</v>
+        <v>2592.956784</v>
       </c>
       <c r="F58" s="4">
-        <v>2.940331198358508E-3</v>
+        <v>1.8052595511364291E-3</v>
       </c>
       <c r="G58" s="4">
-        <v>9.1745863922704425E-4</v>
+        <v>8.4950123873718997E-4</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D59" s="3">
-        <v>201018.8383422663</v>
+        <v>332033.64455055603</v>
       </c>
       <c r="E59" s="3">
-        <v>1914.6587492000001</v>
+        <v>1720.9347523199999</v>
       </c>
       <c r="F59" s="4">
-        <v>2.4675821537253392E-3</v>
+        <v>5.4438237053266124E-4</v>
       </c>
       <c r="G59" s="4">
-        <v>4.9806477545852595E-4</v>
+        <v>1.095196036606934E-3</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="C60" s="2">
         <v>2022</v>
       </c>
       <c r="D60" s="3">
-        <v>97959.145876195587</v>
+        <v>262055.5197426404</v>
       </c>
       <c r="E60" s="3">
-        <v>683.65838265999992</v>
+        <v>1735.1564722600001</v>
       </c>
       <c r="F60" s="4">
-        <v>5.6993377084615887E-5</v>
+        <v>3.0591654094954831E-3</v>
       </c>
       <c r="G60" s="4">
-        <v>2.003412193486057E-3</v>
+        <v>7.4264450532327117E-4</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="C61" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D61" s="3">
-        <v>95591.120637130909</v>
+        <v>208604.95707132079</v>
       </c>
       <c r="E61" s="3">
-        <v>1766.41918304</v>
+        <v>1402.2910079999999</v>
       </c>
       <c r="F61" s="4">
-        <v>1.0827214844375309E-3</v>
+        <v>2.940331198358508E-3</v>
       </c>
       <c r="G61" s="4">
-        <v>1.157616504413661E-3</v>
+        <v>9.1745863922704425E-4</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="C62" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D62" s="3">
-        <v>82867.321381128873</v>
+        <v>201018.8383422663</v>
       </c>
       <c r="E62" s="3">
-        <v>2276.6300928000001</v>
+        <v>1914.6587492000001</v>
       </c>
       <c r="F62" s="4">
-        <v>2.6907058899788261E-3</v>
+        <v>2.4675821537253392E-3</v>
       </c>
       <c r="G62" s="4">
-        <v>8.8722397476340717E-4</v>
+        <v>4.9806477545852595E-4</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -1999,77 +2007,3865 @@
         <v>481190.63450056087</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B65" s="7"/>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B66" s="7" t="s">
         <v>40</v>
       </c>
       <c r="D66" s="3">
         <f>AVERAGE(D2:D31)</f>
-        <v>1124212.4339560324</v>
+        <v>655349.05308665475</v>
       </c>
       <c r="E66" s="3">
         <f t="shared" ref="E66:G66" si="0">AVERAGE(E2:E31)</f>
-        <v>21247.447441487337</v>
+        <v>17273.303883399334</v>
       </c>
       <c r="F66" s="4">
         <f t="shared" si="0"/>
-        <v>1.7925682509706109E-2</v>
+        <v>8.1223329477286606E-3</v>
       </c>
       <c r="G66" s="4">
         <f t="shared" si="0"/>
-        <v>2.4906293556901716E-3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+        <v>3.1965856646829407E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B67" s="7" t="s">
         <v>41</v>
       </c>
       <c r="D67" s="3">
         <f>AVERAGE(D33:D62)</f>
-        <v>313456.52033605945</v>
+        <v>727998.75488181249</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" ref="E67:G67" si="1">AVERAGE(E33:E62)</f>
-        <v>6530.0444956386673</v>
+        <v>9465.4867188440021</v>
       </c>
       <c r="F67" s="4">
         <f t="shared" si="1"/>
-        <v>4.0228145149423019E-3</v>
+        <v>1.3455747789443185E-2</v>
       </c>
       <c r="G67" s="4">
         <f t="shared" si="1"/>
-        <v>2.1482436181387908E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+        <v>1.4843925181374825E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C69" s="7" t="s">
         <v>42</v>
       </c>
       <c r="D69" s="3">
         <f>D66/D67</f>
-        <v>3.5865019899753703</v>
+        <v>0.90020628289817317</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" ref="E69:G69" si="2">E66/E67</f>
-        <v>3.2537982636532159</v>
+        <v>1.8248722328257498</v>
       </c>
       <c r="F69" s="3">
         <f t="shared" si="2"/>
-        <v>4.4560052279624465</v>
+        <v>0.60363296598804428</v>
       </c>
       <c r="G69" s="3">
         <f t="shared" si="2"/>
-        <v>1.1593793807464068</v>
+        <v>2.1534638753729403</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D72" s="3">
+        <v>332033.64455055603</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1720.9347523199999</v>
+      </c>
+      <c r="F72" s="4">
+        <v>5.4438237053266124E-4</v>
+      </c>
+      <c r="G72" s="4">
+        <v>1.095196036606934E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D73" s="3">
+        <v>262055.5197426404</v>
+      </c>
+      <c r="E73" s="3">
+        <v>1735.1564722600001</v>
+      </c>
+      <c r="F73" s="4">
+        <v>3.0591654094954831E-3</v>
+      </c>
+      <c r="G73" s="4">
+        <v>7.4264450532327117E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D74" s="3">
+        <v>208604.95707132079</v>
+      </c>
+      <c r="E74" s="3">
+        <v>1402.2910079999999</v>
+      </c>
+      <c r="F74" s="4">
+        <v>2.940331198358508E-3</v>
+      </c>
+      <c r="G74" s="4">
+        <v>9.1745863922704425E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D75" s="3">
+        <v>201018.8383422663</v>
+      </c>
+      <c r="E75" s="3">
+        <v>1914.6587492000001</v>
+      </c>
+      <c r="F75" s="4">
+        <v>2.4675821537253392E-3</v>
+      </c>
+      <c r="G75" s="4">
+        <v>4.9806477545852595E-4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D77" s="3">
+        <f>AVERAGE(D72:D73)</f>
+        <v>297044.5821465982</v>
+      </c>
+      <c r="E77" s="3">
+        <f t="shared" ref="E77:G77" si="3">AVERAGE(E72:E73)</f>
+        <v>1728.04561229</v>
+      </c>
+      <c r="F77" s="4">
+        <f t="shared" si="3"/>
+        <v>1.8017738900140722E-3</v>
+      </c>
+      <c r="G77" s="4">
+        <f t="shared" si="3"/>
+        <v>9.1892027096510251E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D78" s="3">
+        <f>AVERAGE(D74:D75)</f>
+        <v>204811.89770679356</v>
+      </c>
+      <c r="E78" s="3">
+        <f t="shared" ref="E78:G78" si="4">AVERAGE(E74:E75)</f>
+        <v>1658.4748786</v>
+      </c>
+      <c r="F78" s="4">
+        <f t="shared" si="4"/>
+        <v>2.7039566760419234E-3</v>
+      </c>
+      <c r="G78" s="4">
+        <f t="shared" si="4"/>
+        <v>7.0776170734278515E-4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C80" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D80" s="3">
+        <f>D77/D78</f>
+        <v>1.4503287429709963</v>
+      </c>
+      <c r="E80" s="3">
+        <f t="shared" ref="E80:G80" si="5">E77/E78</f>
+        <v>1.0419486207404769</v>
+      </c>
+      <c r="F80" s="3">
+        <f t="shared" si="5"/>
+        <v>0.6663471741165341</v>
+      </c>
+      <c r="G80" s="3">
+        <f t="shared" si="5"/>
+        <v>1.2983469738919464</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C83" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D83" s="3">
+        <v>2237559.59010129</v>
+      </c>
+      <c r="E83" s="3">
+        <v>28962.7912646</v>
+      </c>
+      <c r="F83" s="4">
+        <v>0.18094518011478611</v>
+      </c>
+      <c r="G83" s="4">
+        <v>2.339677504868966E-4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D84" s="3">
+        <v>2136662.9096641121</v>
+      </c>
+      <c r="E84" s="3">
+        <v>34419.6404244</v>
+      </c>
+      <c r="F84" s="4">
+        <v>1.2450489874850871E-3</v>
+      </c>
+      <c r="G84" s="4">
+        <v>2.6914455891389468E-4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D85" s="3">
+        <v>1963532.5336935241</v>
+      </c>
+      <c r="E85" s="3">
+        <v>38266.632667600003</v>
+      </c>
+      <c r="F85" s="4">
+        <v>0.1254843771395045</v>
+      </c>
+      <c r="G85" s="4">
+        <v>3.2594779133939081E-4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D86" s="3">
+        <v>1438073.2884498299</v>
+      </c>
+      <c r="E86" s="3">
+        <v>33002.728752000003</v>
+      </c>
+      <c r="F86" s="4">
+        <v>1.2530342781881009E-2</v>
+      </c>
+      <c r="G86" s="4">
+        <v>4.7058508757579111E-4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B88" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D88" s="3">
+        <f>AVERAGE(D83:D84)</f>
+        <v>2187111.2498827009</v>
+      </c>
+      <c r="E88" s="3">
+        <f t="shared" ref="E88:G88" si="6">AVERAGE(E83:E84)</f>
+        <v>31691.215844500002</v>
+      </c>
+      <c r="F88" s="4">
+        <f t="shared" si="6"/>
+        <v>9.10951145511356E-2</v>
+      </c>
+      <c r="G88" s="4">
+        <f t="shared" si="6"/>
+        <v>2.5155615470039562E-4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B89" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D89" s="3">
+        <f>AVERAGE(D85:D86)</f>
+        <v>1700802.911071677</v>
+      </c>
+      <c r="E89" s="3">
+        <f t="shared" ref="E89:G89" si="7">AVERAGE(E85:E86)</f>
+        <v>35634.680709799999</v>
+      </c>
+      <c r="F89" s="4">
+        <f t="shared" si="7"/>
+        <v>6.9007359960692752E-2</v>
+      </c>
+      <c r="G89" s="4">
+        <f t="shared" si="7"/>
+        <v>3.9826643945759096E-4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C91" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D91" s="3">
+        <f>D88/D89</f>
+        <v>1.2859286844144691</v>
+      </c>
+      <c r="E91" s="3">
+        <f t="shared" ref="E91:G91" si="8">E88/E89</f>
+        <v>0.88933632105715787</v>
+      </c>
+      <c r="F91" s="3">
+        <f t="shared" si="8"/>
+        <v>1.3200782438717298</v>
+      </c>
+      <c r="G91" s="3">
+        <f t="shared" si="8"/>
+        <v>0.63162779932699387</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D94" s="3">
+        <v>1501058.080583167</v>
+      </c>
+      <c r="E94" s="3">
+        <v>10016.90090194</v>
+      </c>
+      <c r="F94" s="4">
+        <v>4.8543989239808157E-3</v>
+      </c>
+      <c r="G94" s="4">
+        <v>2.722411311338672E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D95" s="3">
+        <v>1291276.529800517</v>
+      </c>
+      <c r="E95" s="3">
+        <v>12420.628572240001</v>
+      </c>
+      <c r="F95" s="4">
+        <v>9.5505969516812179E-3</v>
+      </c>
+      <c r="G95" s="4">
+        <v>7.1947529628030547E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D96" s="3">
+        <v>1235191.2922385989</v>
+      </c>
+      <c r="E96" s="3">
+        <v>17766.839759999999</v>
+      </c>
+      <c r="F96" s="4">
+        <v>9.3958949512133153E-4</v>
+      </c>
+      <c r="G96" s="4">
+        <v>8.8262764857625984E-4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D97" s="3">
+        <v>1202957.7138338401</v>
+      </c>
+      <c r="E97" s="3">
+        <v>13409.25543712</v>
+      </c>
+      <c r="F97" s="4">
+        <v>1.2431315547808089E-3</v>
+      </c>
+      <c r="G97" s="4">
+        <v>1.4794270549193711E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B99" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D99" s="3">
+        <f>AVERAGE(D94:D95)</f>
+        <v>1396167.3051918419</v>
+      </c>
+      <c r="E99" s="3">
+        <f t="shared" ref="E99:G99" si="9">AVERAGE(E94:E95)</f>
+        <v>11218.764737090001</v>
+      </c>
+      <c r="F99" s="4">
+        <f t="shared" si="9"/>
+        <v>7.2024979378310164E-3</v>
+      </c>
+      <c r="G99" s="4">
+        <f t="shared" si="9"/>
+        <v>4.9585821370708629E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B100" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D100" s="3">
+        <f>AVERAGE(D96:D97)</f>
+        <v>1219074.5030362196</v>
+      </c>
+      <c r="E100" s="3">
+        <f t="shared" ref="E100:G100" si="10">AVERAGE(E96:E97)</f>
+        <v>15588.047598559999</v>
+      </c>
+      <c r="F100" s="4">
+        <f t="shared" si="10"/>
+        <v>1.0913605249510702E-3</v>
+      </c>
+      <c r="G100" s="4">
+        <f t="shared" si="10"/>
+        <v>1.1810273517478154E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C102" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D102" s="3">
+        <f>D99/D100</f>
+        <v>1.1452682356283854</v>
+      </c>
+      <c r="E102" s="3">
+        <f t="shared" ref="E102:G102" si="11">E99/E100</f>
+        <v>0.71970300745850779</v>
+      </c>
+      <c r="F102" s="3">
+        <f t="shared" si="11"/>
+        <v>6.5995587829731441</v>
+      </c>
+      <c r="G102" s="3">
+        <f t="shared" si="11"/>
+        <v>4.1985328533946333</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D105" s="3">
+        <v>391236.03926557873</v>
+      </c>
+      <c r="E105" s="3">
+        <v>9174.7777388399991</v>
+      </c>
+      <c r="F105" s="4">
+        <v>7.2720955318134649E-3</v>
+      </c>
+      <c r="G105" s="4">
+        <v>4.0538663342816288E-4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D106" s="3">
+        <v>331000.25434189721</v>
+      </c>
+      <c r="E106" s="3">
+        <v>7502.6813292799998</v>
+      </c>
+      <c r="F106" s="4">
+        <v>1.753601618218082E-3</v>
+      </c>
+      <c r="G106" s="4">
+        <v>3.3407912051630981E-4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D107" s="3">
+        <v>315114.80271184049</v>
+      </c>
+      <c r="E107" s="3">
+        <v>3780.5631839999992</v>
+      </c>
+      <c r="F107" s="4">
+        <v>1.04121883656369E-2</v>
+      </c>
+      <c r="G107" s="4">
+        <v>1.4970467955548929E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D108" s="3">
+        <v>311812.99097068148</v>
+      </c>
+      <c r="E108" s="3">
+        <v>3403.6800820799999</v>
+      </c>
+      <c r="F108" s="4">
+        <v>7.8396110552474759E-4</v>
+      </c>
+      <c r="G108" s="4">
+        <v>1.35821810761219E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B110" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D110" s="3">
+        <f>AVERAGE(D105:D106)</f>
+        <v>361118.14680373797</v>
+      </c>
+      <c r="E110" s="3">
+        <f t="shared" ref="E110:G110" si="12">AVERAGE(E105:E106)</f>
+        <v>8338.7295340599994</v>
+      </c>
+      <c r="F110" s="4">
+        <f t="shared" si="12"/>
+        <v>4.5128485750157736E-3</v>
+      </c>
+      <c r="G110" s="4">
+        <f t="shared" si="12"/>
+        <v>3.6973287697223637E-4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B111" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D111" s="3">
+        <f>AVERAGE(D107:D108)</f>
+        <v>313463.89684126095</v>
+      </c>
+      <c r="E111" s="3">
+        <f t="shared" ref="E111:G111" si="13">AVERAGE(E107:E108)</f>
+        <v>3592.1216330399993</v>
+      </c>
+      <c r="F111" s="4">
+        <f t="shared" si="13"/>
+        <v>5.5980747355808243E-3</v>
+      </c>
+      <c r="G111" s="4">
+        <f t="shared" si="13"/>
+        <v>1.4276324515835415E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C113" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D113" s="3">
+        <f>D110/D111</f>
+        <v>1.1520246843183004</v>
+      </c>
+      <c r="E113" s="3">
+        <f t="shared" ref="E113:G113" si="14">E110/E111</f>
+        <v>2.3213939799145842</v>
+      </c>
+      <c r="F113" s="3">
+        <f t="shared" si="14"/>
+        <v>0.80614296667612206</v>
+      </c>
+      <c r="G113" s="3">
+        <f t="shared" si="14"/>
+        <v>0.25898323939199175</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C116" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D116" s="3">
+        <v>327266.01547195681</v>
+      </c>
+      <c r="E116" s="3">
+        <v>2736.7203125999999</v>
+      </c>
+      <c r="F116" s="4">
+        <v>6.5575458761258591E-4</v>
+      </c>
+      <c r="G116" s="4">
+        <v>9.6186040198574876E-4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D117" s="3">
+        <v>323997.44760210218</v>
+      </c>
+      <c r="E117" s="3">
+        <v>2594.2840083999999</v>
+      </c>
+      <c r="F117" s="4">
+        <v>4.4144095106468531E-4</v>
+      </c>
+      <c r="G117" s="4">
+        <v>4.2813564143465432E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D118" s="3">
+        <v>321762.90970591619</v>
+      </c>
+      <c r="E118" s="3">
+        <v>2793.945984</v>
+      </c>
+      <c r="F118" s="4">
+        <v>3.0877619142976242E-4</v>
+      </c>
+      <c r="G118" s="4">
+        <v>1.0062327675981299E-3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C119" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D119" s="3">
+        <v>297602.00445720641</v>
+      </c>
+      <c r="E119" s="3">
+        <v>3256.4356082999998</v>
+      </c>
+      <c r="F119" s="4">
+        <v>3.8592436982227681E-4</v>
+      </c>
+      <c r="G119" s="4">
+        <v>2.369477916386043E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B121" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D121" s="3">
+        <f>AVERAGE(D116:D117)</f>
+        <v>325631.7315370295</v>
+      </c>
+      <c r="E121" s="3">
+        <f t="shared" ref="E121:G121" si="15">AVERAGE(E116:E117)</f>
+        <v>2665.5021605000002</v>
+      </c>
+      <c r="F121" s="4">
+        <f t="shared" si="15"/>
+        <v>5.4859776933863561E-4</v>
+      </c>
+      <c r="G121" s="4">
+        <f t="shared" si="15"/>
+        <v>2.6216084081661459E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B122" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D122" s="3">
+        <f>AVERAGE(D118:D119)</f>
+        <v>309682.45708156133</v>
+      </c>
+      <c r="E122" s="3">
+        <f t="shared" ref="E122:G122" si="16">AVERAGE(E118:E119)</f>
+        <v>3025.1907961500001</v>
+      </c>
+      <c r="F122" s="4">
+        <f t="shared" si="16"/>
+        <v>3.4735028062601961E-4</v>
+      </c>
+      <c r="G122" s="4">
+        <f t="shared" si="16"/>
+        <v>1.6878553419920864E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C124" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D124" s="3">
+        <f>D121/D122</f>
+        <v>1.0515020276116822</v>
+      </c>
+      <c r="E124" s="3">
+        <f t="shared" ref="E124:G124" si="17">E121/E122</f>
+        <v>0.88110216515673767</v>
+      </c>
+      <c r="F124" s="3">
+        <f t="shared" si="17"/>
+        <v>1.5793790877321685</v>
+      </c>
+      <c r="G124" s="3">
+        <f t="shared" si="17"/>
+        <v>1.5532186573951297</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C127" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D127" s="3">
+        <v>589836.07301855378</v>
+      </c>
+      <c r="E127" s="3">
+        <v>3459.2387039999999</v>
+      </c>
+      <c r="F127" s="4">
+        <v>2.6129124854981389E-3</v>
+      </c>
+      <c r="G127" s="4">
+        <v>2.2962786554205951E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C128" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D128" s="3">
+        <v>585427.26654459862</v>
+      </c>
+      <c r="E128" s="3">
+        <v>4854.6591208600003</v>
+      </c>
+      <c r="F128" s="4">
+        <v>3.7612999688359748E-4</v>
+      </c>
+      <c r="G128" s="4">
+        <v>2.0756040556386131E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C129" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D129" s="3">
+        <v>575669.32501484314</v>
+      </c>
+      <c r="E129" s="3">
+        <v>4774.9529707199999</v>
+      </c>
+      <c r="F129" s="4">
+        <v>2.8738600116371028E-4</v>
+      </c>
+      <c r="G129" s="4">
+        <v>1.316480132589062E-3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C130" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D130" s="3">
+        <v>532258.74860418728</v>
+      </c>
+      <c r="E130" s="3">
+        <v>5998.8555937799993</v>
+      </c>
+      <c r="F130" s="4">
+        <v>3.3561812091085249E-3</v>
+      </c>
+      <c r="G130" s="4">
+        <v>1.7434020366891251E-3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B132" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D132" s="3">
+        <f>AVERAGE(D127:D128)</f>
+        <v>587631.66978157614</v>
+      </c>
+      <c r="E132" s="3">
+        <f t="shared" ref="E132:G132" si="18">AVERAGE(E127:E128)</f>
+        <v>4156.9489124299998</v>
+      </c>
+      <c r="F132" s="4">
+        <f t="shared" si="18"/>
+        <v>1.4945212411908682E-3</v>
+      </c>
+      <c r="G132" s="4">
+        <f t="shared" si="18"/>
+        <v>2.1859413555296043E-3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B133" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D133" s="3">
+        <f>AVERAGE(D129:D130)</f>
+        <v>553964.03680951521</v>
+      </c>
+      <c r="E133" s="3">
+        <f t="shared" ref="E133:G133" si="19">AVERAGE(E129:E130)</f>
+        <v>5386.9042822499996</v>
+      </c>
+      <c r="F133" s="4">
+        <f t="shared" si="19"/>
+        <v>1.8217836051361176E-3</v>
+      </c>
+      <c r="G133" s="4">
+        <f t="shared" si="19"/>
+        <v>1.5299410846390934E-3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C135" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D135" s="3">
+        <f>D132/D133</f>
+        <v>1.0607758459664012</v>
+      </c>
+      <c r="E135" s="3">
+        <f t="shared" ref="E135:G135" si="20">E132/E133</f>
+        <v>0.77167677289668257</v>
+      </c>
+      <c r="F135" s="3">
+        <f t="shared" si="20"/>
+        <v>0.82036156049346076</v>
+      </c>
+      <c r="G135" s="3">
+        <f t="shared" si="20"/>
+        <v>1.4287748577228767</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C138" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D138" s="3">
+        <v>2688475.9724428668</v>
+      </c>
+      <c r="E138" s="3">
+        <v>22918.622383440001</v>
+      </c>
+      <c r="F138" s="4">
+        <v>1.411209606183382E-2</v>
+      </c>
+      <c r="G138" s="4">
+        <v>6.7540592802753808E-4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C139" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D139" s="3">
+        <v>2199098.9702055152</v>
+      </c>
+      <c r="E139" s="3">
+        <v>27186.587841839999</v>
+      </c>
+      <c r="F139" s="4">
+        <v>1.428164445640567E-2</v>
+      </c>
+      <c r="G139" s="4">
+        <v>1.063284111568874E-3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C140" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D140" s="3">
+        <v>2110825.0242093089</v>
+      </c>
+      <c r="E140" s="3">
+        <v>36820.330575920001</v>
+      </c>
+      <c r="F140" s="4">
+        <v>1.1388913987487259E-2</v>
+      </c>
+      <c r="G140" s="4">
+        <v>1.346627653376551E-3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D141" s="3">
+        <v>2060147.693651289</v>
+      </c>
+      <c r="E141" s="3">
+        <v>24111.565200000001</v>
+      </c>
+      <c r="F141" s="4">
+        <v>1.6816288641435851E-2</v>
+      </c>
+      <c r="G141" s="4">
+        <v>4.7603910840263489E-4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B143" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D143" s="3">
+        <f>AVERAGE(D138:D139)</f>
+        <v>2443787.471324191</v>
+      </c>
+      <c r="E143" s="3">
+        <f t="shared" ref="E143:G143" si="21">AVERAGE(E138:E139)</f>
+        <v>25052.605112639998</v>
+      </c>
+      <c r="F143" s="4">
+        <f t="shared" si="21"/>
+        <v>1.4196870259119745E-2</v>
+      </c>
+      <c r="G143" s="4">
+        <f t="shared" si="21"/>
+        <v>8.6934501979820604E-4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B144" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D144" s="3">
+        <f>AVERAGE(D140:D141)</f>
+        <v>2085486.3589302991</v>
+      </c>
+      <c r="E144" s="3">
+        <f t="shared" ref="E144:G144" si="22">AVERAGE(E140:E141)</f>
+        <v>30465.947887959999</v>
+      </c>
+      <c r="F144" s="4">
+        <f t="shared" si="22"/>
+        <v>1.4102601314461555E-2</v>
+      </c>
+      <c r="G144" s="4">
+        <f t="shared" si="22"/>
+        <v>9.1133338088959293E-4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C146" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D146" s="3">
+        <f>D143/D144</f>
+        <v>1.1718069796331221</v>
+      </c>
+      <c r="E146" s="3">
+        <f t="shared" ref="E146:G146" si="23">E143/E144</f>
+        <v>0.82231497292558131</v>
+      </c>
+      <c r="F146" s="3">
+        <f t="shared" si="23"/>
+        <v>1.0066845075285169</v>
+      </c>
+      <c r="G146" s="3">
+        <f t="shared" si="23"/>
+        <v>0.95392645329154935</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D149" s="3">
+        <v>1079590.799601601</v>
+      </c>
+      <c r="E149" s="3">
+        <v>29824.255583999999</v>
+      </c>
+      <c r="F149" s="4">
+        <v>1.7700063980245699E-2</v>
+      </c>
+      <c r="G149" s="4">
+        <v>1.8406361575525849E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C150" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D150" s="3">
+        <v>917032.53729645221</v>
+      </c>
+      <c r="E150" s="3">
+        <v>21948.7441788</v>
+      </c>
+      <c r="F150" s="4">
+        <v>5.1385668600091312E-2</v>
+      </c>
+      <c r="G150" s="4">
+        <v>1.045825844659099E-3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C151" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D151" s="3">
+        <v>802566.08061441511</v>
+      </c>
+      <c r="E151" s="3">
+        <v>12046.641059559999</v>
+      </c>
+      <c r="F151" s="4">
+        <v>1.264319260007594E-2</v>
+      </c>
+      <c r="G151" s="4">
+        <v>9.2646432850616075E-4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C152" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D152" s="3">
+        <v>774599.50938466226</v>
+      </c>
+      <c r="E152" s="3">
+        <v>31768.917493320001</v>
+      </c>
+      <c r="F152" s="4">
+        <v>4.5024994770462897E-3</v>
+      </c>
+      <c r="G152" s="4">
+        <v>6.1504127372638605E-4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B154" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D154" s="3">
+        <f>AVERAGE(D149:D150)</f>
+        <v>998311.66844902653</v>
+      </c>
+      <c r="E154" s="3">
+        <f t="shared" ref="E154:G154" si="24">AVERAGE(E149:E150)</f>
+        <v>25886.499881399999</v>
+      </c>
+      <c r="F154" s="4">
+        <f t="shared" si="24"/>
+        <v>3.4542866290168506E-2</v>
+      </c>
+      <c r="G154" s="4">
+        <f t="shared" si="24"/>
+        <v>9.7260937100924743E-3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B155" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D155" s="3">
+        <f>AVERAGE(D151:D152)</f>
+        <v>788582.79499953869</v>
+      </c>
+      <c r="E155" s="3">
+        <f t="shared" ref="E155:G155" si="25">AVERAGE(E151:E152)</f>
+        <v>21907.77927644</v>
+      </c>
+      <c r="F155" s="4">
+        <f t="shared" si="25"/>
+        <v>8.5728460385611147E-3</v>
+      </c>
+      <c r="G155" s="4">
+        <f t="shared" si="25"/>
+        <v>7.7075280111627334E-4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C157" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D157" s="3">
+        <f>D154/D155</f>
+        <v>1.2659566944389276</v>
+      </c>
+      <c r="E157" s="3">
+        <f t="shared" ref="E157:G157" si="26">E154/E155</f>
+        <v>1.1816122280015293</v>
+      </c>
+      <c r="F157" s="3">
+        <f t="shared" si="26"/>
+        <v>4.0293347314057506</v>
+      </c>
+      <c r="G157" s="3">
+        <f t="shared" si="26"/>
+        <v>12.618953438776055</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B160" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C160" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D160" s="3">
+        <v>702640.28510284843</v>
+      </c>
+      <c r="E160" s="3">
+        <v>24692.815392</v>
+      </c>
+      <c r="F160" s="4">
+        <v>1.2473785395074479E-2</v>
+      </c>
+      <c r="G160" s="4">
+        <v>1.210844187888221E-3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B161" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C161" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D161" s="3">
+        <v>648523.59030139784</v>
+      </c>
+      <c r="E161" s="3">
+        <v>20365.73930736</v>
+      </c>
+      <c r="F161" s="4">
+        <v>2.3285205202868371E-2</v>
+      </c>
+      <c r="G161" s="4">
+        <v>1.5783067550306741E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C162" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D162" s="3">
+        <v>525586.90611574077</v>
+      </c>
+      <c r="E162" s="3">
+        <v>57596.7124071</v>
+      </c>
+      <c r="F162" s="4">
+        <v>6.9328647193893768E-4</v>
+      </c>
+      <c r="G162" s="4">
+        <v>1.2640594598421069E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C163" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D163" s="3">
+        <v>489831.22166003252</v>
+      </c>
+      <c r="E163" s="3">
+        <v>28233.8392518</v>
+      </c>
+      <c r="F163" s="4">
+        <v>1.7629362658082969E-3</v>
+      </c>
+      <c r="G163" s="4">
+        <v>1.091290811894655E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B165" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D165" s="3">
+        <f>AVERAGE(D160:D161)</f>
+        <v>675581.93770212308</v>
+      </c>
+      <c r="E165" s="3">
+        <f t="shared" ref="E165:G165" si="27">AVERAGE(E160:E161)</f>
+        <v>22529.27734968</v>
+      </c>
+      <c r="F165" s="4">
+        <f t="shared" si="27"/>
+        <v>1.7879495298971426E-2</v>
+      </c>
+      <c r="G165" s="4">
+        <f t="shared" si="27"/>
+        <v>1.3945754714594475E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B166" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D166" s="3">
+        <f>AVERAGE(D162:D163)</f>
+        <v>507709.06388788664</v>
+      </c>
+      <c r="E166" s="3">
+        <f t="shared" ref="E166:G166" si="28">AVERAGE(E162:E163)</f>
+        <v>42915.275829450002</v>
+      </c>
+      <c r="F166" s="4">
+        <f t="shared" si="28"/>
+        <v>1.2281113688736172E-3</v>
+      </c>
+      <c r="G166" s="4">
+        <f t="shared" si="28"/>
+        <v>6.8659427051578625E-3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C168" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D168" s="3">
+        <f>D165/D166</f>
+        <v>1.3306477779394272</v>
+      </c>
+      <c r="E168" s="3">
+        <f t="shared" ref="E168:G168" si="29">E165/E166</f>
+        <v>0.52497104851926879</v>
+      </c>
+      <c r="F168" s="3">
+        <f t="shared" si="29"/>
+        <v>14.558529260558757</v>
+      </c>
+      <c r="G168" s="3">
+        <f t="shared" si="29"/>
+        <v>0.20311492992969613</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C171" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D171" s="3">
+        <v>333902.21266145178</v>
+      </c>
+      <c r="E171" s="3">
+        <v>6590.0541599999997</v>
+      </c>
+      <c r="F171" s="4">
+        <v>3.968817154607421E-3</v>
+      </c>
+      <c r="G171" s="4">
+        <v>1.4273582237145071E-3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C172" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D172" s="3">
+        <v>289865.32010952412</v>
+      </c>
+      <c r="E172" s="3">
+        <v>5130.8202951200001</v>
+      </c>
+      <c r="F172" s="4">
+        <v>7.1409024001186736E-3</v>
+      </c>
+      <c r="G172" s="4">
+        <v>1.6292149323472839E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C173" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D173" s="3">
+        <v>259818.50988372459</v>
+      </c>
+      <c r="E173" s="3">
+        <v>45922.658233419999</v>
+      </c>
+      <c r="F173" s="4">
+        <v>4.0433840100499702E-5</v>
+      </c>
+      <c r="G173" s="4">
+        <v>1.5232724169502069E-4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C174" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D174" s="3">
+        <v>234189.89306239539</v>
+      </c>
+      <c r="E174" s="3">
+        <v>4733.3383234200001</v>
+      </c>
+      <c r="F174" s="4">
+        <v>6.6356632156617178E-4</v>
+      </c>
+      <c r="G174" s="4">
+        <v>3.1476572520248271E-3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B176" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D176" s="3">
+        <f>AVERAGE(D171:D172)</f>
+        <v>311883.76638548798</v>
+      </c>
+      <c r="E176" s="3">
+        <f t="shared" ref="E176:G176" si="30">AVERAGE(E171:E172)</f>
+        <v>5860.4372275599999</v>
+      </c>
+      <c r="F176" s="4">
+        <f t="shared" si="30"/>
+        <v>5.5548597773630477E-3</v>
+      </c>
+      <c r="G176" s="4">
+        <f t="shared" si="30"/>
+        <v>1.5282865780308955E-3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B177" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D177" s="3">
+        <f>AVERAGE(D173:D174)</f>
+        <v>247004.20147306001</v>
+      </c>
+      <c r="E177" s="3">
+        <f t="shared" ref="E177:G177" si="31">AVERAGE(E173:E174)</f>
+        <v>25327.99827842</v>
+      </c>
+      <c r="F177" s="4">
+        <f t="shared" si="31"/>
+        <v>3.5200008083333573E-4</v>
+      </c>
+      <c r="G177" s="4">
+        <f t="shared" si="31"/>
+        <v>1.6499922468599239E-3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C179" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D179" s="3">
+        <f>D176/D177</f>
+        <v>1.2626658353400688</v>
+      </c>
+      <c r="E179" s="3">
+        <f t="shared" ref="E179:G179" si="32">E176/E177</f>
+        <v>0.23138177613322164</v>
+      </c>
+      <c r="F179" s="3">
+        <f t="shared" si="32"/>
+        <v>15.780848016319494</v>
+      </c>
+      <c r="G179" s="3">
+        <f t="shared" si="32"/>
+        <v>0.9262386419932308</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C182" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D182" s="3">
+        <v>615324.90182869229</v>
+      </c>
+      <c r="E182" s="3">
+        <v>12188.037840000001</v>
+      </c>
+      <c r="F182" s="4">
+        <v>3.5563801629943082E-3</v>
+      </c>
+      <c r="G182" s="4">
+        <v>2.3262126662383252E-3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C183" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D183" s="3">
+        <v>463470.71898289572</v>
+      </c>
+      <c r="E183" s="3">
+        <v>9380.3853557600014</v>
+      </c>
+      <c r="F183" s="4">
+        <v>2.4821681068467739E-3</v>
+      </c>
+      <c r="G183" s="4">
+        <v>1.7821392198706289E-3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C184" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D184" s="3">
+        <v>441905.15975913568</v>
+      </c>
+      <c r="E184" s="3">
+        <v>8680.9984719799995</v>
+      </c>
+      <c r="F184" s="4">
+        <v>5.3628300774693723E-2</v>
+      </c>
+      <c r="G184" s="4">
+        <v>1.9809359137092151E-3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C185" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D185" s="3">
+        <v>396416.47748978873</v>
+      </c>
+      <c r="E185" s="3">
+        <v>10615.43888874</v>
+      </c>
+      <c r="F185" s="4">
+        <v>5.7122249315871114E-3</v>
+      </c>
+      <c r="G185" s="4">
+        <v>1.223257961926933E-3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B187" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D187" s="3">
+        <f>AVERAGE(D182:D183)</f>
+        <v>539397.81040579407</v>
+      </c>
+      <c r="E187" s="3">
+        <f t="shared" ref="E187:G187" si="33">AVERAGE(E182:E183)</f>
+        <v>10784.211597880001</v>
+      </c>
+      <c r="F187" s="4">
+        <f t="shared" si="33"/>
+        <v>3.0192741349205411E-3</v>
+      </c>
+      <c r="G187" s="4">
+        <f t="shared" si="33"/>
+        <v>2.0541759430544771E-3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B188" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D188" s="3">
+        <f>AVERAGE(D184:D185)</f>
+        <v>419160.81862446223</v>
+      </c>
+      <c r="E188" s="3">
+        <f t="shared" ref="E188:G188" si="34">AVERAGE(E184:E185)</f>
+        <v>9648.2186803599998</v>
+      </c>
+      <c r="F188" s="4">
+        <f t="shared" si="34"/>
+        <v>2.9670262853140415E-2</v>
+      </c>
+      <c r="G188" s="4">
+        <f t="shared" si="34"/>
+        <v>1.602096937818074E-3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C190" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D190" s="3">
+        <f>D187/D188</f>
+        <v>1.2868516961482879</v>
+      </c>
+      <c r="E190" s="3">
+        <f t="shared" ref="E190:G190" si="35">E187/E188</f>
+        <v>1.1177412074865631</v>
+      </c>
+      <c r="F190" s="3">
+        <f t="shared" si="35"/>
+        <v>0.10176095000792922</v>
+      </c>
+      <c r="G190" s="3">
+        <f t="shared" si="35"/>
+        <v>1.2821795576565411</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C193" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D193" s="3">
+        <v>480752.63075950177</v>
+      </c>
+      <c r="E193" s="3">
+        <v>13713.99982974</v>
+      </c>
+      <c r="F193" s="4">
+        <v>1.8909555433829729E-4</v>
+      </c>
+      <c r="G193" s="4">
+        <v>1.421912259449817E-2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C194" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D194" s="3">
+        <v>430680.74778667098</v>
+      </c>
+      <c r="E194" s="3">
+        <v>9650.7308639999992</v>
+      </c>
+      <c r="F194" s="4">
+        <v>3.2382873836611008E-4</v>
+      </c>
+      <c r="G194" s="4">
+        <v>1.307147425181787E-3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C195" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D195" s="3">
+        <v>344818.33344279532</v>
+      </c>
+      <c r="E195" s="3">
+        <v>7766.5175531200011</v>
+      </c>
+      <c r="F195" s="4">
+        <v>5.6879237956854514E-4</v>
+      </c>
+      <c r="G195" s="4">
+        <v>9.2862762115340628E-4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C196" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D196" s="3">
+        <v>310794.74797233898</v>
+      </c>
+      <c r="E196" s="3">
+        <v>8210.8821614400003</v>
+      </c>
+      <c r="F196" s="4">
+        <v>1.515288413031857E-4</v>
+      </c>
+      <c r="G196" s="4">
+        <v>1.134724744407487E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B198" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D198" s="3">
+        <f>AVERAGE(D193:D194)</f>
+        <v>455716.68927308638</v>
+      </c>
+      <c r="E198" s="3">
+        <f t="shared" ref="E198:G198" si="36">AVERAGE(E193:E194)</f>
+        <v>11682.365346869999</v>
+      </c>
+      <c r="F198" s="4">
+        <f t="shared" si="36"/>
+        <v>2.5646214635220368E-4</v>
+      </c>
+      <c r="G198" s="4">
+        <f t="shared" si="36"/>
+        <v>7.7631350098399787E-3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B199" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D199" s="3">
+        <f>AVERAGE(D195:D196)</f>
+        <v>327806.54070756712</v>
+      </c>
+      <c r="E199" s="3">
+        <f t="shared" ref="E199:G199" si="37">AVERAGE(E195:E196)</f>
+        <v>7988.6998572800003</v>
+      </c>
+      <c r="F199" s="4">
+        <f t="shared" si="37"/>
+        <v>3.6016061043586542E-4</v>
+      </c>
+      <c r="G199" s="4">
+        <f t="shared" si="37"/>
+        <v>6.1379375326141381E-3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C201" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D201" s="3">
+        <f>D198/D199</f>
+        <v>1.3902001109844437</v>
+      </c>
+      <c r="E201" s="3">
+        <f t="shared" ref="E201:G201" si="38">E198/E199</f>
+        <v>1.462361279754929</v>
+      </c>
+      <c r="F201" s="3">
+        <f t="shared" si="38"/>
+        <v>0.71207716480109773</v>
+      </c>
+      <c r="G201" s="3">
+        <f t="shared" si="38"/>
+        <v>1.2647790839496653</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C204" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D204" s="3">
+        <v>624490.81179662514</v>
+      </c>
+      <c r="E204" s="3">
+        <v>23490.718752000001</v>
+      </c>
+      <c r="F204" s="4">
+        <v>1.927088927244758E-3</v>
+      </c>
+      <c r="G204" s="4">
+        <v>1.8760825696850091E-3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C205" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D205" s="3">
+        <v>615005.46689121344</v>
+      </c>
+      <c r="E205" s="3">
+        <v>18304.5266156</v>
+      </c>
+      <c r="F205" s="4">
+        <v>2.0544865338363899E-3</v>
+      </c>
+      <c r="G205" s="4">
+        <v>2.397692315221963E-3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B206" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C206" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D206" s="3">
+        <v>557880.96074185451</v>
+      </c>
+      <c r="E206" s="3">
+        <v>17673.58753398</v>
+      </c>
+      <c r="F206" s="4">
+        <v>1.2639185721094849E-3</v>
+      </c>
+      <c r="G206" s="4">
+        <v>7.224852054202324E-4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C207" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D207" s="3">
+        <v>528936.59684355662</v>
+      </c>
+      <c r="E207" s="3">
+        <v>14840.029964359999</v>
+      </c>
+      <c r="F207" s="4">
+        <v>3.348617336982791E-3</v>
+      </c>
+      <c r="G207" s="4">
+        <v>9.7700369843055682E-4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B209" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D209" s="3">
+        <f>AVERAGE(D204:D205)</f>
+        <v>619748.13934391923</v>
+      </c>
+      <c r="E209" s="3">
+        <f t="shared" ref="E209:G209" si="39">AVERAGE(E204:E205)</f>
+        <v>20897.6226838</v>
+      </c>
+      <c r="F209" s="4">
+        <f t="shared" si="39"/>
+        <v>1.9907877305405742E-3</v>
+      </c>
+      <c r="G209" s="4">
+        <f t="shared" si="39"/>
+        <v>2.1368874424534858E-3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B210" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D210" s="3">
+        <f>AVERAGE(D206:D207)</f>
+        <v>543408.77879270562</v>
+      </c>
+      <c r="E210" s="3">
+        <f t="shared" ref="E210:G210" si="40">AVERAGE(E206:E207)</f>
+        <v>16256.808749169999</v>
+      </c>
+      <c r="F210" s="4">
+        <f t="shared" si="40"/>
+        <v>2.3062679545461382E-3</v>
+      </c>
+      <c r="G210" s="4">
+        <f t="shared" si="40"/>
+        <v>8.4974445192539461E-4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C212" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D212" s="3">
+        <f>D209/D210</f>
+        <v>1.1404823836685474</v>
+      </c>
+      <c r="E212" s="3">
+        <f t="shared" ref="E212:G212" si="41">E209/E210</f>
+        <v>1.2854689383527957</v>
+      </c>
+      <c r="F212" s="3">
+        <f t="shared" si="41"/>
+        <v>0.8632074718882139</v>
+      </c>
+      <c r="G212" s="3">
+        <f t="shared" si="41"/>
+        <v>2.5147412702861627</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B215" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C215" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D215" s="3">
+        <v>496312.33844584553</v>
+      </c>
+      <c r="E215" s="3">
+        <v>6058.6276942799996</v>
+      </c>
+      <c r="F215" s="4">
+        <v>1.149126975828702E-3</v>
+      </c>
+      <c r="G215" s="4">
+        <v>4.3326889923906344E-3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C216" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D216" s="3">
+        <v>481190.63450056087</v>
+      </c>
+      <c r="E216" s="3">
+        <v>5659.2905294400007</v>
+      </c>
+      <c r="F216" s="4">
+        <v>2.7642536319032169E-4</v>
+      </c>
+      <c r="G216" s="4">
+        <v>2.609783923120391E-3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B217" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C217" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D217" s="3">
+        <v>463554.2380744408</v>
+      </c>
+      <c r="E217" s="3">
+        <v>6405.1162323599992</v>
+      </c>
+      <c r="F217" s="4">
+        <v>1.36542870460566E-3</v>
+      </c>
+      <c r="G217" s="4">
+        <v>1.06191448730258E-3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B218" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C218" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D218" s="3">
+        <v>463215.01884109463</v>
+      </c>
+      <c r="E218" s="3">
+        <v>6600.4823040000001</v>
+      </c>
+      <c r="F218" s="4">
+        <v>1.0184783005820781E-3</v>
+      </c>
+      <c r="G218" s="4">
+        <v>1.1952508372333631E-3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B220" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D220" s="3">
+        <f>AVERAGE(D215:D216)</f>
+        <v>488751.48647320317</v>
+      </c>
+      <c r="E220" s="3">
+        <f t="shared" ref="E220:G220" si="42">AVERAGE(E215:E216)</f>
+        <v>5858.9591118600001</v>
+      </c>
+      <c r="F220" s="4">
+        <f t="shared" si="42"/>
+        <v>7.1277616950951182E-4</v>
+      </c>
+      <c r="G220" s="4">
+        <f t="shared" si="42"/>
+        <v>3.4712364577555127E-3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B221" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D221" s="3">
+        <f>AVERAGE(D217:D218)</f>
+        <v>463384.62845776771</v>
+      </c>
+      <c r="E221" s="3">
+        <f t="shared" ref="E221:G221" si="43">AVERAGE(E217:E218)</f>
+        <v>6502.7992681799997</v>
+      </c>
+      <c r="F221" s="4">
+        <f t="shared" si="43"/>
+        <v>1.191953502593869E-3</v>
+      </c>
+      <c r="G221" s="4">
+        <f t="shared" si="43"/>
+        <v>1.1285826622679715E-3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C223" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D223" s="3">
+        <f>D220/D221</f>
+        <v>1.0547425539337831</v>
+      </c>
+      <c r="E223" s="3">
+        <f t="shared" ref="E223:G223" si="44">E220/E221</f>
+        <v>0.9009903074402914</v>
+      </c>
+      <c r="F223" s="3">
+        <f t="shared" si="44"/>
+        <v>0.59798991148430225</v>
+      </c>
+      <c r="G223" s="3">
+        <f t="shared" si="44"/>
+        <v>3.0757485240645135</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:G62">
-    <sortCondition descending="1" ref="D2:D62"/>
+  <sortState ref="A149:G152">
+    <sortCondition descending="1" ref="D149:D152"/>
   </sortState>
   <conditionalFormatting sqref="D2:D62">
+    <cfRule type="colorScale" priority="128">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E62">
+    <cfRule type="colorScale" priority="127">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F62">
+    <cfRule type="colorScale" priority="126">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G62">
+    <cfRule type="colorScale" priority="125">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D66:D67">
+    <cfRule type="colorScale" priority="120">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E66:E67">
+    <cfRule type="colorScale" priority="119">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F66:F67">
+    <cfRule type="colorScale" priority="118">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G66:G67">
+    <cfRule type="colorScale" priority="117">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D72:D75">
+    <cfRule type="colorScale" priority="116">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E72:E75">
+    <cfRule type="colorScale" priority="115">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F72:F75">
+    <cfRule type="colorScale" priority="114">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G72:G75">
+    <cfRule type="colorScale" priority="113">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D77:D78">
+    <cfRule type="colorScale" priority="108">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E77:E78">
+    <cfRule type="colorScale" priority="107">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F77:F78">
+    <cfRule type="colorScale" priority="106">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G77:G78">
+    <cfRule type="colorScale" priority="105">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D83:D86">
+    <cfRule type="colorScale" priority="104">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E83:E86">
+    <cfRule type="colorScale" priority="103">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F83:F86">
+    <cfRule type="colorScale" priority="102">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G83:G86">
+    <cfRule type="colorScale" priority="101">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D88:D89">
+    <cfRule type="colorScale" priority="100">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E88:E89">
+    <cfRule type="colorScale" priority="99">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F88:F89">
+    <cfRule type="colorScale" priority="98">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G88:G89">
+    <cfRule type="colorScale" priority="97">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D94:D97">
+    <cfRule type="colorScale" priority="96">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E94:E97">
+    <cfRule type="colorScale" priority="95">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F94:F97">
+    <cfRule type="colorScale" priority="94">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G94:G97">
+    <cfRule type="colorScale" priority="93">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D99:D100">
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E99:E100">
+    <cfRule type="colorScale" priority="91">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F99:F100">
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G99:G100">
+    <cfRule type="colorScale" priority="89">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D105:D108">
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E105:E108">
+    <cfRule type="colorScale" priority="87">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F105:F108">
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G105:G108">
+    <cfRule type="colorScale" priority="85">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D110:D111">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E110:E111">
+    <cfRule type="colorScale" priority="83">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F110:F111">
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G110:G111">
+    <cfRule type="colorScale" priority="81">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D116:D119">
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E116:E119">
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F116:F119">
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G116:G119">
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D121:D122">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E121:E122">
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F121:F122">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G121:G122">
+    <cfRule type="colorScale" priority="73">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D127:D130">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E127:E130">
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F127:F130">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G127:G130">
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D132:D133">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E132:E133">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F132:F133">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G132:G133">
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D138:D141">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E138:E141">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F138:F141">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G138:G141">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D143:D144">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E143:E144">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F143:F144">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G143:G144">
+    <cfRule type="colorScale" priority="57">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D149:D152">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E149:E152">
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F149:F152">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G149:G152">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D154:D155">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E154:E155">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F154:F155">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G154:G155">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D160:D163">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E160:E163">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F160:F163">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G160:G163">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D165:D166">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E165:E166">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F165:F166">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G165:G166">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D171:D174">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E171:E174">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F171:F174">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G171:G174">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D176:D177">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E176:E177">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F176:F177">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G176:G177">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D182:D185">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E182:E185">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F182:F185">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G182:G185">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D187:D188">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E187:E188">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F187:F188">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G187:G188">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D193:D196">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E193:E196">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F193:F196">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G193:G196">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D198:D199">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E198:E199">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F198:F199">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G198:G199">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D204:D207">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E204:E207">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F204:F207">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G204:G207">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D209:D210">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -2081,7 +5877,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E62">
+  <conditionalFormatting sqref="E209:E210">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -2093,7 +5889,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F62">
+  <conditionalFormatting sqref="F209:F210">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -2105,7 +5901,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G62">
+  <conditionalFormatting sqref="G209:G210">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2117,7 +5913,55 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D66:D67">
+  <conditionalFormatting sqref="D215:D218">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E215:E218">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F215:F218">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G215:G218">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D220:D221">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2129,7 +5973,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E66:E67">
+  <conditionalFormatting sqref="E220:E221">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2141,7 +5985,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F66:F67">
+  <conditionalFormatting sqref="F220:F221">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2153,7 +5997,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G66:G67">
+  <conditionalFormatting sqref="G220:G221">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
@@ -597,968 +597,968 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2">
         <v>2021</v>
       </c>
       <c r="D2" s="3">
-        <v>496312.33844584553</v>
+        <v>2688475.9724428668</v>
       </c>
       <c r="E2" s="3">
-        <v>6058.6276942799996</v>
+        <v>22918.622383440001</v>
       </c>
       <c r="F2" s="4">
-        <v>1.149126975828702E-3</v>
+        <v>1.411209606183382E-2</v>
       </c>
       <c r="G2" s="4">
-        <v>4.3326889923906344E-3</v>
+        <v>6.7540592802753808E-4</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="5">
-        <v>2023</v>
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2022</v>
       </c>
       <c r="D3" s="3">
-        <v>481190.63450056087</v>
+        <v>2237559.59010129</v>
       </c>
       <c r="E3" s="3">
-        <v>5659.2905294400007</v>
+        <v>28962.7912646</v>
       </c>
       <c r="F3" s="4">
-        <v>2.7642536319032169E-4</v>
+        <v>0.18094518011478611</v>
       </c>
       <c r="G3" s="4">
-        <v>2.609783923120391E-3</v>
+        <v>2.339677504868966E-4</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2">
         <v>2022</v>
       </c>
       <c r="D4" s="3">
-        <v>463554.2380744408</v>
+        <v>2199098.9702055152</v>
       </c>
       <c r="E4" s="3">
-        <v>6405.1162323599992</v>
+        <v>27186.587841839999</v>
       </c>
       <c r="F4" s="4">
-        <v>1.36542870460566E-3</v>
+        <v>1.428164445640567E-2</v>
       </c>
       <c r="G4" s="4">
-        <v>1.06191448730258E-3</v>
+        <v>1.063284111568874E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D5" s="3">
-        <v>463215.01884109463</v>
+        <v>2136662.9096641121</v>
       </c>
       <c r="E5" s="3">
-        <v>6600.4823040000001</v>
+        <v>34419.6404244</v>
       </c>
       <c r="F5" s="4">
-        <v>1.0184783005820781E-3</v>
+        <v>1.2450489874850871E-3</v>
       </c>
       <c r="G5" s="4">
-        <v>1.1952508372333631E-3</v>
+        <v>2.6914455891389468E-4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D6" s="3">
-        <v>624490.81179662514</v>
+        <v>2110825.0242093089</v>
       </c>
       <c r="E6" s="3">
-        <v>23490.718752000001</v>
+        <v>36820.330575920001</v>
       </c>
       <c r="F6" s="4">
-        <v>1.927088927244758E-3</v>
+        <v>1.1388913987487259E-2</v>
       </c>
       <c r="G6" s="4">
-        <v>1.8760825696850091E-3</v>
+        <v>1.346627653376551E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D7" s="3">
-        <v>615005.46689121344</v>
+        <v>2060147.693651289</v>
       </c>
       <c r="E7" s="3">
-        <v>18304.5266156</v>
+        <v>24111.565200000001</v>
       </c>
       <c r="F7" s="4">
-        <v>2.0544865338363899E-3</v>
+        <v>1.6816288641435851E-2</v>
       </c>
       <c r="G7" s="4">
-        <v>2.397692315221963E-3</v>
+        <v>4.7603910840263489E-4</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D8" s="3">
-        <v>557880.96074185451</v>
+        <v>1963532.5336935241</v>
       </c>
       <c r="E8" s="3">
-        <v>17673.58753398</v>
+        <v>38266.632667600003</v>
       </c>
       <c r="F8" s="4">
-        <v>1.2639185721094849E-3</v>
+        <v>0.1254843771395045</v>
       </c>
       <c r="G8" s="4">
-        <v>7.224852054202324E-4</v>
+        <v>3.2594779133939081E-4</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2">
         <v>2022</v>
       </c>
       <c r="D9" s="3">
-        <v>528936.59684355662</v>
+        <v>1501058.080583167</v>
       </c>
       <c r="E9" s="3">
-        <v>14840.029964359999</v>
+        <v>10016.90090194</v>
       </c>
       <c r="F9" s="4">
-        <v>3.348617336982791E-3</v>
+        <v>4.8543989239808157E-3</v>
       </c>
       <c r="G9" s="4">
-        <v>9.7700369843055682E-4</v>
+        <v>2.722411311338672E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D10" s="3">
-        <v>480752.63075950177</v>
+        <v>1438073.2884498299</v>
       </c>
       <c r="E10" s="3">
-        <v>13713.99982974</v>
+        <v>33002.728752000003</v>
       </c>
       <c r="F10" s="4">
-        <v>1.8909555433829729E-4</v>
+        <v>1.2530342781881009E-2</v>
       </c>
       <c r="G10" s="4">
-        <v>1.421912259449817E-2</v>
+        <v>4.7058508757579111E-4</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C11" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D11" s="3">
-        <v>430680.74778667098</v>
+        <v>1291276.529800517</v>
       </c>
       <c r="E11" s="3">
-        <v>9650.7308639999992</v>
+        <v>12420.628572240001</v>
       </c>
       <c r="F11" s="4">
-        <v>3.2382873836611008E-4</v>
+        <v>9.5505969516812179E-3</v>
       </c>
       <c r="G11" s="4">
-        <v>1.307147425181787E-3</v>
+        <v>7.1947529628030547E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D12" s="3">
-        <v>344818.33344279532</v>
+        <v>1235191.2922385989</v>
       </c>
       <c r="E12" s="3">
-        <v>7766.5175531200011</v>
+        <v>17766.839759999999</v>
       </c>
       <c r="F12" s="4">
-        <v>5.6879237956854514E-4</v>
+        <v>9.3958949512133153E-4</v>
       </c>
       <c r="G12" s="4">
-        <v>9.2862762115340628E-4</v>
+        <v>8.8262764857625984E-4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C13" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D13" s="3">
-        <v>310794.74797233898</v>
+        <v>1202957.7138338401</v>
       </c>
       <c r="E13" s="3">
-        <v>8210.8821614400003</v>
+        <v>13409.25543712</v>
       </c>
       <c r="F13" s="4">
-        <v>1.515288413031857E-4</v>
+        <v>1.2431315547808089E-3</v>
       </c>
       <c r="G13" s="4">
-        <v>1.134724744407487E-2</v>
+        <v>1.4794270549193711E-3</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C14" s="2">
         <v>2024</v>
       </c>
       <c r="D14" s="3">
-        <v>615324.90182869229</v>
+        <v>1079590.799601601</v>
       </c>
       <c r="E14" s="3">
-        <v>12188.037840000001</v>
+        <v>29824.255583999999</v>
       </c>
       <c r="F14" s="4">
-        <v>3.5563801629943082E-3</v>
+        <v>1.7700063980245699E-2</v>
       </c>
       <c r="G14" s="4">
-        <v>2.3262126662383252E-3</v>
+        <v>1.8406361575525849E-2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C15" s="2">
         <v>2023</v>
       </c>
       <c r="D15" s="3">
-        <v>463470.71898289572</v>
+        <v>917032.53729645221</v>
       </c>
       <c r="E15" s="3">
-        <v>9380.3853557600014</v>
+        <v>21948.7441788</v>
       </c>
       <c r="F15" s="4">
-        <v>2.4821681068467739E-3</v>
+        <v>5.1385668600091312E-2</v>
       </c>
       <c r="G15" s="4">
-        <v>1.7821392198706289E-3</v>
+        <v>1.045825844659099E-3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C16" s="2">
         <v>2022</v>
       </c>
       <c r="D16" s="3">
-        <v>441905.15975913568</v>
+        <v>802566.08061441511</v>
       </c>
       <c r="E16" s="3">
-        <v>8680.9984719799995</v>
+        <v>12046.641059559999</v>
       </c>
       <c r="F16" s="4">
-        <v>5.3628300774693723E-2</v>
+        <v>1.264319260007594E-2</v>
       </c>
       <c r="G16" s="4">
-        <v>1.9809359137092151E-3</v>
+        <v>9.2646432850616075E-4</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C17" s="2">
         <v>2021</v>
       </c>
       <c r="D17" s="3">
-        <v>396416.47748978873</v>
+        <v>774599.50938466226</v>
       </c>
       <c r="E17" s="3">
-        <v>10615.43888874</v>
+        <v>31768.917493320001</v>
       </c>
       <c r="F17" s="4">
-        <v>5.7122249315871114E-3</v>
+        <v>4.5024994770462897E-3</v>
       </c>
       <c r="G17" s="4">
-        <v>1.223257961926933E-3</v>
+        <v>6.1504127372638605E-4</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2">
         <v>2024</v>
       </c>
       <c r="D18" s="3">
-        <v>333902.21266145178</v>
+        <v>702640.28510284843</v>
       </c>
       <c r="E18" s="3">
-        <v>6590.0541599999997</v>
+        <v>24692.815392</v>
       </c>
       <c r="F18" s="4">
-        <v>3.968817154607421E-3</v>
+        <v>1.2473785395074479E-2</v>
       </c>
       <c r="G18" s="4">
-        <v>1.4273582237145071E-3</v>
+        <v>1.210844187888221E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C19" s="2">
         <v>2023</v>
       </c>
       <c r="D19" s="3">
-        <v>289865.32010952412</v>
+        <v>648523.59030139784</v>
       </c>
       <c r="E19" s="3">
-        <v>5130.8202951200001</v>
+        <v>20365.73930736</v>
       </c>
       <c r="F19" s="4">
-        <v>7.1409024001186736E-3</v>
+        <v>2.3285205202868371E-2</v>
       </c>
       <c r="G19" s="4">
-        <v>1.6292149323472839E-3</v>
+        <v>1.5783067550306741E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C20" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D20" s="3">
-        <v>259818.50988372459</v>
+        <v>624490.81179662514</v>
       </c>
       <c r="E20" s="3">
-        <v>45922.658233419999</v>
+        <v>23490.718752000001</v>
       </c>
       <c r="F20" s="4">
-        <v>4.0433840100499702E-5</v>
+        <v>1.927088927244758E-3</v>
       </c>
       <c r="G20" s="4">
-        <v>1.5232724169502069E-4</v>
+        <v>1.8760825696850091E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C21" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D21" s="3">
-        <v>234189.89306239539</v>
+        <v>615324.90182869229</v>
       </c>
       <c r="E21" s="3">
-        <v>4733.3383234200001</v>
+        <v>12188.037840000001</v>
       </c>
       <c r="F21" s="4">
-        <v>6.6356632156617178E-4</v>
+        <v>3.5563801629943082E-3</v>
       </c>
       <c r="G21" s="4">
-        <v>3.1476572520248271E-3</v>
+        <v>2.3262126662383252E-3</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C22" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D22" s="3">
-        <v>702640.28510284843</v>
+        <v>615005.46689121344</v>
       </c>
       <c r="E22" s="3">
-        <v>24692.815392</v>
+        <v>18304.5266156</v>
       </c>
       <c r="F22" s="4">
-        <v>1.2473785395074479E-2</v>
+        <v>2.0544865338363899E-3</v>
       </c>
       <c r="G22" s="4">
-        <v>1.210844187888221E-3</v>
+        <v>2.397692315221963E-3</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C23" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D23" s="3">
-        <v>648523.59030139784</v>
+        <v>589836.07301855378</v>
       </c>
       <c r="E23" s="3">
-        <v>20365.73930736</v>
+        <v>3459.2387039999999</v>
       </c>
       <c r="F23" s="4">
-        <v>2.3285205202868371E-2</v>
+        <v>2.6129124854981389E-3</v>
       </c>
       <c r="G23" s="4">
-        <v>1.5783067550306741E-3</v>
+        <v>2.2962786554205951E-3</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C24" s="2">
         <v>2022</v>
       </c>
       <c r="D24" s="3">
-        <v>525586.90611574077</v>
+        <v>585427.26654459862</v>
       </c>
       <c r="E24" s="3">
-        <v>57596.7124071</v>
+        <v>4854.6591208600003</v>
       </c>
       <c r="F24" s="4">
-        <v>6.9328647193893768E-4</v>
+        <v>3.7612999688359748E-4</v>
       </c>
       <c r="G24" s="4">
-        <v>1.2640594598421069E-2</v>
+        <v>2.0756040556386131E-3</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C25" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D25" s="3">
-        <v>489831.22166003252</v>
+        <v>575669.32501484314</v>
       </c>
       <c r="E25" s="3">
-        <v>28233.8392518</v>
+        <v>4774.9529707199999</v>
       </c>
       <c r="F25" s="4">
-        <v>1.7629362658082969E-3</v>
+        <v>2.8738600116371028E-4</v>
       </c>
       <c r="G25" s="4">
-        <v>1.091290811894655E-3</v>
+        <v>1.316480132589062E-3</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C26" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D26" s="3">
-        <v>1079590.799601601</v>
+        <v>557880.96074185451</v>
       </c>
       <c r="E26" s="3">
-        <v>29824.255583999999</v>
+        <v>17673.58753398</v>
       </c>
       <c r="F26" s="4">
-        <v>1.7700063980245699E-2</v>
+        <v>1.2639185721094849E-3</v>
       </c>
       <c r="G26" s="4">
-        <v>1.8406361575525849E-2</v>
+        <v>7.224852054202324E-4</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C27" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D27" s="3">
-        <v>917032.53729645221</v>
+        <v>532258.74860418728</v>
       </c>
       <c r="E27" s="3">
-        <v>21948.7441788</v>
+        <v>5998.8555937799993</v>
       </c>
       <c r="F27" s="4">
-        <v>5.1385668600091312E-2</v>
+        <v>3.3561812091085249E-3</v>
       </c>
       <c r="G27" s="4">
-        <v>1.045825844659099E-3</v>
+        <v>1.7434020366891251E-3</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C28" s="2">
         <v>2022</v>
       </c>
       <c r="D28" s="3">
-        <v>802566.08061441511</v>
+        <v>528936.59684355662</v>
       </c>
       <c r="E28" s="3">
-        <v>12046.641059559999</v>
+        <v>14840.029964359999</v>
       </c>
       <c r="F28" s="4">
-        <v>1.264319260007594E-2</v>
+        <v>3.348617336982791E-3</v>
       </c>
       <c r="G28" s="4">
-        <v>9.2646432850616075E-4</v>
+        <v>9.7700369843055682E-4</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D29" s="3">
-        <v>774599.50938466226</v>
+        <v>525586.90611574077</v>
       </c>
       <c r="E29" s="3">
-        <v>31768.917493320001</v>
+        <v>57596.7124071</v>
       </c>
       <c r="F29" s="4">
-        <v>4.5024994770462897E-3</v>
+        <v>6.9328647193893768E-4</v>
       </c>
       <c r="G29" s="4">
-        <v>6.1504127372638605E-4</v>
+        <v>1.2640594598421069E-2</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C30" s="2">
         <v>2021</v>
       </c>
       <c r="D30" s="3">
-        <v>2688475.9724428668</v>
+        <v>496312.33844584553</v>
       </c>
       <c r="E30" s="3">
-        <v>22918.622383440001</v>
+        <v>6058.6276942799996</v>
       </c>
       <c r="F30" s="4">
-        <v>1.411209606183382E-2</v>
+        <v>1.149126975828702E-3</v>
       </c>
       <c r="G30" s="4">
-        <v>6.7540592802753808E-4</v>
+        <v>4.3326889923906344E-3</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C31" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D31" s="3">
-        <v>2199098.9702055152</v>
+        <v>489831.22166003252</v>
       </c>
       <c r="E31" s="3">
-        <v>27186.587841839999</v>
+        <v>28233.8392518</v>
       </c>
       <c r="F31" s="4">
-        <v>1.428164445640567E-2</v>
+        <v>1.7629362658082969E-3</v>
       </c>
       <c r="G31" s="4">
-        <v>1.063284111568874E-3</v>
+        <v>1.091290811894655E-3</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="2">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="5">
         <v>2023</v>
       </c>
       <c r="D32" s="3">
-        <v>2110825.0242093089</v>
+        <v>481190.63450056087</v>
       </c>
       <c r="E32" s="3">
-        <v>36820.330575920001</v>
+        <v>5659.2905294400007</v>
       </c>
       <c r="F32" s="4">
-        <v>1.1388913987487259E-2</v>
+        <v>2.7642536319032169E-4</v>
       </c>
       <c r="G32" s="4">
-        <v>1.346627653376551E-3</v>
+        <v>2.609783923120391E-3</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C33" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D33" s="3">
-        <v>2060147.693651289</v>
+        <v>480752.63075950177</v>
       </c>
       <c r="E33" s="3">
-        <v>24111.565200000001</v>
+        <v>13713.99982974</v>
       </c>
       <c r="F33" s="4">
-        <v>1.6816288641435851E-2</v>
+        <v>1.8909555433829729E-4</v>
       </c>
       <c r="G33" s="4">
-        <v>4.7603910840263489E-4</v>
+        <v>1.421912259449817E-2</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C34" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D34" s="3">
-        <v>589836.07301855378</v>
+        <v>463554.2380744408</v>
       </c>
       <c r="E34" s="3">
-        <v>3459.2387039999999</v>
+        <v>6405.1162323599992</v>
       </c>
       <c r="F34" s="4">
-        <v>2.6129124854981389E-3</v>
+        <v>1.36542870460566E-3</v>
       </c>
       <c r="G34" s="4">
-        <v>2.2962786554205951E-3</v>
+        <v>1.06191448730258E-3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C35" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D35" s="3">
-        <v>585427.26654459862</v>
+        <v>463470.71898289572</v>
       </c>
       <c r="E35" s="3">
-        <v>4854.6591208600003</v>
+        <v>9380.3853557600014</v>
       </c>
       <c r="F35" s="4">
-        <v>3.7612999688359748E-4</v>
+        <v>2.4821681068467739E-3</v>
       </c>
       <c r="G35" s="4">
-        <v>2.0756040556386131E-3</v>
+        <v>1.7821392198706289E-3</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C36" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D36" s="3">
-        <v>575669.32501484314</v>
+        <v>463215.01884109463</v>
       </c>
       <c r="E36" s="3">
-        <v>4774.9529707199999</v>
+        <v>6600.4823040000001</v>
       </c>
       <c r="F36" s="4">
-        <v>2.8738600116371028E-4</v>
+        <v>1.0184783005820781E-3</v>
       </c>
       <c r="G36" s="4">
-        <v>1.316480132589062E-3</v>
+        <v>1.1952508372333631E-3</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C37" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D37" s="3">
-        <v>532258.74860418728</v>
+        <v>441905.15975913568</v>
       </c>
       <c r="E37" s="3">
-        <v>5998.8555937799993</v>
+        <v>8680.9984719799995</v>
       </c>
       <c r="F37" s="4">
-        <v>3.3561812091085249E-3</v>
+        <v>5.3628300774693723E-2</v>
       </c>
       <c r="G37" s="4">
-        <v>1.7434020366891251E-3</v>
+        <v>1.9809359137092151E-3</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C38" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D38" s="3">
-        <v>327266.01547195681</v>
+        <v>430680.74778667098</v>
       </c>
       <c r="E38" s="3">
-        <v>2736.7203125999999</v>
+        <v>9650.7308639999992</v>
       </c>
       <c r="F38" s="4">
-        <v>6.5575458761258591E-4</v>
+        <v>3.2382873836611008E-4</v>
       </c>
       <c r="G38" s="4">
-        <v>9.6186040198574876E-4</v>
+        <v>1.307147425181787E-3</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C39" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D39" s="3">
-        <v>323997.44760210218</v>
+        <v>396416.47748978873</v>
       </c>
       <c r="E39" s="3">
-        <v>2594.2840083999999</v>
+        <v>10615.43888874</v>
       </c>
       <c r="F39" s="4">
-        <v>4.4144095106468531E-4</v>
+        <v>5.7122249315871114E-3</v>
       </c>
       <c r="G39" s="4">
-        <v>4.2813564143465432E-3</v>
+        <v>1.223257961926933E-3</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C40" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D40" s="3">
-        <v>321762.90970591619</v>
+        <v>391236.03926557873</v>
       </c>
       <c r="E40" s="3">
-        <v>2793.945984</v>
+        <v>9174.7777388399991</v>
       </c>
       <c r="F40" s="4">
-        <v>3.0877619142976242E-4</v>
+        <v>7.2720955318134649E-3</v>
       </c>
       <c r="G40" s="4">
-        <v>1.0062327675981299E-3</v>
+        <v>4.0538663342816288E-4</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C41" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D41" s="3">
-        <v>297602.00445720641</v>
+        <v>344818.33344279532</v>
       </c>
       <c r="E41" s="3">
-        <v>3256.4356082999998</v>
+        <v>7766.5175531200011</v>
       </c>
       <c r="F41" s="4">
-        <v>3.8592436982227681E-4</v>
+        <v>5.6879237956854514E-4</v>
       </c>
       <c r="G41" s="4">
-        <v>2.369477916386043E-3</v>
+        <v>9.2862762115340628E-4</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C42" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D42" s="3">
-        <v>391236.03926557873</v>
+        <v>333902.21266145178</v>
       </c>
       <c r="E42" s="3">
-        <v>9174.7777388399991</v>
+        <v>6590.0541599999997</v>
       </c>
       <c r="F42" s="4">
-        <v>7.2720955318134649E-3</v>
+        <v>3.968817154607421E-3</v>
       </c>
       <c r="G42" s="4">
-        <v>4.0538663342816288E-4</v>
+        <v>1.4273582237145071E-3</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C43" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D43" s="3">
-        <v>331000.25434189721</v>
+        <v>332033.64455055603</v>
       </c>
       <c r="E43" s="3">
-        <v>7502.6813292799998</v>
+        <v>1720.9347523199999</v>
       </c>
       <c r="F43" s="4">
-        <v>1.753601618218082E-3</v>
+        <v>5.4438237053266124E-4</v>
       </c>
       <c r="G43" s="4">
-        <v>3.3407912051630981E-4</v>
+        <v>1.095196036606934E-3</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1569,341 +1569,341 @@
         <v>18</v>
       </c>
       <c r="C44" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D44" s="3">
-        <v>315114.80271184049</v>
+        <v>331000.25434189721</v>
       </c>
       <c r="E44" s="3">
-        <v>3780.5631839999992</v>
+        <v>7502.6813292799998</v>
       </c>
       <c r="F44" s="4">
-        <v>1.04121883656369E-2</v>
+        <v>1.753601618218082E-3</v>
       </c>
       <c r="G44" s="4">
-        <v>1.4970467955548929E-3</v>
+        <v>3.3407912051630981E-4</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C45" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D45" s="3">
-        <v>311812.99097068148</v>
+        <v>327266.01547195681</v>
       </c>
       <c r="E45" s="3">
-        <v>3403.6800820799999</v>
+        <v>2736.7203125999999</v>
       </c>
       <c r="F45" s="4">
-        <v>7.8396110552474759E-4</v>
+        <v>6.5575458761258591E-4</v>
       </c>
       <c r="G45" s="4">
-        <v>1.35821810761219E-3</v>
+        <v>9.6186040198574876E-4</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C46" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D46" s="3">
-        <v>1501058.080583167</v>
+        <v>323997.44760210218</v>
       </c>
       <c r="E46" s="3">
-        <v>10016.90090194</v>
+        <v>2594.2840083999999</v>
       </c>
       <c r="F46" s="4">
-        <v>4.8543989239808157E-3</v>
+        <v>4.4144095106468531E-4</v>
       </c>
       <c r="G46" s="4">
-        <v>2.722411311338672E-3</v>
+        <v>4.2813564143465432E-3</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C47" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D47" s="3">
-        <v>1291276.529800517</v>
+        <v>321762.90970591619</v>
       </c>
       <c r="E47" s="3">
-        <v>12420.628572240001</v>
+        <v>2793.945984</v>
       </c>
       <c r="F47" s="4">
-        <v>9.5505969516812179E-3</v>
+        <v>3.0877619142976242E-4</v>
       </c>
       <c r="G47" s="4">
-        <v>7.1947529628030547E-3</v>
+        <v>1.0062327675981299E-3</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C48" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D48" s="3">
-        <v>1235191.2922385989</v>
+        <v>320449.11322310509</v>
       </c>
       <c r="E48" s="3">
-        <v>17766.839759999999</v>
+        <v>3164.1185242800002</v>
       </c>
       <c r="F48" s="4">
-        <v>9.3958949512133153E-4</v>
+        <v>6.7699852441129374E-3</v>
       </c>
       <c r="G48" s="4">
-        <v>8.8262764857625984E-4</v>
+        <v>2.6803313639870169E-3</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C49" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D49" s="3">
-        <v>1202957.7138338401</v>
+        <v>315114.80271184049</v>
       </c>
       <c r="E49" s="3">
-        <v>13409.25543712</v>
+        <v>3780.5631839999992</v>
       </c>
       <c r="F49" s="4">
-        <v>1.2431315547808089E-3</v>
+        <v>1.04121883656369E-2</v>
       </c>
       <c r="G49" s="4">
-        <v>1.4794270549193711E-3</v>
+        <v>1.4970467955548929E-3</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C50" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D50" s="3">
-        <v>2237559.59010129</v>
+        <v>311812.99097068148</v>
       </c>
       <c r="E50" s="3">
-        <v>28962.7912646</v>
+        <v>3403.6800820799999</v>
       </c>
       <c r="F50" s="4">
-        <v>0.18094518011478611</v>
+        <v>7.8396110552474759E-4</v>
       </c>
       <c r="G50" s="4">
-        <v>2.339677504868966E-4</v>
+        <v>1.35821810761219E-3</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C51" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D51" s="3">
-        <v>2136662.9096641121</v>
+        <v>310794.74797233898</v>
       </c>
       <c r="E51" s="3">
-        <v>34419.6404244</v>
+        <v>8210.8821614400003</v>
       </c>
       <c r="F51" s="4">
-        <v>1.2450489874850871E-3</v>
+        <v>1.515288413031857E-4</v>
       </c>
       <c r="G51" s="4">
-        <v>2.6914455891389468E-4</v>
+        <v>1.134724744407487E-2</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C52" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D52" s="3">
-        <v>1963532.5336935241</v>
+        <v>297602.00445720641</v>
       </c>
       <c r="E52" s="3">
-        <v>38266.632667600003</v>
+        <v>3256.4356082999998</v>
       </c>
       <c r="F52" s="4">
-        <v>0.1254843771395045</v>
+        <v>3.8592436982227681E-4</v>
       </c>
       <c r="G52" s="4">
-        <v>3.2594779133939081E-4</v>
+        <v>2.369477916386043E-3</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C53" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D53" s="3">
-        <v>1438073.2884498299</v>
+        <v>289865.32010952412</v>
       </c>
       <c r="E53" s="3">
-        <v>33002.728752000003</v>
+        <v>5130.8202951200001</v>
       </c>
       <c r="F53" s="4">
-        <v>1.2530342781881009E-2</v>
+        <v>7.1409024001186736E-3</v>
       </c>
       <c r="G53" s="4">
-        <v>4.7058508757579111E-4</v>
+        <v>1.6292149323472839E-3</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C54" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D54" s="3">
-        <v>97959.145876195587</v>
+        <v>269939.47590449912</v>
       </c>
       <c r="E54" s="3">
-        <v>683.65838265999992</v>
+        <v>2592.956784</v>
       </c>
       <c r="F54" s="4">
-        <v>5.6993377084615887E-5</v>
+        <v>1.8052595511364291E-3</v>
       </c>
       <c r="G54" s="4">
-        <v>2.003412193486057E-3</v>
+        <v>8.4950123873718997E-4</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C55" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D55" s="3">
-        <v>95591.120637130909</v>
+        <v>262055.5197426404</v>
       </c>
       <c r="E55" s="3">
-        <v>1766.41918304</v>
+        <v>1735.1564722600001</v>
       </c>
       <c r="F55" s="4">
-        <v>1.0827214844375309E-3</v>
+        <v>3.0591654094954831E-3</v>
       </c>
       <c r="G55" s="4">
-        <v>1.157616504413661E-3</v>
+        <v>7.4264450532327117E-4</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C56" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D56" s="3">
-        <v>82867.321381128873</v>
+        <v>259818.50988372459</v>
       </c>
       <c r="E56" s="3">
-        <v>2276.6300928000001</v>
+        <v>45922.658233419999</v>
       </c>
       <c r="F56" s="4">
-        <v>2.6907058899788261E-3</v>
+        <v>4.0433840100499702E-5</v>
       </c>
       <c r="G56" s="4">
-        <v>8.8722397476340717E-4</v>
+        <v>1.5232724169502069E-4</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C57" s="2">
         <v>2021</v>
       </c>
       <c r="D57" s="3">
-        <v>320449.11322310509</v>
+        <v>234189.89306239539</v>
       </c>
       <c r="E57" s="3">
-        <v>3164.1185242800002</v>
+        <v>4733.3383234200001</v>
       </c>
       <c r="F57" s="4">
-        <v>6.7699852441129374E-3</v>
+        <v>6.6356632156617178E-4</v>
       </c>
       <c r="G57" s="4">
-        <v>2.6803313639870169E-3</v>
+        <v>3.1476572520248271E-3</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C58" s="2">
         <v>2024</v>
       </c>
       <c r="D58" s="3">
-        <v>269939.47590449912</v>
+        <v>208604.95707132079</v>
       </c>
       <c r="E58" s="3">
-        <v>2592.956784</v>
+        <v>1402.2910079999999</v>
       </c>
       <c r="F58" s="4">
-        <v>1.8052595511364291E-3</v>
+        <v>2.940331198358508E-3</v>
       </c>
       <c r="G58" s="4">
-        <v>8.4950123873718997E-4</v>
+        <v>9.1745863922704425E-4</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -1914,88 +1914,88 @@
         <v>8</v>
       </c>
       <c r="C59" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D59" s="3">
-        <v>332033.64455055603</v>
+        <v>201018.8383422663</v>
       </c>
       <c r="E59" s="3">
-        <v>1720.9347523199999</v>
+        <v>1914.6587492000001</v>
       </c>
       <c r="F59" s="4">
-        <v>5.4438237053266124E-4</v>
+        <v>2.4675821537253392E-3</v>
       </c>
       <c r="G59" s="4">
-        <v>1.095196036606934E-3</v>
+        <v>4.9806477545852595E-4</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C60" s="2">
         <v>2022</v>
       </c>
       <c r="D60" s="3">
-        <v>262055.5197426404</v>
+        <v>97959.145876195587</v>
       </c>
       <c r="E60" s="3">
-        <v>1735.1564722600001</v>
+        <v>683.65838265999992</v>
       </c>
       <c r="F60" s="4">
-        <v>3.0591654094954831E-3</v>
+        <v>5.6993377084615887E-5</v>
       </c>
       <c r="G60" s="4">
-        <v>7.4264450532327117E-4</v>
+        <v>2.003412193486057E-3</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C61" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D61" s="3">
-        <v>208604.95707132079</v>
+        <v>95591.120637130909</v>
       </c>
       <c r="E61" s="3">
-        <v>1402.2910079999999</v>
+        <v>1766.41918304</v>
       </c>
       <c r="F61" s="4">
-        <v>2.940331198358508E-3</v>
+        <v>1.0827214844375309E-3</v>
       </c>
       <c r="G61" s="4">
-        <v>9.1745863922704425E-4</v>
+        <v>1.157616504413661E-3</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C62" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D62" s="3">
-        <v>201018.8383422663</v>
+        <v>82867.321381128873</v>
       </c>
       <c r="E62" s="3">
-        <v>1914.6587492000001</v>
+        <v>2276.6300928000001</v>
       </c>
       <c r="F62" s="4">
-        <v>2.4675821537253392E-3</v>
+        <v>2.6907058899788261E-3</v>
       </c>
       <c r="G62" s="4">
-        <v>4.9806477545852595E-4</v>
+        <v>8.8722397476340717E-4</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="D66" s="3">
         <f>AVERAGE(D2:D31)</f>
-        <v>655349.05308665475</v>
+        <v>1124212.4339560324</v>
       </c>
       <c r="E66" s="3">
         <f t="shared" ref="E66:G66" si="0">AVERAGE(E2:E31)</f>
-        <v>17273.303883399334</v>
+        <v>21247.447441487337</v>
       </c>
       <c r="F66" s="4">
         <f t="shared" si="0"/>
-        <v>8.1223329477286606E-3</v>
+        <v>1.7925682509706109E-2</v>
       </c>
       <c r="G66" s="4">
         <f t="shared" si="0"/>
-        <v>3.1965856646829407E-3</v>
+        <v>2.4906293556901716E-3</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -2037,19 +2037,19 @@
       </c>
       <c r="D67" s="3">
         <f>AVERAGE(D33:D62)</f>
-        <v>727998.75488181249</v>
+        <v>313456.52033605945</v>
       </c>
       <c r="E67" s="3">
         <f t="shared" ref="E67:G67" si="1">AVERAGE(E33:E62)</f>
-        <v>9465.4867188440021</v>
+        <v>6530.0444956386673</v>
       </c>
       <c r="F67" s="4">
         <f t="shared" si="1"/>
-        <v>1.3455747789443185E-2</v>
+        <v>4.0228145149423019E-3</v>
       </c>
       <c r="G67" s="4">
         <f t="shared" si="1"/>
-        <v>1.4843925181374825E-3</v>
+        <v>2.1482436181387908E-3</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -2058,19 +2058,19 @@
       </c>
       <c r="D69" s="3">
         <f>D66/D67</f>
-        <v>0.90020628289817317</v>
+        <v>3.5865019899753703</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" ref="E69:G69" si="2">E66/E67</f>
-        <v>1.8248722328257498</v>
+        <v>3.2537982636532159</v>
       </c>
       <c r="F69" s="3">
         <f t="shared" si="2"/>
-        <v>0.60363296598804428</v>
+        <v>4.4560052279624465</v>
       </c>
       <c r="G69" s="3">
         <f t="shared" si="2"/>
-        <v>2.1534638753729403</v>
+        <v>1.1593793807464068</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4566,8 +4566,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A149:G152">
-    <sortCondition descending="1" ref="D149:D152"/>
+  <sortState ref="A2:G62">
+    <sortCondition descending="1" ref="D2:D62"/>
   </sortState>
   <conditionalFormatting sqref="D2:D62">
     <cfRule type="colorScale" priority="128">

--- a/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="44">
   <si>
     <t>sector</t>
   </si>
@@ -149,6 +152,9 @@
   <si>
     <t>разница</t>
   </si>
+  <si>
+    <t>Year</t>
+  </si>
 </sst>
 </file>
 
@@ -231,7 +237,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -258,6 +264,9 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -274,6 +283,3516 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t> Производство кокса и нефтепродуктов</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$114</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,64</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$114:$G$114</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.86244141308893119</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.9249386880226055E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-48A5-4E9B-8E97-537E0DDE442D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$115</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,88</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$115:$G$115</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69349389168532172</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.69264368962158107</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-48A5-4E9B-8E97-537E0DDE442D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$116</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,95</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$116:$G$116</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.89946875449908048</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.8808076937736939E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.57193601331565147</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-48A5-4E9B-8E97-537E0DDE442D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$117</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$117:$G$117</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75686804000192376</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.49718479540475113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-48A5-4E9B-8E97-537E0DDE442D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t> Производство химических веществ и химических продуктов</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$138</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,80</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$138:$G$138</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75473497922288912</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13016270721820974</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.20562583073637467</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3263-4778-9FE4-27A25304FFCB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$139</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,82</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$139:$G$139</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.8380185016176708E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.12267657460088674</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3263-4778-9FE4-27A25304FFCB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$140</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,86</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$140:$G$140</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.6990904820453</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3263-4778-9FE4-27A25304FFCB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$141:$G$141</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.56379755979405544</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.50828225173152997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.37838843465697375</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3263-4778-9FE4-27A25304FFCB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Производ. изд. из дерева</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$90</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,61</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$89:$G$89</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$90:$G$90</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.80661939562538798</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.45477225885659545</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BB71-415F-8913-10F086746BF9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$91</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,63</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$89:$G$89</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$91:$G$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7323973572762863</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.9611546957323327</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.83771179639168136</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BB71-415F-8913-10F086746BF9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$92</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,79</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$89:$G$89</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$92:$G$92</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.90624842311195075</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.67809276193519175</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-BB71-415F-8913-10F086746BF9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$93</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$89:$G$89</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$93:$G$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.89882061387652312</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17795127025264079</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-BB71-415F-8913-10F086746BF9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>582634</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>574192</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>94957</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Диаграмма 7"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>162049</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>85353</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>153609</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>30632</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Диаграмма 8"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>51954</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>173182</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>43513</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>118461</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Диаграмма 9"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="inf16"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="39">
+          <cell r="D39" t="str">
+            <v>Year</v>
+          </cell>
+          <cell r="E39" t="str">
+            <v>ITcosts_s</v>
+          </cell>
+          <cell r="F39" t="str">
+            <v>skvozcosts_s</v>
+          </cell>
+          <cell r="G39" t="str">
+            <v>trainingcosts_s</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="C40">
+            <v>0.75320035180004941</v>
+          </cell>
+          <cell r="D40">
+            <v>1</v>
+          </cell>
+          <cell r="E40">
+            <v>0.8576536031471178</v>
+          </cell>
+          <cell r="F40">
+            <v>9.4632036706885733E-2</v>
+          </cell>
+          <cell r="G40">
+            <v>0.30845304233506288</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="C41">
+            <v>0.80558451044020529</v>
+          </cell>
+          <cell r="D41">
+            <v>0.75</v>
+          </cell>
+          <cell r="E41">
+            <v>0.80890079918421609</v>
+          </cell>
+          <cell r="F41">
+            <v>0.27164901806536035</v>
+          </cell>
+          <cell r="G41">
+            <v>0.46444703398099701</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="C42">
+            <v>0.94055185443048506</v>
+          </cell>
+          <cell r="D42">
+            <v>0.5</v>
+          </cell>
+          <cell r="E42">
+            <v>0.79155969555065653</v>
+          </cell>
+          <cell r="F42">
+            <v>0.13278607396570202</v>
+          </cell>
+          <cell r="G42">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>1</v>
+          </cell>
+          <cell r="D43">
+            <v>0.25</v>
+          </cell>
+          <cell r="E43">
+            <v>1</v>
+          </cell>
+          <cell r="F43">
+            <v>1</v>
+          </cell>
+          <cell r="G43">
+            <v>0.47223470956791447</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -561,7 +4080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G223"/>
+  <dimension ref="A1:G279"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.42578125" customWidth="1"/>
@@ -2104,7 +5623,7 @@
         <v>8</v>
       </c>
       <c r="C72" s="2">
-        <v>2021</v>
+        <v>1</v>
       </c>
       <c r="D72" s="3">
         <v>332033.64455055603</v>
@@ -2127,7 +5646,7 @@
         <v>8</v>
       </c>
       <c r="C73" s="2">
-        <v>2022</v>
+        <v>2</v>
       </c>
       <c r="D73" s="3">
         <v>262055.5197426404</v>
@@ -2150,7 +5669,7 @@
         <v>8</v>
       </c>
       <c r="C74" s="2">
-        <v>2024</v>
+        <v>4</v>
       </c>
       <c r="D74" s="3">
         <v>208604.95707132079</v>
@@ -2173,7 +5692,7 @@
         <v>8</v>
       </c>
       <c r="C75" s="2">
-        <v>2023</v>
+        <v>3</v>
       </c>
       <c r="D75" s="3">
         <v>201018.8383422663</v>
@@ -2252,2322 +5771,2954 @@
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+      <c r="C82" s="2">
+        <f>MAX(C72:C75)</f>
+        <v>4</v>
+      </c>
+      <c r="D82" s="2">
+        <f t="shared" ref="D82:G82" si="6">MAX(D72:D75)</f>
+        <v>332033.64455055603</v>
+      </c>
+      <c r="E82" s="2">
+        <f t="shared" si="6"/>
+        <v>1914.6587492000001</v>
+      </c>
+      <c r="F82" s="2">
+        <f t="shared" si="6"/>
+        <v>3.0591654094954831E-3</v>
+      </c>
+      <c r="G82" s="2">
+        <f t="shared" si="6"/>
+        <v>1.095196036606934E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C83" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C84" s="2">
+        <f>C72/C$82</f>
+        <v>0.25</v>
+      </c>
+      <c r="D84" s="2">
+        <f>D72/D$82</f>
+        <v>1</v>
+      </c>
+      <c r="E84" s="2">
+        <f t="shared" ref="E84:G84" si="7">E72/E$82</f>
+        <v>0.89882061387652312</v>
+      </c>
+      <c r="F84" s="2">
+        <f t="shared" si="7"/>
+        <v>0.17795127025264079</v>
+      </c>
+      <c r="G84" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C85" s="2">
+        <f t="shared" ref="C85:G87" si="8">C73/C$82</f>
+        <v>0.5</v>
+      </c>
+      <c r="D85" s="2">
+        <f t="shared" si="8"/>
+        <v>0.78924387345553881</v>
+      </c>
+      <c r="E85" s="2">
+        <f t="shared" si="8"/>
+        <v>0.90624842311195075</v>
+      </c>
+      <c r="F85" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="G85" s="2">
+        <f t="shared" si="8"/>
+        <v>0.67809276193519175</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C86" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="D86" s="2">
+        <f t="shared" si="8"/>
+        <v>0.62826451624711255</v>
+      </c>
+      <c r="E86" s="2">
+        <f t="shared" si="8"/>
+        <v>0.7323973572762863</v>
+      </c>
+      <c r="F86" s="2">
+        <f t="shared" si="8"/>
+        <v>0.9611546957323327</v>
+      </c>
+      <c r="G86" s="2">
+        <f t="shared" si="8"/>
+        <v>0.83771179639168136</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C87" s="2">
+        <f t="shared" si="8"/>
+        <v>0.75</v>
+      </c>
+      <c r="D87" s="2">
+        <f t="shared" si="8"/>
+        <v>0.60541707637600206</v>
+      </c>
+      <c r="E87" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="F87" s="2">
+        <f t="shared" si="8"/>
+        <v>0.80661939562538798</v>
+      </c>
+      <c r="G87" s="2">
+        <f t="shared" si="8"/>
+        <v>0.45477225885659545</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C89" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C90" s="3">
+        <v>0.60541707637600206</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E90" s="2">
+        <v>1</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0.80661939562538798</v>
+      </c>
+      <c r="G90" s="2">
+        <v>0.45477225885659545</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C91" s="3">
+        <v>0.62826451624711255</v>
+      </c>
+      <c r="D91" s="2">
+        <v>1</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0.7323973572762863</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0.9611546957323327</v>
+      </c>
+      <c r="G91" s="2">
+        <v>0.83771179639168136</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C92" s="3">
+        <v>0.78924387345553881</v>
+      </c>
+      <c r="D92" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.90624842311195075</v>
+      </c>
+      <c r="F92" s="2">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2">
+        <v>0.67809276193519175</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C93" s="3">
+        <v>1</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.89882061387652312</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0.17795127025264079</v>
+      </c>
+      <c r="G93" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F95" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="G95" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C83" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D83" s="3">
-        <v>2237559.59010129</v>
-      </c>
-      <c r="E83" s="3">
-        <v>28962.7912646</v>
-      </c>
-      <c r="F83" s="4">
-        <v>0.18094518011478611</v>
-      </c>
-      <c r="G83" s="4">
-        <v>2.339677504868966E-4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C84" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D84" s="3">
-        <v>2136662.9096641121</v>
-      </c>
-      <c r="E84" s="3">
-        <v>34419.6404244</v>
-      </c>
-      <c r="F84" s="4">
-        <v>1.2450489874850871E-3</v>
-      </c>
-      <c r="G84" s="4">
-        <v>2.6914455891389468E-4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C85" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D85" s="3">
-        <v>1963532.5336935241</v>
-      </c>
-      <c r="E85" s="3">
-        <v>38266.632667600003</v>
-      </c>
-      <c r="F85" s="4">
-        <v>0.1254843771395045</v>
-      </c>
-      <c r="G85" s="4">
-        <v>3.2594779133939081E-4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C86" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D86" s="3">
-        <v>1438073.2884498299</v>
-      </c>
-      <c r="E86" s="3">
-        <v>33002.728752000003</v>
-      </c>
-      <c r="F86" s="4">
-        <v>1.2530342781881009E-2</v>
-      </c>
-      <c r="G86" s="4">
-        <v>4.7058508757579111E-4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B88" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D88" s="3">
-        <f>AVERAGE(D83:D84)</f>
-        <v>2187111.2498827009</v>
-      </c>
-      <c r="E88" s="3">
-        <f t="shared" ref="E88:G88" si="6">AVERAGE(E83:E84)</f>
-        <v>31691.215844500002</v>
-      </c>
-      <c r="F88" s="4">
-        <f t="shared" si="6"/>
-        <v>9.10951145511356E-2</v>
-      </c>
-      <c r="G88" s="4">
-        <f t="shared" si="6"/>
-        <v>2.5155615470039562E-4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B89" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D89" s="3">
-        <f>AVERAGE(D85:D86)</f>
-        <v>1700802.911071677</v>
-      </c>
-      <c r="E89" s="3">
-        <f t="shared" ref="E89:G89" si="7">AVERAGE(E85:E86)</f>
-        <v>35634.680709799999</v>
-      </c>
-      <c r="F89" s="4">
-        <f t="shared" si="7"/>
-        <v>6.9007359960692752E-2</v>
-      </c>
-      <c r="G89" s="4">
-        <f t="shared" si="7"/>
-        <v>3.9826643945759096E-4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C91" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D91" s="3">
-        <f>D88/D89</f>
-        <v>1.2859286844144691</v>
-      </c>
-      <c r="E91" s="3">
-        <f t="shared" ref="E91:G91" si="8">E88/E89</f>
-        <v>0.88933632105715787</v>
-      </c>
-      <c r="F91" s="3">
-        <f t="shared" si="8"/>
-        <v>1.3200782438717298</v>
-      </c>
-      <c r="G91" s="3">
-        <f t="shared" si="8"/>
-        <v>0.63162779932699387</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D94" s="3">
-        <v>1501058.080583167</v>
-      </c>
-      <c r="E94" s="3">
-        <v>10016.90090194</v>
-      </c>
-      <c r="F94" s="4">
-        <v>4.8543989239808157E-3</v>
-      </c>
-      <c r="G94" s="4">
-        <v>2.722411311338672E-3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D95" s="3">
-        <v>1291276.529800517</v>
-      </c>
-      <c r="E95" s="3">
-        <v>12420.628572240001</v>
-      </c>
-      <c r="F95" s="4">
-        <v>9.5505969516812179E-3</v>
-      </c>
-      <c r="G95" s="4">
-        <v>7.1947529628030547E-3</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C96" s="2">
-        <v>2024</v>
+        <v>2</v>
       </c>
       <c r="D96" s="3">
-        <v>1235191.2922385989</v>
+        <v>2237559.59010129</v>
       </c>
       <c r="E96" s="3">
-        <v>17766.839759999999</v>
+        <v>28962.7912646</v>
       </c>
       <c r="F96" s="4">
-        <v>9.3958949512133153E-4</v>
+        <v>0.18094518011478611</v>
       </c>
       <c r="G96" s="4">
-        <v>8.8262764857625984E-4</v>
+        <v>2.339677504868966E-4</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97" s="2">
+        <v>1</v>
+      </c>
+      <c r="D97" s="3">
+        <v>2136662.9096641121</v>
+      </c>
+      <c r="E97" s="3">
+        <v>34419.6404244</v>
+      </c>
+      <c r="F97" s="4">
+        <v>1.2450489874850871E-3</v>
+      </c>
+      <c r="G97" s="4">
+        <v>2.6914455891389468E-4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" s="2">
+        <v>3</v>
+      </c>
+      <c r="D98" s="3">
+        <v>1963532.5336935241</v>
+      </c>
+      <c r="E98" s="3">
+        <v>38266.632667600003</v>
+      </c>
+      <c r="F98" s="4">
+        <v>0.1254843771395045</v>
+      </c>
+      <c r="G98" s="4">
+        <v>3.2594779133939081E-4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C99" s="2">
+        <v>4</v>
+      </c>
+      <c r="D99" s="3">
+        <v>1438073.2884498299</v>
+      </c>
+      <c r="E99" s="3">
+        <v>33002.728752000003</v>
+      </c>
+      <c r="F99" s="4">
+        <v>1.2530342781881009E-2</v>
+      </c>
+      <c r="G99" s="4">
+        <v>4.7058508757579111E-4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B101" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D101" s="3">
+        <f>AVERAGE(D96:D97)</f>
+        <v>2187111.2498827009</v>
+      </c>
+      <c r="E101" s="3">
+        <f t="shared" ref="E101:G101" si="9">AVERAGE(E96:E97)</f>
+        <v>31691.215844500002</v>
+      </c>
+      <c r="F101" s="4">
+        <f t="shared" si="9"/>
+        <v>9.10951145511356E-2</v>
+      </c>
+      <c r="G101" s="4">
+        <f t="shared" si="9"/>
+        <v>2.5155615470039562E-4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B102" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D102" s="3">
+        <f>AVERAGE(D98:D99)</f>
+        <v>1700802.911071677</v>
+      </c>
+      <c r="E102" s="3">
+        <f t="shared" ref="E102:G102" si="10">AVERAGE(E98:E99)</f>
+        <v>35634.680709799999</v>
+      </c>
+      <c r="F102" s="4">
+        <f t="shared" si="10"/>
+        <v>6.9007359960692752E-2</v>
+      </c>
+      <c r="G102" s="4">
+        <f t="shared" si="10"/>
+        <v>3.9826643945759096E-4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C104" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D104" s="3">
+        <f>D101/D102</f>
+        <v>1.2859286844144691</v>
+      </c>
+      <c r="E104" s="3">
+        <f t="shared" ref="E104:G104" si="11">E101/E102</f>
+        <v>0.88933632105715787</v>
+      </c>
+      <c r="F104" s="3">
+        <f t="shared" si="11"/>
+        <v>1.3200782438717298</v>
+      </c>
+      <c r="G104" s="3">
+        <f t="shared" si="11"/>
+        <v>0.63162779932699387</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C106" s="2">
+        <f>MAX(C96:C99)</f>
+        <v>4</v>
+      </c>
+      <c r="D106" s="2">
+        <f t="shared" ref="D106:G106" si="12">MAX(D96:D99)</f>
+        <v>2237559.59010129</v>
+      </c>
+      <c r="E106" s="2">
+        <f t="shared" si="12"/>
+        <v>38266.632667600003</v>
+      </c>
+      <c r="F106" s="2">
+        <f t="shared" si="12"/>
+        <v>0.18094518011478611</v>
+      </c>
+      <c r="G106" s="2">
+        <f t="shared" si="12"/>
+        <v>4.7058508757579111E-4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C107" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C108" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D108" s="2">
+        <f>D96/D$106</f>
+        <v>1</v>
+      </c>
+      <c r="E108" s="2">
+        <f t="shared" ref="E108:G108" si="13">E96/E$106</f>
+        <v>0.75686804000192376</v>
+      </c>
+      <c r="F108" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="G108" s="2">
+        <f t="shared" si="13"/>
+        <v>0.49718479540475113</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C109" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D109" s="2">
+        <f t="shared" ref="D109:G111" si="14">D97/D$106</f>
+        <v>0.95490771245443773</v>
+      </c>
+      <c r="E109" s="2">
+        <f t="shared" si="14"/>
+        <v>0.89946875449908048</v>
+      </c>
+      <c r="F109" s="2">
+        <f t="shared" si="14"/>
+        <v>6.8808076937736939E-3</v>
+      </c>
+      <c r="G109" s="2">
+        <f t="shared" si="14"/>
+        <v>0.57193601331565147</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C110" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D110" s="2">
+        <f t="shared" si="14"/>
+        <v>0.87753306878617643</v>
+      </c>
+      <c r="E110" s="2">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="F110" s="2">
+        <f t="shared" si="14"/>
+        <v>0.69349389168532172</v>
+      </c>
+      <c r="G110" s="2">
+        <f t="shared" si="14"/>
+        <v>0.69264368962158107</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C111" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D111" s="2">
+        <f t="shared" si="14"/>
+        <v>0.6426972022607591</v>
+      </c>
+      <c r="E111" s="2">
+        <f t="shared" si="14"/>
+        <v>0.86244141308893119</v>
+      </c>
+      <c r="F111" s="2">
+        <f t="shared" si="14"/>
+        <v>6.9249386880226055E-2</v>
+      </c>
+      <c r="G111" s="2">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C113" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F113" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G113" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C114" s="3">
+        <v>0.6426972022607591</v>
+      </c>
+      <c r="D114" s="2">
+        <v>1</v>
+      </c>
+      <c r="E114" s="2">
+        <v>0.86244141308893119</v>
+      </c>
+      <c r="F114" s="2">
+        <v>6.9249386880226055E-2</v>
+      </c>
+      <c r="G114" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C115" s="3">
+        <v>0.87753306878617643</v>
+      </c>
+      <c r="D115" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E115" s="2">
+        <v>1</v>
+      </c>
+      <c r="F115" s="2">
+        <v>0.69349389168532172</v>
+      </c>
+      <c r="G115" s="2">
+        <v>0.69264368962158107</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C116" s="3">
+        <v>0.95490771245443773</v>
+      </c>
+      <c r="D116" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E116" s="2">
+        <v>0.89946875449908048</v>
+      </c>
+      <c r="F116" s="2">
+        <v>6.8808076937736939E-3</v>
+      </c>
+      <c r="G116" s="2">
+        <v>0.57193601331565147</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C117" s="3">
+        <v>1</v>
+      </c>
+      <c r="D117" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E117" s="2">
+        <v>0.75686804000192376</v>
+      </c>
+      <c r="F117" s="2">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2">
+        <v>0.49718479540475113</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B120" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C120" s="2">
+        <v>2</v>
+      </c>
+      <c r="D120" s="3">
+        <v>1501058.080583167</v>
+      </c>
+      <c r="E120" s="3">
+        <v>10016.90090194</v>
+      </c>
+      <c r="F120" s="4">
+        <v>4.8543989239808157E-3</v>
+      </c>
+      <c r="G120" s="4">
+        <v>2.722411311338672E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+      <c r="D121" s="3">
+        <v>1291276.529800517</v>
+      </c>
+      <c r="E121" s="3">
+        <v>12420.628572240001</v>
+      </c>
+      <c r="F121" s="4">
+        <v>9.5505969516812179E-3</v>
+      </c>
+      <c r="G121" s="4">
+        <v>7.1947529628030547E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" s="2">
+        <v>4</v>
+      </c>
+      <c r="D122" s="3">
+        <v>1235191.2922385989</v>
+      </c>
+      <c r="E122" s="3">
+        <v>17766.839759999999</v>
+      </c>
+      <c r="F122" s="4">
+        <v>9.3958949512133153E-4</v>
+      </c>
+      <c r="G122" s="4">
+        <v>8.8262764857625984E-4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" s="2">
+        <v>3</v>
+      </c>
+      <c r="D123" s="3">
+        <v>1202957.7138338401</v>
+      </c>
+      <c r="E123" s="3">
+        <v>13409.25543712</v>
+      </c>
+      <c r="F123" s="4">
+        <v>1.2431315547808089E-3</v>
+      </c>
+      <c r="G123" s="4">
+        <v>1.4794270549193711E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B125" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D125" s="3">
+        <f>AVERAGE(D120:D121)</f>
+        <v>1396167.3051918419</v>
+      </c>
+      <c r="E125" s="3">
+        <f t="shared" ref="E125:G125" si="15">AVERAGE(E120:E121)</f>
+        <v>11218.764737090001</v>
+      </c>
+      <c r="F125" s="4">
+        <f t="shared" si="15"/>
+        <v>7.2024979378310164E-3</v>
+      </c>
+      <c r="G125" s="4">
+        <f t="shared" si="15"/>
+        <v>4.9585821370708629E-3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B126" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D126" s="3">
+        <f>AVERAGE(D122:D123)</f>
+        <v>1219074.5030362196</v>
+      </c>
+      <c r="E126" s="3">
+        <f t="shared" ref="E126:G126" si="16">AVERAGE(E122:E123)</f>
+        <v>15588.047598559999</v>
+      </c>
+      <c r="F126" s="4">
+        <f t="shared" si="16"/>
+        <v>1.0913605249510702E-3</v>
+      </c>
+      <c r="G126" s="4">
+        <f t="shared" si="16"/>
+        <v>1.1810273517478154E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C128" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D128" s="3">
+        <f>D125/D126</f>
+        <v>1.1452682356283854</v>
+      </c>
+      <c r="E128" s="3">
+        <f t="shared" ref="E128:G128" si="17">E125/E126</f>
+        <v>0.71970300745850779</v>
+      </c>
+      <c r="F128" s="3">
+        <f t="shared" si="17"/>
+        <v>6.5995587829731441</v>
+      </c>
+      <c r="G128" s="3">
+        <f t="shared" si="17"/>
+        <v>4.1985328533946333</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C130" s="2">
+        <f>MAX(C120:C123)</f>
+        <v>4</v>
+      </c>
+      <c r="D130" s="2">
+        <f t="shared" ref="D130:G130" si="18">MAX(D120:D123)</f>
+        <v>1501058.080583167</v>
+      </c>
+      <c r="E130" s="2">
+        <f t="shared" si="18"/>
+        <v>17766.839759999999</v>
+      </c>
+      <c r="F130" s="2">
+        <f t="shared" si="18"/>
+        <v>9.5505969516812179E-3</v>
+      </c>
+      <c r="G130" s="2">
+        <f t="shared" si="18"/>
+        <v>7.1947529628030547E-3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C131" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C132" s="2">
+        <f>C120/C$82</f>
+        <v>0.5</v>
+      </c>
+      <c r="D132" s="2">
+        <f>D120/D$130</f>
+        <v>1</v>
+      </c>
+      <c r="E132" s="2">
+        <f t="shared" ref="E132:G132" si="19">E120/E$130</f>
+        <v>0.56379755979405544</v>
+      </c>
+      <c r="F132" s="2">
+        <f t="shared" si="19"/>
+        <v>0.50828225173152997</v>
+      </c>
+      <c r="G132" s="2">
+        <f t="shared" si="19"/>
+        <v>0.37838843465697375</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C133" s="2">
+        <f t="shared" ref="C133:C135" si="20">C121/C$82</f>
+        <v>0.25</v>
+      </c>
+      <c r="D133" s="2">
+        <f t="shared" ref="D133:G135" si="21">D121/D$130</f>
+        <v>0.86024421473341717</v>
+      </c>
+      <c r="E133" s="2">
+        <f t="shared" si="21"/>
+        <v>0.6990904820453</v>
+      </c>
+      <c r="F133" s="2">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="G133" s="2">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C134" s="2">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="D134" s="2">
+        <f t="shared" si="21"/>
+        <v>0.82288041230138287</v>
+      </c>
+      <c r="E134" s="2">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F134" s="2">
+        <f t="shared" si="21"/>
+        <v>9.8380185016176708E-2</v>
+      </c>
+      <c r="G134" s="2">
+        <f t="shared" si="21"/>
+        <v>0.12267657460088674</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C135" s="2">
+        <f t="shared" si="20"/>
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="2">
+        <f t="shared" si="21"/>
+        <v>0.80140650744605846</v>
+      </c>
+      <c r="E135" s="2">
+        <f t="shared" si="21"/>
+        <v>0.75473497922288912</v>
+      </c>
+      <c r="F135" s="2">
+        <f t="shared" si="21"/>
+        <v>0.13016270721820974</v>
+      </c>
+      <c r="G135" s="2">
+        <f t="shared" si="21"/>
+        <v>0.20562583073637467</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C137" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F137" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G137" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C138" s="3">
+        <v>0.80140650744605846</v>
+      </c>
+      <c r="D138" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E138" s="2">
+        <v>0.75473497922288912</v>
+      </c>
+      <c r="F138" s="2">
+        <v>0.13016270721820974</v>
+      </c>
+      <c r="G138" s="2">
+        <v>0.20562583073637467</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C139" s="3">
+        <v>0.82288041230138287</v>
+      </c>
+      <c r="D139" s="2">
+        <v>1</v>
+      </c>
+      <c r="E139" s="2">
+        <v>1</v>
+      </c>
+      <c r="F139" s="2">
+        <v>9.8380185016176708E-2</v>
+      </c>
+      <c r="G139" s="2">
+        <v>0.12267657460088674</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C140" s="3">
+        <v>0.86024421473341717</v>
+      </c>
+      <c r="D140" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E140" s="2">
+        <v>0.6990904820453</v>
+      </c>
+      <c r="F140" s="2">
+        <v>1</v>
+      </c>
+      <c r="G140" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C141" s="3">
+        <v>1</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E141" s="2">
+        <v>0.56379755979405544</v>
+      </c>
+      <c r="F141" s="2">
+        <v>0.50828225173152997</v>
+      </c>
+      <c r="G141" s="2">
+        <v>0.37838843465697375</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C144" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D144" s="3">
+        <v>391236.03926557873</v>
+      </c>
+      <c r="E144" s="3">
+        <v>9174.7777388399991</v>
+      </c>
+      <c r="F144" s="4">
+        <v>7.2720955318134649E-3</v>
+      </c>
+      <c r="G144" s="4">
+        <v>4.0538663342816288E-4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C145" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D145" s="3">
+        <v>331000.25434189721</v>
+      </c>
+      <c r="E145" s="3">
+        <v>7502.6813292799998</v>
+      </c>
+      <c r="F145" s="4">
+        <v>1.753601618218082E-3</v>
+      </c>
+      <c r="G145" s="4">
+        <v>3.3407912051630981E-4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C146" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D146" s="3">
+        <v>315114.80271184049</v>
+      </c>
+      <c r="E146" s="3">
+        <v>3780.5631839999992</v>
+      </c>
+      <c r="F146" s="4">
+        <v>1.04121883656369E-2</v>
+      </c>
+      <c r="G146" s="4">
+        <v>1.4970467955548929E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C147" s="2">
         <v>2023</v>
       </c>
-      <c r="D97" s="3">
-        <v>1202957.7138338401</v>
-      </c>
-      <c r="E97" s="3">
-        <v>13409.25543712</v>
-      </c>
-      <c r="F97" s="4">
-        <v>1.2431315547808089E-3</v>
-      </c>
-      <c r="G97" s="4">
-        <v>1.4794270549193711E-3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B99" s="7" t="s">
+      <c r="D147" s="3">
+        <v>311812.99097068148</v>
+      </c>
+      <c r="E147" s="3">
+        <v>3403.6800820799999</v>
+      </c>
+      <c r="F147" s="4">
+        <v>7.8396110552474759E-4</v>
+      </c>
+      <c r="G147" s="4">
+        <v>1.35821810761219E-3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B149" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D99" s="3">
-        <f>AVERAGE(D94:D95)</f>
-        <v>1396167.3051918419</v>
-      </c>
-      <c r="E99" s="3">
-        <f t="shared" ref="E99:G99" si="9">AVERAGE(E94:E95)</f>
-        <v>11218.764737090001</v>
-      </c>
-      <c r="F99" s="4">
-        <f t="shared" si="9"/>
-        <v>7.2024979378310164E-3</v>
-      </c>
-      <c r="G99" s="4">
-        <f t="shared" si="9"/>
-        <v>4.9585821370708629E-3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B100" s="7" t="s">
+      <c r="D149" s="3">
+        <f>AVERAGE(D144:D145)</f>
+        <v>361118.14680373797</v>
+      </c>
+      <c r="E149" s="3">
+        <f t="shared" ref="E149:G149" si="22">AVERAGE(E144:E145)</f>
+        <v>8338.7295340599994</v>
+      </c>
+      <c r="F149" s="4">
+        <f t="shared" si="22"/>
+        <v>4.5128485750157736E-3</v>
+      </c>
+      <c r="G149" s="4">
+        <f t="shared" si="22"/>
+        <v>3.6973287697223637E-4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B150" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D100" s="3">
-        <f>AVERAGE(D96:D97)</f>
-        <v>1219074.5030362196</v>
-      </c>
-      <c r="E100" s="3">
-        <f t="shared" ref="E100:G100" si="10">AVERAGE(E96:E97)</f>
-        <v>15588.047598559999</v>
-      </c>
-      <c r="F100" s="4">
-        <f t="shared" si="10"/>
-        <v>1.0913605249510702E-3</v>
-      </c>
-      <c r="G100" s="4">
-        <f t="shared" si="10"/>
-        <v>1.1810273517478154E-3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C102" s="7" t="s">
+      <c r="D150" s="3">
+        <f>AVERAGE(D146:D147)</f>
+        <v>313463.89684126095</v>
+      </c>
+      <c r="E150" s="3">
+        <f t="shared" ref="E150:G150" si="23">AVERAGE(E146:E147)</f>
+        <v>3592.1216330399993</v>
+      </c>
+      <c r="F150" s="4">
+        <f t="shared" si="23"/>
+        <v>5.5980747355808243E-3</v>
+      </c>
+      <c r="G150" s="4">
+        <f t="shared" si="23"/>
+        <v>1.4276324515835415E-3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C152" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D102" s="3">
-        <f>D99/D100</f>
-        <v>1.1452682356283854</v>
-      </c>
-      <c r="E102" s="3">
-        <f t="shared" ref="E102:G102" si="11">E99/E100</f>
-        <v>0.71970300745850779</v>
-      </c>
-      <c r="F102" s="3">
-        <f t="shared" si="11"/>
-        <v>6.5995587829731441</v>
-      </c>
-      <c r="G102" s="3">
-        <f t="shared" si="11"/>
-        <v>4.1985328533946333</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
+      <c r="D152" s="3">
+        <f>D149/D150</f>
+        <v>1.1520246843183004</v>
+      </c>
+      <c r="E152" s="3">
+        <f t="shared" ref="E152:G152" si="24">E149/E150</f>
+        <v>2.3213939799145842</v>
+      </c>
+      <c r="F152" s="3">
+        <f t="shared" si="24"/>
+        <v>0.80614296667612206</v>
+      </c>
+      <c r="G152" s="3">
+        <f t="shared" si="24"/>
+        <v>0.25898323939199175</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B171" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C171" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="D171" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F104" s="1" t="s">
+      <c r="F171" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G104" s="1" t="s">
+      <c r="G171" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C105" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D105" s="3">
-        <v>391236.03926557873</v>
-      </c>
-      <c r="E105" s="3">
-        <v>9174.7777388399991</v>
-      </c>
-      <c r="F105" s="4">
-        <v>7.2720955318134649E-3</v>
-      </c>
-      <c r="G105" s="4">
-        <v>4.0538663342816288E-4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C106" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D106" s="3">
-        <v>331000.25434189721</v>
-      </c>
-      <c r="E106" s="3">
-        <v>7502.6813292799998</v>
-      </c>
-      <c r="F106" s="4">
-        <v>1.753601618218082E-3</v>
-      </c>
-      <c r="G106" s="4">
-        <v>3.3407912051630981E-4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B107" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C107" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D107" s="3">
-        <v>315114.80271184049</v>
-      </c>
-      <c r="E107" s="3">
-        <v>3780.5631839999992</v>
-      </c>
-      <c r="F107" s="4">
-        <v>1.04121883656369E-2</v>
-      </c>
-      <c r="G107" s="4">
-        <v>1.4970467955548929E-3</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B108" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C108" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D108" s="3">
-        <v>311812.99097068148</v>
-      </c>
-      <c r="E108" s="3">
-        <v>3403.6800820799999</v>
-      </c>
-      <c r="F108" s="4">
-        <v>7.8396110552474759E-4</v>
-      </c>
-      <c r="G108" s="4">
-        <v>1.35821810761219E-3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B110" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D110" s="3">
-        <f>AVERAGE(D105:D106)</f>
-        <v>361118.14680373797</v>
-      </c>
-      <c r="E110" s="3">
-        <f t="shared" ref="E110:G110" si="12">AVERAGE(E105:E106)</f>
-        <v>8338.7295340599994</v>
-      </c>
-      <c r="F110" s="4">
-        <f t="shared" si="12"/>
-        <v>4.5128485750157736E-3</v>
-      </c>
-      <c r="G110" s="4">
-        <f t="shared" si="12"/>
-        <v>3.6973287697223637E-4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B111" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D111" s="3">
-        <f>AVERAGE(D107:D108)</f>
-        <v>313463.89684126095</v>
-      </c>
-      <c r="E111" s="3">
-        <f t="shared" ref="E111:G111" si="13">AVERAGE(E107:E108)</f>
-        <v>3592.1216330399993</v>
-      </c>
-      <c r="F111" s="4">
-        <f t="shared" si="13"/>
-        <v>5.5980747355808243E-3</v>
-      </c>
-      <c r="G111" s="4">
-        <f t="shared" si="13"/>
-        <v>1.4276324515835415E-3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C113" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D113" s="3">
-        <f>D110/D111</f>
-        <v>1.1520246843183004</v>
-      </c>
-      <c r="E113" s="3">
-        <f t="shared" ref="E113:G113" si="14">E110/E111</f>
-        <v>2.3213939799145842</v>
-      </c>
-      <c r="F113" s="3">
-        <f t="shared" si="14"/>
-        <v>0.80614296667612206</v>
-      </c>
-      <c r="G113" s="3">
-        <f t="shared" si="14"/>
-        <v>0.25898323939199175</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B116" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C116" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D116" s="3">
-        <v>327266.01547195681</v>
-      </c>
-      <c r="E116" s="3">
-        <v>2736.7203125999999</v>
-      </c>
-      <c r="F116" s="4">
-        <v>6.5575458761258591E-4</v>
-      </c>
-      <c r="G116" s="4">
-        <v>9.6186040198574876E-4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B117" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C117" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D117" s="3">
-        <v>323997.44760210218</v>
-      </c>
-      <c r="E117" s="3">
-        <v>2594.2840083999999</v>
-      </c>
-      <c r="F117" s="4">
-        <v>4.4144095106468531E-4</v>
-      </c>
-      <c r="G117" s="4">
-        <v>4.2813564143465432E-3</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B118" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C118" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D118" s="3">
-        <v>321762.90970591619</v>
-      </c>
-      <c r="E118" s="3">
-        <v>2793.945984</v>
-      </c>
-      <c r="F118" s="4">
-        <v>3.0877619142976242E-4</v>
-      </c>
-      <c r="G118" s="4">
-        <v>1.0062327675981299E-3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B119" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C119" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D119" s="3">
-        <v>297602.00445720641</v>
-      </c>
-      <c r="E119" s="3">
-        <v>3256.4356082999998</v>
-      </c>
-      <c r="F119" s="4">
-        <v>3.8592436982227681E-4</v>
-      </c>
-      <c r="G119" s="4">
-        <v>2.369477916386043E-3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B121" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D121" s="3">
-        <f>AVERAGE(D116:D117)</f>
-        <v>325631.7315370295</v>
-      </c>
-      <c r="E121" s="3">
-        <f t="shared" ref="E121:G121" si="15">AVERAGE(E116:E117)</f>
-        <v>2665.5021605000002</v>
-      </c>
-      <c r="F121" s="4">
-        <f t="shared" si="15"/>
-        <v>5.4859776933863561E-4</v>
-      </c>
-      <c r="G121" s="4">
-        <f t="shared" si="15"/>
-        <v>2.6216084081661459E-3</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B122" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D122" s="3">
-        <f>AVERAGE(D118:D119)</f>
-        <v>309682.45708156133</v>
-      </c>
-      <c r="E122" s="3">
-        <f t="shared" ref="E122:G122" si="16">AVERAGE(E118:E119)</f>
-        <v>3025.1907961500001</v>
-      </c>
-      <c r="F122" s="4">
-        <f t="shared" si="16"/>
-        <v>3.4735028062601961E-4</v>
-      </c>
-      <c r="G122" s="4">
-        <f t="shared" si="16"/>
-        <v>1.6878553419920864E-3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C124" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D124" s="3">
-        <f>D121/D122</f>
-        <v>1.0515020276116822</v>
-      </c>
-      <c r="E124" s="3">
-        <f t="shared" ref="E124:G124" si="17">E121/E122</f>
-        <v>0.88110216515673767</v>
-      </c>
-      <c r="F124" s="3">
-        <f t="shared" si="17"/>
-        <v>1.5793790877321685</v>
-      </c>
-      <c r="G124" s="3">
-        <f t="shared" si="17"/>
-        <v>1.5532186573951297</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B127" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C127" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D127" s="3">
-        <v>589836.07301855378</v>
-      </c>
-      <c r="E127" s="3">
-        <v>3459.2387039999999</v>
-      </c>
-      <c r="F127" s="4">
-        <v>2.6129124854981389E-3</v>
-      </c>
-      <c r="G127" s="4">
-        <v>2.2962786554205951E-3</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B128" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C128" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D128" s="3">
-        <v>585427.26654459862</v>
-      </c>
-      <c r="E128" s="3">
-        <v>4854.6591208600003</v>
-      </c>
-      <c r="F128" s="4">
-        <v>3.7612999688359748E-4</v>
-      </c>
-      <c r="G128" s="4">
-        <v>2.0756040556386131E-3</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B129" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C129" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D129" s="3">
-        <v>575669.32501484314</v>
-      </c>
-      <c r="E129" s="3">
-        <v>4774.9529707199999</v>
-      </c>
-      <c r="F129" s="4">
-        <v>2.8738600116371028E-4</v>
-      </c>
-      <c r="G129" s="4">
-        <v>1.316480132589062E-3</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B130" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C130" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D130" s="3">
-        <v>532258.74860418728</v>
-      </c>
-      <c r="E130" s="3">
-        <v>5998.8555937799993</v>
-      </c>
-      <c r="F130" s="4">
-        <v>3.3561812091085249E-3</v>
-      </c>
-      <c r="G130" s="4">
-        <v>1.7434020366891251E-3</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B132" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D132" s="3">
-        <f>AVERAGE(D127:D128)</f>
-        <v>587631.66978157614</v>
-      </c>
-      <c r="E132" s="3">
-        <f t="shared" ref="E132:G132" si="18">AVERAGE(E127:E128)</f>
-        <v>4156.9489124299998</v>
-      </c>
-      <c r="F132" s="4">
-        <f t="shared" si="18"/>
-        <v>1.4945212411908682E-3</v>
-      </c>
-      <c r="G132" s="4">
-        <f t="shared" si="18"/>
-        <v>2.1859413555296043E-3</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B133" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D133" s="3">
-        <f>AVERAGE(D129:D130)</f>
-        <v>553964.03680951521</v>
-      </c>
-      <c r="E133" s="3">
-        <f t="shared" ref="E133:G133" si="19">AVERAGE(E129:E130)</f>
-        <v>5386.9042822499996</v>
-      </c>
-      <c r="F133" s="4">
-        <f t="shared" si="19"/>
-        <v>1.8217836051361176E-3</v>
-      </c>
-      <c r="G133" s="4">
-        <f t="shared" si="19"/>
-        <v>1.5299410846390934E-3</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C135" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D135" s="3">
-        <f>D132/D133</f>
-        <v>1.0607758459664012</v>
-      </c>
-      <c r="E135" s="3">
-        <f t="shared" ref="E135:G135" si="20">E132/E133</f>
-        <v>0.77167677289668257</v>
-      </c>
-      <c r="F135" s="3">
-        <f t="shared" si="20"/>
-        <v>0.82036156049346076</v>
-      </c>
-      <c r="G135" s="3">
-        <f t="shared" si="20"/>
-        <v>1.4287748577228767</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B138" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C138" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D138" s="3">
-        <v>2688475.9724428668</v>
-      </c>
-      <c r="E138" s="3">
-        <v>22918.622383440001</v>
-      </c>
-      <c r="F138" s="4">
-        <v>1.411209606183382E-2</v>
-      </c>
-      <c r="G138" s="4">
-        <v>6.7540592802753808E-4</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B139" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C139" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D139" s="3">
-        <v>2199098.9702055152</v>
-      </c>
-      <c r="E139" s="3">
-        <v>27186.587841839999</v>
-      </c>
-      <c r="F139" s="4">
-        <v>1.428164445640567E-2</v>
-      </c>
-      <c r="G139" s="4">
-        <v>1.063284111568874E-3</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B140" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C140" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D140" s="3">
-        <v>2110825.0242093089</v>
-      </c>
-      <c r="E140" s="3">
-        <v>36820.330575920001</v>
-      </c>
-      <c r="F140" s="4">
-        <v>1.1388913987487259E-2</v>
-      </c>
-      <c r="G140" s="4">
-        <v>1.346627653376551E-3</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B141" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C141" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D141" s="3">
-        <v>2060147.693651289</v>
-      </c>
-      <c r="E141" s="3">
-        <v>24111.565200000001</v>
-      </c>
-      <c r="F141" s="4">
-        <v>1.6816288641435851E-2</v>
-      </c>
-      <c r="G141" s="4">
-        <v>4.7603910840263489E-4</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B143" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D143" s="3">
-        <f>AVERAGE(D138:D139)</f>
-        <v>2443787.471324191</v>
-      </c>
-      <c r="E143" s="3">
-        <f t="shared" ref="E143:G143" si="21">AVERAGE(E138:E139)</f>
-        <v>25052.605112639998</v>
-      </c>
-      <c r="F143" s="4">
-        <f t="shared" si="21"/>
-        <v>1.4196870259119745E-2</v>
-      </c>
-      <c r="G143" s="4">
-        <f t="shared" si="21"/>
-        <v>8.6934501979820604E-4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B144" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D144" s="3">
-        <f>AVERAGE(D140:D141)</f>
-        <v>2085486.3589302991</v>
-      </c>
-      <c r="E144" s="3">
-        <f t="shared" ref="E144:G144" si="22">AVERAGE(E140:E141)</f>
-        <v>30465.947887959999</v>
-      </c>
-      <c r="F144" s="4">
-        <f t="shared" si="22"/>
-        <v>1.4102601314461555E-2</v>
-      </c>
-      <c r="G144" s="4">
-        <f t="shared" si="22"/>
-        <v>9.1133338088959293E-4</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C146" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D146" s="3">
-        <f>D143/D144</f>
-        <v>1.1718069796331221</v>
-      </c>
-      <c r="E146" s="3">
-        <f t="shared" ref="E146:G146" si="23">E143/E144</f>
-        <v>0.82231497292558131</v>
-      </c>
-      <c r="F146" s="3">
-        <f t="shared" si="23"/>
-        <v>1.0066845075285169</v>
-      </c>
-      <c r="G146" s="3">
-        <f t="shared" si="23"/>
-        <v>0.95392645329154935</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B149" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C149" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D149" s="3">
-        <v>1079590.799601601</v>
-      </c>
-      <c r="E149" s="3">
-        <v>29824.255583999999</v>
-      </c>
-      <c r="F149" s="4">
-        <v>1.7700063980245699E-2</v>
-      </c>
-      <c r="G149" s="4">
-        <v>1.8406361575525849E-2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B150" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C150" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D150" s="3">
-        <v>917032.53729645221</v>
-      </c>
-      <c r="E150" s="3">
-        <v>21948.7441788</v>
-      </c>
-      <c r="F150" s="4">
-        <v>5.1385668600091312E-2</v>
-      </c>
-      <c r="G150" s="4">
-        <v>1.045825844659099E-3</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B151" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C151" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D151" s="3">
-        <v>802566.08061441511</v>
-      </c>
-      <c r="E151" s="3">
-        <v>12046.641059559999</v>
-      </c>
-      <c r="F151" s="4">
-        <v>1.264319260007594E-2</v>
-      </c>
-      <c r="G151" s="4">
-        <v>9.2646432850616075E-4</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B152" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C152" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D152" s="3">
-        <v>774599.50938466226</v>
-      </c>
-      <c r="E152" s="3">
-        <v>31768.917493320001</v>
-      </c>
-      <c r="F152" s="4">
-        <v>4.5024994770462897E-3</v>
-      </c>
-      <c r="G152" s="4">
-        <v>6.1504127372638605E-4</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B154" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D154" s="3">
-        <f>AVERAGE(D149:D150)</f>
-        <v>998311.66844902653</v>
-      </c>
-      <c r="E154" s="3">
-        <f t="shared" ref="E154:G154" si="24">AVERAGE(E149:E150)</f>
-        <v>25886.499881399999</v>
-      </c>
-      <c r="F154" s="4">
-        <f t="shared" si="24"/>
-        <v>3.4542866290168506E-2</v>
-      </c>
-      <c r="G154" s="4">
-        <f t="shared" si="24"/>
-        <v>9.7260937100924743E-3</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B155" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D155" s="3">
-        <f>AVERAGE(D151:D152)</f>
-        <v>788582.79499953869</v>
-      </c>
-      <c r="E155" s="3">
-        <f t="shared" ref="E155:G155" si="25">AVERAGE(E151:E152)</f>
-        <v>21907.77927644</v>
-      </c>
-      <c r="F155" s="4">
-        <f t="shared" si="25"/>
-        <v>8.5728460385611147E-3</v>
-      </c>
-      <c r="G155" s="4">
-        <f t="shared" si="25"/>
-        <v>7.7075280111627334E-4</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C157" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D157" s="3">
-        <f>D154/D155</f>
-        <v>1.2659566944389276</v>
-      </c>
-      <c r="E157" s="3">
-        <f t="shared" ref="E157:G157" si="26">E154/E155</f>
-        <v>1.1816122280015293</v>
-      </c>
-      <c r="F157" s="3">
-        <f t="shared" si="26"/>
-        <v>4.0293347314057506</v>
-      </c>
-      <c r="G157" s="3">
-        <f t="shared" si="26"/>
-        <v>12.618953438776055</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B160" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C160" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D160" s="3">
-        <v>702640.28510284843</v>
-      </c>
-      <c r="E160" s="3">
-        <v>24692.815392</v>
-      </c>
-      <c r="F160" s="4">
-        <v>1.2473785395074479E-2</v>
-      </c>
-      <c r="G160" s="4">
-        <v>1.210844187888221E-3</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B161" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C161" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D161" s="3">
-        <v>648523.59030139784</v>
-      </c>
-      <c r="E161" s="3">
-        <v>20365.73930736</v>
-      </c>
-      <c r="F161" s="4">
-        <v>2.3285205202868371E-2</v>
-      </c>
-      <c r="G161" s="4">
-        <v>1.5783067550306741E-3</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A162" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B162" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C162" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D162" s="3">
-        <v>525586.90611574077</v>
-      </c>
-      <c r="E162" s="3">
-        <v>57596.7124071</v>
-      </c>
-      <c r="F162" s="4">
-        <v>6.9328647193893768E-4</v>
-      </c>
-      <c r="G162" s="4">
-        <v>1.2640594598421069E-2</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B163" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C163" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D163" s="3">
-        <v>489831.22166003252</v>
-      </c>
-      <c r="E163" s="3">
-        <v>28233.8392518</v>
-      </c>
-      <c r="F163" s="4">
-        <v>1.7629362658082969E-3</v>
-      </c>
-      <c r="G163" s="4">
-        <v>1.091290811894655E-3</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B165" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D165" s="3">
-        <f>AVERAGE(D160:D161)</f>
-        <v>675581.93770212308</v>
-      </c>
-      <c r="E165" s="3">
-        <f t="shared" ref="E165:G165" si="27">AVERAGE(E160:E161)</f>
-        <v>22529.27734968</v>
-      </c>
-      <c r="F165" s="4">
-        <f t="shared" si="27"/>
-        <v>1.7879495298971426E-2</v>
-      </c>
-      <c r="G165" s="4">
-        <f t="shared" si="27"/>
-        <v>1.3945754714594475E-3</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B166" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D166" s="3">
-        <f>AVERAGE(D162:D163)</f>
-        <v>507709.06388788664</v>
-      </c>
-      <c r="E166" s="3">
-        <f t="shared" ref="E166:G166" si="28">AVERAGE(E162:E163)</f>
-        <v>42915.275829450002</v>
-      </c>
-      <c r="F166" s="4">
-        <f t="shared" si="28"/>
-        <v>1.2281113688736172E-3</v>
-      </c>
-      <c r="G166" s="4">
-        <f t="shared" si="28"/>
-        <v>6.8659427051578625E-3</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C168" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D168" s="3">
-        <f>D165/D166</f>
-        <v>1.3306477779394272</v>
-      </c>
-      <c r="E168" s="3">
-        <f t="shared" ref="E168:G168" si="29">E165/E166</f>
-        <v>0.52497104851926879</v>
-      </c>
-      <c r="F168" s="3">
-        <f t="shared" si="29"/>
-        <v>14.558529260558757</v>
-      </c>
-      <c r="G168" s="3">
-        <f t="shared" si="29"/>
-        <v>0.20311492992969613</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B171" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C171" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D171" s="3">
-        <v>333902.21266145178</v>
-      </c>
-      <c r="E171" s="3">
-        <v>6590.0541599999997</v>
-      </c>
-      <c r="F171" s="4">
-        <v>3.968817154607421E-3</v>
-      </c>
-      <c r="G171" s="4">
-        <v>1.4273582237145071E-3</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C172" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D172" s="3">
-        <v>289865.32010952412</v>
+        <v>327266.01547195681</v>
       </c>
       <c r="E172" s="3">
-        <v>5130.8202951200001</v>
+        <v>2736.7203125999999</v>
       </c>
       <c r="F172" s="4">
-        <v>7.1409024001186736E-3</v>
+        <v>6.5575458761258591E-4</v>
       </c>
       <c r="G172" s="4">
-        <v>1.6292149323472839E-3</v>
+        <v>9.6186040198574876E-4</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C173" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D173" s="3">
-        <v>259818.50988372459</v>
+        <v>323997.44760210218</v>
       </c>
       <c r="E173" s="3">
-        <v>45922.658233419999</v>
+        <v>2594.2840083999999</v>
       </c>
       <c r="F173" s="4">
-        <v>4.0433840100499702E-5</v>
+        <v>4.4144095106468531E-4</v>
       </c>
       <c r="G173" s="4">
-        <v>1.5232724169502069E-4</v>
+        <v>4.2813564143465432E-3</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C174" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D174" s="3">
+        <v>321762.90970591619</v>
+      </c>
+      <c r="E174" s="3">
+        <v>2793.945984</v>
+      </c>
+      <c r="F174" s="4">
+        <v>3.0877619142976242E-4</v>
+      </c>
+      <c r="G174" s="4">
+        <v>1.0062327675981299E-3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C175" s="2">
         <v>2021</v>
       </c>
-      <c r="D174" s="3">
-        <v>234189.89306239539</v>
-      </c>
-      <c r="E174" s="3">
-        <v>4733.3383234200001</v>
-      </c>
-      <c r="F174" s="4">
-        <v>6.6356632156617178E-4</v>
-      </c>
-      <c r="G174" s="4">
-        <v>3.1476572520248271E-3</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B176" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D176" s="3">
-        <f>AVERAGE(D171:D172)</f>
-        <v>311883.76638548798</v>
-      </c>
-      <c r="E176" s="3">
-        <f t="shared" ref="E176:G176" si="30">AVERAGE(E171:E172)</f>
-        <v>5860.4372275599999</v>
-      </c>
-      <c r="F176" s="4">
-        <f t="shared" si="30"/>
-        <v>5.5548597773630477E-3</v>
-      </c>
-      <c r="G176" s="4">
-        <f t="shared" si="30"/>
-        <v>1.5282865780308955E-3</v>
+      <c r="D175" s="3">
+        <v>297602.00445720641</v>
+      </c>
+      <c r="E175" s="3">
+        <v>3256.4356082999998</v>
+      </c>
+      <c r="F175" s="4">
+        <v>3.8592436982227681E-4</v>
+      </c>
+      <c r="G175" s="4">
+        <v>2.369477916386043E-3</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B177" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D177" s="3">
+        <f>AVERAGE(D172:D173)</f>
+        <v>325631.7315370295</v>
+      </c>
+      <c r="E177" s="3">
+        <f t="shared" ref="E177:G177" si="25">AVERAGE(E172:E173)</f>
+        <v>2665.5021605000002</v>
+      </c>
+      <c r="F177" s="4">
+        <f t="shared" si="25"/>
+        <v>5.4859776933863561E-4</v>
+      </c>
+      <c r="G177" s="4">
+        <f t="shared" si="25"/>
+        <v>2.6216084081661459E-3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B178" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D177" s="3">
-        <f>AVERAGE(D173:D174)</f>
-        <v>247004.20147306001</v>
-      </c>
-      <c r="E177" s="3">
-        <f t="shared" ref="E177:G177" si="31">AVERAGE(E173:E174)</f>
-        <v>25327.99827842</v>
-      </c>
-      <c r="F177" s="4">
-        <f t="shared" si="31"/>
-        <v>3.5200008083333573E-4</v>
-      </c>
-      <c r="G177" s="4">
-        <f t="shared" si="31"/>
-        <v>1.6499922468599239E-3</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C179" s="7" t="s">
+      <c r="D178" s="3">
+        <f>AVERAGE(D174:D175)</f>
+        <v>309682.45708156133</v>
+      </c>
+      <c r="E178" s="3">
+        <f t="shared" ref="E178:G178" si="26">AVERAGE(E174:E175)</f>
+        <v>3025.1907961500001</v>
+      </c>
+      <c r="F178" s="4">
+        <f t="shared" si="26"/>
+        <v>3.4735028062601961E-4</v>
+      </c>
+      <c r="G178" s="4">
+        <f t="shared" si="26"/>
+        <v>1.6878553419920864E-3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C180" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D179" s="3">
-        <f>D176/D177</f>
-        <v>1.2626658353400688</v>
-      </c>
-      <c r="E179" s="3">
-        <f t="shared" ref="E179:G179" si="32">E176/E177</f>
-        <v>0.23138177613322164</v>
-      </c>
-      <c r="F179" s="3">
-        <f t="shared" si="32"/>
-        <v>15.780848016319494</v>
-      </c>
-      <c r="G179" s="3">
-        <f t="shared" si="32"/>
-        <v>0.9262386419932308</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181" s="1" t="s">
+      <c r="D180" s="3">
+        <f>D177/D178</f>
+        <v>1.0515020276116822</v>
+      </c>
+      <c r="E180" s="3">
+        <f t="shared" ref="E180:G180" si="27">E177/E178</f>
+        <v>0.88110216515673767</v>
+      </c>
+      <c r="F180" s="3">
+        <f t="shared" si="27"/>
+        <v>1.5793790877321685</v>
+      </c>
+      <c r="G180" s="3">
+        <f t="shared" si="27"/>
+        <v>1.5532186573951297</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B182" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C181" s="1" t="s">
+      <c r="C182" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D181" s="1" t="s">
+      <c r="D182" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E181" s="1" t="s">
+      <c r="E182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F181" s="1" t="s">
+      <c r="F182" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G181" s="1" t="s">
+      <c r="G182" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B182" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C182" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D182" s="3">
-        <v>615324.90182869229</v>
-      </c>
-      <c r="E182" s="3">
-        <v>12188.037840000001</v>
-      </c>
-      <c r="F182" s="4">
-        <v>3.5563801629943082E-3</v>
-      </c>
-      <c r="G182" s="4">
-        <v>2.3262126662383252E-3</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C183" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D183" s="3">
-        <v>463470.71898289572</v>
+        <v>589836.07301855378</v>
       </c>
       <c r="E183" s="3">
-        <v>9380.3853557600014</v>
+        <v>3459.2387039999999</v>
       </c>
       <c r="F183" s="4">
-        <v>2.4821681068467739E-3</v>
+        <v>2.6129124854981389E-3</v>
       </c>
       <c r="G183" s="4">
-        <v>1.7821392198706289E-3</v>
+        <v>2.2962786554205951E-3</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C184" s="2">
         <v>2022</v>
       </c>
       <c r="D184" s="3">
-        <v>441905.15975913568</v>
+        <v>585427.26654459862</v>
       </c>
       <c r="E184" s="3">
-        <v>8680.9984719799995</v>
+        <v>4854.6591208600003</v>
       </c>
       <c r="F184" s="4">
-        <v>5.3628300774693723E-2</v>
+        <v>3.7612999688359748E-4</v>
       </c>
       <c r="G184" s="4">
-        <v>1.9809359137092151E-3</v>
+        <v>2.0756040556386131E-3</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C185" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D185" s="3">
+        <v>575669.32501484314</v>
+      </c>
+      <c r="E185" s="3">
+        <v>4774.9529707199999</v>
+      </c>
+      <c r="F185" s="4">
+        <v>2.8738600116371028E-4</v>
+      </c>
+      <c r="G185" s="4">
+        <v>1.316480132589062E-3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C186" s="2">
         <v>2021</v>
       </c>
-      <c r="D185" s="3">
-        <v>396416.47748978873</v>
-      </c>
-      <c r="E185" s="3">
-        <v>10615.43888874</v>
-      </c>
-      <c r="F185" s="4">
-        <v>5.7122249315871114E-3</v>
-      </c>
-      <c r="G185" s="4">
-        <v>1.223257961926933E-3</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B187" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D187" s="3">
-        <f>AVERAGE(D182:D183)</f>
-        <v>539397.81040579407</v>
-      </c>
-      <c r="E187" s="3">
-        <f t="shared" ref="E187:G187" si="33">AVERAGE(E182:E183)</f>
-        <v>10784.211597880001</v>
-      </c>
-      <c r="F187" s="4">
-        <f t="shared" si="33"/>
-        <v>3.0192741349205411E-3</v>
-      </c>
-      <c r="G187" s="4">
-        <f t="shared" si="33"/>
-        <v>2.0541759430544771E-3</v>
+      <c r="D186" s="3">
+        <v>532258.74860418728</v>
+      </c>
+      <c r="E186" s="3">
+        <v>5998.8555937799993</v>
+      </c>
+      <c r="F186" s="4">
+        <v>3.3561812091085249E-3</v>
+      </c>
+      <c r="G186" s="4">
+        <v>1.7434020366891251E-3</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B188" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D188" s="3">
+        <f>AVERAGE(D183:D184)</f>
+        <v>587631.66978157614</v>
+      </c>
+      <c r="E188" s="3">
+        <f t="shared" ref="E188:G188" si="28">AVERAGE(E183:E184)</f>
+        <v>4156.9489124299998</v>
+      </c>
+      <c r="F188" s="4">
+        <f t="shared" si="28"/>
+        <v>1.4945212411908682E-3</v>
+      </c>
+      <c r="G188" s="4">
+        <f t="shared" si="28"/>
+        <v>2.1859413555296043E-3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B189" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D188" s="3">
-        <f>AVERAGE(D184:D185)</f>
-        <v>419160.81862446223</v>
-      </c>
-      <c r="E188" s="3">
-        <f t="shared" ref="E188:G188" si="34">AVERAGE(E184:E185)</f>
-        <v>9648.2186803599998</v>
-      </c>
-      <c r="F188" s="4">
-        <f t="shared" si="34"/>
-        <v>2.9670262853140415E-2</v>
-      </c>
-      <c r="G188" s="4">
-        <f t="shared" si="34"/>
-        <v>1.602096937818074E-3</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C190" s="7" t="s">
+      <c r="D189" s="3">
+        <f>AVERAGE(D185:D186)</f>
+        <v>553964.03680951521</v>
+      </c>
+      <c r="E189" s="3">
+        <f t="shared" ref="E189:G189" si="29">AVERAGE(E185:E186)</f>
+        <v>5386.9042822499996</v>
+      </c>
+      <c r="F189" s="4">
+        <f t="shared" si="29"/>
+        <v>1.8217836051361176E-3</v>
+      </c>
+      <c r="G189" s="4">
+        <f t="shared" si="29"/>
+        <v>1.5299410846390934E-3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C191" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D190" s="3">
-        <f>D187/D188</f>
-        <v>1.2868516961482879</v>
-      </c>
-      <c r="E190" s="3">
-        <f t="shared" ref="E190:G190" si="35">E187/E188</f>
-        <v>1.1177412074865631</v>
-      </c>
-      <c r="F190" s="3">
-        <f t="shared" si="35"/>
-        <v>0.10176095000792922</v>
-      </c>
-      <c r="G190" s="3">
-        <f t="shared" si="35"/>
-        <v>1.2821795576565411</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" s="1" t="s">
+      <c r="D191" s="3">
+        <f>D188/D189</f>
+        <v>1.0607758459664012</v>
+      </c>
+      <c r="E191" s="3">
+        <f t="shared" ref="E191:G191" si="30">E188/E189</f>
+        <v>0.77167677289668257</v>
+      </c>
+      <c r="F191" s="3">
+        <f t="shared" si="30"/>
+        <v>0.82036156049346076</v>
+      </c>
+      <c r="G191" s="3">
+        <f t="shared" si="30"/>
+        <v>1.4287748577228767</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="B193" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="D193" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E192" s="1" t="s">
+      <c r="E193" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F192" s="1" t="s">
+      <c r="F193" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G192" s="1" t="s">
+      <c r="G193" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A193" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B193" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C193" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D193" s="3">
-        <v>480752.63075950177</v>
-      </c>
-      <c r="E193" s="3">
-        <v>13713.99982974</v>
-      </c>
-      <c r="F193" s="4">
-        <v>1.8909555433829729E-4</v>
-      </c>
-      <c r="G193" s="4">
-        <v>1.421912259449817E-2</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C194" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D194" s="3">
-        <v>430680.74778667098</v>
+        <v>2688475.9724428668</v>
       </c>
       <c r="E194" s="3">
-        <v>9650.7308639999992</v>
+        <v>22918.622383440001</v>
       </c>
       <c r="F194" s="4">
-        <v>3.2382873836611008E-4</v>
+        <v>1.411209606183382E-2</v>
       </c>
       <c r="G194" s="4">
-        <v>1.307147425181787E-3</v>
+        <v>6.7540592802753808E-4</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C195" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D195" s="3">
-        <v>344818.33344279532</v>
+        <v>2199098.9702055152</v>
       </c>
       <c r="E195" s="3">
-        <v>7766.5175531200011</v>
+        <v>27186.587841839999</v>
       </c>
       <c r="F195" s="4">
-        <v>5.6879237956854514E-4</v>
+        <v>1.428164445640567E-2</v>
       </c>
       <c r="G195" s="4">
-        <v>9.2862762115340628E-4</v>
+        <v>1.063284111568874E-3</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C196" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D196" s="3">
-        <v>310794.74797233898</v>
+        <v>2110825.0242093089</v>
       </c>
       <c r="E196" s="3">
-        <v>8210.8821614400003</v>
+        <v>36820.330575920001</v>
       </c>
       <c r="F196" s="4">
-        <v>1.515288413031857E-4</v>
+        <v>1.1388913987487259E-2</v>
       </c>
       <c r="G196" s="4">
-        <v>1.134724744407487E-2</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B198" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D198" s="3">
-        <f>AVERAGE(D193:D194)</f>
-        <v>455716.68927308638</v>
-      </c>
-      <c r="E198" s="3">
-        <f t="shared" ref="E198:G198" si="36">AVERAGE(E193:E194)</f>
-        <v>11682.365346869999</v>
-      </c>
-      <c r="F198" s="4">
-        <f t="shared" si="36"/>
-        <v>2.5646214635220368E-4</v>
-      </c>
-      <c r="G198" s="4">
-        <f t="shared" si="36"/>
-        <v>7.7631350098399787E-3</v>
+        <v>1.346627653376551E-3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C197" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D197" s="3">
+        <v>2060147.693651289</v>
+      </c>
+      <c r="E197" s="3">
+        <v>24111.565200000001</v>
+      </c>
+      <c r="F197" s="4">
+        <v>1.6816288641435851E-2</v>
+      </c>
+      <c r="G197" s="4">
+        <v>4.7603910840263489E-4</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B199" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D199" s="3">
+        <f>AVERAGE(D194:D195)</f>
+        <v>2443787.471324191</v>
+      </c>
+      <c r="E199" s="3">
+        <f t="shared" ref="E199:G199" si="31">AVERAGE(E194:E195)</f>
+        <v>25052.605112639998</v>
+      </c>
+      <c r="F199" s="4">
+        <f t="shared" si="31"/>
+        <v>1.4196870259119745E-2</v>
+      </c>
+      <c r="G199" s="4">
+        <f t="shared" si="31"/>
+        <v>8.6934501979820604E-4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B200" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D199" s="3">
-        <f>AVERAGE(D195:D196)</f>
-        <v>327806.54070756712</v>
-      </c>
-      <c r="E199" s="3">
-        <f t="shared" ref="E199:G199" si="37">AVERAGE(E195:E196)</f>
-        <v>7988.6998572800003</v>
-      </c>
-      <c r="F199" s="4">
-        <f t="shared" si="37"/>
-        <v>3.6016061043586542E-4</v>
-      </c>
-      <c r="G199" s="4">
-        <f t="shared" si="37"/>
-        <v>6.1379375326141381E-3</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C201" s="7" t="s">
+      <c r="D200" s="3">
+        <f>AVERAGE(D196:D197)</f>
+        <v>2085486.3589302991</v>
+      </c>
+      <c r="E200" s="3">
+        <f t="shared" ref="E200:G200" si="32">AVERAGE(E196:E197)</f>
+        <v>30465.947887959999</v>
+      </c>
+      <c r="F200" s="4">
+        <f t="shared" si="32"/>
+        <v>1.4102601314461555E-2</v>
+      </c>
+      <c r="G200" s="4">
+        <f t="shared" si="32"/>
+        <v>9.1133338088959293E-4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C202" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D201" s="3">
-        <f>D198/D199</f>
-        <v>1.3902001109844437</v>
-      </c>
-      <c r="E201" s="3">
-        <f t="shared" ref="E201:G201" si="38">E198/E199</f>
-        <v>1.462361279754929</v>
-      </c>
-      <c r="F201" s="3">
-        <f t="shared" si="38"/>
-        <v>0.71207716480109773</v>
-      </c>
-      <c r="G201" s="3">
-        <f t="shared" si="38"/>
-        <v>1.2647790839496653</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A203" s="1" t="s">
+      <c r="D202" s="3">
+        <f>D199/D200</f>
+        <v>1.1718069796331221</v>
+      </c>
+      <c r="E202" s="3">
+        <f t="shared" ref="E202:G202" si="33">E199/E200</f>
+        <v>0.82231497292558131</v>
+      </c>
+      <c r="F202" s="3">
+        <f t="shared" si="33"/>
+        <v>1.0066845075285169</v>
+      </c>
+      <c r="G202" s="3">
+        <f t="shared" si="33"/>
+        <v>0.95392645329154935</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="B204" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="C204" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D203" s="1" t="s">
+      <c r="D204" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E203" s="1" t="s">
+      <c r="E204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F203" s="1" t="s">
+      <c r="F204" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G203" s="1" t="s">
+      <c r="G204" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A204" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B204" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C204" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D204" s="3">
-        <v>624490.81179662514</v>
-      </c>
-      <c r="E204" s="3">
-        <v>23490.718752000001</v>
-      </c>
-      <c r="F204" s="4">
-        <v>1.927088927244758E-3</v>
-      </c>
-      <c r="G204" s="4">
-        <v>1.8760825696850091E-3</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C205" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D205" s="3">
-        <v>615005.46689121344</v>
+        <v>1079590.799601601</v>
       </c>
       <c r="E205" s="3">
-        <v>18304.5266156</v>
+        <v>29824.255583999999</v>
       </c>
       <c r="F205" s="4">
-        <v>2.0544865338363899E-3</v>
+        <v>1.7700063980245699E-2</v>
       </c>
       <c r="G205" s="4">
-        <v>2.397692315221963E-3</v>
+        <v>1.8406361575525849E-2</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C206" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D206" s="3">
-        <v>557880.96074185451</v>
+        <v>917032.53729645221</v>
       </c>
       <c r="E206" s="3">
-        <v>17673.58753398</v>
+        <v>21948.7441788</v>
       </c>
       <c r="F206" s="4">
-        <v>1.2639185721094849E-3</v>
+        <v>5.1385668600091312E-2</v>
       </c>
       <c r="G206" s="4">
-        <v>7.224852054202324E-4</v>
+        <v>1.045825844659099E-3</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C207" s="2">
         <v>2022</v>
       </c>
       <c r="D207" s="3">
-        <v>528936.59684355662</v>
+        <v>802566.08061441511</v>
       </c>
       <c r="E207" s="3">
-        <v>14840.029964359999</v>
+        <v>12046.641059559999</v>
       </c>
       <c r="F207" s="4">
-        <v>3.348617336982791E-3</v>
+        <v>1.264319260007594E-2</v>
       </c>
       <c r="G207" s="4">
-        <v>9.7700369843055682E-4</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B209" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D209" s="3">
-        <f>AVERAGE(D204:D205)</f>
-        <v>619748.13934391923</v>
-      </c>
-      <c r="E209" s="3">
-        <f t="shared" ref="E209:G209" si="39">AVERAGE(E204:E205)</f>
-        <v>20897.6226838</v>
-      </c>
-      <c r="F209" s="4">
-        <f t="shared" si="39"/>
-        <v>1.9907877305405742E-3</v>
-      </c>
-      <c r="G209" s="4">
-        <f t="shared" si="39"/>
-        <v>2.1368874424534858E-3</v>
+        <v>9.2646432850616075E-4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C208" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D208" s="3">
+        <v>774599.50938466226</v>
+      </c>
+      <c r="E208" s="3">
+        <v>31768.917493320001</v>
+      </c>
+      <c r="F208" s="4">
+        <v>4.5024994770462897E-3</v>
+      </c>
+      <c r="G208" s="4">
+        <v>6.1504127372638605E-4</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B210" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D210" s="3">
+        <f>AVERAGE(D205:D206)</f>
+        <v>998311.66844902653</v>
+      </c>
+      <c r="E210" s="3">
+        <f t="shared" ref="E210:G210" si="34">AVERAGE(E205:E206)</f>
+        <v>25886.499881399999</v>
+      </c>
+      <c r="F210" s="4">
+        <f t="shared" si="34"/>
+        <v>3.4542866290168506E-2</v>
+      </c>
+      <c r="G210" s="4">
+        <f t="shared" si="34"/>
+        <v>9.7260937100924743E-3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B211" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D210" s="3">
-        <f>AVERAGE(D206:D207)</f>
-        <v>543408.77879270562</v>
-      </c>
-      <c r="E210" s="3">
-        <f t="shared" ref="E210:G210" si="40">AVERAGE(E206:E207)</f>
-        <v>16256.808749169999</v>
-      </c>
-      <c r="F210" s="4">
-        <f t="shared" si="40"/>
-        <v>2.3062679545461382E-3</v>
-      </c>
-      <c r="G210" s="4">
-        <f t="shared" si="40"/>
-        <v>8.4974445192539461E-4</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C212" s="7" t="s">
+      <c r="D211" s="3">
+        <f>AVERAGE(D207:D208)</f>
+        <v>788582.79499953869</v>
+      </c>
+      <c r="E211" s="3">
+        <f t="shared" ref="E211:G211" si="35">AVERAGE(E207:E208)</f>
+        <v>21907.77927644</v>
+      </c>
+      <c r="F211" s="4">
+        <f t="shared" si="35"/>
+        <v>8.5728460385611147E-3</v>
+      </c>
+      <c r="G211" s="4">
+        <f t="shared" si="35"/>
+        <v>7.7075280111627334E-4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C213" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D212" s="3">
-        <f>D209/D210</f>
-        <v>1.1404823836685474</v>
-      </c>
-      <c r="E212" s="3">
-        <f t="shared" ref="E212:G212" si="41">E209/E210</f>
-        <v>1.2854689383527957</v>
-      </c>
-      <c r="F212" s="3">
-        <f t="shared" si="41"/>
-        <v>0.8632074718882139</v>
-      </c>
-      <c r="G212" s="3">
-        <f t="shared" si="41"/>
-        <v>2.5147412702861627</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A214" s="1" t="s">
+      <c r="D213" s="3">
+        <f>D210/D211</f>
+        <v>1.2659566944389276</v>
+      </c>
+      <c r="E213" s="3">
+        <f t="shared" ref="E213:G213" si="36">E210/E211</f>
+        <v>1.1816122280015293</v>
+      </c>
+      <c r="F213" s="3">
+        <f t="shared" si="36"/>
+        <v>4.0293347314057506</v>
+      </c>
+      <c r="G213" s="3">
+        <f t="shared" si="36"/>
+        <v>12.618953438776055</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="B215" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C214" s="1" t="s">
+      <c r="C215" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="D215" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E214" s="1" t="s">
+      <c r="E215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F214" s="1" t="s">
+      <c r="F215" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G214" s="1" t="s">
+      <c r="G215" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A215" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B215" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C215" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D215" s="3">
-        <v>496312.33844584553</v>
-      </c>
-      <c r="E215" s="3">
-        <v>6058.6276942799996</v>
-      </c>
-      <c r="F215" s="4">
-        <v>1.149126975828702E-3</v>
-      </c>
-      <c r="G215" s="4">
-        <v>4.3326889923906344E-3</v>
-      </c>
-    </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A216" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B216" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C216" s="5">
-        <v>2023</v>
+      <c r="A216" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B216" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C216" s="2">
+        <v>2024</v>
       </c>
       <c r="D216" s="3">
-        <v>481190.63450056087</v>
+        <v>702640.28510284843</v>
       </c>
       <c r="E216" s="3">
-        <v>5659.2905294400007</v>
+        <v>24692.815392</v>
       </c>
       <c r="F216" s="4">
-        <v>2.7642536319032169E-4</v>
+        <v>1.2473785395074479E-2</v>
       </c>
       <c r="G216" s="4">
-        <v>2.609783923120391E-3</v>
+        <v>1.210844187888221E-3</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C217" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D217" s="3">
-        <v>463554.2380744408</v>
+        <v>648523.59030139784</v>
       </c>
       <c r="E217" s="3">
-        <v>6405.1162323599992</v>
+        <v>20365.73930736</v>
       </c>
       <c r="F217" s="4">
-        <v>1.36542870460566E-3</v>
+        <v>2.3285205202868371E-2</v>
       </c>
       <c r="G217" s="4">
-        <v>1.06191448730258E-3</v>
+        <v>1.5783067550306741E-3</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C218" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D218" s="3">
-        <v>463215.01884109463</v>
+        <v>525586.90611574077</v>
       </c>
       <c r="E218" s="3">
-        <v>6600.4823040000001</v>
+        <v>57596.7124071</v>
       </c>
       <c r="F218" s="4">
-        <v>1.0184783005820781E-3</v>
+        <v>6.9328647193893768E-4</v>
       </c>
       <c r="G218" s="4">
-        <v>1.1952508372333631E-3</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B220" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D220" s="3">
-        <f>AVERAGE(D215:D216)</f>
-        <v>488751.48647320317</v>
-      </c>
-      <c r="E220" s="3">
-        <f t="shared" ref="E220:G220" si="42">AVERAGE(E215:E216)</f>
-        <v>5858.9591118600001</v>
-      </c>
-      <c r="F220" s="4">
-        <f t="shared" si="42"/>
-        <v>7.1277616950951182E-4</v>
-      </c>
-      <c r="G220" s="4">
-        <f t="shared" si="42"/>
-        <v>3.4712364577555127E-3</v>
+        <v>1.2640594598421069E-2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B219" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C219" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D219" s="3">
+        <v>489831.22166003252</v>
+      </c>
+      <c r="E219" s="3">
+        <v>28233.8392518</v>
+      </c>
+      <c r="F219" s="4">
+        <v>1.7629362658082969E-3</v>
+      </c>
+      <c r="G219" s="4">
+        <v>1.091290811894655E-3</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B221" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D221" s="3">
+        <f>AVERAGE(D216:D217)</f>
+        <v>675581.93770212308</v>
+      </c>
+      <c r="E221" s="3">
+        <f t="shared" ref="E221:G221" si="37">AVERAGE(E216:E217)</f>
+        <v>22529.27734968</v>
+      </c>
+      <c r="F221" s="4">
+        <f t="shared" si="37"/>
+        <v>1.7879495298971426E-2</v>
+      </c>
+      <c r="G221" s="4">
+        <f t="shared" si="37"/>
+        <v>1.3945754714594475E-3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B222" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D221" s="3">
-        <f>AVERAGE(D217:D218)</f>
+      <c r="D222" s="3">
+        <f>AVERAGE(D218:D219)</f>
+        <v>507709.06388788664</v>
+      </c>
+      <c r="E222" s="3">
+        <f t="shared" ref="E222:G222" si="38">AVERAGE(E218:E219)</f>
+        <v>42915.275829450002</v>
+      </c>
+      <c r="F222" s="4">
+        <f t="shared" si="38"/>
+        <v>1.2281113688736172E-3</v>
+      </c>
+      <c r="G222" s="4">
+        <f t="shared" si="38"/>
+        <v>6.8659427051578625E-3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C224" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D224" s="3">
+        <f>D221/D222</f>
+        <v>1.3306477779394272</v>
+      </c>
+      <c r="E224" s="3">
+        <f t="shared" ref="E224:G224" si="39">E221/E222</f>
+        <v>0.52497104851926879</v>
+      </c>
+      <c r="F224" s="3">
+        <f t="shared" si="39"/>
+        <v>14.558529260558757</v>
+      </c>
+      <c r="G224" s="3">
+        <f t="shared" si="39"/>
+        <v>0.20311492992969613</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B227" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C227" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D227" s="3">
+        <v>333902.21266145178</v>
+      </c>
+      <c r="E227" s="3">
+        <v>6590.0541599999997</v>
+      </c>
+      <c r="F227" s="4">
+        <v>3.968817154607421E-3</v>
+      </c>
+      <c r="G227" s="4">
+        <v>1.4273582237145071E-3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B228" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C228" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D228" s="3">
+        <v>289865.32010952412</v>
+      </c>
+      <c r="E228" s="3">
+        <v>5130.8202951200001</v>
+      </c>
+      <c r="F228" s="4">
+        <v>7.1409024001186736E-3</v>
+      </c>
+      <c r="G228" s="4">
+        <v>1.6292149323472839E-3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B229" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C229" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D229" s="3">
+        <v>259818.50988372459</v>
+      </c>
+      <c r="E229" s="3">
+        <v>45922.658233419999</v>
+      </c>
+      <c r="F229" s="4">
+        <v>4.0433840100499702E-5</v>
+      </c>
+      <c r="G229" s="4">
+        <v>1.5232724169502069E-4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B230" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C230" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D230" s="3">
+        <v>234189.89306239539</v>
+      </c>
+      <c r="E230" s="3">
+        <v>4733.3383234200001</v>
+      </c>
+      <c r="F230" s="4">
+        <v>6.6356632156617178E-4</v>
+      </c>
+      <c r="G230" s="4">
+        <v>3.1476572520248271E-3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B232" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D232" s="3">
+        <f>AVERAGE(D227:D228)</f>
+        <v>311883.76638548798</v>
+      </c>
+      <c r="E232" s="3">
+        <f t="shared" ref="E232:G232" si="40">AVERAGE(E227:E228)</f>
+        <v>5860.4372275599999</v>
+      </c>
+      <c r="F232" s="4">
+        <f t="shared" si="40"/>
+        <v>5.5548597773630477E-3</v>
+      </c>
+      <c r="G232" s="4">
+        <f t="shared" si="40"/>
+        <v>1.5282865780308955E-3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B233" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D233" s="3">
+        <f>AVERAGE(D229:D230)</f>
+        <v>247004.20147306001</v>
+      </c>
+      <c r="E233" s="3">
+        <f t="shared" ref="E233:G233" si="41">AVERAGE(E229:E230)</f>
+        <v>25327.99827842</v>
+      </c>
+      <c r="F233" s="4">
+        <f t="shared" si="41"/>
+        <v>3.5200008083333573E-4</v>
+      </c>
+      <c r="G233" s="4">
+        <f t="shared" si="41"/>
+        <v>1.6499922468599239E-3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C235" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D235" s="3">
+        <f>D232/D233</f>
+        <v>1.2626658353400688</v>
+      </c>
+      <c r="E235" s="3">
+        <f t="shared" ref="E235:G235" si="42">E232/E233</f>
+        <v>0.23138177613322164</v>
+      </c>
+      <c r="F235" s="3">
+        <f t="shared" si="42"/>
+        <v>15.780848016319494</v>
+      </c>
+      <c r="G235" s="3">
+        <f t="shared" si="42"/>
+        <v>0.9262386419932308</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G237" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B238" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C238" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D238" s="3">
+        <v>615324.90182869229</v>
+      </c>
+      <c r="E238" s="3">
+        <v>12188.037840000001</v>
+      </c>
+      <c r="F238" s="4">
+        <v>3.5563801629943082E-3</v>
+      </c>
+      <c r="G238" s="4">
+        <v>2.3262126662383252E-3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B239" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C239" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D239" s="3">
+        <v>463470.71898289572</v>
+      </c>
+      <c r="E239" s="3">
+        <v>9380.3853557600014</v>
+      </c>
+      <c r="F239" s="4">
+        <v>2.4821681068467739E-3</v>
+      </c>
+      <c r="G239" s="4">
+        <v>1.7821392198706289E-3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B240" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C240" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D240" s="3">
+        <v>441905.15975913568</v>
+      </c>
+      <c r="E240" s="3">
+        <v>8680.9984719799995</v>
+      </c>
+      <c r="F240" s="4">
+        <v>5.3628300774693723E-2</v>
+      </c>
+      <c r="G240" s="4">
+        <v>1.9809359137092151E-3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B241" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C241" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D241" s="3">
+        <v>396416.47748978873</v>
+      </c>
+      <c r="E241" s="3">
+        <v>10615.43888874</v>
+      </c>
+      <c r="F241" s="4">
+        <v>5.7122249315871114E-3</v>
+      </c>
+      <c r="G241" s="4">
+        <v>1.223257961926933E-3</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B243" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D243" s="3">
+        <f>AVERAGE(D238:D239)</f>
+        <v>539397.81040579407</v>
+      </c>
+      <c r="E243" s="3">
+        <f t="shared" ref="E243:G243" si="43">AVERAGE(E238:E239)</f>
+        <v>10784.211597880001</v>
+      </c>
+      <c r="F243" s="4">
+        <f t="shared" si="43"/>
+        <v>3.0192741349205411E-3</v>
+      </c>
+      <c r="G243" s="4">
+        <f t="shared" si="43"/>
+        <v>2.0541759430544771E-3</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B244" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D244" s="3">
+        <f>AVERAGE(D240:D241)</f>
+        <v>419160.81862446223</v>
+      </c>
+      <c r="E244" s="3">
+        <f t="shared" ref="E244:G244" si="44">AVERAGE(E240:E241)</f>
+        <v>9648.2186803599998</v>
+      </c>
+      <c r="F244" s="4">
+        <f t="shared" si="44"/>
+        <v>2.9670262853140415E-2</v>
+      </c>
+      <c r="G244" s="4">
+        <f t="shared" si="44"/>
+        <v>1.602096937818074E-3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C246" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D246" s="3">
+        <f>D243/D244</f>
+        <v>1.2868516961482879</v>
+      </c>
+      <c r="E246" s="3">
+        <f t="shared" ref="E246:G246" si="45">E243/E244</f>
+        <v>1.1177412074865631</v>
+      </c>
+      <c r="F246" s="3">
+        <f t="shared" si="45"/>
+        <v>0.10176095000792922</v>
+      </c>
+      <c r="G246" s="3">
+        <f t="shared" si="45"/>
+        <v>1.2821795576565411</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G248" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B249" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C249" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D249" s="3">
+        <v>480752.63075950177</v>
+      </c>
+      <c r="E249" s="3">
+        <v>13713.99982974</v>
+      </c>
+      <c r="F249" s="4">
+        <v>1.8909555433829729E-4</v>
+      </c>
+      <c r="G249" s="4">
+        <v>1.421912259449817E-2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B250" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C250" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D250" s="3">
+        <v>430680.74778667098</v>
+      </c>
+      <c r="E250" s="3">
+        <v>9650.7308639999992</v>
+      </c>
+      <c r="F250" s="4">
+        <v>3.2382873836611008E-4</v>
+      </c>
+      <c r="G250" s="4">
+        <v>1.307147425181787E-3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C251" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D251" s="3">
+        <v>344818.33344279532</v>
+      </c>
+      <c r="E251" s="3">
+        <v>7766.5175531200011</v>
+      </c>
+      <c r="F251" s="4">
+        <v>5.6879237956854514E-4</v>
+      </c>
+      <c r="G251" s="4">
+        <v>9.2862762115340628E-4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C252" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D252" s="3">
+        <v>310794.74797233898</v>
+      </c>
+      <c r="E252" s="3">
+        <v>8210.8821614400003</v>
+      </c>
+      <c r="F252" s="4">
+        <v>1.515288413031857E-4</v>
+      </c>
+      <c r="G252" s="4">
+        <v>1.134724744407487E-2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B254" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D254" s="3">
+        <f>AVERAGE(D249:D250)</f>
+        <v>455716.68927308638</v>
+      </c>
+      <c r="E254" s="3">
+        <f t="shared" ref="E254:G254" si="46">AVERAGE(E249:E250)</f>
+        <v>11682.365346869999</v>
+      </c>
+      <c r="F254" s="4">
+        <f t="shared" si="46"/>
+        <v>2.5646214635220368E-4</v>
+      </c>
+      <c r="G254" s="4">
+        <f t="shared" si="46"/>
+        <v>7.7631350098399787E-3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B255" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D255" s="3">
+        <f>AVERAGE(D251:D252)</f>
+        <v>327806.54070756712</v>
+      </c>
+      <c r="E255" s="3">
+        <f t="shared" ref="E255:G255" si="47">AVERAGE(E251:E252)</f>
+        <v>7988.6998572800003</v>
+      </c>
+      <c r="F255" s="4">
+        <f t="shared" si="47"/>
+        <v>3.6016061043586542E-4</v>
+      </c>
+      <c r="G255" s="4">
+        <f t="shared" si="47"/>
+        <v>6.1379375326141381E-3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C257" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D257" s="3">
+        <f>D254/D255</f>
+        <v>1.3902001109844437</v>
+      </c>
+      <c r="E257" s="3">
+        <f t="shared" ref="E257:G257" si="48">E254/E255</f>
+        <v>1.462361279754929</v>
+      </c>
+      <c r="F257" s="3">
+        <f t="shared" si="48"/>
+        <v>0.71207716480109773</v>
+      </c>
+      <c r="G257" s="3">
+        <f t="shared" si="48"/>
+        <v>1.2647790839496653</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G259" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C260" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D260" s="3">
+        <v>624490.81179662514</v>
+      </c>
+      <c r="E260" s="3">
+        <v>23490.718752000001</v>
+      </c>
+      <c r="F260" s="4">
+        <v>1.927088927244758E-3</v>
+      </c>
+      <c r="G260" s="4">
+        <v>1.8760825696850091E-3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B261" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C261" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D261" s="3">
+        <v>615005.46689121344</v>
+      </c>
+      <c r="E261" s="3">
+        <v>18304.5266156</v>
+      </c>
+      <c r="F261" s="4">
+        <v>2.0544865338363899E-3</v>
+      </c>
+      <c r="G261" s="4">
+        <v>2.397692315221963E-3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B262" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C262" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D262" s="3">
+        <v>557880.96074185451</v>
+      </c>
+      <c r="E262" s="3">
+        <v>17673.58753398</v>
+      </c>
+      <c r="F262" s="4">
+        <v>1.2639185721094849E-3</v>
+      </c>
+      <c r="G262" s="4">
+        <v>7.224852054202324E-4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B263" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C263" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D263" s="3">
+        <v>528936.59684355662</v>
+      </c>
+      <c r="E263" s="3">
+        <v>14840.029964359999</v>
+      </c>
+      <c r="F263" s="4">
+        <v>3.348617336982791E-3</v>
+      </c>
+      <c r="G263" s="4">
+        <v>9.7700369843055682E-4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B265" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D265" s="3">
+        <f>AVERAGE(D260:D261)</f>
+        <v>619748.13934391923</v>
+      </c>
+      <c r="E265" s="3">
+        <f t="shared" ref="E265:G265" si="49">AVERAGE(E260:E261)</f>
+        <v>20897.6226838</v>
+      </c>
+      <c r="F265" s="4">
+        <f t="shared" si="49"/>
+        <v>1.9907877305405742E-3</v>
+      </c>
+      <c r="G265" s="4">
+        <f t="shared" si="49"/>
+        <v>2.1368874424534858E-3</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B266" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D266" s="3">
+        <f>AVERAGE(D262:D263)</f>
+        <v>543408.77879270562</v>
+      </c>
+      <c r="E266" s="3">
+        <f t="shared" ref="E266:G266" si="50">AVERAGE(E262:E263)</f>
+        <v>16256.808749169999</v>
+      </c>
+      <c r="F266" s="4">
+        <f t="shared" si="50"/>
+        <v>2.3062679545461382E-3</v>
+      </c>
+      <c r="G266" s="4">
+        <f t="shared" si="50"/>
+        <v>8.4974445192539461E-4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C268" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D268" s="3">
+        <f>D265/D266</f>
+        <v>1.1404823836685474</v>
+      </c>
+      <c r="E268" s="3">
+        <f t="shared" ref="E268:G268" si="51">E265/E266</f>
+        <v>1.2854689383527957</v>
+      </c>
+      <c r="F268" s="3">
+        <f t="shared" si="51"/>
+        <v>0.8632074718882139</v>
+      </c>
+      <c r="G268" s="3">
+        <f t="shared" si="51"/>
+        <v>2.5147412702861627</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G270" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C271" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D271" s="3">
+        <v>496312.33844584553</v>
+      </c>
+      <c r="E271" s="3">
+        <v>6058.6276942799996</v>
+      </c>
+      <c r="F271" s="4">
+        <v>1.149126975828702E-3</v>
+      </c>
+      <c r="G271" s="4">
+        <v>4.3326889923906344E-3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B272" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C272" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D272" s="3">
+        <v>481190.63450056087</v>
+      </c>
+      <c r="E272" s="3">
+        <v>5659.2905294400007</v>
+      </c>
+      <c r="F272" s="4">
+        <v>2.7642536319032169E-4</v>
+      </c>
+      <c r="G272" s="4">
+        <v>2.609783923120391E-3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C273" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D273" s="3">
+        <v>463554.2380744408</v>
+      </c>
+      <c r="E273" s="3">
+        <v>6405.1162323599992</v>
+      </c>
+      <c r="F273" s="4">
+        <v>1.36542870460566E-3</v>
+      </c>
+      <c r="G273" s="4">
+        <v>1.06191448730258E-3</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C274" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D274" s="3">
+        <v>463215.01884109463</v>
+      </c>
+      <c r="E274" s="3">
+        <v>6600.4823040000001</v>
+      </c>
+      <c r="F274" s="4">
+        <v>1.0184783005820781E-3</v>
+      </c>
+      <c r="G274" s="4">
+        <v>1.1952508372333631E-3</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B276" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D276" s="3">
+        <f>AVERAGE(D271:D272)</f>
+        <v>488751.48647320317</v>
+      </c>
+      <c r="E276" s="3">
+        <f t="shared" ref="E276:G276" si="52">AVERAGE(E271:E272)</f>
+        <v>5858.9591118600001</v>
+      </c>
+      <c r="F276" s="4">
+        <f t="shared" si="52"/>
+        <v>7.1277616950951182E-4</v>
+      </c>
+      <c r="G276" s="4">
+        <f t="shared" si="52"/>
+        <v>3.4712364577555127E-3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B277" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D277" s="3">
+        <f>AVERAGE(D273:D274)</f>
         <v>463384.62845776771</v>
       </c>
-      <c r="E221" s="3">
-        <f t="shared" ref="E221:G221" si="43">AVERAGE(E217:E218)</f>
+      <c r="E277" s="3">
+        <f t="shared" ref="E277:G277" si="53">AVERAGE(E273:E274)</f>
         <v>6502.7992681799997</v>
       </c>
-      <c r="F221" s="4">
-        <f t="shared" si="43"/>
+      <c r="F277" s="4">
+        <f t="shared" si="53"/>
         <v>1.191953502593869E-3</v>
       </c>
-      <c r="G221" s="4">
-        <f t="shared" si="43"/>
+      <c r="G277" s="4">
+        <f t="shared" si="53"/>
         <v>1.1285826622679715E-3</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C223" s="7" t="s">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C279" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D223" s="3">
-        <f>D220/D221</f>
+      <c r="D279" s="3">
+        <f>D276/D277</f>
         <v>1.0547425539337831</v>
       </c>
-      <c r="E223" s="3">
-        <f t="shared" ref="E223:G223" si="44">E220/E221</f>
+      <c r="E279" s="3">
+        <f t="shared" ref="E279:G279" si="54">E276/E277</f>
         <v>0.9009903074402914</v>
       </c>
-      <c r="F223" s="3">
-        <f t="shared" si="44"/>
+      <c r="F279" s="3">
+        <f t="shared" si="54"/>
         <v>0.59798991148430225</v>
       </c>
-      <c r="G223" s="3">
-        <f t="shared" si="44"/>
+      <c r="G279" s="3">
+        <f t="shared" si="54"/>
         <v>3.0757485240645135</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:G62">
-    <sortCondition descending="1" ref="D2:D62"/>
+  <sortState ref="C138:G141">
+    <sortCondition ref="C138:C141"/>
   </sortState>
   <conditionalFormatting sqref="D2:D62">
     <cfRule type="colorScale" priority="128">
@@ -4761,7 +8912,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D83:D86">
+  <conditionalFormatting sqref="D96:D99">
     <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="min"/>
@@ -4773,7 +8924,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E83:E86">
+  <conditionalFormatting sqref="E96:E99">
     <cfRule type="colorScale" priority="103">
       <colorScale>
         <cfvo type="min"/>
@@ -4785,7 +8936,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F83:F86">
+  <conditionalFormatting sqref="F96:F99">
     <cfRule type="colorScale" priority="102">
       <colorScale>
         <cfvo type="min"/>
@@ -4797,7 +8948,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G83:G86">
+  <conditionalFormatting sqref="G96:G99">
     <cfRule type="colorScale" priority="101">
       <colorScale>
         <cfvo type="min"/>
@@ -4809,7 +8960,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D88:D89">
+  <conditionalFormatting sqref="D101:D102">
     <cfRule type="colorScale" priority="100">
       <colorScale>
         <cfvo type="min"/>
@@ -4821,7 +8972,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E88:E89">
+  <conditionalFormatting sqref="E101:E102">
     <cfRule type="colorScale" priority="99">
       <colorScale>
         <cfvo type="min"/>
@@ -4833,7 +8984,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F88:F89">
+  <conditionalFormatting sqref="F101:F102">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
@@ -4845,7 +8996,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G88:G89">
+  <conditionalFormatting sqref="G101:G102">
     <cfRule type="colorScale" priority="97">
       <colorScale>
         <cfvo type="min"/>
@@ -4857,7 +9008,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D94:D97">
+  <conditionalFormatting sqref="D120:D123">
     <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="min"/>
@@ -4869,7 +9020,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E94:E97">
+  <conditionalFormatting sqref="E120:E123">
     <cfRule type="colorScale" priority="95">
       <colorScale>
         <cfvo type="min"/>
@@ -4881,7 +9032,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F94:F97">
+  <conditionalFormatting sqref="F120:F123">
     <cfRule type="colorScale" priority="94">
       <colorScale>
         <cfvo type="min"/>
@@ -4893,7 +9044,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G94:G97">
+  <conditionalFormatting sqref="G120:G123">
     <cfRule type="colorScale" priority="93">
       <colorScale>
         <cfvo type="min"/>
@@ -4905,7 +9056,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D99:D100">
+  <conditionalFormatting sqref="D125:D126">
     <cfRule type="colorScale" priority="92">
       <colorScale>
         <cfvo type="min"/>
@@ -4917,7 +9068,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E99:E100">
+  <conditionalFormatting sqref="E125:E126">
     <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
@@ -4929,7 +9080,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F99:F100">
+  <conditionalFormatting sqref="F125:F126">
     <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="min"/>
@@ -4941,7 +9092,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G99:G100">
+  <conditionalFormatting sqref="G125:G126">
     <cfRule type="colorScale" priority="89">
       <colorScale>
         <cfvo type="min"/>
@@ -4953,7 +9104,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D105:D108">
+  <conditionalFormatting sqref="D144:D147">
     <cfRule type="colorScale" priority="88">
       <colorScale>
         <cfvo type="min"/>
@@ -4965,7 +9116,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E105:E108">
+  <conditionalFormatting sqref="E144:E147">
     <cfRule type="colorScale" priority="87">
       <colorScale>
         <cfvo type="min"/>
@@ -4977,7 +9128,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F105:F108">
+  <conditionalFormatting sqref="F144:F147">
     <cfRule type="colorScale" priority="86">
       <colorScale>
         <cfvo type="min"/>
@@ -4989,7 +9140,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G105:G108">
+  <conditionalFormatting sqref="G144:G147">
     <cfRule type="colorScale" priority="85">
       <colorScale>
         <cfvo type="min"/>
@@ -5001,7 +9152,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D110:D111">
+  <conditionalFormatting sqref="D149:D150">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -5013,7 +9164,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E110:E111">
+  <conditionalFormatting sqref="E149:E150">
     <cfRule type="colorScale" priority="83">
       <colorScale>
         <cfvo type="min"/>
@@ -5025,7 +9176,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F110:F111">
+  <conditionalFormatting sqref="F149:F150">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -5037,7 +9188,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G110:G111">
+  <conditionalFormatting sqref="G149:G150">
     <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
@@ -5049,7 +9200,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D116:D119">
+  <conditionalFormatting sqref="D172:D175">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -5061,7 +9212,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E116:E119">
+  <conditionalFormatting sqref="E172:E175">
     <cfRule type="colorScale" priority="79">
       <colorScale>
         <cfvo type="min"/>
@@ -5073,7 +9224,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F116:F119">
+  <conditionalFormatting sqref="F172:F175">
     <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="min"/>
@@ -5085,7 +9236,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G116:G119">
+  <conditionalFormatting sqref="G172:G175">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -5097,7 +9248,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D121:D122">
+  <conditionalFormatting sqref="D177:D178">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
@@ -5109,7 +9260,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E121:E122">
+  <conditionalFormatting sqref="E177:E178">
     <cfRule type="colorScale" priority="75">
       <colorScale>
         <cfvo type="min"/>
@@ -5121,7 +9272,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F121:F122">
+  <conditionalFormatting sqref="F177:F178">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
@@ -5133,7 +9284,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G121:G122">
+  <conditionalFormatting sqref="G177:G178">
     <cfRule type="colorScale" priority="73">
       <colorScale>
         <cfvo type="min"/>
@@ -5145,7 +9296,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D127:D130">
+  <conditionalFormatting sqref="D183:D186">
     <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="min"/>
@@ -5157,7 +9308,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E127:E130">
+  <conditionalFormatting sqref="E183:E186">
     <cfRule type="colorScale" priority="71">
       <colorScale>
         <cfvo type="min"/>
@@ -5169,7 +9320,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F127:F130">
+  <conditionalFormatting sqref="F183:F186">
     <cfRule type="colorScale" priority="70">
       <colorScale>
         <cfvo type="min"/>
@@ -5181,7 +9332,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G127:G130">
+  <conditionalFormatting sqref="G183:G186">
     <cfRule type="colorScale" priority="69">
       <colorScale>
         <cfvo type="min"/>
@@ -5193,7 +9344,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D132:D133">
+  <conditionalFormatting sqref="D188:D189">
     <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="min"/>
@@ -5205,7 +9356,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E132:E133">
+  <conditionalFormatting sqref="E188:E189">
     <cfRule type="colorScale" priority="67">
       <colorScale>
         <cfvo type="min"/>
@@ -5217,7 +9368,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F132:F133">
+  <conditionalFormatting sqref="F188:F189">
     <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
@@ -5229,7 +9380,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G132:G133">
+  <conditionalFormatting sqref="G188:G189">
     <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
@@ -5241,7 +9392,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D138:D141">
+  <conditionalFormatting sqref="D194:D197">
     <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="min"/>
@@ -5253,7 +9404,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E138:E141">
+  <conditionalFormatting sqref="E194:E197">
     <cfRule type="colorScale" priority="63">
       <colorScale>
         <cfvo type="min"/>
@@ -5265,7 +9416,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F138:F141">
+  <conditionalFormatting sqref="F194:F197">
     <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="min"/>
@@ -5277,7 +9428,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G138:G141">
+  <conditionalFormatting sqref="G194:G197">
     <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="min"/>
@@ -5289,7 +9440,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D143:D144">
+  <conditionalFormatting sqref="D199:D200">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="min"/>
@@ -5301,7 +9452,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E143:E144">
+  <conditionalFormatting sqref="E199:E200">
     <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="min"/>
@@ -5313,7 +9464,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F143:F144">
+  <conditionalFormatting sqref="F199:F200">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="min"/>
@@ -5325,7 +9476,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G143:G144">
+  <conditionalFormatting sqref="G199:G200">
     <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
@@ -5337,7 +9488,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D149:D152">
+  <conditionalFormatting sqref="D205:D208">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
@@ -5349,7 +9500,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E149:E152">
+  <conditionalFormatting sqref="E205:E208">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -5361,7 +9512,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F149:F152">
+  <conditionalFormatting sqref="F205:F208">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
@@ -5373,7 +9524,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G149:G152">
+  <conditionalFormatting sqref="G205:G208">
     <cfRule type="colorScale" priority="53">
       <colorScale>
         <cfvo type="min"/>
@@ -5385,7 +9536,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D154:D155">
+  <conditionalFormatting sqref="D210:D211">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min"/>
@@ -5397,7 +9548,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E154:E155">
+  <conditionalFormatting sqref="E210:E211">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -5409,7 +9560,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F154:F155">
+  <conditionalFormatting sqref="F210:F211">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
@@ -5421,7 +9572,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G154:G155">
+  <conditionalFormatting sqref="G210:G211">
     <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
@@ -5433,7 +9584,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D160:D163">
+  <conditionalFormatting sqref="D216:D219">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
@@ -5445,7 +9596,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E160:E163">
+  <conditionalFormatting sqref="E216:E219">
     <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
@@ -5457,7 +9608,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F160:F163">
+  <conditionalFormatting sqref="F216:F219">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
@@ -5469,7 +9620,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G160:G163">
+  <conditionalFormatting sqref="G216:G219">
     <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
@@ -5481,7 +9632,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D165:D166">
+  <conditionalFormatting sqref="D221:D222">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
@@ -5493,7 +9644,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E165:E166">
+  <conditionalFormatting sqref="E221:E222">
     <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
@@ -5505,7 +9656,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F165:F166">
+  <conditionalFormatting sqref="F221:F222">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
@@ -5517,7 +9668,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G165:G166">
+  <conditionalFormatting sqref="G221:G222">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -5529,7 +9680,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D171:D174">
+  <conditionalFormatting sqref="D227:D230">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -5541,7 +9692,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E171:E174">
+  <conditionalFormatting sqref="E227:E230">
     <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
@@ -5553,7 +9704,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F171:F174">
+  <conditionalFormatting sqref="F227:F230">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
@@ -5565,7 +9716,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G171:G174">
+  <conditionalFormatting sqref="G227:G230">
     <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
@@ -5577,7 +9728,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D176:D177">
+  <conditionalFormatting sqref="D232:D233">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -5589,7 +9740,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E176:E177">
+  <conditionalFormatting sqref="E232:E233">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -5601,7 +9752,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F176:F177">
+  <conditionalFormatting sqref="F232:F233">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
@@ -5613,7 +9764,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G176:G177">
+  <conditionalFormatting sqref="G232:G233">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -5625,7 +9776,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D182:D185">
+  <conditionalFormatting sqref="D238:D241">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
@@ -5637,7 +9788,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E182:E185">
+  <conditionalFormatting sqref="E238:E241">
     <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
@@ -5649,7 +9800,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F182:F185">
+  <conditionalFormatting sqref="F238:F241">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
@@ -5661,7 +9812,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G182:G185">
+  <conditionalFormatting sqref="G238:G241">
     <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
@@ -5673,7 +9824,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D187:D188">
+  <conditionalFormatting sqref="D243:D244">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
@@ -5685,7 +9836,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E187:E188">
+  <conditionalFormatting sqref="E243:E244">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -5697,7 +9848,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F187:F188">
+  <conditionalFormatting sqref="F243:F244">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
@@ -5709,7 +9860,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G187:G188">
+  <conditionalFormatting sqref="G243:G244">
     <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
@@ -5721,7 +9872,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D193:D196">
+  <conditionalFormatting sqref="D249:D252">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
@@ -5733,7 +9884,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E193:E196">
+  <conditionalFormatting sqref="E249:E252">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
@@ -5745,7 +9896,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F193:F196">
+  <conditionalFormatting sqref="F249:F252">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
@@ -5757,7 +9908,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G193:G196">
+  <conditionalFormatting sqref="G249:G252">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -5769,7 +9920,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D198:D199">
+  <conditionalFormatting sqref="D254:D255">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -5781,7 +9932,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E198:E199">
+  <conditionalFormatting sqref="E254:E255">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -5793,7 +9944,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F198:F199">
+  <conditionalFormatting sqref="F254:F255">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -5805,7 +9956,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G198:G199">
+  <conditionalFormatting sqref="G254:G255">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -5817,7 +9968,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D204:D207">
+  <conditionalFormatting sqref="D260:D263">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -5829,7 +9980,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E204:E207">
+  <conditionalFormatting sqref="E260:E263">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -5841,7 +9992,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F204:F207">
+  <conditionalFormatting sqref="F260:F263">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -5853,7 +10004,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G204:G207">
+  <conditionalFormatting sqref="G260:G263">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -5865,7 +10016,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D209:D210">
+  <conditionalFormatting sqref="D265:D266">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -5877,7 +10028,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E209:E210">
+  <conditionalFormatting sqref="E265:E266">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -5889,7 +10040,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F209:F210">
+  <conditionalFormatting sqref="F265:F266">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -5901,7 +10052,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G209:G210">
+  <conditionalFormatting sqref="G265:G266">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -5913,7 +10064,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D215:D218">
+  <conditionalFormatting sqref="D271:D274">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -5925,7 +10076,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E215:E218">
+  <conditionalFormatting sqref="E271:E274">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -5937,7 +10088,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F215:F218">
+  <conditionalFormatting sqref="F271:F274">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -5949,7 +10100,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G215:G218">
+  <conditionalFormatting sqref="G271:G274">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -5961,7 +10112,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D220:D221">
+  <conditionalFormatting sqref="D276:D277">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -5973,7 +10124,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E220:E221">
+  <conditionalFormatting sqref="E276:E277">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -5985,7 +10136,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F220:F221">
+  <conditionalFormatting sqref="F276:F277">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5997,7 +10148,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G220:G221">
+  <conditionalFormatting sqref="G276:G277">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6011,5 +10162,6 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
@@ -346,7 +346,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -796,7 +795,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -903,7 +901,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1353,7 +1350,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1460,7 +1456,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1910,7 +1905,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2017,7 +2011,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2467,7 +2460,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2574,7 +2566,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3024,7 +3015,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3131,7 +3121,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3581,7 +3570,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3741,7 +3729,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4079,7 +4067,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4416,7 +4404,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4754,7 +4742,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5092,7 +5080,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5377,7 +5365,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5827,7 +5814,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5987,7 +5973,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6325,7 +6311,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6663,7 +6649,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -7001,7 +6987,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -7339,7 +7325,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -7677,7 +7663,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -8015,7 +8001,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -8353,7 +8339,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -8691,7 +8677,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -9102,7 +9088,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -9386,7 +9372,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9836,7 +9821,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10069,7 +10053,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -10479,7 +10463,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -10890,7 +10874,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -11301,7 +11285,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -11696,154 +11680,8 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$213</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,98</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$213:$G$213</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.79597731535177796</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.5628869020468137E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.57331026854314004</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5CDE-456F-B145-481E786ED7F0}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$214</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,99</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$214:$G$214</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.80926420797553855</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.11207082497893665</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.9038990327846067</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-5CDE-456F-B145-481E786ED7F0}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>'Best|Worst'!$C$215</c:f>
@@ -11858,7 +11696,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -12253,154 +12091,8 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$238</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,79</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$238:$G$238</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.67725490625943618</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1E7F-4EFF-B9D5-327AF19CDB08}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$239</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,82</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$239:$G$239</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.73835805970790658</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.84927446007410101</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.78959028422057287</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1E7F-4EFF-B9D5-327AF19CDB08}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>'Best|Worst'!$C$240</c:f>
@@ -12415,7 +12107,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -12810,154 +12502,8 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$263</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,74</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$263:$G$263</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.37919583070757845</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.24604511227578876</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.0333919862687079E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3C83-4701-8E2D-FFC92414139A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$264</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,85</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$264:$G$264</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.69088738020157991</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.6818716744632944E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3C83-4701-8E2D-FFC92414139A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>'Best|Worst'!$C$265</c:f>
@@ -12972,7 +12518,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -13367,154 +12913,8 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$288</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,75</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$288:$G$288</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.9773689598128844E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EC1F-4455-AC7E-2F071C4C58A4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$289</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,92</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$289:$G$289</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.3535920446884655</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.12486016719718387</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-EC1F-4455-AC7E-2F071C4C58A4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>'Best|Worst'!$C$290</c:f>
@@ -13529,7 +12929,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -13924,154 +13324,8 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$312</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,78</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$312:$G$312</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.6622871781342003E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.8393846438341249E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7571-4760-AF8F-E6A42698D9E2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$313</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,87</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$313:$G$313</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.11172742372709753</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.5175960410871423</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7571-4760-AF8F-E6A42698D9E2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>'Best|Worst'!$C$314</c:f>
@@ -14086,7 +13340,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -14481,154 +13735,8 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$337</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,72</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$337:$G$337</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.71225562194184977</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.85157128686456229</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F93E-4297-9051-84ACECCDBB3E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$338</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,75</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$338:$G$338</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.76963868006501046</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.6284668188071074E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.76611190616225677</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-F93E-4297-9051-84ACECCDBB3E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>'Best|Worst'!$C$339</c:f>
@@ -14643,7 +13751,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -14928,7 +14036,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -15378,7 +14485,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -15595,154 +14701,8 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$362</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,72</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$362:$G$362</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.56632037695360282</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.5308363085126067E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2AC8-4A5A-B751-D4DD29C015EA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$363</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,90</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$363:$G$363</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.70371379494052133</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.56932678776700363</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9.1928838540822747E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-2AC8-4A5A-B751-D4DD29C015EA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>'Best|Worst'!$C$364</c:f>
@@ -15757,7 +14717,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -16152,154 +15112,8 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$387</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,89</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$387:$G$387</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.7523646986099678</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.3774449108145379</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.30132523711798664</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5C95-4B69-8427-152EC08E0CBE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$388</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,98</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$388:$G$388</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.77922377807369358</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.61353278893537189</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-5C95-4B69-8427-152EC08E0CBE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>'Best|Worst'!$C$389</c:f>
@@ -16314,7 +15128,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -16709,154 +15523,8 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$412</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,93</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$412:$G$412</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.97040124302407327</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.24509363334584758</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F8AB-4395-8B83-C162D20FE09F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Best|Worst'!$C$413</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,97</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Best|Worst'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Best|Worst'!$D$413:$G$413</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.85740560595251925</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.20244584155725229</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.60234739389415504</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-F8AB-4395-8B83-C162D20FE09F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
           <c:tx>
             <c:strRef>
               <c:f>'Best|Worst'!$C$414</c:f>
@@ -16871,7 +15539,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -17156,7 +15824,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -17606,7 +16273,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -17713,7 +16379,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -18163,7 +16828,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -18270,7 +16934,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -18720,7 +17383,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -18827,7 +17489,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -19277,7 +17938,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -19384,7 +18044,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -19834,7 +18493,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -43698,16 +42356,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>253588</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>184314</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>24988</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>31914</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>245147</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>129593</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>16547</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>167693</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -43730,15 +42388,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>439139</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>210539</xdr:colOff>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>189262</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>430698</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>202098</xdr:colOff>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>134541</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -43762,16 +42420,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>51954</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>173182</xdr:rowOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>528204</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>125557</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>43513</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>118461</xdr:rowOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>519763</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>70836</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -43794,16 +42452,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>575397</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>182707</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>537297</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>30307</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>566957</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>127986</xdr:rowOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>528857</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>166086</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -43826,16 +42484,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>616959</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>62779</xdr:rowOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>264534</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>24679</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>608519</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>8058</xdr:rowOff>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>265619</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>160458</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -43858,16 +42516,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>23813</xdr:rowOff>
+      <xdr:col>60</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>372560</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>159592</xdr:rowOff>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>248735</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>169117</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -43890,16 +42548,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>586652</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>62778</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>143739</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>105641</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>578213</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>8057</xdr:rowOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>135300</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>50920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -43922,15 +42580,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>60614</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>403514</xdr:colOff>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>25977</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>52175</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>395075</xdr:colOff>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>161756</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -43954,16 +42612,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>49789</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>162357</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>392689</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9957</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>41349</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>107636</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>384249</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>145736</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -43986,16 +42644,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>363682</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>173182</xdr:rowOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>516082</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>96982</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>355242</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>118461</xdr:rowOff>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>507642</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>42261</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -44018,15 +42676,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>571501</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>342901</xdr:colOff>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>173182</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>563060</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>334460</xdr:colOff>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>118461</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -44050,16 +42708,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>163286</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>396649</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>154845</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>135779</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>388208</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>145304</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -44082,16 +42740,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>34636</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>173182</xdr:rowOff>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>568036</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>58882</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>26195</xdr:colOff>
-      <xdr:row>143</xdr:row>
-      <xdr:rowOff>118461</xdr:rowOff>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>559595</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>4161</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -44114,16 +42772,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>340179</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>559254</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>331738</xdr:colOff>
-      <xdr:row>143</xdr:row>
-      <xdr:rowOff>135779</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>550813</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>131016</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>

--- a/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="2"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
     <sheet name="Original" sheetId="1" r:id="rId1"/>
@@ -346,6 +346,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -670,3118 +671,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-48A5-4E9B-8E97-537E0DDE442D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="744722240"/>
-        <c:axId val="744723072"/>
-      </c:radarChart>
-      <c:catAx>
-        <c:axId val="744722240"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744723072"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="744723072"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744722240"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:effectLst/>
-              </a:rPr>
-              <a:t>27</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:radarChart>
-        <c:radarStyle val="marker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$311</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,70</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$311:$G$311</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.10307195849510592</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.2924715166971622E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7BC3-4249-8E82-1F2D0A530EBD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$312</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,78</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$312:$G$312</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.6622871781342003E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.8393846438341249E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7BC3-4249-8E82-1F2D0A530EBD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$313</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,87</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$313:$G$313</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.11172742372709753</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.5175960410871423</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7BC3-4249-8E82-1F2D0A530EBD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$314</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1,00</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$314:$G$314</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.14350332523225146</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.55578650039264843</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.45346685151196658</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-7BC3-4249-8E82-1F2D0A530EBD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="744722240"/>
-        <c:axId val="744723072"/>
-      </c:radarChart>
-      <c:catAx>
-        <c:axId val="744722240"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744723072"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="744723072"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744722240"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:effectLst/>
-              </a:rPr>
-              <a:t>28</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:radarChart>
-        <c:radarStyle val="marker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$336</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,64</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$336:$G$336</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.87097193396472083</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.10651512073048215</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.52585818127499084</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-21FD-4083-ADAE-7D16E33DB0FD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$337</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,72</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$337:$G$337</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.71225562194184977</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.85157128686456229</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-21FD-4083-ADAE-7D16E33DB0FD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$338</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,75</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$338:$G$338</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.76963868006501046</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.6284668188071074E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.76611190616225677</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-21FD-4083-ADAE-7D16E33DB0FD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$339</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1,00</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$339:$G$339</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.6315361695601274E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-21FD-4083-ADAE-7D16E33DB0FD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="744722240"/>
-        <c:axId val="744723072"/>
-      </c:radarChart>
-      <c:catAx>
-        <c:axId val="744722240"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744723072"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="744723072"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744722240"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:effectLst/>
-              </a:rPr>
-              <a:t>29</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:radarChart>
-        <c:radarStyle val="marker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$361</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,65</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$361:$G$361</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.59872263842631746</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.26640448561938757</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.798027260026964</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3FFB-4B24-BE88-09C62F9BCA5C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$362</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,72</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$362:$G$362</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.56632037695360282</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.5308363085126067E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3FFB-4B24-BE88-09C62F9BCA5C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$363</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,90</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$363:$G$363</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.70371379494052133</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.56932678776700363</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9.1928838540822747E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3FFB-4B24-BE88-09C62F9BCA5C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$364</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1,00</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$364:$G$364</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.33245092784424229</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-3FFB-4B24-BE88-09C62F9BCA5C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="744722240"/>
-        <c:axId val="744723072"/>
-      </c:radarChart>
-      <c:catAx>
-        <c:axId val="744722240"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744723072"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="744723072"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744722240"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:effectLst/>
-              </a:rPr>
-              <a:t>30</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:radarChart>
-        <c:radarStyle val="marker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$386</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,85</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$386:$G$386</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.63174014047980198</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.40747667756532474</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C337-4C7C-835D-103550E1DE2C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$387</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,89</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$387:$G$387</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.7523646986099678</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.3774449108145379</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.30132523711798664</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C337-4C7C-835D-103550E1DE2C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$388</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,98</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$388:$G$388</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.77922377807369358</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.61353278893537189</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C337-4C7C-835D-103550E1DE2C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$389</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1,00</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$389:$G$389</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.57548795019413157</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.78245342731197487</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C337-4C7C-835D-103550E1DE2C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="744722240"/>
-        <c:axId val="744723072"/>
-      </c:radarChart>
-      <c:catAx>
-        <c:axId val="744722240"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744723072"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="744723072"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744722240"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:effectLst/>
-              </a:rPr>
-              <a:t>33</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:radarChart>
-        <c:radarStyle val="marker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$411</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,93</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$411:$G$411</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.7459036836904771</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.27586813623884487</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-86E7-4395-826B-1310EB1B4BE1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$412</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,93</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$412:$G$412</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.97040124302407327</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.24509363334584758</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-86E7-4395-826B-1310EB1B4BE1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$413</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,97</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$413:$G$413</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.85740560595251925</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.20244584155725229</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.60234739389415504</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-86E7-4395-826B-1310EB1B4BE1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$414</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1,00</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$414:$G$414</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.91790681578047295</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.84158694771293341</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-86E7-4395-826B-1310EB1B4BE1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="744722240"/>
-        <c:axId val="744723072"/>
-      </c:radarChart>
-      <c:catAx>
-        <c:axId val="744722240"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744723072"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="744723072"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744722240"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:effectLst/>
-              </a:rPr>
-              <a:t>19</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:radarChart>
-        <c:radarStyle val="marker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Only best'!$C$117</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1,00</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Only best'!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Only best'!$D$117:$G$117</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.75686804000192376</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.49718479540475113</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E119-4F7D-B89E-F819E8ECCAD5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3971,7 +860,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -4008,7 +897,7 @@
               <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
                 <a:effectLst/>
               </a:rPr>
-              <a:t>20</a:t>
+              <a:t>27</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -4055,11 +944,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Only best'!$C$141</c:f>
+              <c:f>Original!$C$311</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1,00</c:v>
+                  <c:v>0,70</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4067,7 +956,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4078,7 +967,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Only best'!$D$113:$G$113</c:f>
+              <c:f>Original!$D$113:$G$113</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -4098,7 +987,80 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Only best'!$D$141:$G$141</c:f>
+              <c:f>Original!$D$311:$G$311</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10307195849510592</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.2924715166971622E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7BC3-4249-8E82-1F2D0A530EBD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$312</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,78</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$312:$G$312</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -4106,20 +1068,166 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.56379755979405544</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.50828225173152997</c:v>
+                  <c:v>5.6622871781342003E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.37838843465697375</c:v>
+                  <c:v>4.8393846438341249E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-68F3-4B0A-B88E-EC4A9DBDFF90}"/>
+              <c16:uniqueId val="{00000001-7BC3-4249-8E82-1F2D0A530EBD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$313</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,87</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$313:$G$313</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.11172742372709753</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.5175960410871423</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7BC3-4249-8E82-1F2D0A530EBD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$314</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$314:$G$314</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.14350332523225146</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.55578650039264843</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.45346685151196658</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7BC3-4249-8E82-1F2D0A530EBD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4309,7 +1417,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -4346,8 +1454,9 @@
               <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
                 <a:effectLst/>
               </a:rPr>
-              <a:t>16</a:t>
+              <a:t>28</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -4392,11 +1501,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Only best'!$C$93</c:f>
+              <c:f>Original!$C$336</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1,00</c:v>
+                  <c:v>0,64</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4404,7 +1513,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4415,7 +1524,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Only best'!$D$89:$G$89</c:f>
+              <c:f>Original!$D$113:$G$113</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -4435,7 +1544,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Only best'!$D$93:$G$93</c:f>
+              <c:f>Original!$D$336:$G$336</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -4443,20 +1552,239 @@
                   <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.89882061387652312</c:v>
+                  <c:v>0.87097193396472083</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.17795127025264079</c:v>
+                  <c:v>0.10651512073048215</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0.52585818127499084</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D314-45B4-BD24-0B2701E5CBD7}"/>
+              <c16:uniqueId val="{00000000-21FD-4083-ADAE-7D16E33DB0FD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$337</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,72</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$337:$G$337</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.71225562194184977</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.85157128686456229</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-21FD-4083-ADAE-7D16E33DB0FD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$338</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,75</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$338:$G$338</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.76963868006501046</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.6284668188071074E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.76611190616225677</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-21FD-4083-ADAE-7D16E33DB0FD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$339</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$339:$G$339</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.6315361695601274E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-21FD-4083-ADAE-7D16E33DB0FD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4646,7 +1974,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -4683,7 +2011,7 @@
               <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
                 <a:effectLst/>
               </a:rPr>
-              <a:t>21</a:t>
+              <a:t>29</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -4730,11 +2058,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Only best'!$C$165</c:f>
+              <c:f>Original!$C$361</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1,00</c:v>
+                  <c:v>0,65</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4742,7 +2070,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4753,7 +2081,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Only best'!$D$113:$G$113</c:f>
+              <c:f>Original!$D$113:$G$113</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -4773,7 +2101,226 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Only best'!$D$165:$G$165</c:f>
+              <c:f>Original!$D$361:$G$361</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.59872263842631746</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.26640448561938757</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.798027260026964</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3FFB-4B24-BE88-09C62F9BCA5C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$362</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,72</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$362:$G$362</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.56632037695360282</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5308363085126067E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3FFB-4B24-BE88-09C62F9BCA5C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$363</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,90</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$363:$G$363</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.70371379494052133</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.56932678776700363</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.1928838540822747E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3FFB-4B24-BE88-09C62F9BCA5C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$364</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$364:$G$364</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -4784,17 +2331,17 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.69842143423119296</c:v>
+                  <c:v>0.33245092784424229</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.27079088952453417</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E519-421F-A0F7-0AEAB9BB9168}"/>
+              <c16:uniqueId val="{00000003-3FFB-4B24-BE88-09C62F9BCA5C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4984,7 +2531,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -5018,10 +2565,10 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
                 <a:effectLst/>
               </a:rPr>
-              <a:t>22</a:t>
+              <a:t>30</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -5068,11 +2615,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Only best'!$C$190</c:f>
+              <c:f>Original!$C$386</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1,00</c:v>
+                  <c:v>0,85</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5080,7 +2627,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5091,7 +2638,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Only best'!$D$113:$G$113</c:f>
+              <c:f>Original!$D$113:$G$113</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -5111,7 +2658,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Only best'!$D$190:$G$190</c:f>
+              <c:f>Original!$D$386:$G$386</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -5119,20 +2666,239 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.84040363200323998</c:v>
+                  <c:v>0.63174014047980198</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22466253890066659</c:v>
+                  <c:v>0.40747667756532474</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-23CF-42C1-BD41-4881695A0362}"/>
+              <c16:uniqueId val="{00000000-C337-4C7C-835D-103550E1DE2C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$387</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,89</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$387:$G$387</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7523646986099678</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.3774449108145379</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30132523711798664</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C337-4C7C-835D-103550E1DE2C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$388</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,98</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$388:$G$388</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.77922377807369358</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.61353278893537189</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C337-4C7C-835D-103550E1DE2C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$389</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$389:$G$389</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.57548795019413157</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.78245342731197487</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C337-4C7C-835D-103550E1DE2C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5322,7 +3088,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -5359,562 +3125,7 @@
               <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
                 <a:effectLst/>
               </a:rPr>
-              <a:t>20</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:radarChart>
-        <c:radarStyle val="marker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$138</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,80</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$138:$G$138</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.75473497922288912</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13016270721820974</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.20562583073637467</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3263-4778-9FE4-27A25304FFCB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$139</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,82</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$139:$G$139</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.8380185016176708E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.12267657460088674</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3263-4778-9FE4-27A25304FFCB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$140</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0,86</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$140:$G$140</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.6990904820453</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3263-4778-9FE4-27A25304FFCB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Original!$C$141</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1,00</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Original!$D$113:$G$113</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Year</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>trainingcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Original!$D$141:$G$141</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.56379755979405544</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.50828225173152997</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.37838843465697375</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-3263-4778-9FE4-27A25304FFCB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="744722240"/>
-        <c:axId val="744723072"/>
-      </c:radarChart>
-      <c:catAx>
-        <c:axId val="744722240"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744723072"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="744723072"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="744722240"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:effectLst/>
-              </a:rPr>
-              <a:t>23</a:t>
+              <a:t>33</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -5961,11 +3172,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Only best'!$C$215</c:f>
+              <c:f>Original!$C$411</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1,00</c:v>
+                  <c:v>0,93</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5973,7 +3184,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5984,7 +3195,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Only best'!$D$113:$G$113</c:f>
+              <c:f>Original!$D$113:$G$113</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -6004,7 +3215,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Only best'!$D$215:$G$215</c:f>
+              <c:f>Original!$D$411:$G$411</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -6012,20 +3223,239 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.57664977093076919</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.77853736812744556</c:v>
+                  <c:v>0.7459036836904771</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0.27586813623884487</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6D9C-432C-8384-9B8CCED70813}"/>
+              <c16:uniqueId val="{00000000-86E7-4395-826B-1310EB1B4BE1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$412</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,93</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$412:$G$412</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97040124302407327</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.24509363334584758</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-86E7-4395-826B-1310EB1B4BE1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$413</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,97</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$413:$G$413</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.85740560595251925</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.20244584155725229</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.60234739389415504</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-86E7-4395-826B-1310EB1B4BE1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$414</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$414:$G$414</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.91790681578047295</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.84158694771293341</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-86E7-4395-826B-1310EB1B4BE1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6215,7 +3645,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -6252,7 +3682,1686 @@
               <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
                 <a:effectLst/>
               </a:rPr>
-              <a:t>24</a:t>
+              <a:t>19</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Only best'!$C$117</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Only best'!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Only best'!$D$117:$G$117</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75686804000192376</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.49718479540475113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E119-4F7D-B89E-F819E8ECCAD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>20</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Only best'!$C$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Only best'!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Only best'!$D$141:$G$141</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.56379755979405544</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.50828225173152997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.37838843465697375</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-68F3-4B0A-B88E-EC4A9DBDFF90}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>16</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Only best'!$C$93</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Only best'!$D$89:$G$89</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Only best'!$D$93:$G$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.89882061387652312</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17795127025264079</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D314-45B4-BD24-0B2701E5CBD7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>21</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Only best'!$C$165</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Only best'!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Only best'!$D$165:$G$165</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69842143423119296</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.27079088952453417</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E519-421F-A0F7-0AEAB9BB9168}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>22</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Only best'!$C$190</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Only best'!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Only best'!$D$190:$G$190</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.84040363200323998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22466253890066659</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-23CF-42C1-BD41-4881695A0362}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>20</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -6299,11 +5408,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Only best'!$C$240</c:f>
+              <c:f>Original!$C$138</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1,00</c:v>
+                  <c:v>0,80</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6311,7 +5420,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6322,7 +5431,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Only best'!$D$113:$G$113</c:f>
+              <c:f>Original!$D$113:$G$113</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -6342,7 +5451,153 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Only best'!$D$240:$G$240</c:f>
+              <c:f>Original!$D$138:$G$138</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75473497922288912</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13016270721820974</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.20562583073637467</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3263-4778-9FE4-27A25304FFCB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$139</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,82</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$139:$G$139</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.8380185016176708E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.12267657460088674</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3263-4778-9FE4-27A25304FFCB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$140</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,86</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$140:$G$140</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -6350,20 +5605,93 @@
                   <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.62244477507294493</c:v>
+                  <c:v>0.6990904820453</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.83919206923346823</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.50155358560624896</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FA98-4046-A9AA-F13CCC4AF512}"/>
+              <c16:uniqueId val="{00000002-3263-4778-9FE4-27A25304FFCB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Original!$C$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Original!$D$141:$G$141</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.56379755979405544</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.50828225173152997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.37838843465697375</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3263-4778-9FE4-27A25304FFCB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6553,6 +5881,678 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>23</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Only best'!$C$215</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Only best'!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Only best'!$D$215:$G$215</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.57664977093076919</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.77853736812744556</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6D9C-432C-8384-9B8CCED70813}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>24</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Only best'!$C$240</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Only best'!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Only best'!$D$240:$G$240</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.62244477507294493</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.83919206923346823</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.50155358560624896</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FA98-4046-A9AA-F13CCC4AF512}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -6596,7 +6596,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6827,7 +6826,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6934,7 +6932,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7165,7 +7162,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7272,7 +7268,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7503,7 +7498,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7610,7 +7604,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7841,7 +7834,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7948,7 +7940,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8179,7 +8170,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8286,7 +8276,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8517,7 +8506,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8624,7 +8612,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8855,7 +8842,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9372,6 +9358,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9821,6 +9808,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14036,6 +14024,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14485,6 +14474,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -15824,6 +15814,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -16273,6 +16264,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -16379,6 +16371,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -16828,6 +16821,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -16934,6 +16928,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -17383,6 +17378,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -17489,6 +17485,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -17938,6 +17935,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -18044,6 +18042,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -18493,6 +18492,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>

--- a/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Original" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="Best|Worst" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Best|Worst'!$C$310:$G$314</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Best|Worst'!$C$305:$G$309</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Only best'!$C$310:$G$314</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Original!$C$310:$G$314</definedName>
   </definedNames>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="46">
   <si>
     <t>sector</t>
   </si>
@@ -158,6 +158,12 @@
   </si>
   <si>
     <t>Year</t>
+  </si>
+  <si>
+    <t>best</t>
+  </si>
+  <si>
+    <t>worst</t>
   </si>
 </sst>
 </file>
@@ -346,7 +352,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -796,7 +801,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -903,7 +907,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1353,7 +1356,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1460,7 +1462,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1910,7 +1911,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2017,7 +2017,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2467,7 +2466,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2574,7 +2572,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3024,7 +3021,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3131,7 +3127,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3581,7 +3576,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5367,7 +5361,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5817,7 +5810,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9358,7 +9350,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9808,7 +9799,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11188,7 +11178,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$187</c:f>
+              <c:f>'Best|Worst'!$C$186</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11231,7 +11221,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$187:$G$187</c:f>
+              <c:f>'Best|Worst'!$D$186:$G$186</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -11261,7 +11251,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$190</c:f>
+              <c:f>'Best|Worst'!$C$189</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11304,7 +11294,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$190:$G$190</c:f>
+              <c:f>'Best|Worst'!$D$189:$G$189</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -11599,7 +11589,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$212</c:f>
+              <c:f>'Best|Worst'!$C$210</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11642,7 +11632,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$212:$G$212</c:f>
+              <c:f>'Best|Worst'!$D$210:$G$210</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -11672,7 +11662,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$215</c:f>
+              <c:f>'Best|Worst'!$C$213</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -11715,7 +11705,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$215:$G$215</c:f>
+              <c:f>'Best|Worst'!$D$213:$G$213</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -12010,7 +12000,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$237</c:f>
+              <c:f>'Best|Worst'!$C$234</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12053,7 +12043,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$237:$G$237</c:f>
+              <c:f>'Best|Worst'!$D$234:$G$234</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -12083,7 +12073,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$240</c:f>
+              <c:f>'Best|Worst'!$C$237</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12126,7 +12116,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$240:$G$240</c:f>
+              <c:f>'Best|Worst'!$D$237:$G$237</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -12421,7 +12411,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$262</c:f>
+              <c:f>'Best|Worst'!$C$258</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12464,7 +12454,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$262:$G$262</c:f>
+              <c:f>'Best|Worst'!$D$258:$G$258</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -12494,7 +12484,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$265</c:f>
+              <c:f>'Best|Worst'!$C$261</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12537,7 +12527,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$265:$G$265</c:f>
+              <c:f>'Best|Worst'!$D$261:$G$261</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -12832,7 +12822,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$287</c:f>
+              <c:f>'Best|Worst'!$C$282</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12875,7 +12865,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$287:$G$287</c:f>
+              <c:f>'Best|Worst'!$D$282:$G$282</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -12905,7 +12895,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$290</c:f>
+              <c:f>'Best|Worst'!$C$285</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12948,7 +12938,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$290:$G$290</c:f>
+              <c:f>'Best|Worst'!$D$285:$G$285</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -13243,7 +13233,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$311</c:f>
+              <c:f>'Best|Worst'!$C$306</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13286,7 +13276,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$311:$G$311</c:f>
+              <c:f>'Best|Worst'!$D$306:$G$306</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -13316,7 +13306,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$314</c:f>
+              <c:f>'Best|Worst'!$C$309</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13359,7 +13349,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$314:$G$314</c:f>
+              <c:f>'Best|Worst'!$D$309:$G$309</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -13654,7 +13644,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$336</c:f>
+              <c:f>'Best|Worst'!$C$330</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13697,7 +13687,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$336:$G$336</c:f>
+              <c:f>'Best|Worst'!$D$330:$G$330</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -13727,7 +13717,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$339</c:f>
+              <c:f>'Best|Worst'!$C$333</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13770,7 +13760,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$339:$G$339</c:f>
+              <c:f>'Best|Worst'!$D$333:$G$333</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -14024,7 +14014,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14474,7 +14463,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14622,7 +14610,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$361</c:f>
+              <c:f>'Best|Worst'!$C$354</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14665,7 +14653,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$361:$G$361</c:f>
+              <c:f>'Best|Worst'!$D$354:$G$354</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -14695,7 +14683,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$364</c:f>
+              <c:f>'Best|Worst'!$C$357</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -14738,7 +14726,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$364:$G$364</c:f>
+              <c:f>'Best|Worst'!$D$357:$G$357</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -15033,7 +15021,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$386</c:f>
+              <c:f>'Best|Worst'!$C$378</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15076,7 +15064,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$386:$G$386</c:f>
+              <c:f>'Best|Worst'!$D$378:$G$378</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -15106,7 +15094,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$389</c:f>
+              <c:f>'Best|Worst'!$C$381</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15149,7 +15137,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$389:$G$389</c:f>
+              <c:f>'Best|Worst'!$D$381:$G$381</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -15444,7 +15432,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$411</c:f>
+              <c:f>'Best|Worst'!$C$402</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15487,7 +15475,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$411:$G$411</c:f>
+              <c:f>'Best|Worst'!$D$402:$G$402</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -15517,7 +15505,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Best|Worst'!$C$414</c:f>
+              <c:f>'Best|Worst'!$C$405</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -15560,7 +15548,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Best|Worst'!$D$414:$G$414</c:f>
+              <c:f>'Best|Worst'!$D$405:$G$405</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -15814,7 +15802,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -16264,7 +16251,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -16371,7 +16357,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -16821,7 +16806,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -16928,7 +16912,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -17378,7 +17361,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -17485,7 +17467,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -17935,7 +17916,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -18042,7 +18022,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -18492,7 +18471,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -59941,7 +59919,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G415"/>
+  <dimension ref="A1:L421"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.42578125" customWidth="1"/>
@@ -61889,7 +61867,7 @@
         <v>2.339677504868966E-4</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>13</v>
       </c>
@@ -61912,7 +61890,7 @@
         <v>2.6914455891389468E-4</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>13</v>
       </c>
@@ -61935,7 +61913,7 @@
         <v>3.2594779133939081E-4</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>13</v>
       </c>
@@ -61958,7 +61936,7 @@
         <v>4.7058508757579111E-4</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B101" s="7" t="s">
         <v>40</v>
       </c>
@@ -61979,7 +61957,7 @@
         <v>2.5155615470039562E-4</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B102" s="7" t="s">
         <v>41</v>
       </c>
@@ -62000,7 +61978,7 @@
         <v>3.9826643945759096E-4</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C104" s="7" t="s">
         <v>42</v>
       </c>
@@ -62021,7 +61999,7 @@
         <v>0.63162779932699387</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C106" s="2">
         <f>MAX(C96:C99)</f>
         <v>4</v>
@@ -62043,7 +62021,7 @@
         <v>4.7058508757579111E-4</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C107" s="10" t="s">
         <v>43</v>
       </c>
@@ -62059,8 +62037,15 @@
       <c r="G107" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J107" s="2"/>
+      <c r="K107" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L107" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C108" s="2">
         <v>2022</v>
       </c>
@@ -62080,8 +62065,19 @@
         <f t="shared" si="13"/>
         <v>0.49718479540475113</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J108" s="10">
+        <v>16</v>
+      </c>
+      <c r="K108" s="3">
+        <f>0.5*(D93*E93+E93*F93+F93*G93+G93*D93)</f>
+        <v>0.4063013468451786</v>
+      </c>
+      <c r="L108" s="3">
+        <f>0.5*(D90*E90+E90*F90+F90*G90+G90*D90)</f>
+        <v>1.1322633571769671</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C109" s="2">
         <v>2021</v>
       </c>
@@ -62101,8 +62097,17 @@
         <f t="shared" si="14"/>
         <v>0.57193601331565147</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J109" s="10">
+        <v>19</v>
+      </c>
+      <c r="K109" s="3">
+        <v>0.94053962655500623</v>
+      </c>
+      <c r="L109" s="3">
+        <v>0.99570716952284077</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C110" s="2">
         <v>2023</v>
       </c>
@@ -62122,8 +62127,17 @@
         <f t="shared" si="14"/>
         <v>0.69264368962158107</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J110" s="10">
+        <v>20</v>
+      </c>
+      <c r="K110" s="3">
+        <v>0.47499470801749727</v>
+      </c>
+      <c r="L110" s="3">
+        <v>0.42263688520000919</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C111" s="2">
         <v>2024</v>
       </c>
@@ -62143,8 +62157,28 @@
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J111" s="10">
+        <v>21</v>
+      </c>
+      <c r="K111" s="3">
+        <v>0.60262265902539602</v>
+      </c>
+      <c r="L111" s="3">
+        <v>0.52746402399944881</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J112" s="10">
+        <v>22</v>
+      </c>
+      <c r="K112" s="3">
+        <v>0.79879962817792993</v>
+      </c>
+      <c r="L112" s="3">
+        <v>0.65129526918017067</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C113" s="10" t="s">
         <v>3</v>
       </c>
@@ -62160,8 +62194,17 @@
       <c r="G113" s="10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J113" s="10">
+        <v>23</v>
+      </c>
+      <c r="K113" s="3">
+        <v>1.4020652670249751</v>
+      </c>
+      <c r="L113" s="3">
+        <v>1.0995183126440389</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C114" s="3">
         <v>0.6426972022607591</v>
       </c>
@@ -62177,8 +62220,17 @@
       <c r="G114" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J114" s="10">
+        <v>24</v>
+      </c>
+      <c r="K114" s="3">
+        <v>0.61212505014159868</v>
+      </c>
+      <c r="L114" s="3">
+        <v>1.0083484287788067</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C115" s="3">
         <v>0.87753306878617643</v>
       </c>
@@ -62194,8 +62246,17 @@
       <c r="G115" s="2">
         <v>0.69264368962158107</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J115" s="10">
+        <v>25</v>
+      </c>
+      <c r="K115" s="3">
+        <v>1.3033063797642059</v>
+      </c>
+      <c r="L115" s="3">
+        <v>0.17445159599518406</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C116" s="3">
         <v>0.95490771245443773</v>
       </c>
@@ -62211,8 +62272,17 @@
       <c r="G116" s="2">
         <v>0.57193601331565147</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J116" s="10">
+        <v>26</v>
+      </c>
+      <c r="K116" s="3">
+        <v>0.40274335862744398</v>
+      </c>
+      <c r="L116" s="3">
+        <v>9.3891127559008247E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C117" s="3">
         <v>1</v>
       </c>
@@ -62228,8 +62298,28 @@
       <c r="G117" s="2">
         <v>0.49718479540475113</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J117" s="10">
+        <v>27</v>
+      </c>
+      <c r="K117" s="3">
+        <v>0.46437907105783394</v>
+      </c>
+      <c r="L117" s="3">
+        <v>0.18913531858780386</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J118" s="10">
+        <v>28</v>
+      </c>
+      <c r="K118" s="3">
+        <v>1.0663153616956014</v>
+      </c>
+      <c r="L118" s="3">
+        <v>0.24899552858732954</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>0</v>
       </c>
@@ -62251,8 +62341,17 @@
       <c r="G119" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J119" s="10">
+        <v>29</v>
+      </c>
+      <c r="K119" s="3">
+        <v>0.58245092784424224</v>
+      </c>
+      <c r="L119" s="3">
+        <v>0.53523769373150953</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>15</v>
       </c>
@@ -62274,8 +62373,17 @@
       <c r="G120" s="4">
         <v>2.722411311338672E-3</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J120" s="10">
+        <v>30</v>
+      </c>
+      <c r="K120" s="3">
+        <v>1.404116948256124</v>
+      </c>
+      <c r="L120" s="3">
+        <v>0.77941261353384506</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>15</v>
       </c>
@@ -62297,8 +62405,17 @@
       <c r="G121" s="4">
         <v>7.1947529628030547E-3</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J121" s="10">
+        <v>33</v>
+      </c>
+      <c r="K121" s="3">
+        <v>1.046781023517819</v>
+      </c>
+      <c r="L121" s="3">
+        <v>1.1137714394813514</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>15</v>
       </c>
@@ -62320,8 +62437,11 @@
       <c r="G122" s="4">
         <v>8.8262764857625984E-4</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J122" s="10"/>
+      <c r="K122" s="3"/>
+      <c r="L122" s="3"/>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>15</v>
       </c>
@@ -62344,7 +62464,7 @@
         <v>1.4794270549193711E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B125" s="7" t="s">
         <v>40</v>
       </c>
@@ -62365,7 +62485,7 @@
         <v>4.9585821370708629E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B126" s="7" t="s">
         <v>41</v>
       </c>
@@ -62386,7 +62506,7 @@
         <v>1.1810273517478154E-3</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C128" s="7" t="s">
         <v>42</v>
       </c>
@@ -62407,7 +62527,7 @@
         <v>4.1985328533946333</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C130" s="2">
         <f>MAX(C120:C123)</f>
         <v>4</v>
@@ -62429,7 +62549,7 @@
         <v>7.1947529628030547E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C131" s="10" t="s">
         <v>43</v>
       </c>
@@ -62445,8 +62565,15 @@
       <c r="G131" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J131" s="2"/>
+      <c r="K131" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L131" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C132" s="2">
         <f>C120/C$82</f>
         <v>0.5</v>
@@ -62467,8 +62594,19 @@
         <f t="shared" si="19"/>
         <v>0.37838843465697375</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J132" s="10">
+        <v>19</v>
+      </c>
+      <c r="K132" s="3">
+        <f>0.5*(D117*E117+E117*F117+F117*G117+G117*D117)</f>
+        <v>0.94053962655500623</v>
+      </c>
+      <c r="L132" s="3">
+        <f>0.5*(D114*E114+E114*F114+F114*G114+G114*D114)</f>
+        <v>0.99570716952284077</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C133" s="2">
         <f t="shared" ref="C133:C135" si="20">C121/C$82</f>
         <v>0.25</v>
@@ -62490,7 +62628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C134" s="2">
         <f t="shared" si="20"/>
         <v>1</v>
@@ -62512,7 +62650,7 @@
         <v>0.12267657460088674</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C135" s="2">
         <f t="shared" si="20"/>
         <v>0.75</v>
@@ -62534,7 +62672,7 @@
         <v>0.20562583073637467</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C137" s="10" t="s">
         <v>3</v>
       </c>
@@ -62551,7 +62689,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C138" s="3">
         <v>0.80140650744605846</v>
       </c>
@@ -62568,7 +62706,7 @@
         <v>0.20562583073637467</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C139" s="3">
         <v>0.82288041230138287</v>
       </c>
@@ -62585,7 +62723,7 @@
         <v>0.12267657460088674</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C140" s="3">
         <v>0.86024421473341717</v>
       </c>
@@ -62602,7 +62740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C141" s="3">
         <v>1</v>
       </c>
@@ -62619,7 +62757,7 @@
         <v>0.37838843465697375</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>0</v>
       </c>
@@ -62642,7 +62780,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>17</v>
       </c>
@@ -62665,7 +62803,7 @@
         <v>4.0538663342816288E-4</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>17</v>
       </c>
@@ -62688,7 +62826,7 @@
         <v>3.3407912051630981E-4</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>17</v>
       </c>
@@ -62711,7 +62849,7 @@
         <v>1.4970467955548929E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>17</v>
       </c>
@@ -62734,7 +62872,7 @@
         <v>1.35821810761219E-3</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B149" s="7" t="s">
         <v>40</v>
       </c>
@@ -62755,7 +62893,7 @@
         <v>3.6973287697223637E-4</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B150" s="7" t="s">
         <v>41</v>
       </c>
@@ -62776,7 +62914,7 @@
         <v>1.4276324515835415E-3</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C152" s="7" t="s">
         <v>42</v>
       </c>
@@ -62797,7 +62935,7 @@
         <v>0.25898323939199175</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C154" s="2">
         <f>MAX(C144:C147)</f>
         <v>4</v>
@@ -62819,7 +62957,7 @@
         <v>1.4970467955548929E-3</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C155" s="10" t="s">
         <v>43</v>
       </c>
@@ -62835,8 +62973,15 @@
       <c r="G155" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J155" s="2"/>
+      <c r="K155" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L155" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C156" s="2">
         <f>C144/C$154</f>
         <v>0.25</v>
@@ -62857,8 +63002,19 @@
         <f t="shared" si="26"/>
         <v>0.27079088952453417</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J156" s="10">
+        <v>20</v>
+      </c>
+      <c r="K156" s="3">
+        <f>0.5*(D141*E141+E141*F141+F141*G141+G141*D141)</f>
+        <v>0.47499470801749727</v>
+      </c>
+      <c r="L156" s="3">
+        <f>0.5*(D138*E138+E138*F138+F138*G138+G138*D138)</f>
+        <v>0.42263688520000919</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C157" s="2">
         <f t="shared" ref="C157:G159" si="27">C145/C$154</f>
         <v>0.5</v>
@@ -62880,7 +63036,7 @@
         <v>0.2231587693238945</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C158" s="2">
         <f t="shared" si="27"/>
         <v>1</v>
@@ -62902,7 +63058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C159" s="2">
         <f t="shared" si="27"/>
         <v>0.75</v>
@@ -63009,27 +63165,50 @@
         <v>0.27079088952453417</v>
       </c>
     </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A168" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C168" s="1" t="s">
+      <c r="A168" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C168" s="2">
         <v>2</v>
       </c>
-      <c r="D168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>6</v>
+      <c r="D168" s="3">
+        <v>327266.01547195681</v>
+      </c>
+      <c r="E168" s="3">
+        <v>2736.7203125999999</v>
+      </c>
+      <c r="F168" s="4">
+        <v>6.5575458761258591E-4</v>
+      </c>
+      <c r="G168" s="4">
+        <v>9.6186040198574876E-4</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -63040,19 +63219,19 @@
         <v>20</v>
       </c>
       <c r="C169" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D169" s="3">
-        <v>327266.01547195681</v>
+        <v>323997.44760210218</v>
       </c>
       <c r="E169" s="3">
-        <v>2736.7203125999999</v>
+        <v>2594.2840083999999</v>
       </c>
       <c r="F169" s="4">
-        <v>6.5575458761258591E-4</v>
+        <v>4.4144095106468531E-4</v>
       </c>
       <c r="G169" s="4">
-        <v>9.6186040198574876E-4</v>
+        <v>4.2813564143465432E-3</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -63063,19 +63242,19 @@
         <v>20</v>
       </c>
       <c r="C170" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D170" s="3">
-        <v>323997.44760210218</v>
+        <v>321762.90970591619</v>
       </c>
       <c r="E170" s="3">
-        <v>2594.2840083999999</v>
+        <v>2793.945984</v>
       </c>
       <c r="F170" s="4">
-        <v>4.4144095106468531E-4</v>
+        <v>3.0877619142976242E-4</v>
       </c>
       <c r="G170" s="4">
-        <v>4.2813564143465432E-3</v>
+        <v>1.0062327675981299E-3</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -63086,343 +63265,390 @@
         <v>20</v>
       </c>
       <c r="C171" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D171" s="3">
-        <v>321762.90970591619</v>
+        <v>297602.00445720641</v>
       </c>
       <c r="E171" s="3">
-        <v>2793.945984</v>
+        <v>3256.4356082999998</v>
       </c>
       <c r="F171" s="4">
-        <v>3.0877619142976242E-4</v>
+        <v>3.8592436982227681E-4</v>
       </c>
       <c r="G171" s="4">
-        <v>1.0062327675981299E-3</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A172" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B172" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C172" s="2">
-        <v>1</v>
-      </c>
-      <c r="D172" s="3">
-        <v>297602.00445720641</v>
-      </c>
-      <c r="E172" s="3">
-        <v>3256.4356082999998</v>
-      </c>
-      <c r="F172" s="4">
-        <v>3.8592436982227681E-4</v>
-      </c>
-      <c r="G172" s="4">
         <v>2.369477916386043E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B173" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D173" s="3">
+        <f>AVERAGE(D168:D169)</f>
+        <v>325631.7315370295</v>
+      </c>
+      <c r="E173" s="3">
+        <f t="shared" ref="E173:G173" si="28">AVERAGE(E168:E169)</f>
+        <v>2665.5021605000002</v>
+      </c>
+      <c r="F173" s="4">
+        <f t="shared" si="28"/>
+        <v>5.4859776933863561E-4</v>
+      </c>
+      <c r="G173" s="4">
+        <f t="shared" si="28"/>
+        <v>2.6216084081661459E-3</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B174" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D174" s="3">
-        <f>AVERAGE(D169:D170)</f>
-        <v>325631.7315370295</v>
+        <f>AVERAGE(D170:D171)</f>
+        <v>309682.45708156133</v>
       </c>
       <c r="E174" s="3">
-        <f t="shared" ref="E174:G174" si="28">AVERAGE(E169:E170)</f>
-        <v>2665.5021605000002</v>
+        <f t="shared" ref="E174:G174" si="29">AVERAGE(E170:E171)</f>
+        <v>3025.1907961500001</v>
       </c>
       <c r="F174" s="4">
-        <f t="shared" si="28"/>
-        <v>5.4859776933863561E-4</v>
-      </c>
-      <c r="G174" s="4">
-        <f t="shared" si="28"/>
-        <v>2.6216084081661459E-3</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B175" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D175" s="3">
-        <f>AVERAGE(D171:D172)</f>
-        <v>309682.45708156133</v>
-      </c>
-      <c r="E175" s="3">
-        <f t="shared" ref="E175:G175" si="29">AVERAGE(E171:E172)</f>
-        <v>3025.1907961500001</v>
-      </c>
-      <c r="F175" s="4">
         <f t="shared" si="29"/>
         <v>3.4735028062601961E-4</v>
       </c>
-      <c r="G175" s="4">
+      <c r="G174" s="4">
         <f t="shared" si="29"/>
         <v>1.6878553419920864E-3</v>
       </c>
     </row>
-    <row r="177" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C177" s="7" t="s">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C176" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D177" s="3">
-        <f>D174/D175</f>
+      <c r="D176" s="3">
+        <f>D173/D174</f>
         <v>1.0515020276116822</v>
       </c>
-      <c r="E177" s="3">
-        <f t="shared" ref="E177:G177" si="30">E174/E175</f>
+      <c r="E176" s="3">
+        <f t="shared" ref="E176:G176" si="30">E173/E174</f>
         <v>0.88110216515673767</v>
       </c>
-      <c r="F177" s="3">
+      <c r="F176" s="3">
         <f t="shared" si="30"/>
         <v>1.5793790877321685</v>
       </c>
-      <c r="G177" s="3">
+      <c r="G176" s="3">
         <f t="shared" si="30"/>
         <v>1.5532186573951297</v>
       </c>
     </row>
-    <row r="179" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C179" s="2">
-        <f>MAX(C169:C172)</f>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C178" s="2">
+        <f>MAX(C168:C171)</f>
         <v>4</v>
       </c>
-      <c r="D179" s="2">
-        <f t="shared" ref="D179:G179" si="31">MAX(D169:D172)</f>
+      <c r="D178" s="2">
+        <f t="shared" ref="D178:G178" si="31">MAX(D168:D171)</f>
         <v>327266.01547195681</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E178" s="2">
         <f t="shared" si="31"/>
         <v>3256.4356082999998</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F178" s="2">
         <f t="shared" si="31"/>
         <v>6.5575458761258591E-4</v>
       </c>
-      <c r="G179" s="2">
+      <c r="G178" s="2">
         <f t="shared" si="31"/>
         <v>4.2813564143465432E-3</v>
       </c>
     </row>
-    <row r="180" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C180" s="10" t="s">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C179" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D180" s="10" t="s">
+      <c r="D179" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E180" s="1" t="s">
+      <c r="E179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F180" s="1" t="s">
+      <c r="F179" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G180" s="1" t="s">
+      <c r="G179" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="181" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="J179" s="2"/>
+      <c r="K179" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L179" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C180" s="2">
+        <f>C168/C$178</f>
+        <v>0.5</v>
+      </c>
+      <c r="D180" s="2">
+        <f>D168/D$178</f>
+        <v>1</v>
+      </c>
+      <c r="E180" s="2">
+        <f>E168/E$178</f>
+        <v>0.84040363200323998</v>
+      </c>
+      <c r="F180" s="2">
+        <f>F168/F$178</f>
+        <v>1</v>
+      </c>
+      <c r="G180" s="2">
+        <f>G168/G$178</f>
+        <v>0.22466253890066659</v>
+      </c>
+      <c r="J180" s="10">
+        <v>21</v>
+      </c>
+      <c r="K180" s="3">
+        <f>0.5*(D165*E165+E165*F165+F165*G165+G165*D165)</f>
+        <v>0.60262265902539602</v>
+      </c>
+      <c r="L180" s="3">
+        <f>0.5*(D162*E162+E162*F162+F162*G162+G162*D162)</f>
+        <v>0.52746402399944881</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C181" s="2">
-        <f t="shared" ref="C181:G184" si="32">C169/C$179</f>
+        <f>C169/C$178</f>
+        <v>0.75</v>
+      </c>
+      <c r="D181" s="2">
+        <f>D169/D$178</f>
+        <v>0.99001250446019895</v>
+      </c>
+      <c r="E181" s="2">
+        <f>E169/E$178</f>
+        <v>0.796663690136446</v>
+      </c>
+      <c r="F181" s="2">
+        <f>F169/F$178</f>
+        <v>0.67318011860480464</v>
+      </c>
+      <c r="G181" s="2">
+        <f>G169/G$178</f>
+        <v>1</v>
+      </c>
+      <c r="J181" s="2"/>
+      <c r="K181" s="10"/>
+      <c r="L181" s="10"/>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C182" s="2">
+        <f>C170/C$178</f>
+        <v>1</v>
+      </c>
+      <c r="D182" s="2">
+        <f>D170/D$178</f>
+        <v>0.98318460974903099</v>
+      </c>
+      <c r="E182" s="2">
+        <f>E170/E$178</f>
+        <v>0.85797673286669429</v>
+      </c>
+      <c r="F182" s="2">
+        <f>F170/F$178</f>
+        <v>0.47087156881956077</v>
+      </c>
+      <c r="G182" s="2">
+        <f>G170/G$178</f>
+        <v>0.23502662946404326</v>
+      </c>
+      <c r="J182" s="10"/>
+      <c r="K182" s="3"/>
+      <c r="L182" s="3"/>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C183" s="2">
+        <f>C171/C$178</f>
+        <v>0.25</v>
+      </c>
+      <c r="D183" s="2">
+        <f>D171/D$178</f>
+        <v>0.90935810743449375</v>
+      </c>
+      <c r="E183" s="2">
+        <f>E171/E$178</f>
+        <v>1</v>
+      </c>
+      <c r="F183" s="2">
+        <f>F171/F$178</f>
+        <v>0.58851951189135643</v>
+      </c>
+      <c r="G183" s="2">
+        <f>G171/G$178</f>
+        <v>0.55344093952236229</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C185" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E185" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F185" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G185" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C186" s="3">
+        <v>0.90935810743449375</v>
+      </c>
+      <c r="D186" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E186" s="2">
+        <v>1</v>
+      </c>
+      <c r="F186" s="2">
+        <v>0.58851951189135643</v>
+      </c>
+      <c r="G186" s="2">
+        <v>0.55344093952236229</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C187" s="3">
+        <v>0.98318460974903099</v>
+      </c>
+      <c r="D187" s="2">
+        <v>1</v>
+      </c>
+      <c r="E187" s="2">
+        <v>0.85797673286669429</v>
+      </c>
+      <c r="F187" s="2">
+        <v>0.47087156881956077</v>
+      </c>
+      <c r="G187" s="2">
+        <v>0.23502662946404326</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C188" s="3">
+        <v>0.99001250446019895</v>
+      </c>
+      <c r="D188" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E188" s="2">
+        <v>0.796663690136446</v>
+      </c>
+      <c r="F188" s="2">
+        <v>0.67318011860480464</v>
+      </c>
+      <c r="G188" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C189" s="3">
+        <v>1</v>
+      </c>
+      <c r="D189" s="2">
         <v>0.5</v>
       </c>
-      <c r="D181" s="2">
-        <f t="shared" si="32"/>
+      <c r="E189" s="2">
+        <v>0.84040363200323998</v>
+      </c>
+      <c r="F189" s="2">
         <v>1</v>
       </c>
-      <c r="E181" s="2">
-        <f t="shared" si="32"/>
-        <v>0.84040363200323998</v>
-      </c>
-      <c r="F181" s="2">
-        <f t="shared" si="32"/>
+      <c r="G189" s="2">
+        <v>0.22466253890066659</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G181" s="2">
-        <f t="shared" si="32"/>
-        <v>0.22466253890066659</v>
-      </c>
-    </row>
-    <row r="182" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C182" s="2">
-        <f t="shared" si="32"/>
-        <v>0.75</v>
-      </c>
-      <c r="D182" s="2">
-        <f t="shared" si="32"/>
-        <v>0.99001250446019895</v>
-      </c>
-      <c r="E182" s="2">
-        <f t="shared" si="32"/>
-        <v>0.796663690136446</v>
-      </c>
-      <c r="F182" s="2">
-        <f t="shared" si="32"/>
-        <v>0.67318011860480464</v>
-      </c>
-      <c r="G182" s="2">
-        <f t="shared" si="32"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C183" s="2">
-        <f t="shared" si="32"/>
-        <v>1</v>
-      </c>
-      <c r="D183" s="2">
-        <f t="shared" si="32"/>
-        <v>0.98318460974903099</v>
-      </c>
-      <c r="E183" s="2">
-        <f t="shared" si="32"/>
-        <v>0.85797673286669429</v>
-      </c>
-      <c r="F183" s="2">
-        <f t="shared" si="32"/>
-        <v>0.47087156881956077</v>
-      </c>
-      <c r="G183" s="2">
-        <f t="shared" si="32"/>
-        <v>0.23502662946404326</v>
-      </c>
-    </row>
-    <row r="184" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C184" s="2">
-        <f t="shared" si="32"/>
-        <v>0.25</v>
-      </c>
-      <c r="D184" s="2">
-        <f t="shared" si="32"/>
-        <v>0.90935810743449375</v>
-      </c>
-      <c r="E184" s="2">
-        <f t="shared" si="32"/>
-        <v>1</v>
-      </c>
-      <c r="F184" s="2">
-        <f t="shared" si="32"/>
-        <v>0.58851951189135643</v>
-      </c>
-      <c r="G184" s="2">
-        <f t="shared" si="32"/>
-        <v>0.55344093952236229</v>
-      </c>
-    </row>
-    <row r="186" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C186" s="10" t="s">
+      <c r="C191" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D186" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E186" s="10" t="s">
+      <c r="E191" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F186" s="10" t="s">
+      <c r="F191" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G186" s="10" t="s">
+      <c r="G191" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="187" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C187" s="3">
-        <v>0.90935810743449375</v>
-      </c>
-      <c r="D187" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E187" s="2">
-        <v>1</v>
-      </c>
-      <c r="F187" s="2">
-        <v>0.58851951189135643</v>
-      </c>
-      <c r="G187" s="2">
-        <v>0.55344093952236229</v>
-      </c>
-    </row>
-    <row r="188" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C188" s="3">
-        <v>0.98318460974903099</v>
-      </c>
-      <c r="D188" s="2">
-        <v>1</v>
-      </c>
-      <c r="E188" s="2">
-        <v>0.85797673286669429</v>
-      </c>
-      <c r="F188" s="2">
-        <v>0.47087156881956077</v>
-      </c>
-      <c r="G188" s="2">
-        <v>0.23502662946404326</v>
-      </c>
-    </row>
-    <row r="189" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C189" s="3">
-        <v>0.99001250446019895</v>
-      </c>
-      <c r="D189" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E189" s="2">
-        <v>0.796663690136446</v>
-      </c>
-      <c r="F189" s="2">
-        <v>0.67318011860480464</v>
-      </c>
-      <c r="G189" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C190" s="3">
-        <v>1</v>
-      </c>
-      <c r="D190" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E190" s="2">
-        <v>0.84040363200323998</v>
-      </c>
-      <c r="F190" s="2">
-        <v>1</v>
-      </c>
-      <c r="G190" s="2">
-        <v>0.22466253890066659</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A193" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C193" s="1" t="s">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B192" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C192" s="2">
+        <v>4</v>
+      </c>
+      <c r="D192" s="3">
+        <v>589836.07301855378</v>
+      </c>
+      <c r="E192" s="3">
+        <v>3459.2387039999999</v>
+      </c>
+      <c r="F192" s="4">
+        <v>2.6129124854981389E-3</v>
+      </c>
+      <c r="G192" s="4">
+        <v>2.2962786554205951E-3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C193" s="2">
         <v>2</v>
       </c>
-      <c r="D193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D193" s="3">
+        <v>585427.26654459862</v>
+      </c>
+      <c r="E193" s="3">
+        <v>4854.6591208600003</v>
+      </c>
+      <c r="F193" s="4">
+        <v>3.7612999688359748E-4</v>
+      </c>
+      <c r="G193" s="4">
+        <v>2.0756040556386131E-3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>21</v>
       </c>
@@ -63430,22 +63656,22 @@
         <v>22</v>
       </c>
       <c r="C194" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D194" s="3">
-        <v>589836.07301855378</v>
+        <v>575669.32501484314</v>
       </c>
       <c r="E194" s="3">
-        <v>3459.2387039999999</v>
+        <v>4774.9529707199999</v>
       </c>
       <c r="F194" s="4">
-        <v>2.6129124854981389E-3</v>
+        <v>2.8738600116371028E-4</v>
       </c>
       <c r="G194" s="4">
-        <v>2.2962786554205951E-3</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1.316480132589062E-3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>21</v>
       </c>
@@ -63453,363 +63679,404 @@
         <v>22</v>
       </c>
       <c r="C195" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D195" s="3">
-        <v>585427.26654459862</v>
+        <v>532258.74860418728</v>
       </c>
       <c r="E195" s="3">
-        <v>4854.6591208600003</v>
+        <v>5998.8555937799993</v>
       </c>
       <c r="F195" s="4">
-        <v>3.7612999688359748E-4</v>
+        <v>3.3561812091085249E-3</v>
       </c>
       <c r="G195" s="4">
-        <v>2.0756040556386131E-3</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A196" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B196" s="8" t="s">
+        <v>1.7434020366891251E-3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B197" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D197" s="3">
+        <f>AVERAGE(D192:D193)</f>
+        <v>587631.66978157614</v>
+      </c>
+      <c r="E197" s="3">
+        <f t="shared" ref="E197:G197" si="32">AVERAGE(E192:E193)</f>
+        <v>4156.9489124299998</v>
+      </c>
+      <c r="F197" s="4">
+        <f t="shared" si="32"/>
+        <v>1.4945212411908682E-3</v>
+      </c>
+      <c r="G197" s="4">
+        <f t="shared" si="32"/>
+        <v>2.1859413555296043E-3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B198" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D198" s="3">
+        <f>AVERAGE(D194:D195)</f>
+        <v>553964.03680951521</v>
+      </c>
+      <c r="E198" s="3">
+        <f t="shared" ref="E198:G198" si="33">AVERAGE(E194:E195)</f>
+        <v>5386.9042822499996</v>
+      </c>
+      <c r="F198" s="4">
+        <f t="shared" si="33"/>
+        <v>1.8217836051361176E-3</v>
+      </c>
+      <c r="G198" s="4">
+        <f t="shared" si="33"/>
+        <v>1.5299410846390934E-3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C200" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D200" s="3">
+        <f>D197/D198</f>
+        <v>1.0607758459664012</v>
+      </c>
+      <c r="E200" s="3">
+        <f t="shared" ref="E200:G200" si="34">E197/E198</f>
+        <v>0.77167677289668257</v>
+      </c>
+      <c r="F200" s="3">
+        <f t="shared" si="34"/>
+        <v>0.82036156049346076</v>
+      </c>
+      <c r="G200" s="3">
+        <f t="shared" si="34"/>
+        <v>1.4287748577228767</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C202" s="2">
+        <f>MAX(C192:C195)</f>
+        <v>4</v>
+      </c>
+      <c r="D202" s="2">
+        <f t="shared" ref="D202:G202" si="35">MAX(D192:D195)</f>
+        <v>589836.07301855378</v>
+      </c>
+      <c r="E202" s="2">
+        <f t="shared" si="35"/>
+        <v>5998.8555937799993</v>
+      </c>
+      <c r="F202" s="2">
+        <f t="shared" si="35"/>
+        <v>3.3561812091085249E-3</v>
+      </c>
+      <c r="G202" s="2">
+        <f t="shared" si="35"/>
+        <v>2.2962786554205951E-3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C203" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D203" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J203" s="2"/>
+      <c r="K203" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L203" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C204" s="2">
+        <f>C192/C$202</f>
+        <v>1</v>
+      </c>
+      <c r="D204" s="2">
+        <f>D192/D$202</f>
+        <v>1</v>
+      </c>
+      <c r="E204" s="2">
+        <f>E192/E$202</f>
+        <v>0.57664977093076919</v>
+      </c>
+      <c r="F204" s="2">
+        <f>F192/F$202</f>
+        <v>0.77853736812744556</v>
+      </c>
+      <c r="G204" s="2">
+        <f>G192/G$202</f>
+        <v>1</v>
+      </c>
+      <c r="J204" s="10">
         <v>22</v>
       </c>
-      <c r="C196" s="2">
+      <c r="K204" s="3">
+        <f>0.5*(D189*E189+E189*F189+F189*G189+G189*D189)</f>
+        <v>0.79879962817792993</v>
+      </c>
+      <c r="L204" s="3">
+        <f>0.5*(D186*E186+E186*F186+F186*G186+G186*D186)</f>
+        <v>0.65129526918017067</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C205" s="2">
+        <f>C193/C$202</f>
+        <v>0.5</v>
+      </c>
+      <c r="D205" s="2">
+        <f>D193/D$202</f>
+        <v>0.99252536988558093</v>
+      </c>
+      <c r="E205" s="2">
+        <f>E193/E$202</f>
+        <v>0.80926420797553855</v>
+      </c>
+      <c r="F205" s="2">
+        <f>F193/F$202</f>
+        <v>0.11207082497893665</v>
+      </c>
+      <c r="G205" s="2">
+        <f>G193/G$202</f>
+        <v>0.9038990327846067</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C206" s="2">
+        <f>C194/C$202</f>
+        <v>0.75</v>
+      </c>
+      <c r="D206" s="2">
+        <f>D194/D$202</f>
+        <v>0.97598188945750519</v>
+      </c>
+      <c r="E206" s="2">
+        <f>E194/E$202</f>
+        <v>0.79597731535177796</v>
+      </c>
+      <c r="F206" s="2">
+        <f>F194/F$202</f>
+        <v>8.5628869020468137E-2</v>
+      </c>
+      <c r="G206" s="2">
+        <f>G194/G$202</f>
+        <v>0.57331026854314004</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C207" s="2">
+        <f>C195/C$202</f>
+        <v>0.25</v>
+      </c>
+      <c r="D207" s="2">
+        <f>D195/D$202</f>
+        <v>0.90238419274747317</v>
+      </c>
+      <c r="E207" s="2">
+        <f>E195/E$202</f>
+        <v>1</v>
+      </c>
+      <c r="F207" s="2">
+        <f>F195/F$202</f>
+        <v>1</v>
+      </c>
+      <c r="G207" s="2">
+        <f>G195/G$202</f>
+        <v>0.7592293002304622</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C209" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D196" s="3">
-        <v>575669.32501484314</v>
-      </c>
-      <c r="E196" s="3">
-        <v>4774.9529707199999</v>
-      </c>
-      <c r="F196" s="4">
-        <v>2.8738600116371028E-4</v>
-      </c>
-      <c r="G196" s="4">
-        <v>1.316480132589062E-3</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A197" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B197" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C197" s="2">
+      <c r="D209" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E209" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F209" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G209" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C210" s="12">
+        <v>0.90238419274747317</v>
+      </c>
+      <c r="D210" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="E210" s="11">
         <v>1</v>
       </c>
-      <c r="D197" s="3">
-        <v>532258.74860418728</v>
-      </c>
-      <c r="E197" s="3">
-        <v>5998.8555937799993</v>
-      </c>
-      <c r="F197" s="4">
-        <v>3.3561812091085249E-3</v>
-      </c>
-      <c r="G197" s="4">
-        <v>1.7434020366891251E-3</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B199" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D199" s="3">
-        <f>AVERAGE(D194:D195)</f>
-        <v>587631.66978157614</v>
-      </c>
-      <c r="E199" s="3">
-        <f t="shared" ref="E199:G199" si="33">AVERAGE(E194:E195)</f>
-        <v>4156.9489124299998</v>
-      </c>
-      <c r="F199" s="4">
-        <f t="shared" si="33"/>
-        <v>1.4945212411908682E-3</v>
-      </c>
-      <c r="G199" s="4">
-        <f t="shared" si="33"/>
-        <v>2.1859413555296043E-3</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B200" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D200" s="3">
-        <f>AVERAGE(D196:D197)</f>
-        <v>553964.03680951521</v>
-      </c>
-      <c r="E200" s="3">
-        <f t="shared" ref="E200:G200" si="34">AVERAGE(E196:E197)</f>
-        <v>5386.9042822499996</v>
-      </c>
-      <c r="F200" s="4">
-        <f t="shared" si="34"/>
-        <v>1.8217836051361176E-3</v>
-      </c>
-      <c r="G200" s="4">
-        <f t="shared" si="34"/>
-        <v>1.5299410846390934E-3</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C202" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D202" s="3">
-        <f>D199/D200</f>
-        <v>1.0607758459664012</v>
-      </c>
-      <c r="E202" s="3">
-        <f t="shared" ref="E202:G202" si="35">E199/E200</f>
-        <v>0.77167677289668257</v>
-      </c>
-      <c r="F202" s="3">
-        <f t="shared" si="35"/>
-        <v>0.82036156049346076</v>
-      </c>
-      <c r="G202" s="3">
-        <f t="shared" si="35"/>
-        <v>1.4287748577228767</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C204" s="2">
-        <f>MAX(C194:C197)</f>
-        <v>4</v>
-      </c>
-      <c r="D204" s="2">
-        <f t="shared" ref="D204:G204" si="36">MAX(D194:D197)</f>
-        <v>589836.07301855378</v>
-      </c>
-      <c r="E204" s="2">
-        <f t="shared" si="36"/>
-        <v>5998.8555937799993</v>
-      </c>
-      <c r="F204" s="2">
-        <f t="shared" si="36"/>
-        <v>3.3561812091085249E-3</v>
-      </c>
-      <c r="G204" s="2">
-        <f t="shared" si="36"/>
-        <v>2.2962786554205951E-3</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C205" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D205" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F205" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C206" s="2">
-        <f t="shared" ref="C206:G209" si="37">C194/C$204</f>
+      <c r="F210" s="11">
         <v>1</v>
       </c>
-      <c r="D206" s="2">
-        <f t="shared" si="37"/>
-        <v>1</v>
-      </c>
-      <c r="E206" s="2">
-        <f t="shared" si="37"/>
-        <v>0.57664977093076919</v>
-      </c>
-      <c r="F206" s="2">
-        <f t="shared" si="37"/>
-        <v>0.77853736812744556</v>
-      </c>
-      <c r="G206" s="2">
-        <f t="shared" si="37"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C207" s="2">
-        <f t="shared" si="37"/>
-        <v>0.5</v>
-      </c>
-      <c r="D207" s="2">
-        <f t="shared" si="37"/>
-        <v>0.99252536988558093</v>
-      </c>
-      <c r="E207" s="2">
-        <f t="shared" si="37"/>
-        <v>0.80926420797553855</v>
-      </c>
-      <c r="F207" s="2">
-        <f t="shared" si="37"/>
-        <v>0.11207082497893665</v>
-      </c>
-      <c r="G207" s="2">
-        <f t="shared" si="37"/>
-        <v>0.9038990327846067</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C208" s="2">
-        <f t="shared" si="37"/>
+      <c r="G210" s="11">
+        <v>0.7592293002304622</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C211" s="12">
+        <v>0.97598188945750519</v>
+      </c>
+      <c r="D211" s="11">
         <v>0.75</v>
       </c>
-      <c r="D208" s="2">
-        <f t="shared" si="37"/>
-        <v>0.97598188945750519</v>
-      </c>
-      <c r="E208" s="2">
-        <f t="shared" si="37"/>
+      <c r="E211" s="11">
         <v>0.79597731535177796</v>
       </c>
-      <c r="F208" s="2">
-        <f t="shared" si="37"/>
+      <c r="F211" s="11">
         <v>8.5628869020468137E-2</v>
       </c>
-      <c r="G208" s="2">
-        <f t="shared" si="37"/>
+      <c r="G211" s="11">
         <v>0.57331026854314004</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C209" s="2">
-        <f t="shared" si="37"/>
-        <v>0.25</v>
-      </c>
-      <c r="D209" s="2">
-        <f t="shared" si="37"/>
-        <v>0.90238419274747317</v>
-      </c>
-      <c r="E209" s="2">
-        <f t="shared" si="37"/>
-        <v>1</v>
-      </c>
-      <c r="F209" s="2">
-        <f t="shared" si="37"/>
-        <v>1</v>
-      </c>
-      <c r="G209" s="2">
-        <f t="shared" si="37"/>
-        <v>0.7592293002304622</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C211" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D211" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E211" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F211" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G211" s="10" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C212" s="12">
-        <v>0.90238419274747317</v>
+        <v>0.99252536988558093</v>
       </c>
       <c r="D212" s="11">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E212" s="11">
-        <v>1</v>
+        <v>0.80926420797553855</v>
       </c>
       <c r="F212" s="11">
-        <v>1</v>
+        <v>0.11207082497893665</v>
       </c>
       <c r="G212" s="11">
-        <v>0.7592293002304622</v>
+        <v>0.9038990327846067</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C213" s="12">
-        <v>0.97598188945750519</v>
+        <v>1</v>
       </c>
       <c r="D213" s="11">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E213" s="11">
-        <v>0.79597731535177796</v>
+        <v>0.57664977093076919</v>
       </c>
       <c r="F213" s="11">
-        <v>8.5628869020468137E-2</v>
+        <v>0.77853736812744556</v>
       </c>
       <c r="G213" s="11">
-        <v>0.57331026854314004</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C214" s="12">
-        <v>0.99252536988558093</v>
-      </c>
-      <c r="D214" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="E214" s="11">
-        <v>0.80926420797553855</v>
-      </c>
-      <c r="F214" s="11">
-        <v>0.11207082497893665</v>
-      </c>
-      <c r="G214" s="11">
-        <v>0.9038990327846067</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C215" s="12">
+      <c r="A215" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D215" s="11">
+      <c r="C215" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B216" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C216" s="2">
         <v>1</v>
       </c>
-      <c r="E215" s="11">
-        <v>0.57664977093076919</v>
-      </c>
-      <c r="F215" s="11">
-        <v>0.77853736812744556</v>
-      </c>
-      <c r="G215" s="11">
-        <v>1</v>
+      <c r="D216" s="3">
+        <v>2688475.9724428668</v>
+      </c>
+      <c r="E216" s="3">
+        <v>22918.622383440001</v>
+      </c>
+      <c r="F216" s="4">
+        <v>1.411209606183382E-2</v>
+      </c>
+      <c r="G216" s="4">
+        <v>6.7540592802753808E-4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B217" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C217" s="2">
+        <v>2</v>
+      </c>
+      <c r="D217" s="3">
+        <v>2199098.9702055152</v>
+      </c>
+      <c r="E217" s="3">
+        <v>27186.587841839999</v>
+      </c>
+      <c r="F217" s="4">
+        <v>1.428164445640567E-2</v>
+      </c>
+      <c r="G217" s="4">
+        <v>1.063284111568874E-3</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A218" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D218" s="1" t="s">
+      <c r="A218" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B218" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C218" s="2">
         <v>3</v>
       </c>
-      <c r="E218" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F218" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G218" s="1" t="s">
-        <v>6</v>
+      <c r="D218" s="3">
+        <v>2110825.0242093089</v>
+      </c>
+      <c r="E218" s="3">
+        <v>36820.330575920001</v>
+      </c>
+      <c r="F218" s="4">
+        <v>1.1388913987487259E-2</v>
+      </c>
+      <c r="G218" s="4">
+        <v>1.346627653376551E-3</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -63820,3092 +64087,3167 @@
         <v>24</v>
       </c>
       <c r="C219" s="2">
+        <v>4</v>
+      </c>
+      <c r="D219" s="3">
+        <v>2060147.693651289</v>
+      </c>
+      <c r="E219" s="3">
+        <v>24111.565200000001</v>
+      </c>
+      <c r="F219" s="4">
+        <v>1.6816288641435851E-2</v>
+      </c>
+      <c r="G219" s="4">
+        <v>4.7603910840263489E-4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B221" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D221" s="3">
+        <f>AVERAGE(D216:D217)</f>
+        <v>2443787.471324191</v>
+      </c>
+      <c r="E221" s="3">
+        <f t="shared" ref="E221:G221" si="36">AVERAGE(E216:E217)</f>
+        <v>25052.605112639998</v>
+      </c>
+      <c r="F221" s="4">
+        <f t="shared" si="36"/>
+        <v>1.4196870259119745E-2</v>
+      </c>
+      <c r="G221" s="4">
+        <f t="shared" si="36"/>
+        <v>8.6934501979820604E-4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B222" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D222" s="3">
+        <f>AVERAGE(D218:D219)</f>
+        <v>2085486.3589302991</v>
+      </c>
+      <c r="E222" s="3">
+        <f t="shared" ref="E222:G222" si="37">AVERAGE(E218:E219)</f>
+        <v>30465.947887959999</v>
+      </c>
+      <c r="F222" s="4">
+        <f t="shared" si="37"/>
+        <v>1.4102601314461555E-2</v>
+      </c>
+      <c r="G222" s="4">
+        <f t="shared" si="37"/>
+        <v>9.1133338088959293E-4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C224" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D224" s="3">
+        <f>D221/D222</f>
+        <v>1.1718069796331221</v>
+      </c>
+      <c r="E224" s="3">
+        <f t="shared" ref="E224:G224" si="38">E221/E222</f>
+        <v>0.82231497292558131</v>
+      </c>
+      <c r="F224" s="3">
+        <f t="shared" si="38"/>
+        <v>1.0066845075285169</v>
+      </c>
+      <c r="G224" s="3">
+        <f t="shared" si="38"/>
+        <v>0.95392645329154935</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C226" s="2">
+        <f>MAX(C216:C219)</f>
+        <v>4</v>
+      </c>
+      <c r="D226" s="2">
+        <f t="shared" ref="D226:G226" si="39">MAX(D216:D219)</f>
+        <v>2688475.9724428668</v>
+      </c>
+      <c r="E226" s="2">
+        <f t="shared" si="39"/>
+        <v>36820.330575920001</v>
+      </c>
+      <c r="F226" s="2">
+        <f t="shared" si="39"/>
+        <v>1.6816288641435851E-2</v>
+      </c>
+      <c r="G226" s="2">
+        <f t="shared" si="39"/>
+        <v>1.346627653376551E-3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C227" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D227" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J227" s="2"/>
+      <c r="K227" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L227" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C228" s="2">
+        <f>C216/C$226</f>
+        <v>0.25</v>
+      </c>
+      <c r="D228" s="2">
+        <f>D216/D$226</f>
         <v>1</v>
       </c>
-      <c r="D219" s="3">
-        <v>2688475.9724428668</v>
-      </c>
-      <c r="E219" s="3">
-        <v>22918.622383440001</v>
-      </c>
-      <c r="F219" s="4">
-        <v>1.411209606183382E-2</v>
-      </c>
-      <c r="G219" s="4">
-        <v>6.7540592802753808E-4</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A220" s="2" t="s">
+      <c r="E228" s="2">
+        <f>E216/E$226</f>
+        <v>0.62244477507294493</v>
+      </c>
+      <c r="F228" s="2">
+        <f>F216/F$226</f>
+        <v>0.83919206923346823</v>
+      </c>
+      <c r="G228" s="2">
+        <f>G216/G$226</f>
+        <v>0.50155358560624896</v>
+      </c>
+      <c r="J228" s="10">
         <v>23</v>
       </c>
-      <c r="B220" s="8" t="s">
+      <c r="K228" s="3">
+        <f>0.5*(D213*E213+E213*F213+F213*G213+G213*D213)</f>
+        <v>1.4020652670249751</v>
+      </c>
+      <c r="L228" s="3">
+        <f>0.5*(D210*E210+E210*F210+F210*G210+G210*D210)</f>
+        <v>1.0995183126440389</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C229" s="2">
+        <f>C217/C$226</f>
+        <v>0.5</v>
+      </c>
+      <c r="D229" s="2">
+        <f>D217/D$226</f>
+        <v>0.81797233553377002</v>
+      </c>
+      <c r="E229" s="2">
+        <f>E217/E$226</f>
+        <v>0.73835805970790658</v>
+      </c>
+      <c r="F229" s="2">
+        <f>F217/F$226</f>
+        <v>0.84927446007410101</v>
+      </c>
+      <c r="G229" s="2">
+        <f>G217/G$226</f>
+        <v>0.78959028422057287</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C230" s="2">
+        <f>C218/C$226</f>
+        <v>0.75</v>
+      </c>
+      <c r="D230" s="2">
+        <f>D218/D$226</f>
+        <v>0.78513813991475667</v>
+      </c>
+      <c r="E230" s="2">
+        <f>E218/E$226</f>
+        <v>1</v>
+      </c>
+      <c r="F230" s="2">
+        <f>F218/F$226</f>
+        <v>0.67725490625943618</v>
+      </c>
+      <c r="G230" s="2">
+        <f>G218/G$226</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C231" s="2">
+        <f>C219/C$226</f>
+        <v>1</v>
+      </c>
+      <c r="D231" s="2">
+        <f>D219/D$226</f>
+        <v>0.76628830414256921</v>
+      </c>
+      <c r="E231" s="2">
+        <f>E219/E$226</f>
+        <v>0.65484380022836186</v>
+      </c>
+      <c r="F231" s="2">
+        <f>F219/F$226</f>
+        <v>1</v>
+      </c>
+      <c r="G231" s="2">
+        <f>G219/G$226</f>
+        <v>0.3535046285504449</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C233" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D233" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E233" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F233" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G233" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C234" s="3">
+        <v>0.76628830414256921</v>
+      </c>
+      <c r="D234" s="2">
+        <v>1</v>
+      </c>
+      <c r="E234" s="2">
+        <v>0.65484380022836186</v>
+      </c>
+      <c r="F234" s="2">
+        <v>1</v>
+      </c>
+      <c r="G234" s="2">
+        <v>0.3535046285504449</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C235" s="3">
+        <v>0.78513813991475667</v>
+      </c>
+      <c r="D235" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E235" s="2">
+        <v>1</v>
+      </c>
+      <c r="F235" s="2">
+        <v>0.67725490625943618</v>
+      </c>
+      <c r="G235" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C236" s="3">
+        <v>0.81797233553377002</v>
+      </c>
+      <c r="D236" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E236" s="2">
+        <v>0.73835805970790658</v>
+      </c>
+      <c r="F236" s="2">
+        <v>0.84927446007410101</v>
+      </c>
+      <c r="G236" s="2">
+        <v>0.78959028422057287</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C237" s="3">
+        <v>1</v>
+      </c>
+      <c r="D237" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E237" s="2">
+        <v>0.62244477507294493</v>
+      </c>
+      <c r="F237" s="2">
+        <v>0.83919206923346823</v>
+      </c>
+      <c r="G237" s="2">
+        <v>0.50155358560624896</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G239" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B240" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C240" s="2">
+        <v>4</v>
+      </c>
+      <c r="D240" s="3">
+        <v>1079590.799601601</v>
+      </c>
+      <c r="E240" s="3">
+        <v>29824.255583999999</v>
+      </c>
+      <c r="F240" s="4">
+        <v>1.7700063980245699E-2</v>
+      </c>
+      <c r="G240" s="4">
+        <v>1.8406361575525849E-2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B241" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C241" s="2">
+        <v>3</v>
+      </c>
+      <c r="D241" s="3">
+        <v>917032.53729645221</v>
+      </c>
+      <c r="E241" s="3">
+        <v>21948.7441788</v>
+      </c>
+      <c r="F241" s="4">
+        <v>5.1385668600091312E-2</v>
+      </c>
+      <c r="G241" s="4">
+        <v>1.045825844659099E-3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B242" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C242" s="2">
+        <v>2</v>
+      </c>
+      <c r="D242" s="3">
+        <v>802566.08061441511</v>
+      </c>
+      <c r="E242" s="3">
+        <v>12046.641059559999</v>
+      </c>
+      <c r="F242" s="4">
+        <v>1.264319260007594E-2</v>
+      </c>
+      <c r="G242" s="4">
+        <v>9.2646432850616075E-4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B243" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C243" s="2">
+        <v>1</v>
+      </c>
+      <c r="D243" s="3">
+        <v>774599.50938466226</v>
+      </c>
+      <c r="E243" s="3">
+        <v>31768.917493320001</v>
+      </c>
+      <c r="F243" s="4">
+        <v>4.5024994770462897E-3</v>
+      </c>
+      <c r="G243" s="4">
+        <v>6.1504127372638605E-4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B245" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D245" s="3">
+        <f>AVERAGE(D240:D241)</f>
+        <v>998311.66844902653</v>
+      </c>
+      <c r="E245" s="3">
+        <f t="shared" ref="E245:G245" si="40">AVERAGE(E240:E241)</f>
+        <v>25886.499881399999</v>
+      </c>
+      <c r="F245" s="4">
+        <f t="shared" si="40"/>
+        <v>3.4542866290168506E-2</v>
+      </c>
+      <c r="G245" s="4">
+        <f t="shared" si="40"/>
+        <v>9.7260937100924743E-3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B246" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D246" s="3">
+        <f>AVERAGE(D242:D243)</f>
+        <v>788582.79499953869</v>
+      </c>
+      <c r="E246" s="3">
+        <f t="shared" ref="E246:G246" si="41">AVERAGE(E242:E243)</f>
+        <v>21907.77927644</v>
+      </c>
+      <c r="F246" s="4">
+        <f t="shared" si="41"/>
+        <v>8.5728460385611147E-3</v>
+      </c>
+      <c r="G246" s="4">
+        <f t="shared" si="41"/>
+        <v>7.7075280111627334E-4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C248" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D248" s="3">
+        <f>D245/D246</f>
+        <v>1.2659566944389276</v>
+      </c>
+      <c r="E248" s="3">
+        <f t="shared" ref="E248:G248" si="42">E245/E246</f>
+        <v>1.1816122280015293</v>
+      </c>
+      <c r="F248" s="3">
+        <f t="shared" si="42"/>
+        <v>4.0293347314057506</v>
+      </c>
+      <c r="G248" s="3">
+        <f t="shared" si="42"/>
+        <v>12.618953438776055</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C250" s="2">
+        <f>MAX(C240:C243)</f>
+        <v>4</v>
+      </c>
+      <c r="D250" s="2">
+        <f t="shared" ref="D250:G250" si="43">MAX(D240:D243)</f>
+        <v>1079590.799601601</v>
+      </c>
+      <c r="E250" s="2">
+        <f t="shared" si="43"/>
+        <v>31768.917493320001</v>
+      </c>
+      <c r="F250" s="2">
+        <f t="shared" si="43"/>
+        <v>5.1385668600091312E-2</v>
+      </c>
+      <c r="G250" s="2">
+        <f t="shared" si="43"/>
+        <v>1.8406361575525849E-2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C251" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D251" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J251" s="2"/>
+      <c r="K251" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L251" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C252" s="2">
+        <f>C240/C$250</f>
+        <v>1</v>
+      </c>
+      <c r="D252" s="2">
+        <f>D240/D$250</f>
+        <v>1</v>
+      </c>
+      <c r="E252" s="2">
+        <f>E240/E$250</f>
+        <v>0.93878727817122176</v>
+      </c>
+      <c r="F252" s="2">
+        <f>F240/F$250</f>
+        <v>0.34445526276978805</v>
+      </c>
+      <c r="G252" s="2">
+        <f>G240/G$250</f>
+        <v>1</v>
+      </c>
+      <c r="J252" s="10">
         <v>24</v>
       </c>
-      <c r="C220" s="2">
+      <c r="K252" s="3">
+        <f>0.5*(D237*E237+E237*F237+F237*G237+G237*D237)</f>
+        <v>0.61212505014159868</v>
+      </c>
+      <c r="L252" s="3">
+        <f>0.5*(D234*E234+E234*F234+F234*G234+G234*D234)</f>
+        <v>1.0083484287788067</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C253" s="2">
+        <f>C241/C$250</f>
+        <v>0.75</v>
+      </c>
+      <c r="D253" s="2">
+        <f>D241/D$250</f>
+        <v>0.84942603960209995</v>
+      </c>
+      <c r="E253" s="2">
+        <f>E241/E$250</f>
+        <v>0.69088738020157991</v>
+      </c>
+      <c r="F253" s="2">
+        <f>F241/F$250</f>
+        <v>1</v>
+      </c>
+      <c r="G253" s="2">
+        <f>G241/G$250</f>
+        <v>5.6818716744632944E-2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C254" s="2">
+        <f>C242/C$250</f>
+        <v>0.5</v>
+      </c>
+      <c r="D254" s="2">
+        <f>D242/D$250</f>
+        <v>0.74339840698029691</v>
+      </c>
+      <c r="E254" s="2">
+        <f>E242/E$250</f>
+        <v>0.37919583070757845</v>
+      </c>
+      <c r="F254" s="2">
+        <f>F242/F$250</f>
+        <v>0.24604511227578876</v>
+      </c>
+      <c r="G254" s="2">
+        <f>G242/G$250</f>
+        <v>5.0333919862687079E-2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C255" s="2">
+        <f>C243/C$250</f>
+        <v>0.25</v>
+      </c>
+      <c r="D255" s="2">
+        <f>D243/D$250</f>
+        <v>0.71749361857336225</v>
+      </c>
+      <c r="E255" s="2">
+        <f>E243/E$250</f>
+        <v>1</v>
+      </c>
+      <c r="F255" s="2">
+        <f>F243/F$250</f>
+        <v>8.7621696860402221E-2</v>
+      </c>
+      <c r="G255" s="2">
+        <f>G243/G$250</f>
+        <v>3.3414603489272977E-2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C257" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E257" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F257" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G257" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C258" s="3">
+        <v>0.71749361857336225</v>
+      </c>
+      <c r="D258" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E258" s="2">
+        <v>1</v>
+      </c>
+      <c r="F258" s="2">
+        <v>8.7621696860402221E-2</v>
+      </c>
+      <c r="G258" s="2">
+        <v>3.3414603489272977E-2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C259" s="3">
+        <v>0.74339840698029691</v>
+      </c>
+      <c r="D259" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E259" s="2">
+        <v>0.37919583070757845</v>
+      </c>
+      <c r="F259" s="2">
+        <v>0.24604511227578876</v>
+      </c>
+      <c r="G259" s="2">
+        <v>5.0333919862687079E-2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C260" s="3">
+        <v>0.84942603960209995</v>
+      </c>
+      <c r="D260" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E260" s="2">
+        <v>0.69088738020157991</v>
+      </c>
+      <c r="F260" s="2">
+        <v>1</v>
+      </c>
+      <c r="G260" s="2">
+        <v>5.6818716744632944E-2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C261" s="3">
+        <v>1</v>
+      </c>
+      <c r="D261" s="2">
+        <v>1</v>
+      </c>
+      <c r="E261" s="2">
+        <v>0.93878727817122176</v>
+      </c>
+      <c r="F261" s="2">
+        <v>0.34445526276978805</v>
+      </c>
+      <c r="G261" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C263" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D220" s="3">
-        <v>2199098.9702055152</v>
-      </c>
-      <c r="E220" s="3">
-        <v>27186.587841839999</v>
-      </c>
-      <c r="F220" s="4">
-        <v>1.428164445640567E-2</v>
-      </c>
-      <c r="G220" s="4">
-        <v>1.063284111568874E-3</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A221" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B221" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C221" s="2">
+      <c r="D263" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D221" s="3">
-        <v>2110825.0242093089</v>
-      </c>
-      <c r="E221" s="3">
-        <v>36820.330575920001</v>
-      </c>
-      <c r="F221" s="4">
-        <v>1.1388913987487259E-2</v>
-      </c>
-      <c r="G221" s="4">
-        <v>1.346627653376551E-3</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A222" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B222" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C222" s="2">
+      <c r="E263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="3">
-        <v>2060147.693651289</v>
-      </c>
-      <c r="E222" s="3">
-        <v>24111.565200000001</v>
-      </c>
-      <c r="F222" s="4">
-        <v>1.6816288641435851E-2</v>
-      </c>
-      <c r="G222" s="4">
-        <v>4.7603910840263489E-4</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B224" s="7" t="s">
+      <c r="F263" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G263" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B264" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C264" s="2">
+        <v>4</v>
+      </c>
+      <c r="D264" s="3">
+        <v>702640.28510284843</v>
+      </c>
+      <c r="E264" s="3">
+        <v>24692.815392</v>
+      </c>
+      <c r="F264" s="4">
+        <v>1.2473785395074479E-2</v>
+      </c>
+      <c r="G264" s="4">
+        <v>1.210844187888221E-3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B265" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C265" s="2">
+        <v>3</v>
+      </c>
+      <c r="D265" s="3">
+        <v>648523.59030139784</v>
+      </c>
+      <c r="E265" s="3">
+        <v>20365.73930736</v>
+      </c>
+      <c r="F265" s="4">
+        <v>2.3285205202868371E-2</v>
+      </c>
+      <c r="G265" s="4">
+        <v>1.5783067550306741E-3</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C266" s="2">
+        <v>2</v>
+      </c>
+      <c r="D266" s="3">
+        <v>525586.90611574077</v>
+      </c>
+      <c r="E266" s="3">
+        <v>57596.7124071</v>
+      </c>
+      <c r="F266" s="4">
+        <v>6.9328647193893768E-4</v>
+      </c>
+      <c r="G266" s="4">
+        <v>1.2640594598421069E-2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C267" s="2">
+        <v>1</v>
+      </c>
+      <c r="D267" s="3">
+        <v>489831.22166003252</v>
+      </c>
+      <c r="E267" s="3">
+        <v>28233.8392518</v>
+      </c>
+      <c r="F267" s="4">
+        <v>1.7629362658082969E-3</v>
+      </c>
+      <c r="G267" s="4">
+        <v>1.091290811894655E-3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B269" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D224" s="3">
-        <f>AVERAGE(D219:D220)</f>
-        <v>2443787.471324191</v>
-      </c>
-      <c r="E224" s="3">
-        <f t="shared" ref="E224:G224" si="38">AVERAGE(E219:E220)</f>
-        <v>25052.605112639998</v>
-      </c>
-      <c r="F224" s="4">
-        <f t="shared" si="38"/>
-        <v>1.4196870259119745E-2</v>
-      </c>
-      <c r="G224" s="4">
-        <f t="shared" si="38"/>
-        <v>8.6934501979820604E-4</v>
-      </c>
-    </row>
-    <row r="225" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B225" s="7" t="s">
+      <c r="D269" s="3">
+        <f>AVERAGE(D264:D265)</f>
+        <v>675581.93770212308</v>
+      </c>
+      <c r="E269" s="3">
+        <f t="shared" ref="E269:G269" si="44">AVERAGE(E264:E265)</f>
+        <v>22529.27734968</v>
+      </c>
+      <c r="F269" s="4">
+        <f t="shared" si="44"/>
+        <v>1.7879495298971426E-2</v>
+      </c>
+      <c r="G269" s="4">
+        <f t="shared" si="44"/>
+        <v>1.3945754714594475E-3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B270" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D225" s="3">
-        <f>AVERAGE(D221:D222)</f>
-        <v>2085486.3589302991</v>
-      </c>
-      <c r="E225" s="3">
-        <f t="shared" ref="E225:G225" si="39">AVERAGE(E221:E222)</f>
-        <v>30465.947887959999</v>
-      </c>
-      <c r="F225" s="4">
-        <f t="shared" si="39"/>
-        <v>1.4102601314461555E-2</v>
-      </c>
-      <c r="G225" s="4">
-        <f t="shared" si="39"/>
-        <v>9.1133338088959293E-4</v>
-      </c>
-    </row>
-    <row r="227" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C227" s="7" t="s">
+      <c r="D270" s="3">
+        <f>AVERAGE(D266:D267)</f>
+        <v>507709.06388788664</v>
+      </c>
+      <c r="E270" s="3">
+        <f t="shared" ref="E270:G270" si="45">AVERAGE(E266:E267)</f>
+        <v>42915.275829450002</v>
+      </c>
+      <c r="F270" s="4">
+        <f t="shared" si="45"/>
+        <v>1.2281113688736172E-3</v>
+      </c>
+      <c r="G270" s="4">
+        <f t="shared" si="45"/>
+        <v>6.8659427051578625E-3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C272" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D227" s="3">
-        <f>D224/D225</f>
-        <v>1.1718069796331221</v>
-      </c>
-      <c r="E227" s="3">
-        <f t="shared" ref="E227:G227" si="40">E224/E225</f>
-        <v>0.82231497292558131</v>
-      </c>
-      <c r="F227" s="3">
-        <f t="shared" si="40"/>
-        <v>1.0066845075285169</v>
-      </c>
-      <c r="G227" s="3">
-        <f t="shared" si="40"/>
-        <v>0.95392645329154935</v>
-      </c>
-    </row>
-    <row r="229" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C229" s="2">
-        <f>MAX(C219:C222)</f>
+      <c r="D272" s="3">
+        <f>D269/D270</f>
+        <v>1.3306477779394272</v>
+      </c>
+      <c r="E272" s="3">
+        <f t="shared" ref="E272:G272" si="46">E269/E270</f>
+        <v>0.52497104851926879</v>
+      </c>
+      <c r="F272" s="3">
+        <f t="shared" si="46"/>
+        <v>14.558529260558757</v>
+      </c>
+      <c r="G272" s="3">
+        <f t="shared" si="46"/>
+        <v>0.20311492992969613</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C274" s="2">
+        <f>MAX(C264:C267)</f>
         <v>4</v>
       </c>
-      <c r="D229" s="2">
-        <f t="shared" ref="D229:G229" si="41">MAX(D219:D222)</f>
-        <v>2688475.9724428668</v>
-      </c>
-      <c r="E229" s="2">
-        <f t="shared" si="41"/>
-        <v>36820.330575920001</v>
-      </c>
-      <c r="F229" s="2">
-        <f t="shared" si="41"/>
-        <v>1.6816288641435851E-2</v>
-      </c>
-      <c r="G229" s="2">
-        <f t="shared" si="41"/>
-        <v>1.346627653376551E-3</v>
-      </c>
-    </row>
-    <row r="230" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C230" s="10" t="s">
+      <c r="D274" s="2">
+        <f t="shared" ref="D274:G274" si="47">MAX(D264:D267)</f>
+        <v>702640.28510284843</v>
+      </c>
+      <c r="E274" s="2">
+        <f t="shared" si="47"/>
+        <v>57596.7124071</v>
+      </c>
+      <c r="F274" s="2">
+        <f t="shared" si="47"/>
+        <v>2.3285205202868371E-2</v>
+      </c>
+      <c r="G274" s="2">
+        <f t="shared" si="47"/>
+        <v>1.2640594598421069E-2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C275" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D230" s="10" t="s">
+      <c r="D275" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E230" s="1" t="s">
+      <c r="E275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F230" s="1" t="s">
+      <c r="F275" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G230" s="1" t="s">
+      <c r="G275" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="231" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C231" s="2">
-        <f>C219/C$229</f>
+      <c r="J275" s="2"/>
+      <c r="K275" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L275" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C276" s="2">
+        <f>C264/C$274</f>
+        <v>1</v>
+      </c>
+      <c r="D276" s="2">
+        <f>D264/D$274</f>
+        <v>1</v>
+      </c>
+      <c r="E276" s="2">
+        <f>E264/E$274</f>
+        <v>0.4287191813565403</v>
+      </c>
+      <c r="F276" s="2">
+        <f>F264/F$274</f>
+        <v>0.53569574699465849</v>
+      </c>
+      <c r="G276" s="2">
+        <f>G264/G$274</f>
+        <v>9.5790129052906028E-2</v>
+      </c>
+      <c r="J276" s="10">
+        <v>25</v>
+      </c>
+      <c r="K276" s="3">
+        <f>0.5*(D261*E261+E261*F261+F261*G261+G261*D261)</f>
+        <v>1.3033063797642059</v>
+      </c>
+      <c r="L276" s="3">
+        <f>0.5*(D258*E258+E258*F258+F258*G258+G258*D258)</f>
+        <v>0.17445159599518406</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C277" s="2">
+        <f>C265/C$274</f>
+        <v>0.75</v>
+      </c>
+      <c r="D277" s="2">
+        <f>D265/D$274</f>
+        <v>0.9229809392532492</v>
+      </c>
+      <c r="E277" s="2">
+        <f>E265/E$274</f>
+        <v>0.3535920446884655</v>
+      </c>
+      <c r="F277" s="2">
+        <f>F265/F$274</f>
+        <v>1</v>
+      </c>
+      <c r="G277" s="2">
+        <f>G265/G$274</f>
+        <v>0.12486016719718387</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C278" s="2">
+        <f>C266/C$274</f>
+        <v>0.5</v>
+      </c>
+      <c r="D278" s="2">
+        <f>D266/D$274</f>
+        <v>0.74801703981263812</v>
+      </c>
+      <c r="E278" s="2">
+        <f>E266/E$274</f>
+        <v>1</v>
+      </c>
+      <c r="F278" s="2">
+        <f>F266/F$274</f>
+        <v>2.9773689598128844E-2</v>
+      </c>
+      <c r="G278" s="2">
+        <f>G266/G$274</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C279" s="2">
+        <f>C267/C$274</f>
         <v>0.25</v>
       </c>
-      <c r="D231" s="2">
-        <f t="shared" ref="D231:G231" si="42">D219/D$229</f>
+      <c r="D279" s="2">
+        <f>D267/D$274</f>
+        <v>0.69712943030064645</v>
+      </c>
+      <c r="E279" s="2">
+        <f>E267/E$274</f>
+        <v>0.49019879906061425</v>
+      </c>
+      <c r="F279" s="2">
+        <f>F267/F$274</f>
+        <v>7.571057460945764E-2</v>
+      </c>
+      <c r="G279" s="2">
+        <f>G267/G$274</f>
+        <v>8.6332237253377908E-2</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C281" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D281" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E281" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F281" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G281" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C282" s="3">
+        <v>0.69712943030064645</v>
+      </c>
+      <c r="D282" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E282" s="2">
+        <v>0.49019879906061425</v>
+      </c>
+      <c r="F282" s="2">
+        <v>7.571057460945764E-2</v>
+      </c>
+      <c r="G282" s="2">
+        <v>8.6332237253377908E-2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C283" s="3">
+        <v>0.74801703981263812</v>
+      </c>
+      <c r="D283" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E283" s="2">
         <v>1</v>
       </c>
-      <c r="E231" s="2">
-        <f t="shared" si="42"/>
-        <v>0.62244477507294493</v>
-      </c>
-      <c r="F231" s="2">
-        <f t="shared" si="42"/>
-        <v>0.83919206923346823</v>
-      </c>
-      <c r="G231" s="2">
-        <f t="shared" si="42"/>
-        <v>0.50155358560624896</v>
-      </c>
-    </row>
-    <row r="232" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C232" s="2">
-        <f t="shared" ref="C232:G234" si="43">C220/C$229</f>
+      <c r="F283" s="2">
+        <v>2.9773689598128844E-2</v>
+      </c>
+      <c r="G283" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C284" s="3">
+        <v>0.9229809392532492</v>
+      </c>
+      <c r="D284" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E284" s="2">
+        <v>0.3535920446884655</v>
+      </c>
+      <c r="F284" s="2">
+        <v>1</v>
+      </c>
+      <c r="G284" s="2">
+        <v>0.12486016719718387</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C285" s="3">
+        <v>1</v>
+      </c>
+      <c r="D285" s="2">
+        <v>1</v>
+      </c>
+      <c r="E285" s="2">
+        <v>0.4287191813565403</v>
+      </c>
+      <c r="F285" s="2">
+        <v>0.53569574699465849</v>
+      </c>
+      <c r="G285" s="2">
+        <v>9.5790129052906028E-2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F287" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G287" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A288" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C288" s="2">
+        <v>4</v>
+      </c>
+      <c r="D288" s="3">
+        <v>333902.21266145178</v>
+      </c>
+      <c r="E288" s="3">
+        <v>6590.0541599999997</v>
+      </c>
+      <c r="F288" s="4">
+        <v>3.968817154607421E-3</v>
+      </c>
+      <c r="G288" s="4">
+        <v>1.4273582237145071E-3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A289" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C289" s="2">
+        <v>3</v>
+      </c>
+      <c r="D289" s="3">
+        <v>289865.32010952412</v>
+      </c>
+      <c r="E289" s="3">
+        <v>5130.8202951200001</v>
+      </c>
+      <c r="F289" s="4">
+        <v>7.1409024001186736E-3</v>
+      </c>
+      <c r="G289" s="4">
+        <v>1.6292149323472839E-3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A290" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C290" s="2">
+        <v>2</v>
+      </c>
+      <c r="D290" s="3">
+        <v>259818.50988372459</v>
+      </c>
+      <c r="E290" s="3">
+        <v>45922.658233419999</v>
+      </c>
+      <c r="F290" s="4">
+        <v>4.0433840100499702E-5</v>
+      </c>
+      <c r="G290" s="4">
+        <v>1.5232724169502069E-4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C291" s="2">
+        <v>1</v>
+      </c>
+      <c r="D291" s="3">
+        <v>234189.89306239539</v>
+      </c>
+      <c r="E291" s="3">
+        <v>4733.3383234200001</v>
+      </c>
+      <c r="F291" s="4">
+        <v>6.6356632156617178E-4</v>
+      </c>
+      <c r="G291" s="4">
+        <v>3.1476572520248271E-3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B293" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D293" s="3">
+        <f>AVERAGE(D288:D289)</f>
+        <v>311883.76638548798</v>
+      </c>
+      <c r="E293" s="3">
+        <f t="shared" ref="E293:G293" si="48">AVERAGE(E288:E289)</f>
+        <v>5860.4372275599999</v>
+      </c>
+      <c r="F293" s="4">
+        <f t="shared" si="48"/>
+        <v>5.5548597773630477E-3</v>
+      </c>
+      <c r="G293" s="4">
+        <f t="shared" si="48"/>
+        <v>1.5282865780308955E-3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B294" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D294" s="3">
+        <f>AVERAGE(D290:D291)</f>
+        <v>247004.20147306001</v>
+      </c>
+      <c r="E294" s="3">
+        <f t="shared" ref="E294:G294" si="49">AVERAGE(E290:E291)</f>
+        <v>25327.99827842</v>
+      </c>
+      <c r="F294" s="4">
+        <f t="shared" si="49"/>
+        <v>3.5200008083333573E-4</v>
+      </c>
+      <c r="G294" s="4">
+        <f t="shared" si="49"/>
+        <v>1.6499922468599239E-3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C296" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D296" s="3">
+        <f>D293/D294</f>
+        <v>1.2626658353400688</v>
+      </c>
+      <c r="E296" s="3">
+        <f t="shared" ref="E296:G296" si="50">E293/E294</f>
+        <v>0.23138177613322164</v>
+      </c>
+      <c r="F296" s="3">
+        <f t="shared" si="50"/>
+        <v>15.780848016319494</v>
+      </c>
+      <c r="G296" s="3">
+        <f t="shared" si="50"/>
+        <v>0.9262386419932308</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C298" s="2">
+        <f>MAX(C288:C291)</f>
+        <v>4</v>
+      </c>
+      <c r="D298" s="2">
+        <f t="shared" ref="D298:G298" si="51">MAX(D288:D291)</f>
+        <v>333902.21266145178</v>
+      </c>
+      <c r="E298" s="2">
+        <f t="shared" si="51"/>
+        <v>45922.658233419999</v>
+      </c>
+      <c r="F298" s="2">
+        <f t="shared" si="51"/>
+        <v>7.1409024001186736E-3</v>
+      </c>
+      <c r="G298" s="2">
+        <f t="shared" si="51"/>
+        <v>3.1476572520248271E-3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C299" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D299" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F299" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G299" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J299" s="2"/>
+      <c r="K299" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L299" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C300" s="2">
+        <f>C288/C$298</f>
+        <v>1</v>
+      </c>
+      <c r="D300" s="2">
+        <f>D288/D$298</f>
+        <v>1</v>
+      </c>
+      <c r="E300" s="2">
+        <f>E288/E$298</f>
+        <v>0.14350332523225146</v>
+      </c>
+      <c r="F300" s="2">
+        <f>F288/F$298</f>
+        <v>0.55578650039264843</v>
+      </c>
+      <c r="G300" s="2">
+        <f>G288/G$298</f>
+        <v>0.45346685151196658</v>
+      </c>
+      <c r="J300" s="10">
+        <v>26</v>
+      </c>
+      <c r="K300" s="3">
+        <f>0.5*(D285*E285+E285*F285+F285*G285+G285*D285)</f>
+        <v>0.40274335862744398</v>
+      </c>
+      <c r="L300" s="3">
+        <f>0.5*(D282*E282+E282*F282+F282*G282+G282*D282)</f>
+        <v>9.3891127559008247E-2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C301" s="2">
+        <f>C289/C$298</f>
+        <v>0.75</v>
+      </c>
+      <c r="D301" s="2">
+        <f>D289/D$298</f>
+        <v>0.86811440331311229</v>
+      </c>
+      <c r="E301" s="2">
+        <f>E289/E$298</f>
+        <v>0.11172742372709753</v>
+      </c>
+      <c r="F301" s="2">
+        <f>F289/F$298</f>
+        <v>1</v>
+      </c>
+      <c r="G301" s="2">
+        <f>G289/G$298</f>
+        <v>0.5175960410871423</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C302" s="2">
+        <f>C290/C$298</f>
         <v>0.5</v>
       </c>
-      <c r="D232" s="2">
-        <f t="shared" si="43"/>
-        <v>0.81797233553377002</v>
-      </c>
-      <c r="E232" s="2">
-        <f t="shared" si="43"/>
-        <v>0.73835805970790658</v>
-      </c>
-      <c r="F232" s="2">
-        <f t="shared" si="43"/>
-        <v>0.84927446007410101</v>
-      </c>
-      <c r="G232" s="2">
-        <f t="shared" si="43"/>
-        <v>0.78959028422057287</v>
-      </c>
-    </row>
-    <row r="233" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C233" s="2">
-        <f t="shared" si="43"/>
+      <c r="D302" s="2">
+        <f>D290/D$298</f>
+        <v>0.77812754762172931</v>
+      </c>
+      <c r="E302" s="2">
+        <f>E290/E$298</f>
+        <v>1</v>
+      </c>
+      <c r="F302" s="2">
+        <f>F290/F$298</f>
+        <v>5.6622871781342003E-3</v>
+      </c>
+      <c r="G302" s="2">
+        <f>G290/G$298</f>
+        <v>4.8393846438341249E-2</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C303" s="2">
+        <f>C291/C$298</f>
+        <v>0.25</v>
+      </c>
+      <c r="D303" s="2">
+        <f>D291/D$298</f>
+        <v>0.70137268991339052</v>
+      </c>
+      <c r="E303" s="2">
+        <f>E291/E$298</f>
+        <v>0.10307195849510592</v>
+      </c>
+      <c r="F303" s="2">
+        <f>F291/F$298</f>
+        <v>9.2924715166971622E-2</v>
+      </c>
+      <c r="G303" s="2">
+        <f>G291/G$298</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C305" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D305" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E305" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F305" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G305" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C306" s="3">
+        <v>0.70137268991339052</v>
+      </c>
+      <c r="D306" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E306" s="2">
+        <v>0.10307195849510592</v>
+      </c>
+      <c r="F306" s="2">
+        <v>9.2924715166971622E-2</v>
+      </c>
+      <c r="G306" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C307" s="3">
+        <v>0.77812754762172931</v>
+      </c>
+      <c r="D307" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E307" s="2">
+        <v>1</v>
+      </c>
+      <c r="F307" s="2">
+        <v>5.6622871781342003E-3</v>
+      </c>
+      <c r="G307" s="2">
+        <v>4.8393846438341249E-2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C308" s="3">
+        <v>0.86811440331311229</v>
+      </c>
+      <c r="D308" s="2">
         <v>0.75</v>
       </c>
-      <c r="D233" s="2">
-        <f t="shared" si="43"/>
-        <v>0.78513813991475667</v>
-      </c>
-      <c r="E233" s="2">
-        <f t="shared" si="43"/>
+      <c r="E308" s="2">
+        <v>0.11172742372709753</v>
+      </c>
+      <c r="F308" s="2">
         <v>1</v>
       </c>
-      <c r="F233" s="2">
-        <f t="shared" si="43"/>
-        <v>0.67725490625943618</v>
-      </c>
-      <c r="G233" s="2">
-        <f t="shared" si="43"/>
+      <c r="G308" s="2">
+        <v>0.5175960410871423</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C309" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="234" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C234" s="2">
-        <f t="shared" si="43"/>
+      <c r="D309" s="2">
         <v>1</v>
       </c>
-      <c r="D234" s="2">
-        <f t="shared" si="43"/>
-        <v>0.76628830414256921</v>
-      </c>
-      <c r="E234" s="2">
-        <f t="shared" si="43"/>
-        <v>0.65484380022836186</v>
-      </c>
-      <c r="F234" s="2">
-        <f t="shared" si="43"/>
+      <c r="E309" s="2">
+        <v>0.14350332523225146</v>
+      </c>
+      <c r="F309" s="2">
+        <v>0.55578650039264843</v>
+      </c>
+      <c r="G309" s="2">
+        <v>0.45346685151196658</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G234" s="2">
-        <f t="shared" si="43"/>
-        <v>0.3535046285504449</v>
-      </c>
-    </row>
-    <row r="236" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C236" s="10" t="s">
+      <c r="C311" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D236" s="10" t="s">
+      <c r="E311" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F311" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G311" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A312" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B312" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C312" s="2">
+        <v>4</v>
+      </c>
+      <c r="D312" s="3">
+        <v>615324.90182869229</v>
+      </c>
+      <c r="E312" s="3">
+        <v>12188.037840000001</v>
+      </c>
+      <c r="F312" s="4">
+        <v>3.5563801629943082E-3</v>
+      </c>
+      <c r="G312" s="4">
+        <v>2.3262126662383252E-3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A313" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B313" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C313" s="2">
+        <v>3</v>
+      </c>
+      <c r="D313" s="3">
+        <v>463470.71898289572</v>
+      </c>
+      <c r="E313" s="3">
+        <v>9380.3853557600014</v>
+      </c>
+      <c r="F313" s="4">
+        <v>2.4821681068467739E-3</v>
+      </c>
+      <c r="G313" s="4">
+        <v>1.7821392198706289E-3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A314" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B314" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C314" s="2">
+        <v>2</v>
+      </c>
+      <c r="D314" s="3">
+        <v>441905.15975913568</v>
+      </c>
+      <c r="E314" s="3">
+        <v>8680.9984719799995</v>
+      </c>
+      <c r="F314" s="4">
+        <v>5.3628300774693723E-2</v>
+      </c>
+      <c r="G314" s="4">
+        <v>1.9809359137092151E-3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A315" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B315" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C315" s="2">
+        <v>1</v>
+      </c>
+      <c r="D315" s="3">
+        <v>396416.47748978873</v>
+      </c>
+      <c r="E315" s="3">
+        <v>10615.43888874</v>
+      </c>
+      <c r="F315" s="4">
+        <v>5.7122249315871114E-3</v>
+      </c>
+      <c r="G315" s="4">
+        <v>1.223257961926933E-3</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B317" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D317" s="3">
+        <f>AVERAGE(D312:D313)</f>
+        <v>539397.81040579407</v>
+      </c>
+      <c r="E317" s="3">
+        <f t="shared" ref="E317:G317" si="52">AVERAGE(E312:E313)</f>
+        <v>10784.211597880001</v>
+      </c>
+      <c r="F317" s="4">
+        <f t="shared" si="52"/>
+        <v>3.0192741349205411E-3</v>
+      </c>
+      <c r="G317" s="4">
+        <f t="shared" si="52"/>
+        <v>2.0541759430544771E-3</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B318" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D318" s="3">
+        <f>AVERAGE(D314:D315)</f>
+        <v>419160.81862446223</v>
+      </c>
+      <c r="E318" s="3">
+        <f t="shared" ref="E318:G318" si="53">AVERAGE(E314:E315)</f>
+        <v>9648.2186803599998</v>
+      </c>
+      <c r="F318" s="4">
+        <f t="shared" si="53"/>
+        <v>2.9670262853140415E-2</v>
+      </c>
+      <c r="G318" s="4">
+        <f t="shared" si="53"/>
+        <v>1.602096937818074E-3</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C320" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D320" s="3">
+        <f>D317/D318</f>
+        <v>1.2868516961482879</v>
+      </c>
+      <c r="E320" s="3">
+        <f t="shared" ref="E320:G320" si="54">E317/E318</f>
+        <v>1.1177412074865631</v>
+      </c>
+      <c r="F320" s="3">
+        <f t="shared" si="54"/>
+        <v>0.10176095000792922</v>
+      </c>
+      <c r="G320" s="3">
+        <f t="shared" si="54"/>
+        <v>1.2821795576565411</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C322" s="2">
+        <f>MAX(C312:C315)</f>
+        <v>4</v>
+      </c>
+      <c r="D322" s="2">
+        <f t="shared" ref="D322:G322" si="55">MAX(D312:D315)</f>
+        <v>615324.90182869229</v>
+      </c>
+      <c r="E322" s="2">
+        <f t="shared" si="55"/>
+        <v>12188.037840000001</v>
+      </c>
+      <c r="F322" s="2">
+        <f t="shared" si="55"/>
+        <v>5.3628300774693723E-2</v>
+      </c>
+      <c r="G322" s="2">
+        <f t="shared" si="55"/>
+        <v>2.3262126662383252E-3</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C323" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E236" s="10" t="s">
+      <c r="D323" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F236" s="10" t="s">
+      <c r="F323" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G236" s="10" t="s">
+      <c r="G323" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="237" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C237" s="3">
-        <v>0.76628830414256921</v>
-      </c>
-      <c r="D237" s="2">
+      <c r="J323" s="2"/>
+      <c r="K323" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L323" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C324" s="2">
+        <f>C312/C$322</f>
         <v>1</v>
       </c>
-      <c r="E237" s="2">
-        <v>0.65484380022836186</v>
-      </c>
-      <c r="F237" s="2">
+      <c r="D324" s="2">
+        <f>D312/D$322</f>
         <v>1</v>
       </c>
-      <c r="G237" s="2">
-        <v>0.3535046285504449</v>
-      </c>
-    </row>
-    <row r="238" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C238" s="3">
-        <v>0.78513813991475667</v>
-      </c>
-      <c r="D238" s="2">
+      <c r="E324" s="2">
+        <f>E312/E$322</f>
+        <v>1</v>
+      </c>
+      <c r="F324" s="2">
+        <f>F312/F$322</f>
+        <v>6.6315361695601274E-2</v>
+      </c>
+      <c r="G324" s="2">
+        <f>G312/G$322</f>
+        <v>1</v>
+      </c>
+      <c r="J324" s="10">
+        <v>27</v>
+      </c>
+      <c r="K324" s="3">
+        <f>0.5*(D309*E309+E309*F309+F309*G309+G309*D309)</f>
+        <v>0.46437907105783394</v>
+      </c>
+      <c r="L324" s="3">
+        <f>0.5*(D306*E306+E306*F306+F306*G306+G306*D306)</f>
+        <v>0.18913531858780386</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C325" s="2">
+        <f>C313/C$322</f>
         <v>0.75</v>
       </c>
-      <c r="E238" s="2">
+      <c r="D325" s="2">
+        <f>D313/D$322</f>
+        <v>0.75321300601601027</v>
+      </c>
+      <c r="E325" s="2">
+        <f>E313/E$322</f>
+        <v>0.76963868006501046</v>
+      </c>
+      <c r="F325" s="2">
+        <f>F313/F$322</f>
+        <v>4.6284668188071074E-2</v>
+      </c>
+      <c r="G325" s="2">
+        <f>G313/G$322</f>
+        <v>0.76611190616225677</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C326" s="2">
+        <f>C314/C$322</f>
+        <v>0.5</v>
+      </c>
+      <c r="D326" s="2">
+        <f>D314/D$322</f>
+        <v>0.71816557146611792</v>
+      </c>
+      <c r="E326" s="2">
+        <f>E314/E$322</f>
+        <v>0.71225562194184977</v>
+      </c>
+      <c r="F326" s="2">
+        <f>F314/F$322</f>
         <v>1</v>
       </c>
-      <c r="F238" s="2">
-        <v>0.67725490625943618</v>
-      </c>
-      <c r="G238" s="2">
+      <c r="G326" s="2">
+        <f>G314/G$322</f>
+        <v>0.85157128686456229</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C327" s="2">
+        <f>C315/C$322</f>
+        <v>0.25</v>
+      </c>
+      <c r="D327" s="2">
+        <f>D315/D$322</f>
+        <v>0.64423928937651198</v>
+      </c>
+      <c r="E327" s="2">
+        <f>E315/E$322</f>
+        <v>0.87097193396472083</v>
+      </c>
+      <c r="F327" s="2">
+        <f>F315/F$322</f>
+        <v>0.10651512073048215</v>
+      </c>
+      <c r="G327" s="2">
+        <f>G315/G$322</f>
+        <v>0.52585818127499084</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C329" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E329" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F329" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G329" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C330" s="3">
+        <v>0.64423928937651198</v>
+      </c>
+      <c r="D330" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E330" s="2">
+        <v>0.87097193396472083</v>
+      </c>
+      <c r="F330" s="2">
+        <v>0.10651512073048215</v>
+      </c>
+      <c r="G330" s="2">
+        <v>0.52585818127499084</v>
+      </c>
+    </row>
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C331" s="3">
+        <v>0.71816557146611792</v>
+      </c>
+      <c r="D331" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E331" s="2">
+        <v>0.71225562194184977</v>
+      </c>
+      <c r="F331" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="239" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C239" s="3">
-        <v>0.81797233553377002</v>
-      </c>
-      <c r="D239" s="2">
+      <c r="G331" s="2">
+        <v>0.85157128686456229</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C332" s="3">
+        <v>0.75321300601601027</v>
+      </c>
+      <c r="D332" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E332" s="2">
+        <v>0.76963868006501046</v>
+      </c>
+      <c r="F332" s="2">
+        <v>4.6284668188071074E-2</v>
+      </c>
+      <c r="G332" s="2">
+        <v>0.76611190616225677</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C333" s="3">
+        <v>1</v>
+      </c>
+      <c r="D333" s="2">
+        <v>1</v>
+      </c>
+      <c r="E333" s="2">
+        <v>1</v>
+      </c>
+      <c r="F333" s="2">
+        <v>6.6315361695601274E-2</v>
+      </c>
+      <c r="G333" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E335" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F335" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G335" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A336" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B336" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C336" s="2">
+        <v>1</v>
+      </c>
+      <c r="D336" s="3">
+        <v>480752.63075950177</v>
+      </c>
+      <c r="E336" s="3">
+        <v>13713.99982974</v>
+      </c>
+      <c r="F336" s="4">
+        <v>1.8909555433829729E-4</v>
+      </c>
+      <c r="G336" s="4">
+        <v>1.421912259449817E-2</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A337" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B337" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C337" s="2">
+        <v>4</v>
+      </c>
+      <c r="D337" s="3">
+        <v>430680.74778667098</v>
+      </c>
+      <c r="E337" s="3">
+        <v>9650.7308639999992</v>
+      </c>
+      <c r="F337" s="4">
+        <v>3.2382873836611008E-4</v>
+      </c>
+      <c r="G337" s="4">
+        <v>1.307147425181787E-3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A338" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C338" s="2">
+        <v>3</v>
+      </c>
+      <c r="D338" s="3">
+        <v>344818.33344279532</v>
+      </c>
+      <c r="E338" s="3">
+        <v>7766.5175531200011</v>
+      </c>
+      <c r="F338" s="4">
+        <v>5.6879237956854514E-4</v>
+      </c>
+      <c r="G338" s="4">
+        <v>9.2862762115340628E-4</v>
+      </c>
+    </row>
+    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A339" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B339" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C339" s="2">
+        <v>2</v>
+      </c>
+      <c r="D339" s="3">
+        <v>310794.74797233898</v>
+      </c>
+      <c r="E339" s="3">
+        <v>8210.8821614400003</v>
+      </c>
+      <c r="F339" s="4">
+        <v>1.515288413031857E-4</v>
+      </c>
+      <c r="G339" s="4">
+        <v>1.134724744407487E-2</v>
+      </c>
+    </row>
+    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B341" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D341" s="3">
+        <f>AVERAGE(D336:D337)</f>
+        <v>455716.68927308638</v>
+      </c>
+      <c r="E341" s="3">
+        <f t="shared" ref="E341:G341" si="56">AVERAGE(E336:E337)</f>
+        <v>11682.365346869999</v>
+      </c>
+      <c r="F341" s="4">
+        <f t="shared" si="56"/>
+        <v>2.5646214635220368E-4</v>
+      </c>
+      <c r="G341" s="4">
+        <f t="shared" si="56"/>
+        <v>7.7631350098399787E-3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B342" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D342" s="3">
+        <f>AVERAGE(D338:D339)</f>
+        <v>327806.54070756712</v>
+      </c>
+      <c r="E342" s="3">
+        <f t="shared" ref="E342:G342" si="57">AVERAGE(E338:E339)</f>
+        <v>7988.6998572800003</v>
+      </c>
+      <c r="F342" s="4">
+        <f t="shared" si="57"/>
+        <v>3.6016061043586542E-4</v>
+      </c>
+      <c r="G342" s="4">
+        <f t="shared" si="57"/>
+        <v>6.1379375326141381E-3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C344" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D344" s="3">
+        <f>D341/D342</f>
+        <v>1.3902001109844437</v>
+      </c>
+      <c r="E344" s="3">
+        <f t="shared" ref="E344:G344" si="58">E341/E342</f>
+        <v>1.462361279754929</v>
+      </c>
+      <c r="F344" s="3">
+        <f t="shared" si="58"/>
+        <v>0.71207716480109773</v>
+      </c>
+      <c r="G344" s="3">
+        <f t="shared" si="58"/>
+        <v>1.2647790839496653</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C346" s="2">
+        <f>MAX(C336:C339)</f>
+        <v>4</v>
+      </c>
+      <c r="D346" s="2">
+        <f t="shared" ref="D346:G346" si="59">MAX(D336:D339)</f>
+        <v>480752.63075950177</v>
+      </c>
+      <c r="E346" s="2">
+        <f t="shared" si="59"/>
+        <v>13713.99982974</v>
+      </c>
+      <c r="F346" s="2">
+        <f t="shared" si="59"/>
+        <v>5.6879237956854514E-4</v>
+      </c>
+      <c r="G346" s="2">
+        <f t="shared" si="59"/>
+        <v>1.421912259449817E-2</v>
+      </c>
+    </row>
+    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C347" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D347" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E347" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F347" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G347" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J347" s="2"/>
+      <c r="K347" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L347" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C348" s="2">
+        <f>C336/C$346</f>
+        <v>0.25</v>
+      </c>
+      <c r="D348" s="2">
+        <f>D336/D$346</f>
+        <v>1</v>
+      </c>
+      <c r="E348" s="2">
+        <f>E336/E$346</f>
+        <v>1</v>
+      </c>
+      <c r="F348" s="2">
+        <f>F336/F$346</f>
+        <v>0.33245092784424229</v>
+      </c>
+      <c r="G348" s="2">
+        <f>G336/G$346</f>
+        <v>1</v>
+      </c>
+      <c r="J348" s="10">
+        <v>28</v>
+      </c>
+      <c r="K348" s="3">
+        <f>0.5*(D333*E333+E333*F333+F333*G333+G333*D333)</f>
+        <v>1.0663153616956014</v>
+      </c>
+      <c r="L348" s="3">
+        <f>0.5*(D330*E330+E330*F330+F330*G330+G330*D330)</f>
+        <v>0.24899552858732954</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C349" s="2">
+        <f>C337/C$346</f>
+        <v>1</v>
+      </c>
+      <c r="D349" s="2">
+        <f>D337/D$346</f>
+        <v>0.89584688721572603</v>
+      </c>
+      <c r="E349" s="2">
+        <f>E337/E$346</f>
+        <v>0.70371379494052133</v>
+      </c>
+      <c r="F349" s="2">
+        <f>F337/F$346</f>
+        <v>0.56932678776700363</v>
+      </c>
+      <c r="G349" s="2">
+        <f>G337/G$346</f>
+        <v>9.1928838540822747E-2</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C350" s="2">
+        <f>C338/C$346</f>
+        <v>0.75</v>
+      </c>
+      <c r="D350" s="2">
+        <f>D338/D$346</f>
+        <v>0.7172468986764462</v>
+      </c>
+      <c r="E350" s="2">
+        <f>E338/E$346</f>
+        <v>0.56632037695360282</v>
+      </c>
+      <c r="F350" s="2">
+        <f>F338/F$346</f>
+        <v>1</v>
+      </c>
+      <c r="G350" s="2">
+        <f>G338/G$346</f>
+        <v>6.5308363085126067E-2</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C351" s="2">
+        <f>C339/C$346</f>
         <v>0.5</v>
       </c>
-      <c r="E239" s="2">
-        <v>0.73835805970790658</v>
-      </c>
-      <c r="F239" s="2">
-        <v>0.84927446007410101</v>
-      </c>
-      <c r="G239" s="2">
-        <v>0.78959028422057287</v>
-      </c>
-    </row>
-    <row r="240" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C240" s="3">
+      <c r="D351" s="2">
+        <f>D339/D$346</f>
+        <v>0.64647539729806525</v>
+      </c>
+      <c r="E351" s="2">
+        <f>E339/E$346</f>
+        <v>0.59872263842631746</v>
+      </c>
+      <c r="F351" s="2">
+        <f>F339/F$346</f>
+        <v>0.26640448561938757</v>
+      </c>
+      <c r="G351" s="2">
+        <f>G339/G$346</f>
+        <v>0.798027260026964</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C353" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E353" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F353" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G353" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C354" s="3">
+        <v>0.64647539729806525</v>
+      </c>
+      <c r="D354" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E354" s="2">
+        <v>0.59872263842631746</v>
+      </c>
+      <c r="F354" s="2">
+        <v>0.26640448561938757</v>
+      </c>
+      <c r="G354" s="2">
+        <v>0.798027260026964</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C355" s="3">
+        <v>0.7172468986764462</v>
+      </c>
+      <c r="D355" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E355" s="2">
+        <v>0.56632037695360282</v>
+      </c>
+      <c r="F355" s="2">
         <v>1</v>
       </c>
-      <c r="D240" s="2">
+      <c r="G355" s="2">
+        <v>6.5308363085126067E-2</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C356" s="3">
+        <v>0.89584688721572603</v>
+      </c>
+      <c r="D356" s="2">
+        <v>1</v>
+      </c>
+      <c r="E356" s="2">
+        <v>0.70371379494052133</v>
+      </c>
+      <c r="F356" s="2">
+        <v>0.56932678776700363</v>
+      </c>
+      <c r="G356" s="2">
+        <v>9.1928838540822747E-2</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C357" s="3">
+        <v>1</v>
+      </c>
+      <c r="D357" s="2">
         <v>0.25</v>
       </c>
-      <c r="E240" s="2">
-        <v>0.62244477507294493</v>
-      </c>
-      <c r="F240" s="2">
-        <v>0.83919206923346823</v>
-      </c>
-      <c r="G240" s="2">
-        <v>0.50155358560624896</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A243" s="1" t="s">
+      <c r="E357" s="2">
+        <v>1</v>
+      </c>
+      <c r="F357" s="2">
+        <v>0.33245092784424229</v>
+      </c>
+      <c r="G357" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B243" s="1" t="s">
+      <c r="B359" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C243" s="1" t="s">
+      <c r="C359" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D243" s="1" t="s">
+      <c r="D359" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E243" s="1" t="s">
+      <c r="E359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F243" s="1" t="s">
+      <c r="F359" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G243" s="1" t="s">
+      <c r="G359" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A244" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B244" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C244" s="2">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A360" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B360" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C360" s="2">
         <v>4</v>
       </c>
-      <c r="D244" s="3">
-        <v>1079590.799601601</v>
-      </c>
-      <c r="E244" s="3">
-        <v>29824.255583999999</v>
-      </c>
-      <c r="F244" s="4">
-        <v>1.7700063980245699E-2</v>
-      </c>
-      <c r="G244" s="4">
-        <v>1.8406361575525849E-2</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A245" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B245" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C245" s="2">
+      <c r="D360" s="3">
+        <v>624490.81179662514</v>
+      </c>
+      <c r="E360" s="3">
+        <v>23490.718752000001</v>
+      </c>
+      <c r="F360" s="4">
+        <v>1.927088927244758E-3</v>
+      </c>
+      <c r="G360" s="4">
+        <v>1.8760825696850091E-3</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A361" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B361" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C361" s="2">
         <v>3</v>
       </c>
-      <c r="D245" s="3">
-        <v>917032.53729645221</v>
-      </c>
-      <c r="E245" s="3">
-        <v>21948.7441788</v>
-      </c>
-      <c r="F245" s="4">
-        <v>5.1385668600091312E-2</v>
-      </c>
-      <c r="G245" s="4">
-        <v>1.045825844659099E-3</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A246" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B246" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C246" s="2">
+      <c r="D361" s="3">
+        <v>615005.46689121344</v>
+      </c>
+      <c r="E361" s="3">
+        <v>18304.5266156</v>
+      </c>
+      <c r="F361" s="4">
+        <v>2.0544865338363899E-3</v>
+      </c>
+      <c r="G361" s="4">
+        <v>2.397692315221963E-3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A362" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B362" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C362" s="2">
+        <v>1</v>
+      </c>
+      <c r="D362" s="3">
+        <v>557880.96074185451</v>
+      </c>
+      <c r="E362" s="3">
+        <v>17673.58753398</v>
+      </c>
+      <c r="F362" s="4">
+        <v>1.2639185721094849E-3</v>
+      </c>
+      <c r="G362" s="4">
+        <v>7.224852054202324E-4</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A363" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B363" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C363" s="2">
         <v>2</v>
       </c>
-      <c r="D246" s="3">
-        <v>802566.08061441511</v>
-      </c>
-      <c r="E246" s="3">
-        <v>12046.641059559999</v>
-      </c>
-      <c r="F246" s="4">
-        <v>1.264319260007594E-2</v>
-      </c>
-      <c r="G246" s="4">
-        <v>9.2646432850616075E-4</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A247" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B247" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C247" s="2">
+      <c r="D363" s="3">
+        <v>528936.59684355662</v>
+      </c>
+      <c r="E363" s="3">
+        <v>14840.029964359999</v>
+      </c>
+      <c r="F363" s="4">
+        <v>3.348617336982791E-3</v>
+      </c>
+      <c r="G363" s="4">
+        <v>9.7700369843055682E-4</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B365" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D365" s="3">
+        <f>AVERAGE(D360:D361)</f>
+        <v>619748.13934391923</v>
+      </c>
+      <c r="E365" s="3">
+        <f t="shared" ref="E365:G365" si="60">AVERAGE(E360:E361)</f>
+        <v>20897.6226838</v>
+      </c>
+      <c r="F365" s="4">
+        <f t="shared" si="60"/>
+        <v>1.9907877305405742E-3</v>
+      </c>
+      <c r="G365" s="4">
+        <f t="shared" si="60"/>
+        <v>2.1368874424534858E-3</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B366" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D366" s="3">
+        <f>AVERAGE(D362:D363)</f>
+        <v>543408.77879270562</v>
+      </c>
+      <c r="E366" s="3">
+        <f t="shared" ref="E366:G366" si="61">AVERAGE(E362:E363)</f>
+        <v>16256.808749169999</v>
+      </c>
+      <c r="F366" s="4">
+        <f t="shared" si="61"/>
+        <v>2.3062679545461382E-3</v>
+      </c>
+      <c r="G366" s="4">
+        <f t="shared" si="61"/>
+        <v>8.4974445192539461E-4</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C368" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D368" s="3">
+        <f>D365/D366</f>
+        <v>1.1404823836685474</v>
+      </c>
+      <c r="E368" s="3">
+        <f t="shared" ref="E368:G368" si="62">E365/E366</f>
+        <v>1.2854689383527957</v>
+      </c>
+      <c r="F368" s="3">
+        <f t="shared" si="62"/>
+        <v>0.8632074718882139</v>
+      </c>
+      <c r="G368" s="3">
+        <f t="shared" si="62"/>
+        <v>2.5147412702861627</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C370" s="2">
+        <f>MAX(C360:C363)</f>
+        <v>4</v>
+      </c>
+      <c r="D370" s="2">
+        <f t="shared" ref="D370:G370" si="63">MAX(D360:D363)</f>
+        <v>624490.81179662514</v>
+      </c>
+      <c r="E370" s="2">
+        <f t="shared" si="63"/>
+        <v>23490.718752000001</v>
+      </c>
+      <c r="F370" s="2">
+        <f t="shared" si="63"/>
+        <v>3.348617336982791E-3</v>
+      </c>
+      <c r="G370" s="2">
+        <f t="shared" si="63"/>
+        <v>2.397692315221963E-3</v>
+      </c>
+    </row>
+    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C371" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D371" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E371" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F371" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G371" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J371" s="2"/>
+      <c r="K371" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L371" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C372" s="2">
+        <f>C360/C$370</f>
         <v>1</v>
       </c>
-      <c r="D247" s="3">
-        <v>774599.50938466226</v>
-      </c>
-      <c r="E247" s="3">
-        <v>31768.917493320001</v>
-      </c>
-      <c r="F247" s="4">
-        <v>4.5024994770462897E-3</v>
-      </c>
-      <c r="G247" s="4">
-        <v>6.1504127372638605E-4</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B249" s="7" t="s">
+      <c r="D372" s="2">
+        <f>D360/D$370</f>
+        <v>1</v>
+      </c>
+      <c r="E372" s="2">
+        <f>E360/E$370</f>
+        <v>1</v>
+      </c>
+      <c r="F372" s="2">
+        <f>F360/F$370</f>
+        <v>0.57548795019413157</v>
+      </c>
+      <c r="G372" s="2">
+        <f>G360/G$370</f>
+        <v>0.78245342731197487</v>
+      </c>
+      <c r="J372" s="10">
+        <v>29</v>
+      </c>
+      <c r="K372" s="3">
+        <f>0.5*(D357*E357+E357*F357+F357*G357+G357*D357)</f>
+        <v>0.58245092784424224</v>
+      </c>
+      <c r="L372" s="3">
+        <f>0.5*(D354*E354+E354*F354+F354*G354+G354*D354)</f>
+        <v>0.53523769373150953</v>
+      </c>
+    </row>
+    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C373" s="2">
+        <f>C361/C$370</f>
+        <v>0.75</v>
+      </c>
+      <c r="D373" s="2">
+        <f>D361/D$370</f>
+        <v>0.98481107371600407</v>
+      </c>
+      <c r="E373" s="2">
+        <f>E361/E$370</f>
+        <v>0.77922377807369358</v>
+      </c>
+      <c r="F373" s="2">
+        <f>F361/F$370</f>
+        <v>0.61353278893537189</v>
+      </c>
+      <c r="G373" s="2">
+        <f>G361/G$370</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C374" s="2">
+        <f>C362/C$370</f>
+        <v>0.25</v>
+      </c>
+      <c r="D374" s="2">
+        <f>D362/D$370</f>
+        <v>0.89333734012332733</v>
+      </c>
+      <c r="E374" s="2">
+        <f>E362/E$370</f>
+        <v>0.7523646986099678</v>
+      </c>
+      <c r="F374" s="2">
+        <f>F362/F$370</f>
+        <v>0.3774449108145379</v>
+      </c>
+      <c r="G374" s="2">
+        <f>G362/G$370</f>
+        <v>0.30132523711798664</v>
+      </c>
+    </row>
+    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C375" s="2">
+        <f>C363/C$370</f>
+        <v>0.5</v>
+      </c>
+      <c r="D375" s="2">
+        <f>D363/D$370</f>
+        <v>0.84698859751328548</v>
+      </c>
+      <c r="E375" s="2">
+        <f>E363/E$370</f>
+        <v>0.63174014047980198</v>
+      </c>
+      <c r="F375" s="2">
+        <f>F363/F$370</f>
+        <v>1</v>
+      </c>
+      <c r="G375" s="2">
+        <f>G363/G$370</f>
+        <v>0.40747667756532474</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C377" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D377" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E377" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F377" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G377" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C378" s="3">
+        <v>0.84698859751328548</v>
+      </c>
+      <c r="D378" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E378" s="2">
+        <v>0.63174014047980198</v>
+      </c>
+      <c r="F378" s="2">
+        <v>1</v>
+      </c>
+      <c r="G378" s="2">
+        <v>0.40747667756532474</v>
+      </c>
+    </row>
+    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C379" s="3">
+        <v>0.89333734012332733</v>
+      </c>
+      <c r="D379" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E379" s="2">
+        <v>0.7523646986099678</v>
+      </c>
+      <c r="F379" s="2">
+        <v>0.3774449108145379</v>
+      </c>
+      <c r="G379" s="2">
+        <v>0.30132523711798664</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C380" s="3">
+        <v>0.98481107371600407</v>
+      </c>
+      <c r="D380" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E380" s="2">
+        <v>0.77922377807369358</v>
+      </c>
+      <c r="F380" s="2">
+        <v>0.61353278893537189</v>
+      </c>
+      <c r="G380" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C381" s="3">
+        <v>1</v>
+      </c>
+      <c r="D381" s="2">
+        <v>1</v>
+      </c>
+      <c r="E381" s="2">
+        <v>1</v>
+      </c>
+      <c r="F381" s="2">
+        <v>0.57548795019413157</v>
+      </c>
+      <c r="G381" s="2">
+        <v>0.78245342731197487</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A383" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D383" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E383" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F383" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G383" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A384" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B384" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C384" s="2">
+        <v>1</v>
+      </c>
+      <c r="D384" s="3">
+        <v>496312.33844584553</v>
+      </c>
+      <c r="E384" s="3">
+        <v>6058.6276942799996</v>
+      </c>
+      <c r="F384" s="4">
+        <v>1.149126975828702E-3</v>
+      </c>
+      <c r="G384" s="4">
+        <v>4.3326889923906344E-3</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A385" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B385" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C385" s="5">
+        <v>3</v>
+      </c>
+      <c r="D385" s="3">
+        <v>481190.63450056087</v>
+      </c>
+      <c r="E385" s="3">
+        <v>5659.2905294400007</v>
+      </c>
+      <c r="F385" s="4">
+        <v>2.7642536319032169E-4</v>
+      </c>
+      <c r="G385" s="4">
+        <v>2.609783923120391E-3</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A386" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B386" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C386" s="2">
+        <v>2</v>
+      </c>
+      <c r="D386" s="3">
+        <v>463554.2380744408</v>
+      </c>
+      <c r="E386" s="3">
+        <v>6405.1162323599992</v>
+      </c>
+      <c r="F386" s="4">
+        <v>1.36542870460566E-3</v>
+      </c>
+      <c r="G386" s="4">
+        <v>1.06191448730258E-3</v>
+      </c>
+    </row>
+    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A387" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B387" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C387" s="2">
+        <v>4</v>
+      </c>
+      <c r="D387" s="3">
+        <v>463215.01884109463</v>
+      </c>
+      <c r="E387" s="3">
+        <v>6600.4823040000001</v>
+      </c>
+      <c r="F387" s="4">
+        <v>1.0184783005820781E-3</v>
+      </c>
+      <c r="G387" s="4">
+        <v>1.1952508372333631E-3</v>
+      </c>
+    </row>
+    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B389" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D249" s="3">
-        <f>AVERAGE(D244:D245)</f>
-        <v>998311.66844902653</v>
-      </c>
-      <c r="E249" s="3">
-        <f t="shared" ref="E249:G249" si="44">AVERAGE(E244:E245)</f>
-        <v>25886.499881399999</v>
-      </c>
-      <c r="F249" s="4">
-        <f t="shared" si="44"/>
-        <v>3.4542866290168506E-2</v>
-      </c>
-      <c r="G249" s="4">
-        <f t="shared" si="44"/>
-        <v>9.7260937100924743E-3</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B250" s="7" t="s">
+      <c r="D389" s="3">
+        <f>AVERAGE(D384:D385)</f>
+        <v>488751.48647320317</v>
+      </c>
+      <c r="E389" s="3">
+        <f t="shared" ref="E389:G389" si="64">AVERAGE(E384:E385)</f>
+        <v>5858.9591118600001</v>
+      </c>
+      <c r="F389" s="4">
+        <f t="shared" si="64"/>
+        <v>7.1277616950951182E-4</v>
+      </c>
+      <c r="G389" s="4">
+        <f t="shared" si="64"/>
+        <v>3.4712364577555127E-3</v>
+      </c>
+    </row>
+    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B390" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D250" s="3">
-        <f>AVERAGE(D246:D247)</f>
-        <v>788582.79499953869</v>
-      </c>
-      <c r="E250" s="3">
-        <f t="shared" ref="E250:G250" si="45">AVERAGE(E246:E247)</f>
-        <v>21907.77927644</v>
-      </c>
-      <c r="F250" s="4">
-        <f t="shared" si="45"/>
-        <v>8.5728460385611147E-3</v>
-      </c>
-      <c r="G250" s="4">
-        <f t="shared" si="45"/>
-        <v>7.7075280111627334E-4</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C252" s="7" t="s">
+      <c r="D390" s="3">
+        <f>AVERAGE(D386:D387)</f>
+        <v>463384.62845776771</v>
+      </c>
+      <c r="E390" s="3">
+        <f t="shared" ref="E390:G390" si="65">AVERAGE(E386:E387)</f>
+        <v>6502.7992681799997</v>
+      </c>
+      <c r="F390" s="4">
+        <f t="shared" si="65"/>
+        <v>1.191953502593869E-3</v>
+      </c>
+      <c r="G390" s="4">
+        <f t="shared" si="65"/>
+        <v>1.1285826622679715E-3</v>
+      </c>
+    </row>
+    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C392" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D252" s="3">
-        <f>D249/D250</f>
-        <v>1.2659566944389276</v>
-      </c>
-      <c r="E252" s="3">
-        <f t="shared" ref="E252:G252" si="46">E249/E250</f>
-        <v>1.1816122280015293</v>
-      </c>
-      <c r="F252" s="3">
-        <f t="shared" si="46"/>
-        <v>4.0293347314057506</v>
-      </c>
-      <c r="G252" s="3">
-        <f t="shared" si="46"/>
-        <v>12.618953438776055</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C254" s="2">
-        <f>MAX(C244:C247)</f>
+      <c r="D392" s="3">
+        <f>D389/D390</f>
+        <v>1.0547425539337831</v>
+      </c>
+      <c r="E392" s="3">
+        <f t="shared" ref="E392:G392" si="66">E389/E390</f>
+        <v>0.9009903074402914</v>
+      </c>
+      <c r="F392" s="3">
+        <f t="shared" si="66"/>
+        <v>0.59798991148430225</v>
+      </c>
+      <c r="G392" s="3">
+        <f t="shared" si="66"/>
+        <v>3.0757485240645135</v>
+      </c>
+    </row>
+    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C394" s="2">
+        <f>MAX(C384:C387)</f>
         <v>4</v>
       </c>
-      <c r="D254" s="2">
-        <f t="shared" ref="D254:G254" si="47">MAX(D244:D247)</f>
-        <v>1079590.799601601</v>
-      </c>
-      <c r="E254" s="2">
-        <f t="shared" si="47"/>
-        <v>31768.917493320001</v>
-      </c>
-      <c r="F254" s="2">
-        <f t="shared" si="47"/>
-        <v>5.1385668600091312E-2</v>
-      </c>
-      <c r="G254" s="2">
-        <f t="shared" si="47"/>
-        <v>1.8406361575525849E-2</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C255" s="10" t="s">
+      <c r="D394" s="2">
+        <f t="shared" ref="D394:G394" si="67">MAX(D384:D387)</f>
+        <v>496312.33844584553</v>
+      </c>
+      <c r="E394" s="2">
+        <f t="shared" si="67"/>
+        <v>6600.4823040000001</v>
+      </c>
+      <c r="F394" s="2">
+        <f t="shared" si="67"/>
+        <v>1.36542870460566E-3</v>
+      </c>
+      <c r="G394" s="2">
+        <f t="shared" si="67"/>
+        <v>4.3326889923906344E-3</v>
+      </c>
+    </row>
+    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C395" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D255" s="10" t="s">
+      <c r="D395" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E255" s="1" t="s">
+      <c r="E395" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F255" s="1" t="s">
+      <c r="F395" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G255" s="1" t="s">
+      <c r="G395" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C256" s="2">
-        <f>C244/C$254</f>
+      <c r="J395" s="2"/>
+      <c r="K395" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L395" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C396" s="2">
+        <f>C384/C$394</f>
+        <v>0.25</v>
+      </c>
+      <c r="D396" s="2">
+        <f>D384/D$394</f>
         <v>1</v>
       </c>
-      <c r="D256" s="2">
-        <f t="shared" ref="D256:G256" si="48">D244/D$254</f>
+      <c r="E396" s="2">
+        <f>E384/E$394</f>
+        <v>0.91790681578047295</v>
+      </c>
+      <c r="F396" s="2">
+        <f>F384/F$394</f>
+        <v>0.84158694771293341</v>
+      </c>
+      <c r="G396" s="2">
+        <f>G384/G$394</f>
         <v>1</v>
       </c>
-      <c r="E256" s="2">
-        <f t="shared" si="48"/>
-        <v>0.93878727817122176</v>
-      </c>
-      <c r="F256" s="2">
-        <f t="shared" si="48"/>
-        <v>0.34445526276978805</v>
-      </c>
-      <c r="G256" s="2">
-        <f t="shared" si="48"/>
+      <c r="J396" s="10">
+        <v>30</v>
+      </c>
+      <c r="K396" s="3">
+        <f>0.5*(D381*E381+E381*F381+F381*G381+G381*D381)</f>
+        <v>1.404116948256124</v>
+      </c>
+      <c r="L396" s="3">
+        <f>0.5*(D378*E378+E378*F378+F378*G378+G378*D378)</f>
+        <v>0.77941261353384506</v>
+      </c>
+    </row>
+    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C397" s="2">
+        <f>C385/C$394</f>
+        <v>0.75</v>
+      </c>
+      <c r="D397" s="2">
+        <f>D385/D$394</f>
+        <v>0.96953187987903577</v>
+      </c>
+      <c r="E397" s="2">
+        <f>E385/E$394</f>
+        <v>0.85740560595251925</v>
+      </c>
+      <c r="F397" s="2">
+        <f>F385/F$394</f>
+        <v>0.20244584155725229</v>
+      </c>
+      <c r="G397" s="2">
+        <f>G385/G$394</f>
+        <v>0.60234739389415504</v>
+      </c>
+    </row>
+    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C398" s="2">
+        <f>C386/C$394</f>
+        <v>0.5</v>
+      </c>
+      <c r="D398" s="2">
+        <f>D386/D$394</f>
+        <v>0.93399700584921264</v>
+      </c>
+      <c r="E398" s="2">
+        <f>E386/E$394</f>
+        <v>0.97040124302407327</v>
+      </c>
+      <c r="F398" s="2">
+        <f>F386/F$394</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C257" s="2">
-        <f t="shared" ref="C257:G259" si="49">C245/C$254</f>
+      <c r="G398" s="2">
+        <f>G386/G$394</f>
+        <v>0.24509363334584758</v>
+      </c>
+    </row>
+    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C399" s="2">
+        <f>C387/C$394</f>
+        <v>1</v>
+      </c>
+      <c r="D399" s="2">
+        <f>D387/D$394</f>
+        <v>0.93331352650149302</v>
+      </c>
+      <c r="E399" s="2">
+        <f>E387/E$394</f>
+        <v>1</v>
+      </c>
+      <c r="F399" s="2">
+        <f>F387/F$394</f>
+        <v>0.7459036836904771</v>
+      </c>
+      <c r="G399" s="2">
+        <f>G387/G$394</f>
+        <v>0.27586813623884487</v>
+      </c>
+    </row>
+    <row r="401" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C401" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D401" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E401" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F401" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G401" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="402" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C402" s="3">
+        <v>0.93331352650149302</v>
+      </c>
+      <c r="D402" s="2">
+        <v>1</v>
+      </c>
+      <c r="E402" s="2">
+        <v>1</v>
+      </c>
+      <c r="F402" s="2">
+        <v>0.7459036836904771</v>
+      </c>
+      <c r="G402" s="2">
+        <v>0.27586813623884487</v>
+      </c>
+    </row>
+    <row r="403" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C403" s="3">
+        <v>0.93399700584921264</v>
+      </c>
+      <c r="D403" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E403" s="2">
+        <v>0.97040124302407327</v>
+      </c>
+      <c r="F403" s="2">
+        <v>1</v>
+      </c>
+      <c r="G403" s="2">
+        <v>0.24509363334584758</v>
+      </c>
+    </row>
+    <row r="404" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C404" s="3">
+        <v>0.96953187987903577</v>
+      </c>
+      <c r="D404" s="2">
         <v>0.75</v>
       </c>
-      <c r="D257" s="2">
-        <f t="shared" si="49"/>
-        <v>0.84942603960209995</v>
-      </c>
-      <c r="E257" s="2">
-        <f t="shared" si="49"/>
-        <v>0.69088738020157991</v>
-      </c>
-      <c r="F257" s="2">
-        <f t="shared" si="49"/>
+      <c r="E404" s="2">
+        <v>0.85740560595251925</v>
+      </c>
+      <c r="F404" s="2">
+        <v>0.20244584155725229</v>
+      </c>
+      <c r="G404" s="2">
+        <v>0.60234739389415504</v>
+      </c>
+    </row>
+    <row r="405" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C405" s="3">
         <v>1</v>
       </c>
-      <c r="G257" s="2">
-        <f t="shared" si="49"/>
-        <v>5.6818716744632944E-2</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C258" s="2">
-        <f t="shared" si="49"/>
-        <v>0.5</v>
-      </c>
-      <c r="D258" s="2">
-        <f t="shared" si="49"/>
-        <v>0.74339840698029691</v>
-      </c>
-      <c r="E258" s="2">
-        <f t="shared" si="49"/>
-        <v>0.37919583070757845</v>
-      </c>
-      <c r="F258" s="2">
-        <f t="shared" si="49"/>
-        <v>0.24604511227578876</v>
-      </c>
-      <c r="G258" s="2">
-        <f t="shared" si="49"/>
-        <v>5.0333919862687079E-2</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C259" s="2">
-        <f t="shared" si="49"/>
+      <c r="D405" s="2">
         <v>0.25</v>
       </c>
-      <c r="D259" s="2">
-        <f t="shared" si="49"/>
-        <v>0.71749361857336225</v>
-      </c>
-      <c r="E259" s="2">
-        <f t="shared" si="49"/>
-        <v>1</v>
-      </c>
-      <c r="F259" s="2">
-        <f t="shared" si="49"/>
-        <v>8.7621696860402221E-2</v>
-      </c>
-      <c r="G259" s="2">
-        <f t="shared" si="49"/>
-        <v>3.3414603489272977E-2</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C261" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D261" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E261" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F261" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G261" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C262" s="3">
-        <v>0.71749361857336225</v>
-      </c>
-      <c r="D262" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E262" s="2">
-        <v>1</v>
-      </c>
-      <c r="F262" s="2">
-        <v>8.7621696860402221E-2</v>
-      </c>
-      <c r="G262" s="2">
-        <v>3.3414603489272977E-2</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C263" s="3">
-        <v>0.74339840698029691</v>
-      </c>
-      <c r="D263" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E263" s="2">
-        <v>0.37919583070757845</v>
-      </c>
-      <c r="F263" s="2">
-        <v>0.24604511227578876</v>
-      </c>
-      <c r="G263" s="2">
-        <v>5.0333919862687079E-2</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C264" s="3">
-        <v>0.84942603960209995</v>
-      </c>
-      <c r="D264" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E264" s="2">
-        <v>0.69088738020157991</v>
-      </c>
-      <c r="F264" s="2">
-        <v>1</v>
-      </c>
-      <c r="G264" s="2">
-        <v>5.6818716744632944E-2</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C265" s="3">
-        <v>1</v>
-      </c>
-      <c r="D265" s="2">
-        <v>1</v>
-      </c>
-      <c r="E265" s="2">
-        <v>0.93878727817122176</v>
-      </c>
-      <c r="F265" s="2">
-        <v>0.34445526276978805</v>
-      </c>
-      <c r="G265" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A268" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C268" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E268" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F268" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G268" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A269" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B269" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C269" s="2">
-        <v>4</v>
-      </c>
-      <c r="D269" s="3">
-        <v>702640.28510284843</v>
-      </c>
-      <c r="E269" s="3">
-        <v>24692.815392</v>
-      </c>
-      <c r="F269" s="4">
-        <v>1.2473785395074479E-2</v>
-      </c>
-      <c r="G269" s="4">
-        <v>1.210844187888221E-3</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A270" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B270" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C270" s="2">
-        <v>3</v>
-      </c>
-      <c r="D270" s="3">
-        <v>648523.59030139784</v>
-      </c>
-      <c r="E270" s="3">
-        <v>20365.73930736</v>
-      </c>
-      <c r="F270" s="4">
-        <v>2.3285205202868371E-2</v>
-      </c>
-      <c r="G270" s="4">
-        <v>1.5783067550306741E-3</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A271" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B271" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C271" s="2">
-        <v>2</v>
-      </c>
-      <c r="D271" s="3">
-        <v>525586.90611574077</v>
-      </c>
-      <c r="E271" s="3">
-        <v>57596.7124071</v>
-      </c>
-      <c r="F271" s="4">
-        <v>6.9328647193893768E-4</v>
-      </c>
-      <c r="G271" s="4">
-        <v>1.2640594598421069E-2</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A272" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B272" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C272" s="2">
-        <v>1</v>
-      </c>
-      <c r="D272" s="3">
-        <v>489831.22166003252</v>
-      </c>
-      <c r="E272" s="3">
-        <v>28233.8392518</v>
-      </c>
-      <c r="F272" s="4">
-        <v>1.7629362658082969E-3</v>
-      </c>
-      <c r="G272" s="4">
-        <v>1.091290811894655E-3</v>
-      </c>
-    </row>
-    <row r="274" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B274" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D274" s="3">
-        <f>AVERAGE(D269:D270)</f>
-        <v>675581.93770212308</v>
-      </c>
-      <c r="E274" s="3">
-        <f t="shared" ref="E274:G274" si="50">AVERAGE(E269:E270)</f>
-        <v>22529.27734968</v>
-      </c>
-      <c r="F274" s="4">
-        <f t="shared" si="50"/>
-        <v>1.7879495298971426E-2</v>
-      </c>
-      <c r="G274" s="4">
-        <f t="shared" si="50"/>
-        <v>1.3945754714594475E-3</v>
-      </c>
-    </row>
-    <row r="275" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B275" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D275" s="3">
-        <f>AVERAGE(D271:D272)</f>
-        <v>507709.06388788664</v>
-      </c>
-      <c r="E275" s="3">
-        <f t="shared" ref="E275:G275" si="51">AVERAGE(E271:E272)</f>
-        <v>42915.275829450002</v>
-      </c>
-      <c r="F275" s="4">
-        <f t="shared" si="51"/>
-        <v>1.2281113688736172E-3</v>
-      </c>
-      <c r="G275" s="4">
-        <f t="shared" si="51"/>
-        <v>6.8659427051578625E-3</v>
-      </c>
-    </row>
-    <row r="277" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C277" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D277" s="3">
-        <f>D274/D275</f>
-        <v>1.3306477779394272</v>
-      </c>
-      <c r="E277" s="3">
-        <f t="shared" ref="E277:G277" si="52">E274/E275</f>
-        <v>0.52497104851926879</v>
-      </c>
-      <c r="F277" s="3">
-        <f t="shared" si="52"/>
-        <v>14.558529260558757</v>
-      </c>
-      <c r="G277" s="3">
-        <f t="shared" si="52"/>
-        <v>0.20311492992969613</v>
-      </c>
-    </row>
-    <row r="279" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C279" s="2">
-        <f>MAX(C269:C272)</f>
-        <v>4</v>
-      </c>
-      <c r="D279" s="2">
-        <f t="shared" ref="D279:G279" si="53">MAX(D269:D272)</f>
-        <v>702640.28510284843</v>
-      </c>
-      <c r="E279" s="2">
-        <f t="shared" si="53"/>
-        <v>57596.7124071</v>
-      </c>
-      <c r="F279" s="2">
-        <f t="shared" si="53"/>
-        <v>2.3285205202868371E-2</v>
-      </c>
-      <c r="G279" s="2">
-        <f t="shared" si="53"/>
-        <v>1.2640594598421069E-2</v>
-      </c>
-    </row>
-    <row r="280" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C280" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D280" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E280" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F280" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G280" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="281" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C281" s="2">
-        <f>C269/C$279</f>
-        <v>1</v>
-      </c>
-      <c r="D281" s="2">
-        <f t="shared" ref="D281:G281" si="54">D269/D$279</f>
-        <v>1</v>
-      </c>
-      <c r="E281" s="2">
-        <f t="shared" si="54"/>
-        <v>0.4287191813565403</v>
-      </c>
-      <c r="F281" s="2">
-        <f t="shared" si="54"/>
-        <v>0.53569574699465849</v>
-      </c>
-      <c r="G281" s="2">
-        <f t="shared" si="54"/>
-        <v>9.5790129052906028E-2</v>
-      </c>
-    </row>
-    <row r="282" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C282" s="2">
-        <f t="shared" ref="C282:G284" si="55">C270/C$279</f>
-        <v>0.75</v>
-      </c>
-      <c r="D282" s="2">
-        <f t="shared" si="55"/>
-        <v>0.9229809392532492</v>
-      </c>
-      <c r="E282" s="2">
-        <f t="shared" si="55"/>
-        <v>0.3535920446884655</v>
-      </c>
-      <c r="F282" s="2">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="G282" s="2">
-        <f t="shared" si="55"/>
-        <v>0.12486016719718387</v>
-      </c>
-    </row>
-    <row r="283" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C283" s="2">
-        <f t="shared" si="55"/>
-        <v>0.5</v>
-      </c>
-      <c r="D283" s="2">
-        <f t="shared" si="55"/>
-        <v>0.74801703981263812</v>
-      </c>
-      <c r="E283" s="2">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="F283" s="2">
-        <f t="shared" si="55"/>
-        <v>2.9773689598128844E-2</v>
-      </c>
-      <c r="G283" s="2">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="284" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C284" s="2">
-        <f t="shared" si="55"/>
-        <v>0.25</v>
-      </c>
-      <c r="D284" s="2">
-        <f t="shared" si="55"/>
-        <v>0.69712943030064645</v>
-      </c>
-      <c r="E284" s="2">
-        <f t="shared" si="55"/>
-        <v>0.49019879906061425</v>
-      </c>
-      <c r="F284" s="2">
-        <f t="shared" si="55"/>
-        <v>7.571057460945764E-2</v>
-      </c>
-      <c r="G284" s="2">
-        <f t="shared" si="55"/>
-        <v>8.6332237253377908E-2</v>
-      </c>
-    </row>
-    <row r="286" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C286" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D286" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E286" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F286" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G286" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="287" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C287" s="3">
-        <v>0.69712943030064645</v>
-      </c>
-      <c r="D287" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E287" s="2">
-        <v>0.49019879906061425</v>
-      </c>
-      <c r="F287" s="2">
-        <v>7.571057460945764E-2</v>
-      </c>
-      <c r="G287" s="2">
-        <v>8.6332237253377908E-2</v>
-      </c>
-    </row>
-    <row r="288" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C288" s="3">
-        <v>0.74801703981263812</v>
-      </c>
-      <c r="D288" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E288" s="2">
-        <v>1</v>
-      </c>
-      <c r="F288" s="2">
-        <v>2.9773689598128844E-2</v>
-      </c>
-      <c r="G288" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C289" s="3">
-        <v>0.9229809392532492</v>
-      </c>
-      <c r="D289" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E289" s="2">
-        <v>0.3535920446884655</v>
-      </c>
-      <c r="F289" s="2">
-        <v>1</v>
-      </c>
-      <c r="G289" s="2">
-        <v>0.12486016719718387</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C290" s="3">
-        <v>1</v>
-      </c>
-      <c r="D290" s="2">
-        <v>1</v>
-      </c>
-      <c r="E290" s="2">
-        <v>0.4287191813565403</v>
-      </c>
-      <c r="F290" s="2">
-        <v>0.53569574699465849</v>
-      </c>
-      <c r="G290" s="2">
-        <v>9.5790129052906028E-2</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A292" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B292" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C292" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E292" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F292" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G292" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A293" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B293" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C293" s="2">
-        <v>4</v>
-      </c>
-      <c r="D293" s="3">
-        <v>333902.21266145178</v>
-      </c>
-      <c r="E293" s="3">
-        <v>6590.0541599999997</v>
-      </c>
-      <c r="F293" s="4">
-        <v>3.968817154607421E-3</v>
-      </c>
-      <c r="G293" s="4">
-        <v>1.4273582237145071E-3</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A294" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B294" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C294" s="2">
-        <v>3</v>
-      </c>
-      <c r="D294" s="3">
-        <v>289865.32010952412</v>
-      </c>
-      <c r="E294" s="3">
-        <v>5130.8202951200001</v>
-      </c>
-      <c r="F294" s="4">
-        <v>7.1409024001186736E-3</v>
-      </c>
-      <c r="G294" s="4">
-        <v>1.6292149323472839E-3</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A295" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B295" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C295" s="2">
-        <v>2</v>
-      </c>
-      <c r="D295" s="3">
-        <v>259818.50988372459</v>
-      </c>
-      <c r="E295" s="3">
-        <v>45922.658233419999</v>
-      </c>
-      <c r="F295" s="4">
-        <v>4.0433840100499702E-5</v>
-      </c>
-      <c r="G295" s="4">
-        <v>1.5232724169502069E-4</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A296" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B296" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C296" s="2">
-        <v>1</v>
-      </c>
-      <c r="D296" s="3">
-        <v>234189.89306239539</v>
-      </c>
-      <c r="E296" s="3">
-        <v>4733.3383234200001</v>
-      </c>
-      <c r="F296" s="4">
-        <v>6.6356632156617178E-4</v>
-      </c>
-      <c r="G296" s="4">
-        <v>3.1476572520248271E-3</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B298" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D298" s="3">
-        <f>AVERAGE(D293:D294)</f>
-        <v>311883.76638548798</v>
-      </c>
-      <c r="E298" s="3">
-        <f t="shared" ref="E298:G298" si="56">AVERAGE(E293:E294)</f>
-        <v>5860.4372275599999</v>
-      </c>
-      <c r="F298" s="4">
-        <f t="shared" si="56"/>
-        <v>5.5548597773630477E-3</v>
-      </c>
-      <c r="G298" s="4">
-        <f t="shared" si="56"/>
-        <v>1.5282865780308955E-3</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B299" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D299" s="3">
-        <f>AVERAGE(D295:D296)</f>
-        <v>247004.20147306001</v>
-      </c>
-      <c r="E299" s="3">
-        <f t="shared" ref="E299:G299" si="57">AVERAGE(E295:E296)</f>
-        <v>25327.99827842</v>
-      </c>
-      <c r="F299" s="4">
-        <f t="shared" si="57"/>
-        <v>3.5200008083333573E-4</v>
-      </c>
-      <c r="G299" s="4">
-        <f t="shared" si="57"/>
-        <v>1.6499922468599239E-3</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C301" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D301" s="3">
-        <f>D298/D299</f>
-        <v>1.2626658353400688</v>
-      </c>
-      <c r="E301" s="3">
-        <f t="shared" ref="E301:G301" si="58">E298/E299</f>
-        <v>0.23138177613322164</v>
-      </c>
-      <c r="F301" s="3">
-        <f t="shared" si="58"/>
-        <v>15.780848016319494</v>
-      </c>
-      <c r="G301" s="3">
-        <f t="shared" si="58"/>
-        <v>0.9262386419932308</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C303" s="2">
-        <f>MAX(C293:C296)</f>
-        <v>4</v>
-      </c>
-      <c r="D303" s="2">
-        <f t="shared" ref="D303:G303" si="59">MAX(D293:D296)</f>
-        <v>333902.21266145178</v>
-      </c>
-      <c r="E303" s="2">
-        <f t="shared" si="59"/>
-        <v>45922.658233419999</v>
-      </c>
-      <c r="F303" s="2">
-        <f t="shared" si="59"/>
-        <v>7.1409024001186736E-3</v>
-      </c>
-      <c r="G303" s="2">
-        <f t="shared" si="59"/>
-        <v>3.1476572520248271E-3</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C304" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D304" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E304" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F304" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G304" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C305" s="2">
-        <f>C293/C$303</f>
-        <v>1</v>
-      </c>
-      <c r="D305" s="2">
-        <f t="shared" ref="D305:G305" si="60">D293/D$303</f>
-        <v>1</v>
-      </c>
-      <c r="E305" s="2">
-        <f t="shared" si="60"/>
-        <v>0.14350332523225146</v>
-      </c>
-      <c r="F305" s="2">
-        <f t="shared" si="60"/>
-        <v>0.55578650039264843</v>
-      </c>
-      <c r="G305" s="2">
-        <f t="shared" si="60"/>
-        <v>0.45346685151196658</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C306" s="2">
-        <f t="shared" ref="C306:G308" si="61">C294/C$303</f>
-        <v>0.75</v>
-      </c>
-      <c r="D306" s="2">
-        <f t="shared" si="61"/>
-        <v>0.86811440331311229</v>
-      </c>
-      <c r="E306" s="2">
-        <f t="shared" si="61"/>
-        <v>0.11172742372709753</v>
-      </c>
-      <c r="F306" s="2">
-        <f t="shared" si="61"/>
-        <v>1</v>
-      </c>
-      <c r="G306" s="2">
-        <f t="shared" si="61"/>
-        <v>0.5175960410871423</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C307" s="2">
-        <f t="shared" si="61"/>
-        <v>0.5</v>
-      </c>
-      <c r="D307" s="2">
-        <f t="shared" si="61"/>
-        <v>0.77812754762172931</v>
-      </c>
-      <c r="E307" s="2">
-        <f t="shared" si="61"/>
-        <v>1</v>
-      </c>
-      <c r="F307" s="2">
-        <f t="shared" si="61"/>
-        <v>5.6622871781342003E-3</v>
-      </c>
-      <c r="G307" s="2">
-        <f t="shared" si="61"/>
-        <v>4.8393846438341249E-2</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C308" s="2">
-        <f t="shared" si="61"/>
-        <v>0.25</v>
-      </c>
-      <c r="D308" s="2">
-        <f t="shared" si="61"/>
-        <v>0.70137268991339052</v>
-      </c>
-      <c r="E308" s="2">
-        <f t="shared" si="61"/>
-        <v>0.10307195849510592</v>
-      </c>
-      <c r="F308" s="2">
-        <f t="shared" si="61"/>
-        <v>9.2924715166971622E-2</v>
-      </c>
-      <c r="G308" s="2">
-        <f t="shared" si="61"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C310" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D310" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E310" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F310" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G310" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C311" s="3">
-        <v>0.70137268991339052</v>
-      </c>
-      <c r="D311" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E311" s="2">
-        <v>0.10307195849510592</v>
-      </c>
-      <c r="F311" s="2">
-        <v>9.2924715166971622E-2</v>
-      </c>
-      <c r="G311" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C312" s="3">
-        <v>0.77812754762172931</v>
-      </c>
-      <c r="D312" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E312" s="2">
-        <v>1</v>
-      </c>
-      <c r="F312" s="2">
-        <v>5.6622871781342003E-3</v>
-      </c>
-      <c r="G312" s="2">
-        <v>4.8393846438341249E-2</v>
-      </c>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C313" s="3">
-        <v>0.86811440331311229</v>
-      </c>
-      <c r="D313" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E313" s="2">
-        <v>0.11172742372709753</v>
-      </c>
-      <c r="F313" s="2">
-        <v>1</v>
-      </c>
-      <c r="G313" s="2">
-        <v>0.5175960410871423</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C314" s="3">
-        <v>1</v>
-      </c>
-      <c r="D314" s="2">
-        <v>1</v>
-      </c>
-      <c r="E314" s="2">
-        <v>0.14350332523225146</v>
-      </c>
-      <c r="F314" s="2">
-        <v>0.55578650039264843</v>
-      </c>
-      <c r="G314" s="2">
-        <v>0.45346685151196658</v>
-      </c>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A317" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E317" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F317" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G317" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A318" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B318" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C318" s="2">
-        <v>4</v>
-      </c>
-      <c r="D318" s="3">
-        <v>615324.90182869229</v>
-      </c>
-      <c r="E318" s="3">
-        <v>12188.037840000001</v>
-      </c>
-      <c r="F318" s="4">
-        <v>3.5563801629943082E-3</v>
-      </c>
-      <c r="G318" s="4">
-        <v>2.3262126662383252E-3</v>
-      </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A319" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B319" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C319" s="2">
-        <v>3</v>
-      </c>
-      <c r="D319" s="3">
-        <v>463470.71898289572</v>
-      </c>
-      <c r="E319" s="3">
-        <v>9380.3853557600014</v>
-      </c>
-      <c r="F319" s="4">
-        <v>2.4821681068467739E-3</v>
-      </c>
-      <c r="G319" s="4">
-        <v>1.7821392198706289E-3</v>
-      </c>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A320" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B320" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C320" s="2">
-        <v>2</v>
-      </c>
-      <c r="D320" s="3">
-        <v>441905.15975913568</v>
-      </c>
-      <c r="E320" s="3">
-        <v>8680.9984719799995</v>
-      </c>
-      <c r="F320" s="4">
-        <v>5.3628300774693723E-2</v>
-      </c>
-      <c r="G320" s="4">
-        <v>1.9809359137092151E-3</v>
-      </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A321" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B321" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C321" s="2">
-        <v>1</v>
-      </c>
-      <c r="D321" s="3">
-        <v>396416.47748978873</v>
-      </c>
-      <c r="E321" s="3">
-        <v>10615.43888874</v>
-      </c>
-      <c r="F321" s="4">
-        <v>5.7122249315871114E-3</v>
-      </c>
-      <c r="G321" s="4">
-        <v>1.223257961926933E-3</v>
-      </c>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B323" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D323" s="3">
-        <f>AVERAGE(D318:D319)</f>
-        <v>539397.81040579407</v>
-      </c>
-      <c r="E323" s="3">
-        <f t="shared" ref="E323:G323" si="62">AVERAGE(E318:E319)</f>
-        <v>10784.211597880001</v>
-      </c>
-      <c r="F323" s="4">
-        <f t="shared" si="62"/>
-        <v>3.0192741349205411E-3</v>
-      </c>
-      <c r="G323" s="4">
-        <f t="shared" si="62"/>
-        <v>2.0541759430544771E-3</v>
-      </c>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B324" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D324" s="3">
-        <f>AVERAGE(D320:D321)</f>
-        <v>419160.81862446223</v>
-      </c>
-      <c r="E324" s="3">
-        <f t="shared" ref="E324:G324" si="63">AVERAGE(E320:E321)</f>
-        <v>9648.2186803599998</v>
-      </c>
-      <c r="F324" s="4">
-        <f t="shared" si="63"/>
-        <v>2.9670262853140415E-2</v>
-      </c>
-      <c r="G324" s="4">
-        <f t="shared" si="63"/>
-        <v>1.602096937818074E-3</v>
-      </c>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C326" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D326" s="3">
-        <f>D323/D324</f>
-        <v>1.2868516961482879</v>
-      </c>
-      <c r="E326" s="3">
-        <f t="shared" ref="E326:G326" si="64">E323/E324</f>
-        <v>1.1177412074865631</v>
-      </c>
-      <c r="F326" s="3">
-        <f t="shared" si="64"/>
-        <v>0.10176095000792922</v>
-      </c>
-      <c r="G326" s="3">
-        <f t="shared" si="64"/>
-        <v>1.2821795576565411</v>
-      </c>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C328" s="2">
-        <f>MAX(C318:C321)</f>
-        <v>4</v>
-      </c>
-      <c r="D328" s="2">
-        <f t="shared" ref="D328:G328" si="65">MAX(D318:D321)</f>
-        <v>615324.90182869229</v>
-      </c>
-      <c r="E328" s="2">
-        <f t="shared" si="65"/>
-        <v>12188.037840000001</v>
-      </c>
-      <c r="F328" s="2">
-        <f t="shared" si="65"/>
-        <v>5.3628300774693723E-2</v>
-      </c>
-      <c r="G328" s="2">
-        <f t="shared" si="65"/>
-        <v>2.3262126662383252E-3</v>
-      </c>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C329" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D329" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E329" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F329" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G329" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C330" s="2">
-        <f>C318/C$328</f>
-        <v>1</v>
-      </c>
-      <c r="D330" s="2">
-        <f t="shared" ref="D330:G330" si="66">D318/D$328</f>
-        <v>1</v>
-      </c>
-      <c r="E330" s="2">
-        <f t="shared" si="66"/>
-        <v>1</v>
-      </c>
-      <c r="F330" s="2">
-        <f t="shared" si="66"/>
-        <v>6.6315361695601274E-2</v>
-      </c>
-      <c r="G330" s="2">
-        <f t="shared" si="66"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C331" s="2">
-        <f t="shared" ref="C331:G333" si="67">C319/C$328</f>
-        <v>0.75</v>
-      </c>
-      <c r="D331" s="2">
-        <f t="shared" si="67"/>
-        <v>0.75321300601601027</v>
-      </c>
-      <c r="E331" s="2">
-        <f t="shared" si="67"/>
-        <v>0.76963868006501046</v>
-      </c>
-      <c r="F331" s="2">
-        <f t="shared" si="67"/>
-        <v>4.6284668188071074E-2</v>
-      </c>
-      <c r="G331" s="2">
-        <f t="shared" si="67"/>
-        <v>0.76611190616225677</v>
-      </c>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C332" s="2">
-        <f t="shared" si="67"/>
-        <v>0.5</v>
-      </c>
-      <c r="D332" s="2">
-        <f t="shared" si="67"/>
-        <v>0.71816557146611792</v>
-      </c>
-      <c r="E332" s="2">
-        <f t="shared" si="67"/>
-        <v>0.71225562194184977</v>
-      </c>
-      <c r="F332" s="2">
-        <f t="shared" si="67"/>
-        <v>1</v>
-      </c>
-      <c r="G332" s="2">
-        <f t="shared" si="67"/>
-        <v>0.85157128686456229</v>
-      </c>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C333" s="2">
-        <f t="shared" si="67"/>
-        <v>0.25</v>
-      </c>
-      <c r="D333" s="2">
-        <f t="shared" si="67"/>
-        <v>0.64423928937651198</v>
-      </c>
-      <c r="E333" s="2">
-        <f t="shared" si="67"/>
-        <v>0.87097193396472083</v>
-      </c>
-      <c r="F333" s="2">
-        <f t="shared" si="67"/>
-        <v>0.10651512073048215</v>
-      </c>
-      <c r="G333" s="2">
-        <f t="shared" si="67"/>
-        <v>0.52585818127499084</v>
-      </c>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C335" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D335" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E335" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F335" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G335" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C336" s="3">
-        <v>0.64423928937651198</v>
-      </c>
-      <c r="D336" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E336" s="2">
-        <v>0.87097193396472083</v>
-      </c>
-      <c r="F336" s="2">
-        <v>0.10651512073048215</v>
-      </c>
-      <c r="G336" s="2">
-        <v>0.52585818127499084</v>
-      </c>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C337" s="3">
-        <v>0.71816557146611792</v>
-      </c>
-      <c r="D337" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E337" s="2">
-        <v>0.71225562194184977</v>
-      </c>
-      <c r="F337" s="2">
-        <v>1</v>
-      </c>
-      <c r="G337" s="2">
-        <v>0.85157128686456229</v>
-      </c>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C338" s="3">
-        <v>0.75321300601601027</v>
-      </c>
-      <c r="D338" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E338" s="2">
-        <v>0.76963868006501046</v>
-      </c>
-      <c r="F338" s="2">
-        <v>4.6284668188071074E-2</v>
-      </c>
-      <c r="G338" s="2">
-        <v>0.76611190616225677</v>
-      </c>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C339" s="3">
-        <v>1</v>
-      </c>
-      <c r="D339" s="2">
-        <v>1</v>
-      </c>
-      <c r="E339" s="2">
-        <v>1</v>
-      </c>
-      <c r="F339" s="2">
-        <v>6.6315361695601274E-2</v>
-      </c>
-      <c r="G339" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A342" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B342" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C342" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D342" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E342" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F342" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G342" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A343" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B343" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C343" s="2">
-        <v>1</v>
-      </c>
-      <c r="D343" s="3">
-        <v>480752.63075950177</v>
-      </c>
-      <c r="E343" s="3">
-        <v>13713.99982974</v>
-      </c>
-      <c r="F343" s="4">
-        <v>1.8909555433829729E-4</v>
-      </c>
-      <c r="G343" s="4">
-        <v>1.421912259449817E-2</v>
-      </c>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A344" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B344" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C344" s="2">
-        <v>4</v>
-      </c>
-      <c r="D344" s="3">
-        <v>430680.74778667098</v>
-      </c>
-      <c r="E344" s="3">
-        <v>9650.7308639999992</v>
-      </c>
-      <c r="F344" s="4">
-        <v>3.2382873836611008E-4</v>
-      </c>
-      <c r="G344" s="4">
-        <v>1.307147425181787E-3</v>
-      </c>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A345" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B345" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C345" s="2">
-        <v>3</v>
-      </c>
-      <c r="D345" s="3">
-        <v>344818.33344279532</v>
-      </c>
-      <c r="E345" s="3">
-        <v>7766.5175531200011</v>
-      </c>
-      <c r="F345" s="4">
-        <v>5.6879237956854514E-4</v>
-      </c>
-      <c r="G345" s="4">
-        <v>9.2862762115340628E-4</v>
-      </c>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A346" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B346" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C346" s="2">
-        <v>2</v>
-      </c>
-      <c r="D346" s="3">
-        <v>310794.74797233898</v>
-      </c>
-      <c r="E346" s="3">
-        <v>8210.8821614400003</v>
-      </c>
-      <c r="F346" s="4">
-        <v>1.515288413031857E-4</v>
-      </c>
-      <c r="G346" s="4">
-        <v>1.134724744407487E-2</v>
-      </c>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B348" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D348" s="3">
-        <f>AVERAGE(D343:D344)</f>
-        <v>455716.68927308638</v>
-      </c>
-      <c r="E348" s="3">
-        <f t="shared" ref="E348:G348" si="68">AVERAGE(E343:E344)</f>
-        <v>11682.365346869999</v>
-      </c>
-      <c r="F348" s="4">
-        <f t="shared" si="68"/>
-        <v>2.5646214635220368E-4</v>
-      </c>
-      <c r="G348" s="4">
-        <f t="shared" si="68"/>
-        <v>7.7631350098399787E-3</v>
-      </c>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B349" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D349" s="3">
-        <f>AVERAGE(D345:D346)</f>
-        <v>327806.54070756712</v>
-      </c>
-      <c r="E349" s="3">
-        <f t="shared" ref="E349:G349" si="69">AVERAGE(E345:E346)</f>
-        <v>7988.6998572800003</v>
-      </c>
-      <c r="F349" s="4">
-        <f t="shared" si="69"/>
-        <v>3.6016061043586542E-4</v>
-      </c>
-      <c r="G349" s="4">
-        <f t="shared" si="69"/>
-        <v>6.1379375326141381E-3</v>
-      </c>
-    </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C351" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D351" s="3">
-        <f>D348/D349</f>
-        <v>1.3902001109844437</v>
-      </c>
-      <c r="E351" s="3">
-        <f t="shared" ref="E351:G351" si="70">E348/E349</f>
-        <v>1.462361279754929</v>
-      </c>
-      <c r="F351" s="3">
-        <f t="shared" si="70"/>
-        <v>0.71207716480109773</v>
-      </c>
-      <c r="G351" s="3">
-        <f t="shared" si="70"/>
-        <v>1.2647790839496653</v>
-      </c>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C353" s="2">
-        <f>MAX(C343:C346)</f>
-        <v>4</v>
-      </c>
-      <c r="D353" s="2">
-        <f t="shared" ref="D353:G353" si="71">MAX(D343:D346)</f>
-        <v>480752.63075950177</v>
-      </c>
-      <c r="E353" s="2">
-        <f t="shared" si="71"/>
-        <v>13713.99982974</v>
-      </c>
-      <c r="F353" s="2">
-        <f t="shared" si="71"/>
-        <v>5.6879237956854514E-4</v>
-      </c>
-      <c r="G353" s="2">
-        <f t="shared" si="71"/>
-        <v>1.421912259449817E-2</v>
-      </c>
-    </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C354" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D354" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F354" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G354" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C355" s="2">
-        <f>C343/C$353</f>
-        <v>0.25</v>
-      </c>
-      <c r="D355" s="2">
-        <f t="shared" ref="D355:G355" si="72">D343/D$353</f>
-        <v>1</v>
-      </c>
-      <c r="E355" s="2">
-        <f t="shared" si="72"/>
-        <v>1</v>
-      </c>
-      <c r="F355" s="2">
-        <f t="shared" si="72"/>
-        <v>0.33245092784424229</v>
-      </c>
-      <c r="G355" s="2">
-        <f t="shared" si="72"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C356" s="2">
-        <f t="shared" ref="C356:G358" si="73">C344/C$353</f>
-        <v>1</v>
-      </c>
-      <c r="D356" s="2">
-        <f t="shared" si="73"/>
-        <v>0.89584688721572603</v>
-      </c>
-      <c r="E356" s="2">
-        <f t="shared" si="73"/>
-        <v>0.70371379494052133</v>
-      </c>
-      <c r="F356" s="2">
-        <f t="shared" si="73"/>
-        <v>0.56932678776700363</v>
-      </c>
-      <c r="G356" s="2">
-        <f t="shared" si="73"/>
-        <v>9.1928838540822747E-2</v>
-      </c>
-    </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C357" s="2">
-        <f t="shared" si="73"/>
-        <v>0.75</v>
-      </c>
-      <c r="D357" s="2">
-        <f t="shared" si="73"/>
-        <v>0.7172468986764462</v>
-      </c>
-      <c r="E357" s="2">
-        <f t="shared" si="73"/>
-        <v>0.56632037695360282</v>
-      </c>
-      <c r="F357" s="2">
-        <f t="shared" si="73"/>
-        <v>1</v>
-      </c>
-      <c r="G357" s="2">
-        <f t="shared" si="73"/>
-        <v>6.5308363085126067E-2</v>
-      </c>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C358" s="2">
-        <f t="shared" si="73"/>
-        <v>0.5</v>
-      </c>
-      <c r="D358" s="2">
-        <f t="shared" si="73"/>
-        <v>0.64647539729806525</v>
-      </c>
-      <c r="E358" s="2">
-        <f t="shared" si="73"/>
-        <v>0.59872263842631746</v>
-      </c>
-      <c r="F358" s="2">
-        <f t="shared" si="73"/>
-        <v>0.26640448561938757</v>
-      </c>
-      <c r="G358" s="2">
-        <f t="shared" si="73"/>
-        <v>0.798027260026964</v>
-      </c>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C360" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D360" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E360" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F360" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G360" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C361" s="3">
-        <v>0.64647539729806525</v>
-      </c>
-      <c r="D361" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E361" s="2">
-        <v>0.59872263842631746</v>
-      </c>
-      <c r="F361" s="2">
-        <v>0.26640448561938757</v>
-      </c>
-      <c r="G361" s="2">
-        <v>0.798027260026964</v>
-      </c>
-    </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C362" s="3">
-        <v>0.7172468986764462</v>
-      </c>
-      <c r="D362" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E362" s="2">
-        <v>0.56632037695360282</v>
-      </c>
-      <c r="F362" s="2">
-        <v>1</v>
-      </c>
-      <c r="G362" s="2">
-        <v>6.5308363085126067E-2</v>
-      </c>
-    </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C363" s="3">
-        <v>0.89584688721572603</v>
-      </c>
-      <c r="D363" s="2">
-        <v>1</v>
-      </c>
-      <c r="E363" s="2">
-        <v>0.70371379494052133</v>
-      </c>
-      <c r="F363" s="2">
-        <v>0.56932678776700363</v>
-      </c>
-      <c r="G363" s="2">
-        <v>9.1928838540822747E-2</v>
-      </c>
-    </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C364" s="3">
-        <v>1</v>
-      </c>
-      <c r="D364" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E364" s="2">
-        <v>1</v>
-      </c>
-      <c r="F364" s="2">
-        <v>0.33245092784424229</v>
-      </c>
-      <c r="G364" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A367" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B367" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C367" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D367" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E367" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F367" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G367" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A368" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B368" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C368" s="2">
-        <v>4</v>
-      </c>
-      <c r="D368" s="3">
-        <v>624490.81179662514</v>
-      </c>
-      <c r="E368" s="3">
-        <v>23490.718752000001</v>
-      </c>
-      <c r="F368" s="4">
-        <v>1.927088927244758E-3</v>
-      </c>
-      <c r="G368" s="4">
-        <v>1.8760825696850091E-3</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A369" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B369" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C369" s="2">
-        <v>3</v>
-      </c>
-      <c r="D369" s="3">
-        <v>615005.46689121344</v>
-      </c>
-      <c r="E369" s="3">
-        <v>18304.5266156</v>
-      </c>
-      <c r="F369" s="4">
-        <v>2.0544865338363899E-3</v>
-      </c>
-      <c r="G369" s="4">
-        <v>2.397692315221963E-3</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A370" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B370" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C370" s="2">
-        <v>1</v>
-      </c>
-      <c r="D370" s="3">
-        <v>557880.96074185451</v>
-      </c>
-      <c r="E370" s="3">
-        <v>17673.58753398</v>
-      </c>
-      <c r="F370" s="4">
-        <v>1.2639185721094849E-3</v>
-      </c>
-      <c r="G370" s="4">
-        <v>7.224852054202324E-4</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A371" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B371" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C371" s="2">
-        <v>2</v>
-      </c>
-      <c r="D371" s="3">
-        <v>528936.59684355662</v>
-      </c>
-      <c r="E371" s="3">
-        <v>14840.029964359999</v>
-      </c>
-      <c r="F371" s="4">
-        <v>3.348617336982791E-3</v>
-      </c>
-      <c r="G371" s="4">
-        <v>9.7700369843055682E-4</v>
-      </c>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B373" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D373" s="3">
-        <f>AVERAGE(D368:D369)</f>
-        <v>619748.13934391923</v>
-      </c>
-      <c r="E373" s="3">
-        <f t="shared" ref="E373:G373" si="74">AVERAGE(E368:E369)</f>
-        <v>20897.6226838</v>
-      </c>
-      <c r="F373" s="4">
-        <f t="shared" si="74"/>
-        <v>1.9907877305405742E-3</v>
-      </c>
-      <c r="G373" s="4">
-        <f t="shared" si="74"/>
-        <v>2.1368874424534858E-3</v>
-      </c>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B374" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D374" s="3">
-        <f>AVERAGE(D370:D371)</f>
-        <v>543408.77879270562</v>
-      </c>
-      <c r="E374" s="3">
-        <f t="shared" ref="E374:G374" si="75">AVERAGE(E370:E371)</f>
-        <v>16256.808749169999</v>
-      </c>
-      <c r="F374" s="4">
-        <f t="shared" si="75"/>
-        <v>2.3062679545461382E-3</v>
-      </c>
-      <c r="G374" s="4">
-        <f t="shared" si="75"/>
-        <v>8.4974445192539461E-4</v>
-      </c>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C376" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D376" s="3">
-        <f>D373/D374</f>
-        <v>1.1404823836685474</v>
-      </c>
-      <c r="E376" s="3">
-        <f t="shared" ref="E376:G376" si="76">E373/E374</f>
-        <v>1.2854689383527957</v>
-      </c>
-      <c r="F376" s="3">
-        <f t="shared" si="76"/>
-        <v>0.8632074718882139</v>
-      </c>
-      <c r="G376" s="3">
-        <f t="shared" si="76"/>
-        <v>2.5147412702861627</v>
-      </c>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C378" s="2">
-        <f>MAX(C368:C371)</f>
-        <v>4</v>
-      </c>
-      <c r="D378" s="2">
-        <f t="shared" ref="D378:G378" si="77">MAX(D368:D371)</f>
-        <v>624490.81179662514</v>
-      </c>
-      <c r="E378" s="2">
-        <f t="shared" si="77"/>
-        <v>23490.718752000001</v>
-      </c>
-      <c r="F378" s="2">
-        <f t="shared" si="77"/>
-        <v>3.348617336982791E-3</v>
-      </c>
-      <c r="G378" s="2">
-        <f t="shared" si="77"/>
-        <v>2.397692315221963E-3</v>
-      </c>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C379" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D379" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E379" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F379" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G379" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C380" s="2">
-        <f>C368/C$378</f>
-        <v>1</v>
-      </c>
-      <c r="D380" s="2">
-        <f t="shared" ref="D380:G380" si="78">D368/D$378</f>
-        <v>1</v>
-      </c>
-      <c r="E380" s="2">
-        <f t="shared" si="78"/>
-        <v>1</v>
-      </c>
-      <c r="F380" s="2">
-        <f t="shared" si="78"/>
-        <v>0.57548795019413157</v>
-      </c>
-      <c r="G380" s="2">
-        <f t="shared" si="78"/>
-        <v>0.78245342731197487</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C381" s="2">
-        <f t="shared" ref="C381:G383" si="79">C369/C$378</f>
-        <v>0.75</v>
-      </c>
-      <c r="D381" s="2">
-        <f t="shared" si="79"/>
-        <v>0.98481107371600407</v>
-      </c>
-      <c r="E381" s="2">
-        <f t="shared" si="79"/>
-        <v>0.77922377807369358</v>
-      </c>
-      <c r="F381" s="2">
-        <f t="shared" si="79"/>
-        <v>0.61353278893537189</v>
-      </c>
-      <c r="G381" s="2">
-        <f t="shared" si="79"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C382" s="2">
-        <f t="shared" si="79"/>
-        <v>0.25</v>
-      </c>
-      <c r="D382" s="2">
-        <f t="shared" si="79"/>
-        <v>0.89333734012332733</v>
-      </c>
-      <c r="E382" s="2">
-        <f t="shared" si="79"/>
-        <v>0.7523646986099678</v>
-      </c>
-      <c r="F382" s="2">
-        <f t="shared" si="79"/>
-        <v>0.3774449108145379</v>
-      </c>
-      <c r="G382" s="2">
-        <f t="shared" si="79"/>
-        <v>0.30132523711798664</v>
-      </c>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C383" s="2">
-        <f t="shared" si="79"/>
-        <v>0.5</v>
-      </c>
-      <c r="D383" s="2">
-        <f t="shared" si="79"/>
-        <v>0.84698859751328548</v>
-      </c>
-      <c r="E383" s="2">
-        <f t="shared" si="79"/>
-        <v>0.63174014047980198</v>
-      </c>
-      <c r="F383" s="2">
-        <f t="shared" si="79"/>
-        <v>1</v>
-      </c>
-      <c r="G383" s="2">
-        <f t="shared" si="79"/>
-        <v>0.40747667756532474</v>
-      </c>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C385" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D385" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E385" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F385" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G385" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C386" s="3">
-        <v>0.84698859751328548</v>
-      </c>
-      <c r="D386" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E386" s="2">
-        <v>0.63174014047980198</v>
-      </c>
-      <c r="F386" s="2">
-        <v>1</v>
-      </c>
-      <c r="G386" s="2">
-        <v>0.40747667756532474</v>
-      </c>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C387" s="3">
-        <v>0.89333734012332733</v>
-      </c>
-      <c r="D387" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E387" s="2">
-        <v>0.7523646986099678</v>
-      </c>
-      <c r="F387" s="2">
-        <v>0.3774449108145379</v>
-      </c>
-      <c r="G387" s="2">
-        <v>0.30132523711798664</v>
-      </c>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C388" s="3">
-        <v>0.98481107371600407</v>
-      </c>
-      <c r="D388" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E388" s="2">
-        <v>0.77922377807369358</v>
-      </c>
-      <c r="F388" s="2">
-        <v>0.61353278893537189</v>
-      </c>
-      <c r="G388" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C389" s="3">
-        <v>1</v>
-      </c>
-      <c r="D389" s="2">
-        <v>1</v>
-      </c>
-      <c r="E389" s="2">
-        <v>1</v>
-      </c>
-      <c r="F389" s="2">
-        <v>0.57548795019413157</v>
-      </c>
-      <c r="G389" s="2">
-        <v>0.78245342731197487</v>
-      </c>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A392" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B392" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C392" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D392" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E392" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F392" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G392" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A393" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B393" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C393" s="2">
-        <v>1</v>
-      </c>
-      <c r="D393" s="3">
-        <v>496312.33844584553</v>
-      </c>
-      <c r="E393" s="3">
-        <v>6058.6276942799996</v>
-      </c>
-      <c r="F393" s="4">
-        <v>1.149126975828702E-3</v>
-      </c>
-      <c r="G393" s="4">
-        <v>4.3326889923906344E-3</v>
-      </c>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A394" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B394" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C394" s="5">
-        <v>3</v>
-      </c>
-      <c r="D394" s="3">
-        <v>481190.63450056087</v>
-      </c>
-      <c r="E394" s="3">
-        <v>5659.2905294400007</v>
-      </c>
-      <c r="F394" s="4">
-        <v>2.7642536319032169E-4</v>
-      </c>
-      <c r="G394" s="4">
-        <v>2.609783923120391E-3</v>
-      </c>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A395" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B395" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C395" s="2">
-        <v>2</v>
-      </c>
-      <c r="D395" s="3">
-        <v>463554.2380744408</v>
-      </c>
-      <c r="E395" s="3">
-        <v>6405.1162323599992</v>
-      </c>
-      <c r="F395" s="4">
-        <v>1.36542870460566E-3</v>
-      </c>
-      <c r="G395" s="4">
-        <v>1.06191448730258E-3</v>
-      </c>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A396" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B396" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C396" s="2">
-        <v>4</v>
-      </c>
-      <c r="D396" s="3">
-        <v>463215.01884109463</v>
-      </c>
-      <c r="E396" s="3">
-        <v>6600.4823040000001</v>
-      </c>
-      <c r="F396" s="4">
-        <v>1.0184783005820781E-3</v>
-      </c>
-      <c r="G396" s="4">
-        <v>1.1952508372333631E-3</v>
-      </c>
-    </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B398" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D398" s="3">
-        <f>AVERAGE(D393:D394)</f>
-        <v>488751.48647320317</v>
-      </c>
-      <c r="E398" s="3">
-        <f t="shared" ref="E398:G398" si="80">AVERAGE(E393:E394)</f>
-        <v>5858.9591118600001</v>
-      </c>
-      <c r="F398" s="4">
-        <f t="shared" si="80"/>
-        <v>7.1277616950951182E-4</v>
-      </c>
-      <c r="G398" s="4">
-        <f t="shared" si="80"/>
-        <v>3.4712364577555127E-3</v>
-      </c>
-    </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B399" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D399" s="3">
-        <f>AVERAGE(D395:D396)</f>
-        <v>463384.62845776771</v>
-      </c>
-      <c r="E399" s="3">
-        <f t="shared" ref="E399:G399" si="81">AVERAGE(E395:E396)</f>
-        <v>6502.7992681799997</v>
-      </c>
-      <c r="F399" s="4">
-        <f t="shared" si="81"/>
-        <v>1.191953502593869E-3</v>
-      </c>
-      <c r="G399" s="4">
-        <f t="shared" si="81"/>
-        <v>1.1285826622679715E-3</v>
-      </c>
-    </row>
-    <row r="401" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C401" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D401" s="3">
-        <f>D398/D399</f>
-        <v>1.0547425539337831</v>
-      </c>
-      <c r="E401" s="3">
-        <f t="shared" ref="E401:G401" si="82">E398/E399</f>
-        <v>0.9009903074402914</v>
-      </c>
-      <c r="F401" s="3">
-        <f t="shared" si="82"/>
-        <v>0.59798991148430225</v>
-      </c>
-      <c r="G401" s="3">
-        <f t="shared" si="82"/>
-        <v>3.0757485240645135</v>
-      </c>
-    </row>
-    <row r="403" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C403" s="2">
-        <f>MAX(C393:C396)</f>
-        <v>4</v>
-      </c>
-      <c r="D403" s="2">
-        <f t="shared" ref="D403:G403" si="83">MAX(D393:D396)</f>
-        <v>496312.33844584553</v>
-      </c>
-      <c r="E403" s="2">
-        <f t="shared" si="83"/>
-        <v>6600.4823040000001</v>
-      </c>
-      <c r="F403" s="2">
-        <f t="shared" si="83"/>
-        <v>1.36542870460566E-3</v>
-      </c>
-      <c r="G403" s="2">
-        <f t="shared" si="83"/>
-        <v>4.3326889923906344E-3</v>
-      </c>
-    </row>
-    <row r="404" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C404" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D404" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E404" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F404" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G404" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="405" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C405" s="2">
-        <f>C393/C$403</f>
-        <v>0.25</v>
-      </c>
-      <c r="D405" s="2">
-        <f t="shared" ref="D405:G405" si="84">D393/D$403</f>
-        <v>1</v>
-      </c>
       <c r="E405" s="2">
-        <f t="shared" si="84"/>
         <v>0.91790681578047295</v>
       </c>
       <c r="F405" s="2">
-        <f t="shared" si="84"/>
         <v>0.84158694771293341</v>
       </c>
       <c r="G405" s="2">
-        <f t="shared" si="84"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="406" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C406" s="2">
-        <f t="shared" ref="C406:G408" si="85">C394/C$403</f>
-        <v>0.75</v>
-      </c>
-      <c r="D406" s="2">
-        <f t="shared" si="85"/>
-        <v>0.96953187987903577</v>
-      </c>
-      <c r="E406" s="2">
-        <f t="shared" si="85"/>
-        <v>0.85740560595251925</v>
-      </c>
-      <c r="F406" s="2">
-        <f t="shared" si="85"/>
-        <v>0.20244584155725229</v>
-      </c>
-      <c r="G406" s="2">
-        <f t="shared" si="85"/>
-        <v>0.60234739389415504</v>
-      </c>
-    </row>
-    <row r="407" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C407" s="2">
-        <f t="shared" si="85"/>
-        <v>0.5</v>
-      </c>
-      <c r="D407" s="2">
-        <f t="shared" si="85"/>
-        <v>0.93399700584921264</v>
-      </c>
-      <c r="E407" s="2">
-        <f t="shared" si="85"/>
-        <v>0.97040124302407327</v>
-      </c>
-      <c r="F407" s="2">
-        <f t="shared" si="85"/>
-        <v>1</v>
-      </c>
-      <c r="G407" s="2">
-        <f t="shared" si="85"/>
-        <v>0.24509363334584758</v>
-      </c>
-    </row>
-    <row r="408" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C408" s="2">
-        <f t="shared" si="85"/>
-        <v>1</v>
-      </c>
-      <c r="D408" s="2">
-        <f t="shared" si="85"/>
-        <v>0.93331352650149302</v>
-      </c>
-      <c r="E408" s="2">
-        <f t="shared" si="85"/>
-        <v>1</v>
-      </c>
-      <c r="F408" s="2">
-        <f t="shared" si="85"/>
-        <v>0.7459036836904771</v>
-      </c>
-      <c r="G408" s="2">
-        <f t="shared" si="85"/>
-        <v>0.27586813623884487</v>
-      </c>
-    </row>
-    <row r="410" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C410" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D410" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E410" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F410" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G410" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="411" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C411" s="3">
-        <v>0.93331352650149302</v>
-      </c>
-      <c r="D411" s="2">
-        <v>1</v>
-      </c>
-      <c r="E411" s="2">
-        <v>1</v>
-      </c>
-      <c r="F411" s="2">
-        <v>0.7459036836904771</v>
-      </c>
-      <c r="G411" s="2">
-        <v>0.27586813623884487</v>
-      </c>
-    </row>
-    <row r="412" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C412" s="3">
-        <v>0.93399700584921264</v>
-      </c>
-      <c r="D412" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E412" s="2">
-        <v>0.97040124302407327</v>
-      </c>
-      <c r="F412" s="2">
-        <v>1</v>
-      </c>
-      <c r="G412" s="2">
-        <v>0.24509363334584758</v>
-      </c>
-    </row>
-    <row r="413" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C413" s="3">
-        <v>0.96953187987903577</v>
-      </c>
-      <c r="D413" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E413" s="2">
-        <v>0.85740560595251925</v>
-      </c>
-      <c r="F413" s="2">
-        <v>0.20244584155725229</v>
-      </c>
-      <c r="G413" s="2">
-        <v>0.60234739389415504</v>
-      </c>
-    </row>
-    <row r="414" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C414" s="3">
-        <v>1</v>
-      </c>
-      <c r="D414" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E414" s="2">
-        <v>0.91790681578047295</v>
-      </c>
-      <c r="F414" s="2">
-        <v>0.84158694771293341</v>
-      </c>
-      <c r="G414" s="2">
         <v>1</v>
       </c>
     </row>
@@ -66915,6 +67257,31 @@
       <c r="E415" s="2"/>
       <c r="F415" s="2"/>
       <c r="G415" s="2"/>
+    </row>
+    <row r="419" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J419" s="2"/>
+      <c r="K419" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L419" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="420" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J420" s="10">
+        <v>33</v>
+      </c>
+      <c r="K420" s="3">
+        <f>0.5*(D405*E405+E405*F405+F405*G405+G405*D405)</f>
+        <v>1.046781023517819</v>
+      </c>
+      <c r="L420" s="3">
+        <f>0.5*(D402*E402+E402*F402+F402*G402+G402*D402)</f>
+        <v>1.1137714394813514</v>
+      </c>
+    </row>
+    <row r="421" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J421" s="10"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D62">
@@ -67397,7 +67764,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D169:D172">
+  <conditionalFormatting sqref="D168:D171">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -67409,7 +67776,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E169:E172">
+  <conditionalFormatting sqref="E168:E171">
     <cfRule type="colorScale" priority="79">
       <colorScale>
         <cfvo type="min"/>
@@ -67421,7 +67788,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F169:F172">
+  <conditionalFormatting sqref="F168:F171">
     <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="min"/>
@@ -67433,7 +67800,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G169:G172">
+  <conditionalFormatting sqref="G168:G171">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -67445,7 +67812,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D174:D175">
+  <conditionalFormatting sqref="D173:D174">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
@@ -67457,7 +67824,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E174:E175">
+  <conditionalFormatting sqref="E173:E174">
     <cfRule type="colorScale" priority="75">
       <colorScale>
         <cfvo type="min"/>
@@ -67469,7 +67836,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F174:F175">
+  <conditionalFormatting sqref="F173:F174">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
@@ -67481,7 +67848,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G174:G175">
+  <conditionalFormatting sqref="G173:G174">
     <cfRule type="colorScale" priority="73">
       <colorScale>
         <cfvo type="min"/>
@@ -67493,7 +67860,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D194:D197">
+  <conditionalFormatting sqref="D192:D195">
     <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="min"/>
@@ -67505,7 +67872,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E194:E197">
+  <conditionalFormatting sqref="E192:E195">
     <cfRule type="colorScale" priority="71">
       <colorScale>
         <cfvo type="min"/>
@@ -67517,7 +67884,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F194:F197">
+  <conditionalFormatting sqref="F192:F195">
     <cfRule type="colorScale" priority="70">
       <colorScale>
         <cfvo type="min"/>
@@ -67529,7 +67896,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G194:G197">
+  <conditionalFormatting sqref="G192:G195">
     <cfRule type="colorScale" priority="69">
       <colorScale>
         <cfvo type="min"/>
@@ -67541,7 +67908,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D199:D200">
+  <conditionalFormatting sqref="D197:D198">
     <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="min"/>
@@ -67553,7 +67920,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E199:E200">
+  <conditionalFormatting sqref="E197:E198">
     <cfRule type="colorScale" priority="67">
       <colorScale>
         <cfvo type="min"/>
@@ -67565,7 +67932,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F199:F200">
+  <conditionalFormatting sqref="F197:F198">
     <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
@@ -67577,7 +67944,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G199:G200">
+  <conditionalFormatting sqref="G197:G198">
     <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
@@ -67589,7 +67956,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D219:D222">
+  <conditionalFormatting sqref="D216:D219">
     <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="min"/>
@@ -67601,7 +67968,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E219:E222">
+  <conditionalFormatting sqref="E216:E219">
     <cfRule type="colorScale" priority="63">
       <colorScale>
         <cfvo type="min"/>
@@ -67613,7 +67980,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F219:F222">
+  <conditionalFormatting sqref="F216:F219">
     <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="min"/>
@@ -67625,7 +67992,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G219:G222">
+  <conditionalFormatting sqref="G216:G219">
     <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="min"/>
@@ -67637,7 +68004,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D224:D225">
+  <conditionalFormatting sqref="D221:D222">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="min"/>
@@ -67649,7 +68016,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E224:E225">
+  <conditionalFormatting sqref="E221:E222">
     <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="min"/>
@@ -67661,7 +68028,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F224:F225">
+  <conditionalFormatting sqref="F221:F222">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="min"/>
@@ -67673,7 +68040,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G224:G225">
+  <conditionalFormatting sqref="G221:G222">
     <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
@@ -67685,7 +68052,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D244:D247">
+  <conditionalFormatting sqref="D240:D243">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
@@ -67697,7 +68064,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E244:E247">
+  <conditionalFormatting sqref="E240:E243">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -67709,7 +68076,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F244:F247">
+  <conditionalFormatting sqref="F240:F243">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
@@ -67721,7 +68088,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G244:G247">
+  <conditionalFormatting sqref="G240:G243">
     <cfRule type="colorScale" priority="53">
       <colorScale>
         <cfvo type="min"/>
@@ -67733,7 +68100,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D249:D250">
+  <conditionalFormatting sqref="D245:D246">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min"/>
@@ -67745,7 +68112,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E249:E250">
+  <conditionalFormatting sqref="E245:E246">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -67757,7 +68124,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F249:F250">
+  <conditionalFormatting sqref="F245:F246">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
@@ -67769,7 +68136,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G249:G250">
+  <conditionalFormatting sqref="G245:G246">
     <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
@@ -67781,7 +68148,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D269:D272">
+  <conditionalFormatting sqref="D264:D267">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
@@ -67793,7 +68160,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E269:E272">
+  <conditionalFormatting sqref="E264:E267">
     <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
@@ -67805,7 +68172,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F269:F272">
+  <conditionalFormatting sqref="F264:F267">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
@@ -67817,7 +68184,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G269:G272">
+  <conditionalFormatting sqref="G264:G267">
     <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
@@ -67829,7 +68196,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D274:D275">
+  <conditionalFormatting sqref="D269:D270">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
@@ -67841,7 +68208,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E274:E275">
+  <conditionalFormatting sqref="E269:E270">
     <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
@@ -67853,7 +68220,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F274:F275">
+  <conditionalFormatting sqref="F269:F270">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
@@ -67865,7 +68232,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G274:G275">
+  <conditionalFormatting sqref="G269:G270">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -67877,7 +68244,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D293:D296">
+  <conditionalFormatting sqref="D288:D291">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -67889,7 +68256,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E293:E296">
+  <conditionalFormatting sqref="E288:E291">
     <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
@@ -67901,7 +68268,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F293:F296">
+  <conditionalFormatting sqref="F288:F291">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
@@ -67913,7 +68280,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G293:G296">
+  <conditionalFormatting sqref="G288:G291">
     <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
@@ -67925,7 +68292,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D298:D299">
+  <conditionalFormatting sqref="D293:D294">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -67937,7 +68304,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E298:E299">
+  <conditionalFormatting sqref="E293:E294">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -67949,7 +68316,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F298:F299">
+  <conditionalFormatting sqref="F293:F294">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
@@ -67961,7 +68328,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G298:G299">
+  <conditionalFormatting sqref="G293:G294">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -67973,7 +68340,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D318:D321">
+  <conditionalFormatting sqref="D312:D315">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
@@ -67985,7 +68352,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E318:E321">
+  <conditionalFormatting sqref="E312:E315">
     <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
@@ -67997,7 +68364,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F318:F321">
+  <conditionalFormatting sqref="F312:F315">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
@@ -68009,7 +68376,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G318:G321">
+  <conditionalFormatting sqref="G312:G315">
     <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
@@ -68021,7 +68388,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D323:D324">
+  <conditionalFormatting sqref="D317:D318">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
@@ -68033,7 +68400,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E323:E324">
+  <conditionalFormatting sqref="E317:E318">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -68045,7 +68412,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F323:F324">
+  <conditionalFormatting sqref="F317:F318">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
@@ -68057,7 +68424,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G323:G324">
+  <conditionalFormatting sqref="G317:G318">
     <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
@@ -68069,7 +68436,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D343:D346">
+  <conditionalFormatting sqref="D336:D339">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
@@ -68081,7 +68448,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E343:E346">
+  <conditionalFormatting sqref="E336:E339">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
@@ -68093,7 +68460,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F343:F346">
+  <conditionalFormatting sqref="F336:F339">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
@@ -68105,7 +68472,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G343:G346">
+  <conditionalFormatting sqref="G336:G339">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -68117,7 +68484,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D348:D349">
+  <conditionalFormatting sqref="D341:D342">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -68129,7 +68496,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E348:E349">
+  <conditionalFormatting sqref="E341:E342">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -68141,7 +68508,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F348:F349">
+  <conditionalFormatting sqref="F341:F342">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -68153,7 +68520,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G348:G349">
+  <conditionalFormatting sqref="G341:G342">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -68165,7 +68532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D368:D371">
+  <conditionalFormatting sqref="D360:D363">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -68177,7 +68544,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E368:E371">
+  <conditionalFormatting sqref="E360:E363">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -68189,7 +68556,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F368:F371">
+  <conditionalFormatting sqref="F360:F363">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -68201,7 +68568,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G368:G371">
+  <conditionalFormatting sqref="G360:G363">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -68213,7 +68580,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D373:D374">
+  <conditionalFormatting sqref="D365:D366">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -68225,7 +68592,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E373:E374">
+  <conditionalFormatting sqref="E365:E366">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -68237,7 +68604,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F373:F374">
+  <conditionalFormatting sqref="F365:F366">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -68249,7 +68616,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G373:G374">
+  <conditionalFormatting sqref="G365:G366">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -68261,7 +68628,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D393:D396">
+  <conditionalFormatting sqref="D384:D387">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -68273,7 +68640,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E393:E396">
+  <conditionalFormatting sqref="E384:E387">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -68285,7 +68652,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F393:F396">
+  <conditionalFormatting sqref="F384:F387">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -68297,7 +68664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G393:G396">
+  <conditionalFormatting sqref="G384:G387">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -68309,7 +68676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D398:D399">
+  <conditionalFormatting sqref="D389:D390">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -68321,7 +68688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E398:E399">
+  <conditionalFormatting sqref="E389:E390">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -68333,7 +68700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F398:F399">
+  <conditionalFormatting sqref="F389:F390">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -68345,7 +68712,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G398:G399">
+  <conditionalFormatting sqref="G389:G390">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="2"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Original" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="47">
   <si>
     <t>sector</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>worst</t>
+  </si>
+  <si>
+    <t>сред</t>
   </si>
 </sst>
 </file>
@@ -8940,7 +8943,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9244,7 +9246,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9905,7 +9906,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10209,7 +10209,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10315,7 +10314,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10619,7 +10617,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10726,7 +10723,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11030,7 +11026,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11137,7 +11132,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11441,7 +11435,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11548,7 +11541,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11852,7 +11844,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11959,7 +11950,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -12263,7 +12253,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -12370,7 +12359,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -12674,7 +12662,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -12781,7 +12768,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13085,7 +13071,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13192,7 +13177,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13496,7 +13480,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13603,7 +13586,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13907,7 +13889,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14980,7 +14961,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -15284,7 +15264,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -62463,6 +62442,17 @@
       <c r="G123" s="4">
         <v>1.4794270549193711E-3</v>
       </c>
+      <c r="J123" t="s">
+        <v>46</v>
+      </c>
+      <c r="K123" s="3">
+        <f>AVERAGE(K108:K121)</f>
+        <v>0.82196723975363228</v>
+      </c>
+      <c r="L123" s="3">
+        <f>AVERAGE(L108:L121)</f>
+        <v>0.64086634028416523</v>
+      </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B125" s="7" t="s">
@@ -63391,23 +63381,23 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C180" s="2">
-        <f>C168/C$178</f>
+        <f t="shared" ref="C180:G183" si="32">C168/C$178</f>
         <v>0.5</v>
       </c>
       <c r="D180" s="2">
-        <f>D168/D$178</f>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="E180" s="2">
-        <f>E168/E$178</f>
+        <f t="shared" si="32"/>
         <v>0.84040363200323998</v>
       </c>
       <c r="F180" s="2">
-        <f>F168/F$178</f>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G180" s="2">
-        <f>G168/G$178</f>
+        <f t="shared" si="32"/>
         <v>0.22466253890066659</v>
       </c>
       <c r="J180" s="10">
@@ -63424,23 +63414,23 @@
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C181" s="2">
-        <f>C169/C$178</f>
+        <f t="shared" si="32"/>
         <v>0.75</v>
       </c>
       <c r="D181" s="2">
-        <f>D169/D$178</f>
+        <f t="shared" si="32"/>
         <v>0.99001250446019895</v>
       </c>
       <c r="E181" s="2">
-        <f>E169/E$178</f>
+        <f t="shared" si="32"/>
         <v>0.796663690136446</v>
       </c>
       <c r="F181" s="2">
-        <f>F169/F$178</f>
+        <f t="shared" si="32"/>
         <v>0.67318011860480464</v>
       </c>
       <c r="G181" s="2">
-        <f>G169/G$178</f>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="J181" s="2"/>
@@ -63449,23 +63439,23 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C182" s="2">
-        <f>C170/C$178</f>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="D182" s="2">
-        <f>D170/D$178</f>
+        <f t="shared" si="32"/>
         <v>0.98318460974903099</v>
       </c>
       <c r="E182" s="2">
-        <f>E170/E$178</f>
+        <f t="shared" si="32"/>
         <v>0.85797673286669429</v>
       </c>
       <c r="F182" s="2">
-        <f>F170/F$178</f>
+        <f t="shared" si="32"/>
         <v>0.47087156881956077</v>
       </c>
       <c r="G182" s="2">
-        <f>G170/G$178</f>
+        <f t="shared" si="32"/>
         <v>0.23502662946404326</v>
       </c>
       <c r="J182" s="10"/>
@@ -63474,23 +63464,23 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C183" s="2">
-        <f>C171/C$178</f>
+        <f t="shared" si="32"/>
         <v>0.25</v>
       </c>
       <c r="D183" s="2">
-        <f>D171/D$178</f>
+        <f t="shared" si="32"/>
         <v>0.90935810743449375</v>
       </c>
       <c r="E183" s="2">
-        <f>E171/E$178</f>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F183" s="2">
-        <f>F171/F$178</f>
+        <f t="shared" si="32"/>
         <v>0.58851951189135643</v>
       </c>
       <c r="G183" s="2">
-        <f>G171/G$178</f>
+        <f t="shared" si="32"/>
         <v>0.55344093952236229</v>
       </c>
     </row>
@@ -63703,15 +63693,15 @@
         <v>587631.66978157614</v>
       </c>
       <c r="E197" s="3">
-        <f t="shared" ref="E197:G197" si="32">AVERAGE(E192:E193)</f>
+        <f t="shared" ref="E197:G197" si="33">AVERAGE(E192:E193)</f>
         <v>4156.9489124299998</v>
       </c>
       <c r="F197" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1.4945212411908682E-3</v>
       </c>
       <c r="G197" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2.1859413555296043E-3</v>
       </c>
     </row>
@@ -63724,15 +63714,15 @@
         <v>553964.03680951521</v>
       </c>
       <c r="E198" s="3">
-        <f t="shared" ref="E198:G198" si="33">AVERAGE(E194:E195)</f>
+        <f t="shared" ref="E198:G198" si="34">AVERAGE(E194:E195)</f>
         <v>5386.9042822499996</v>
       </c>
       <c r="F198" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1.8217836051361176E-3</v>
       </c>
       <c r="G198" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1.5299410846390934E-3</v>
       </c>
     </row>
@@ -63745,15 +63735,15 @@
         <v>1.0607758459664012</v>
       </c>
       <c r="E200" s="3">
-        <f t="shared" ref="E200:G200" si="34">E197/E198</f>
+        <f t="shared" ref="E200:G200" si="35">E197/E198</f>
         <v>0.77167677289668257</v>
       </c>
       <c r="F200" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.82036156049346076</v>
       </c>
       <c r="G200" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1.4287748577228767</v>
       </c>
     </row>
@@ -63763,19 +63753,19 @@
         <v>4</v>
       </c>
       <c r="D202" s="2">
-        <f t="shared" ref="D202:G202" si="35">MAX(D192:D195)</f>
+        <f t="shared" ref="D202:G202" si="36">MAX(D192:D195)</f>
         <v>589836.07301855378</v>
       </c>
       <c r="E202" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>5998.8555937799993</v>
       </c>
       <c r="F202" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.3561812091085249E-3</v>
       </c>
       <c r="G202" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>2.2962786554205951E-3</v>
       </c>
     </row>
@@ -63805,23 +63795,23 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C204" s="2">
-        <f>C192/C$202</f>
+        <f t="shared" ref="C204:G207" si="37">C192/C$202</f>
         <v>1</v>
       </c>
       <c r="D204" s="2">
-        <f>D192/D$202</f>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="E204" s="2">
-        <f>E192/E$202</f>
+        <f t="shared" si="37"/>
         <v>0.57664977093076919</v>
       </c>
       <c r="F204" s="2">
-        <f>F192/F$202</f>
+        <f t="shared" si="37"/>
         <v>0.77853736812744556</v>
       </c>
       <c r="G204" s="2">
-        <f>G192/G$202</f>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="J204" s="10">
@@ -63838,67 +63828,67 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C205" s="2">
-        <f>C193/C$202</f>
+        <f t="shared" si="37"/>
         <v>0.5</v>
       </c>
       <c r="D205" s="2">
-        <f>D193/D$202</f>
+        <f t="shared" si="37"/>
         <v>0.99252536988558093</v>
       </c>
       <c r="E205" s="2">
-        <f>E193/E$202</f>
+        <f t="shared" si="37"/>
         <v>0.80926420797553855</v>
       </c>
       <c r="F205" s="2">
-        <f>F193/F$202</f>
+        <f t="shared" si="37"/>
         <v>0.11207082497893665</v>
       </c>
       <c r="G205" s="2">
-        <f>G193/G$202</f>
+        <f t="shared" si="37"/>
         <v>0.9038990327846067</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C206" s="2">
-        <f>C194/C$202</f>
+        <f t="shared" si="37"/>
         <v>0.75</v>
       </c>
       <c r="D206" s="2">
-        <f>D194/D$202</f>
+        <f t="shared" si="37"/>
         <v>0.97598188945750519</v>
       </c>
       <c r="E206" s="2">
-        <f>E194/E$202</f>
+        <f t="shared" si="37"/>
         <v>0.79597731535177796</v>
       </c>
       <c r="F206" s="2">
-        <f>F194/F$202</f>
+        <f t="shared" si="37"/>
         <v>8.5628869020468137E-2</v>
       </c>
       <c r="G206" s="2">
-        <f>G194/G$202</f>
+        <f t="shared" si="37"/>
         <v>0.57331026854314004</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C207" s="2">
-        <f>C195/C$202</f>
+        <f t="shared" si="37"/>
         <v>0.25</v>
       </c>
       <c r="D207" s="2">
-        <f>D195/D$202</f>
+        <f t="shared" si="37"/>
         <v>0.90238419274747317</v>
       </c>
       <c r="E207" s="2">
-        <f>E195/E$202</f>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="F207" s="2">
-        <f>F195/F$202</f>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="G207" s="2">
-        <f>G195/G$202</f>
+        <f t="shared" si="37"/>
         <v>0.7592293002304622</v>
       </c>
     </row>
@@ -64111,15 +64101,15 @@
         <v>2443787.471324191</v>
       </c>
       <c r="E221" s="3">
-        <f t="shared" ref="E221:G221" si="36">AVERAGE(E216:E217)</f>
+        <f t="shared" ref="E221:G221" si="38">AVERAGE(E216:E217)</f>
         <v>25052.605112639998</v>
       </c>
       <c r="F221" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>1.4196870259119745E-2</v>
       </c>
       <c r="G221" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>8.6934501979820604E-4</v>
       </c>
     </row>
@@ -64132,15 +64122,15 @@
         <v>2085486.3589302991</v>
       </c>
       <c r="E222" s="3">
-        <f t="shared" ref="E222:G222" si="37">AVERAGE(E218:E219)</f>
+        <f t="shared" ref="E222:G222" si="39">AVERAGE(E218:E219)</f>
         <v>30465.947887959999</v>
       </c>
       <c r="F222" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1.4102601314461555E-2</v>
       </c>
       <c r="G222" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>9.1133338088959293E-4</v>
       </c>
     </row>
@@ -64153,15 +64143,15 @@
         <v>1.1718069796331221</v>
       </c>
       <c r="E224" s="3">
-        <f t="shared" ref="E224:G224" si="38">E221/E222</f>
+        <f t="shared" ref="E224:G224" si="40">E221/E222</f>
         <v>0.82231497292558131</v>
       </c>
       <c r="F224" s="3">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1.0066845075285169</v>
       </c>
       <c r="G224" s="3">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.95392645329154935</v>
       </c>
     </row>
@@ -64171,19 +64161,19 @@
         <v>4</v>
       </c>
       <c r="D226" s="2">
-        <f t="shared" ref="D226:G226" si="39">MAX(D216:D219)</f>
+        <f t="shared" ref="D226:G226" si="41">MAX(D216:D219)</f>
         <v>2688475.9724428668</v>
       </c>
       <c r="E226" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>36820.330575920001</v>
       </c>
       <c r="F226" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>1.6816288641435851E-2</v>
       </c>
       <c r="G226" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>1.346627653376551E-3</v>
       </c>
     </row>
@@ -64213,23 +64203,23 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C228" s="2">
-        <f>C216/C$226</f>
+        <f t="shared" ref="C228:G231" si="42">C216/C$226</f>
         <v>0.25</v>
       </c>
       <c r="D228" s="2">
-        <f>D216/D$226</f>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="E228" s="2">
-        <f>E216/E$226</f>
+        <f t="shared" si="42"/>
         <v>0.62244477507294493</v>
       </c>
       <c r="F228" s="2">
-        <f>F216/F$226</f>
+        <f t="shared" si="42"/>
         <v>0.83919206923346823</v>
       </c>
       <c r="G228" s="2">
-        <f>G216/G$226</f>
+        <f t="shared" si="42"/>
         <v>0.50155358560624896</v>
       </c>
       <c r="J228" s="10">
@@ -64246,67 +64236,67 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C229" s="2">
-        <f>C217/C$226</f>
+        <f t="shared" si="42"/>
         <v>0.5</v>
       </c>
       <c r="D229" s="2">
-        <f>D217/D$226</f>
+        <f t="shared" si="42"/>
         <v>0.81797233553377002</v>
       </c>
       <c r="E229" s="2">
-        <f>E217/E$226</f>
+        <f t="shared" si="42"/>
         <v>0.73835805970790658</v>
       </c>
       <c r="F229" s="2">
-        <f>F217/F$226</f>
+        <f t="shared" si="42"/>
         <v>0.84927446007410101</v>
       </c>
       <c r="G229" s="2">
-        <f>G217/G$226</f>
+        <f t="shared" si="42"/>
         <v>0.78959028422057287</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C230" s="2">
-        <f>C218/C$226</f>
+        <f t="shared" si="42"/>
         <v>0.75</v>
       </c>
       <c r="D230" s="2">
-        <f>D218/D$226</f>
+        <f t="shared" si="42"/>
         <v>0.78513813991475667</v>
       </c>
       <c r="E230" s="2">
-        <f>E218/E$226</f>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="F230" s="2">
-        <f>F218/F$226</f>
+        <f t="shared" si="42"/>
         <v>0.67725490625943618</v>
       </c>
       <c r="G230" s="2">
-        <f>G218/G$226</f>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C231" s="2">
-        <f>C219/C$226</f>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="D231" s="2">
-        <f>D219/D$226</f>
+        <f t="shared" si="42"/>
         <v>0.76628830414256921</v>
       </c>
       <c r="E231" s="2">
-        <f>E219/E$226</f>
+        <f t="shared" si="42"/>
         <v>0.65484380022836186</v>
       </c>
       <c r="F231" s="2">
-        <f>F219/F$226</f>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="G231" s="2">
-        <f>G219/G$226</f>
+        <f t="shared" si="42"/>
         <v>0.3535046285504449</v>
       </c>
     </row>
@@ -64519,15 +64509,15 @@
         <v>998311.66844902653</v>
       </c>
       <c r="E245" s="3">
-        <f t="shared" ref="E245:G245" si="40">AVERAGE(E240:E241)</f>
+        <f t="shared" ref="E245:G245" si="43">AVERAGE(E240:E241)</f>
         <v>25886.499881399999</v>
       </c>
       <c r="F245" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>3.4542866290168506E-2</v>
       </c>
       <c r="G245" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>9.7260937100924743E-3</v>
       </c>
     </row>
@@ -64540,15 +64530,15 @@
         <v>788582.79499953869</v>
       </c>
       <c r="E246" s="3">
-        <f t="shared" ref="E246:G246" si="41">AVERAGE(E242:E243)</f>
+        <f t="shared" ref="E246:G246" si="44">AVERAGE(E242:E243)</f>
         <v>21907.77927644</v>
       </c>
       <c r="F246" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>8.5728460385611147E-3</v>
       </c>
       <c r="G246" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>7.7075280111627334E-4</v>
       </c>
     </row>
@@ -64561,15 +64551,15 @@
         <v>1.2659566944389276</v>
       </c>
       <c r="E248" s="3">
-        <f t="shared" ref="E248:G248" si="42">E245/E246</f>
+        <f t="shared" ref="E248:G248" si="45">E245/E246</f>
         <v>1.1816122280015293</v>
       </c>
       <c r="F248" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>4.0293347314057506</v>
       </c>
       <c r="G248" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>12.618953438776055</v>
       </c>
     </row>
@@ -64579,19 +64569,19 @@
         <v>4</v>
       </c>
       <c r="D250" s="2">
-        <f t="shared" ref="D250:G250" si="43">MAX(D240:D243)</f>
+        <f t="shared" ref="D250:G250" si="46">MAX(D240:D243)</f>
         <v>1079590.799601601</v>
       </c>
       <c r="E250" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>31768.917493320001</v>
       </c>
       <c r="F250" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>5.1385668600091312E-2</v>
       </c>
       <c r="G250" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>1.8406361575525849E-2</v>
       </c>
     </row>
@@ -64621,23 +64611,23 @@
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C252" s="2">
-        <f>C240/C$250</f>
+        <f t="shared" ref="C252:G255" si="47">C240/C$250</f>
         <v>1</v>
       </c>
       <c r="D252" s="2">
-        <f>D240/D$250</f>
+        <f t="shared" si="47"/>
         <v>1</v>
       </c>
       <c r="E252" s="2">
-        <f>E240/E$250</f>
+        <f t="shared" si="47"/>
         <v>0.93878727817122176</v>
       </c>
       <c r="F252" s="2">
-        <f>F240/F$250</f>
+        <f t="shared" si="47"/>
         <v>0.34445526276978805</v>
       </c>
       <c r="G252" s="2">
-        <f>G240/G$250</f>
+        <f t="shared" si="47"/>
         <v>1</v>
       </c>
       <c r="J252" s="10">
@@ -64654,67 +64644,67 @@
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C253" s="2">
-        <f>C241/C$250</f>
+        <f t="shared" si="47"/>
         <v>0.75</v>
       </c>
       <c r="D253" s="2">
-        <f>D241/D$250</f>
+        <f t="shared" si="47"/>
         <v>0.84942603960209995</v>
       </c>
       <c r="E253" s="2">
-        <f>E241/E$250</f>
+        <f t="shared" si="47"/>
         <v>0.69088738020157991</v>
       </c>
       <c r="F253" s="2">
-        <f>F241/F$250</f>
+        <f t="shared" si="47"/>
         <v>1</v>
       </c>
       <c r="G253" s="2">
-        <f>G241/G$250</f>
+        <f t="shared" si="47"/>
         <v>5.6818716744632944E-2</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C254" s="2">
-        <f>C242/C$250</f>
+        <f t="shared" si="47"/>
         <v>0.5</v>
       </c>
       <c r="D254" s="2">
-        <f>D242/D$250</f>
+        <f t="shared" si="47"/>
         <v>0.74339840698029691</v>
       </c>
       <c r="E254" s="2">
-        <f>E242/E$250</f>
+        <f t="shared" si="47"/>
         <v>0.37919583070757845</v>
       </c>
       <c r="F254" s="2">
-        <f>F242/F$250</f>
+        <f t="shared" si="47"/>
         <v>0.24604511227578876</v>
       </c>
       <c r="G254" s="2">
-        <f>G242/G$250</f>
+        <f t="shared" si="47"/>
         <v>5.0333919862687079E-2</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C255" s="2">
-        <f>C243/C$250</f>
+        <f t="shared" si="47"/>
         <v>0.25</v>
       </c>
       <c r="D255" s="2">
-        <f>D243/D$250</f>
+        <f t="shared" si="47"/>
         <v>0.71749361857336225</v>
       </c>
       <c r="E255" s="2">
-        <f>E243/E$250</f>
+        <f t="shared" si="47"/>
         <v>1</v>
       </c>
       <c r="F255" s="2">
-        <f>F243/F$250</f>
+        <f t="shared" si="47"/>
         <v>8.7621696860402221E-2</v>
       </c>
       <c r="G255" s="2">
-        <f>G243/G$250</f>
+        <f t="shared" si="47"/>
         <v>3.3414603489272977E-2</v>
       </c>
     </row>
@@ -64927,15 +64917,15 @@
         <v>675581.93770212308</v>
       </c>
       <c r="E269" s="3">
-        <f t="shared" ref="E269:G269" si="44">AVERAGE(E264:E265)</f>
+        <f t="shared" ref="E269:G269" si="48">AVERAGE(E264:E265)</f>
         <v>22529.27734968</v>
       </c>
       <c r="F269" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>1.7879495298971426E-2</v>
       </c>
       <c r="G269" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>1.3945754714594475E-3</v>
       </c>
     </row>
@@ -64948,15 +64938,15 @@
         <v>507709.06388788664</v>
       </c>
       <c r="E270" s="3">
-        <f t="shared" ref="E270:G270" si="45">AVERAGE(E266:E267)</f>
+        <f t="shared" ref="E270:G270" si="49">AVERAGE(E266:E267)</f>
         <v>42915.275829450002</v>
       </c>
       <c r="F270" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>1.2281113688736172E-3</v>
       </c>
       <c r="G270" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>6.8659427051578625E-3</v>
       </c>
     </row>
@@ -64969,15 +64959,15 @@
         <v>1.3306477779394272</v>
       </c>
       <c r="E272" s="3">
-        <f t="shared" ref="E272:G272" si="46">E269/E270</f>
+        <f t="shared" ref="E272:G272" si="50">E269/E270</f>
         <v>0.52497104851926879</v>
       </c>
       <c r="F272" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>14.558529260558757</v>
       </c>
       <c r="G272" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>0.20311492992969613</v>
       </c>
     </row>
@@ -64987,19 +64977,19 @@
         <v>4</v>
       </c>
       <c r="D274" s="2">
-        <f t="shared" ref="D274:G274" si="47">MAX(D264:D267)</f>
+        <f t="shared" ref="D274:G274" si="51">MAX(D264:D267)</f>
         <v>702640.28510284843</v>
       </c>
       <c r="E274" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>57596.7124071</v>
       </c>
       <c r="F274" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>2.3285205202868371E-2</v>
       </c>
       <c r="G274" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>1.2640594598421069E-2</v>
       </c>
     </row>
@@ -65029,23 +65019,23 @@
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C276" s="2">
-        <f>C264/C$274</f>
+        <f t="shared" ref="C276:G279" si="52">C264/C$274</f>
         <v>1</v>
       </c>
       <c r="D276" s="2">
-        <f>D264/D$274</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="E276" s="2">
-        <f>E264/E$274</f>
+        <f t="shared" si="52"/>
         <v>0.4287191813565403</v>
       </c>
       <c r="F276" s="2">
-        <f>F264/F$274</f>
+        <f t="shared" si="52"/>
         <v>0.53569574699465849</v>
       </c>
       <c r="G276" s="2">
-        <f>G264/G$274</f>
+        <f t="shared" si="52"/>
         <v>9.5790129052906028E-2</v>
       </c>
       <c r="J276" s="10">
@@ -65062,67 +65052,67 @@
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C277" s="2">
-        <f>C265/C$274</f>
+        <f t="shared" si="52"/>
         <v>0.75</v>
       </c>
       <c r="D277" s="2">
-        <f>D265/D$274</f>
+        <f t="shared" si="52"/>
         <v>0.9229809392532492</v>
       </c>
       <c r="E277" s="2">
-        <f>E265/E$274</f>
+        <f t="shared" si="52"/>
         <v>0.3535920446884655</v>
       </c>
       <c r="F277" s="2">
-        <f>F265/F$274</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="G277" s="2">
-        <f>G265/G$274</f>
+        <f t="shared" si="52"/>
         <v>0.12486016719718387</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C278" s="2">
-        <f>C266/C$274</f>
+        <f t="shared" si="52"/>
         <v>0.5</v>
       </c>
       <c r="D278" s="2">
-        <f>D266/D$274</f>
+        <f t="shared" si="52"/>
         <v>0.74801703981263812</v>
       </c>
       <c r="E278" s="2">
-        <f>E266/E$274</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="F278" s="2">
-        <f>F266/F$274</f>
+        <f t="shared" si="52"/>
         <v>2.9773689598128844E-2</v>
       </c>
       <c r="G278" s="2">
-        <f>G266/G$274</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C279" s="2">
-        <f>C267/C$274</f>
+        <f t="shared" si="52"/>
         <v>0.25</v>
       </c>
       <c r="D279" s="2">
-        <f>D267/D$274</f>
+        <f t="shared" si="52"/>
         <v>0.69712943030064645</v>
       </c>
       <c r="E279" s="2">
-        <f>E267/E$274</f>
+        <f t="shared" si="52"/>
         <v>0.49019879906061425</v>
       </c>
       <c r="F279" s="2">
-        <f>F267/F$274</f>
+        <f t="shared" si="52"/>
         <v>7.571057460945764E-2</v>
       </c>
       <c r="G279" s="2">
-        <f>G267/G$274</f>
+        <f t="shared" si="52"/>
         <v>8.6332237253377908E-2</v>
       </c>
     </row>
@@ -65335,15 +65325,15 @@
         <v>311883.76638548798</v>
       </c>
       <c r="E293" s="3">
-        <f t="shared" ref="E293:G293" si="48">AVERAGE(E288:E289)</f>
+        <f t="shared" ref="E293:G293" si="53">AVERAGE(E288:E289)</f>
         <v>5860.4372275599999</v>
       </c>
       <c r="F293" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
         <v>5.5548597773630477E-3</v>
       </c>
       <c r="G293" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
         <v>1.5282865780308955E-3</v>
       </c>
     </row>
@@ -65356,15 +65346,15 @@
         <v>247004.20147306001</v>
       </c>
       <c r="E294" s="3">
-        <f t="shared" ref="E294:G294" si="49">AVERAGE(E290:E291)</f>
+        <f t="shared" ref="E294:G294" si="54">AVERAGE(E290:E291)</f>
         <v>25327.99827842</v>
       </c>
       <c r="F294" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>3.5200008083333573E-4</v>
       </c>
       <c r="G294" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>1.6499922468599239E-3</v>
       </c>
     </row>
@@ -65377,15 +65367,15 @@
         <v>1.2626658353400688</v>
       </c>
       <c r="E296" s="3">
-        <f t="shared" ref="E296:G296" si="50">E293/E294</f>
+        <f t="shared" ref="E296:G296" si="55">E293/E294</f>
         <v>0.23138177613322164</v>
       </c>
       <c r="F296" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="55"/>
         <v>15.780848016319494</v>
       </c>
       <c r="G296" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="55"/>
         <v>0.9262386419932308</v>
       </c>
     </row>
@@ -65395,19 +65385,19 @@
         <v>4</v>
       </c>
       <c r="D298" s="2">
-        <f t="shared" ref="D298:G298" si="51">MAX(D288:D291)</f>
+        <f t="shared" ref="D298:G298" si="56">MAX(D288:D291)</f>
         <v>333902.21266145178</v>
       </c>
       <c r="E298" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>45922.658233419999</v>
       </c>
       <c r="F298" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>7.1409024001186736E-3</v>
       </c>
       <c r="G298" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>3.1476572520248271E-3</v>
       </c>
     </row>
@@ -65437,23 +65427,23 @@
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C300" s="2">
-        <f>C288/C$298</f>
+        <f t="shared" ref="C300:G303" si="57">C288/C$298</f>
         <v>1</v>
       </c>
       <c r="D300" s="2">
-        <f>D288/D$298</f>
+        <f t="shared" si="57"/>
         <v>1</v>
       </c>
       <c r="E300" s="2">
-        <f>E288/E$298</f>
+        <f t="shared" si="57"/>
         <v>0.14350332523225146</v>
       </c>
       <c r="F300" s="2">
-        <f>F288/F$298</f>
+        <f t="shared" si="57"/>
         <v>0.55578650039264843</v>
       </c>
       <c r="G300" s="2">
-        <f>G288/G$298</f>
+        <f t="shared" si="57"/>
         <v>0.45346685151196658</v>
       </c>
       <c r="J300" s="10">
@@ -65470,67 +65460,67 @@
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C301" s="2">
-        <f>C289/C$298</f>
+        <f t="shared" si="57"/>
         <v>0.75</v>
       </c>
       <c r="D301" s="2">
-        <f>D289/D$298</f>
+        <f t="shared" si="57"/>
         <v>0.86811440331311229</v>
       </c>
       <c r="E301" s="2">
-        <f>E289/E$298</f>
+        <f t="shared" si="57"/>
         <v>0.11172742372709753</v>
       </c>
       <c r="F301" s="2">
-        <f>F289/F$298</f>
+        <f t="shared" si="57"/>
         <v>1</v>
       </c>
       <c r="G301" s="2">
-        <f>G289/G$298</f>
+        <f t="shared" si="57"/>
         <v>0.5175960410871423</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C302" s="2">
-        <f>C290/C$298</f>
+        <f t="shared" si="57"/>
         <v>0.5</v>
       </c>
       <c r="D302" s="2">
-        <f>D290/D$298</f>
+        <f t="shared" si="57"/>
         <v>0.77812754762172931</v>
       </c>
       <c r="E302" s="2">
-        <f>E290/E$298</f>
+        <f t="shared" si="57"/>
         <v>1</v>
       </c>
       <c r="F302" s="2">
-        <f>F290/F$298</f>
+        <f t="shared" si="57"/>
         <v>5.6622871781342003E-3</v>
       </c>
       <c r="G302" s="2">
-        <f>G290/G$298</f>
+        <f t="shared" si="57"/>
         <v>4.8393846438341249E-2</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C303" s="2">
-        <f>C291/C$298</f>
+        <f t="shared" si="57"/>
         <v>0.25</v>
       </c>
       <c r="D303" s="2">
-        <f>D291/D$298</f>
+        <f t="shared" si="57"/>
         <v>0.70137268991339052</v>
       </c>
       <c r="E303" s="2">
-        <f>E291/E$298</f>
+        <f t="shared" si="57"/>
         <v>0.10307195849510592</v>
       </c>
       <c r="F303" s="2">
-        <f>F291/F$298</f>
+        <f t="shared" si="57"/>
         <v>9.2924715166971622E-2</v>
       </c>
       <c r="G303" s="2">
-        <f>G291/G$298</f>
+        <f t="shared" si="57"/>
         <v>1</v>
       </c>
     </row>
@@ -65743,15 +65733,15 @@
         <v>539397.81040579407</v>
       </c>
       <c r="E317" s="3">
-        <f t="shared" ref="E317:G317" si="52">AVERAGE(E312:E313)</f>
+        <f t="shared" ref="E317:G317" si="58">AVERAGE(E312:E313)</f>
         <v>10784.211597880001</v>
       </c>
       <c r="F317" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>3.0192741349205411E-3</v>
       </c>
       <c r="G317" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>2.0541759430544771E-3</v>
       </c>
     </row>
@@ -65764,15 +65754,15 @@
         <v>419160.81862446223</v>
       </c>
       <c r="E318" s="3">
-        <f t="shared" ref="E318:G318" si="53">AVERAGE(E314:E315)</f>
+        <f t="shared" ref="E318:G318" si="59">AVERAGE(E314:E315)</f>
         <v>9648.2186803599998</v>
       </c>
       <c r="F318" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>2.9670262853140415E-2</v>
       </c>
       <c r="G318" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>1.602096937818074E-3</v>
       </c>
     </row>
@@ -65785,15 +65775,15 @@
         <v>1.2868516961482879</v>
       </c>
       <c r="E320" s="3">
-        <f t="shared" ref="E320:G320" si="54">E317/E318</f>
+        <f t="shared" ref="E320:G320" si="60">E317/E318</f>
         <v>1.1177412074865631</v>
       </c>
       <c r="F320" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="60"/>
         <v>0.10176095000792922</v>
       </c>
       <c r="G320" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="60"/>
         <v>1.2821795576565411</v>
       </c>
     </row>
@@ -65803,19 +65793,19 @@
         <v>4</v>
       </c>
       <c r="D322" s="2">
-        <f t="shared" ref="D322:G322" si="55">MAX(D312:D315)</f>
+        <f t="shared" ref="D322:G322" si="61">MAX(D312:D315)</f>
         <v>615324.90182869229</v>
       </c>
       <c r="E322" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>12188.037840000001</v>
       </c>
       <c r="F322" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>5.3628300774693723E-2</v>
       </c>
       <c r="G322" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>2.3262126662383252E-3</v>
       </c>
     </row>
@@ -65845,23 +65835,23 @@
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C324" s="2">
-        <f>C312/C$322</f>
+        <f t="shared" ref="C324:G327" si="62">C312/C$322</f>
         <v>1</v>
       </c>
       <c r="D324" s="2">
-        <f>D312/D$322</f>
+        <f t="shared" si="62"/>
         <v>1</v>
       </c>
       <c r="E324" s="2">
-        <f>E312/E$322</f>
+        <f t="shared" si="62"/>
         <v>1</v>
       </c>
       <c r="F324" s="2">
-        <f>F312/F$322</f>
+        <f t="shared" si="62"/>
         <v>6.6315361695601274E-2</v>
       </c>
       <c r="G324" s="2">
-        <f>G312/G$322</f>
+        <f t="shared" si="62"/>
         <v>1</v>
       </c>
       <c r="J324" s="10">
@@ -65878,67 +65868,67 @@
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C325" s="2">
-        <f>C313/C$322</f>
+        <f t="shared" si="62"/>
         <v>0.75</v>
       </c>
       <c r="D325" s="2">
-        <f>D313/D$322</f>
+        <f t="shared" si="62"/>
         <v>0.75321300601601027</v>
       </c>
       <c r="E325" s="2">
-        <f>E313/E$322</f>
+        <f t="shared" si="62"/>
         <v>0.76963868006501046</v>
       </c>
       <c r="F325" s="2">
-        <f>F313/F$322</f>
+        <f t="shared" si="62"/>
         <v>4.6284668188071074E-2</v>
       </c>
       <c r="G325" s="2">
-        <f>G313/G$322</f>
+        <f t="shared" si="62"/>
         <v>0.76611190616225677</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C326" s="2">
-        <f>C314/C$322</f>
+        <f t="shared" si="62"/>
         <v>0.5</v>
       </c>
       <c r="D326" s="2">
-        <f>D314/D$322</f>
+        <f t="shared" si="62"/>
         <v>0.71816557146611792</v>
       </c>
       <c r="E326" s="2">
-        <f>E314/E$322</f>
+        <f t="shared" si="62"/>
         <v>0.71225562194184977</v>
       </c>
       <c r="F326" s="2">
-        <f>F314/F$322</f>
+        <f t="shared" si="62"/>
         <v>1</v>
       </c>
       <c r="G326" s="2">
-        <f>G314/G$322</f>
+        <f t="shared" si="62"/>
         <v>0.85157128686456229</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C327" s="2">
-        <f>C315/C$322</f>
+        <f t="shared" si="62"/>
         <v>0.25</v>
       </c>
       <c r="D327" s="2">
-        <f>D315/D$322</f>
+        <f t="shared" si="62"/>
         <v>0.64423928937651198</v>
       </c>
       <c r="E327" s="2">
-        <f>E315/E$322</f>
+        <f t="shared" si="62"/>
         <v>0.87097193396472083</v>
       </c>
       <c r="F327" s="2">
-        <f>F315/F$322</f>
+        <f t="shared" si="62"/>
         <v>0.10651512073048215</v>
       </c>
       <c r="G327" s="2">
-        <f>G315/G$322</f>
+        <f t="shared" si="62"/>
         <v>0.52585818127499084</v>
       </c>
     </row>
@@ -66151,15 +66141,15 @@
         <v>455716.68927308638</v>
       </c>
       <c r="E341" s="3">
-        <f t="shared" ref="E341:G341" si="56">AVERAGE(E336:E337)</f>
+        <f t="shared" ref="E341:G341" si="63">AVERAGE(E336:E337)</f>
         <v>11682.365346869999</v>
       </c>
       <c r="F341" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="63"/>
         <v>2.5646214635220368E-4</v>
       </c>
       <c r="G341" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="63"/>
         <v>7.7631350098399787E-3</v>
       </c>
     </row>
@@ -66172,15 +66162,15 @@
         <v>327806.54070756712</v>
       </c>
       <c r="E342" s="3">
-        <f t="shared" ref="E342:G342" si="57">AVERAGE(E338:E339)</f>
+        <f t="shared" ref="E342:G342" si="64">AVERAGE(E338:E339)</f>
         <v>7988.6998572800003</v>
       </c>
       <c r="F342" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>3.6016061043586542E-4</v>
       </c>
       <c r="G342" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>6.1379375326141381E-3</v>
       </c>
     </row>
@@ -66193,15 +66183,15 @@
         <v>1.3902001109844437</v>
       </c>
       <c r="E344" s="3">
-        <f t="shared" ref="E344:G344" si="58">E341/E342</f>
+        <f t="shared" ref="E344:G344" si="65">E341/E342</f>
         <v>1.462361279754929</v>
       </c>
       <c r="F344" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>0.71207716480109773</v>
       </c>
       <c r="G344" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>1.2647790839496653</v>
       </c>
     </row>
@@ -66211,19 +66201,19 @@
         <v>4</v>
       </c>
       <c r="D346" s="2">
-        <f t="shared" ref="D346:G346" si="59">MAX(D336:D339)</f>
+        <f t="shared" ref="D346:G346" si="66">MAX(D336:D339)</f>
         <v>480752.63075950177</v>
       </c>
       <c r="E346" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>13713.99982974</v>
       </c>
       <c r="F346" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>5.6879237956854514E-4</v>
       </c>
       <c r="G346" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>1.421912259449817E-2</v>
       </c>
     </row>
@@ -66253,23 +66243,23 @@
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C348" s="2">
-        <f>C336/C$346</f>
+        <f t="shared" ref="C348:G351" si="67">C336/C$346</f>
         <v>0.25</v>
       </c>
       <c r="D348" s="2">
-        <f>D336/D$346</f>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="E348" s="2">
-        <f>E336/E$346</f>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="F348" s="2">
-        <f>F336/F$346</f>
+        <f t="shared" si="67"/>
         <v>0.33245092784424229</v>
       </c>
       <c r="G348" s="2">
-        <f>G336/G$346</f>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="J348" s="10">
@@ -66286,67 +66276,67 @@
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C349" s="2">
-        <f>C337/C$346</f>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="D349" s="2">
-        <f>D337/D$346</f>
+        <f t="shared" si="67"/>
         <v>0.89584688721572603</v>
       </c>
       <c r="E349" s="2">
-        <f>E337/E$346</f>
+        <f t="shared" si="67"/>
         <v>0.70371379494052133</v>
       </c>
       <c r="F349" s="2">
-        <f>F337/F$346</f>
+        <f t="shared" si="67"/>
         <v>0.56932678776700363</v>
       </c>
       <c r="G349" s="2">
-        <f>G337/G$346</f>
+        <f t="shared" si="67"/>
         <v>9.1928838540822747E-2</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C350" s="2">
-        <f>C338/C$346</f>
+        <f t="shared" si="67"/>
         <v>0.75</v>
       </c>
       <c r="D350" s="2">
-        <f>D338/D$346</f>
+        <f t="shared" si="67"/>
         <v>0.7172468986764462</v>
       </c>
       <c r="E350" s="2">
-        <f>E338/E$346</f>
+        <f t="shared" si="67"/>
         <v>0.56632037695360282</v>
       </c>
       <c r="F350" s="2">
-        <f>F338/F$346</f>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="G350" s="2">
-        <f>G338/G$346</f>
+        <f t="shared" si="67"/>
         <v>6.5308363085126067E-2</v>
       </c>
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C351" s="2">
-        <f>C339/C$346</f>
+        <f t="shared" si="67"/>
         <v>0.5</v>
       </c>
       <c r="D351" s="2">
-        <f>D339/D$346</f>
+        <f t="shared" si="67"/>
         <v>0.64647539729806525</v>
       </c>
       <c r="E351" s="2">
-        <f>E339/E$346</f>
+        <f t="shared" si="67"/>
         <v>0.59872263842631746</v>
       </c>
       <c r="F351" s="2">
-        <f>F339/F$346</f>
+        <f t="shared" si="67"/>
         <v>0.26640448561938757</v>
       </c>
       <c r="G351" s="2">
-        <f>G339/G$346</f>
+        <f t="shared" si="67"/>
         <v>0.798027260026964</v>
       </c>
     </row>
@@ -66559,15 +66549,15 @@
         <v>619748.13934391923</v>
       </c>
       <c r="E365" s="3">
-        <f t="shared" ref="E365:G365" si="60">AVERAGE(E360:E361)</f>
+        <f t="shared" ref="E365:G365" si="68">AVERAGE(E360:E361)</f>
         <v>20897.6226838</v>
       </c>
       <c r="F365" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>1.9907877305405742E-3</v>
       </c>
       <c r="G365" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>2.1368874424534858E-3</v>
       </c>
     </row>
@@ -66580,15 +66570,15 @@
         <v>543408.77879270562</v>
       </c>
       <c r="E366" s="3">
-        <f t="shared" ref="E366:G366" si="61">AVERAGE(E362:E363)</f>
+        <f t="shared" ref="E366:G366" si="69">AVERAGE(E362:E363)</f>
         <v>16256.808749169999</v>
       </c>
       <c r="F366" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>2.3062679545461382E-3</v>
       </c>
       <c r="G366" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>8.4974445192539461E-4</v>
       </c>
     </row>
@@ -66601,15 +66591,15 @@
         <v>1.1404823836685474</v>
       </c>
       <c r="E368" s="3">
-        <f t="shared" ref="E368:G368" si="62">E365/E366</f>
+        <f t="shared" ref="E368:G368" si="70">E365/E366</f>
         <v>1.2854689383527957</v>
       </c>
       <c r="F368" s="3">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>0.8632074718882139</v>
       </c>
       <c r="G368" s="3">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>2.5147412702861627</v>
       </c>
     </row>
@@ -66619,19 +66609,19 @@
         <v>4</v>
       </c>
       <c r="D370" s="2">
-        <f t="shared" ref="D370:G370" si="63">MAX(D360:D363)</f>
+        <f t="shared" ref="D370:G370" si="71">MAX(D360:D363)</f>
         <v>624490.81179662514</v>
       </c>
       <c r="E370" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>23490.718752000001</v>
       </c>
       <c r="F370" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>3.348617336982791E-3</v>
       </c>
       <c r="G370" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>2.397692315221963E-3</v>
       </c>
     </row>
@@ -66661,23 +66651,23 @@
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C372" s="2">
-        <f>C360/C$370</f>
+        <f t="shared" ref="C372:G375" si="72">C360/C$370</f>
         <v>1</v>
       </c>
       <c r="D372" s="2">
-        <f>D360/D$370</f>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
       <c r="E372" s="2">
-        <f>E360/E$370</f>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
       <c r="F372" s="2">
-        <f>F360/F$370</f>
+        <f t="shared" si="72"/>
         <v>0.57548795019413157</v>
       </c>
       <c r="G372" s="2">
-        <f>G360/G$370</f>
+        <f t="shared" si="72"/>
         <v>0.78245342731197487</v>
       </c>
       <c r="J372" s="10">
@@ -66694,67 +66684,67 @@
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C373" s="2">
-        <f>C361/C$370</f>
+        <f t="shared" si="72"/>
         <v>0.75</v>
       </c>
       <c r="D373" s="2">
-        <f>D361/D$370</f>
+        <f t="shared" si="72"/>
         <v>0.98481107371600407</v>
       </c>
       <c r="E373" s="2">
-        <f>E361/E$370</f>
+        <f t="shared" si="72"/>
         <v>0.77922377807369358</v>
       </c>
       <c r="F373" s="2">
-        <f>F361/F$370</f>
+        <f t="shared" si="72"/>
         <v>0.61353278893537189</v>
       </c>
       <c r="G373" s="2">
-        <f>G361/G$370</f>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C374" s="2">
-        <f>C362/C$370</f>
+        <f t="shared" si="72"/>
         <v>0.25</v>
       </c>
       <c r="D374" s="2">
-        <f>D362/D$370</f>
+        <f t="shared" si="72"/>
         <v>0.89333734012332733</v>
       </c>
       <c r="E374" s="2">
-        <f>E362/E$370</f>
+        <f t="shared" si="72"/>
         <v>0.7523646986099678</v>
       </c>
       <c r="F374" s="2">
-        <f>F362/F$370</f>
+        <f t="shared" si="72"/>
         <v>0.3774449108145379</v>
       </c>
       <c r="G374" s="2">
-        <f>G362/G$370</f>
+        <f t="shared" si="72"/>
         <v>0.30132523711798664</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C375" s="2">
-        <f>C363/C$370</f>
+        <f t="shared" si="72"/>
         <v>0.5</v>
       </c>
       <c r="D375" s="2">
-        <f>D363/D$370</f>
+        <f t="shared" si="72"/>
         <v>0.84698859751328548</v>
       </c>
       <c r="E375" s="2">
-        <f>E363/E$370</f>
+        <f t="shared" si="72"/>
         <v>0.63174014047980198</v>
       </c>
       <c r="F375" s="2">
-        <f>F363/F$370</f>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
       <c r="G375" s="2">
-        <f>G363/G$370</f>
+        <f t="shared" si="72"/>
         <v>0.40747667756532474</v>
       </c>
     </row>
@@ -66967,15 +66957,15 @@
         <v>488751.48647320317</v>
       </c>
       <c r="E389" s="3">
-        <f t="shared" ref="E389:G389" si="64">AVERAGE(E384:E385)</f>
+        <f t="shared" ref="E389:G389" si="73">AVERAGE(E384:E385)</f>
         <v>5858.9591118600001</v>
       </c>
       <c r="F389" s="4">
-        <f t="shared" si="64"/>
+        <f t="shared" si="73"/>
         <v>7.1277616950951182E-4</v>
       </c>
       <c r="G389" s="4">
-        <f t="shared" si="64"/>
+        <f t="shared" si="73"/>
         <v>3.4712364577555127E-3</v>
       </c>
     </row>
@@ -66988,15 +66978,15 @@
         <v>463384.62845776771</v>
       </c>
       <c r="E390" s="3">
-        <f t="shared" ref="E390:G390" si="65">AVERAGE(E386:E387)</f>
+        <f t="shared" ref="E390:G390" si="74">AVERAGE(E386:E387)</f>
         <v>6502.7992681799997</v>
       </c>
       <c r="F390" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="74"/>
         <v>1.191953502593869E-3</v>
       </c>
       <c r="G390" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="74"/>
         <v>1.1285826622679715E-3</v>
       </c>
     </row>
@@ -67009,15 +66999,15 @@
         <v>1.0547425539337831</v>
       </c>
       <c r="E392" s="3">
-        <f t="shared" ref="E392:G392" si="66">E389/E390</f>
+        <f t="shared" ref="E392:G392" si="75">E389/E390</f>
         <v>0.9009903074402914</v>
       </c>
       <c r="F392" s="3">
-        <f t="shared" si="66"/>
+        <f t="shared" si="75"/>
         <v>0.59798991148430225</v>
       </c>
       <c r="G392" s="3">
-        <f t="shared" si="66"/>
+        <f t="shared" si="75"/>
         <v>3.0757485240645135</v>
       </c>
     </row>
@@ -67027,19 +67017,19 @@
         <v>4</v>
       </c>
       <c r="D394" s="2">
-        <f t="shared" ref="D394:G394" si="67">MAX(D384:D387)</f>
+        <f t="shared" ref="D394:G394" si="76">MAX(D384:D387)</f>
         <v>496312.33844584553</v>
       </c>
       <c r="E394" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="76"/>
         <v>6600.4823040000001</v>
       </c>
       <c r="F394" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="76"/>
         <v>1.36542870460566E-3</v>
       </c>
       <c r="G394" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="76"/>
         <v>4.3326889923906344E-3</v>
       </c>
     </row>
@@ -67069,23 +67059,23 @@
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C396" s="2">
-        <f>C384/C$394</f>
+        <f t="shared" ref="C396:G399" si="77">C384/C$394</f>
         <v>0.25</v>
       </c>
       <c r="D396" s="2">
-        <f>D384/D$394</f>
+        <f t="shared" si="77"/>
         <v>1</v>
       </c>
       <c r="E396" s="2">
-        <f>E384/E$394</f>
+        <f t="shared" si="77"/>
         <v>0.91790681578047295</v>
       </c>
       <c r="F396" s="2">
-        <f>F384/F$394</f>
+        <f t="shared" si="77"/>
         <v>0.84158694771293341</v>
       </c>
       <c r="G396" s="2">
-        <f>G384/G$394</f>
+        <f t="shared" si="77"/>
         <v>1</v>
       </c>
       <c r="J396" s="10">
@@ -67102,67 +67092,67 @@
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C397" s="2">
-        <f>C385/C$394</f>
+        <f t="shared" si="77"/>
         <v>0.75</v>
       </c>
       <c r="D397" s="2">
-        <f>D385/D$394</f>
+        <f t="shared" si="77"/>
         <v>0.96953187987903577</v>
       </c>
       <c r="E397" s="2">
-        <f>E385/E$394</f>
+        <f t="shared" si="77"/>
         <v>0.85740560595251925</v>
       </c>
       <c r="F397" s="2">
-        <f>F385/F$394</f>
+        <f t="shared" si="77"/>
         <v>0.20244584155725229</v>
       </c>
       <c r="G397" s="2">
-        <f>G385/G$394</f>
+        <f t="shared" si="77"/>
         <v>0.60234739389415504</v>
       </c>
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C398" s="2">
-        <f>C386/C$394</f>
+        <f t="shared" si="77"/>
         <v>0.5</v>
       </c>
       <c r="D398" s="2">
-        <f>D386/D$394</f>
+        <f t="shared" si="77"/>
         <v>0.93399700584921264</v>
       </c>
       <c r="E398" s="2">
-        <f>E386/E$394</f>
+        <f t="shared" si="77"/>
         <v>0.97040124302407327</v>
       </c>
       <c r="F398" s="2">
-        <f>F386/F$394</f>
+        <f t="shared" si="77"/>
         <v>1</v>
       </c>
       <c r="G398" s="2">
-        <f>G386/G$394</f>
+        <f t="shared" si="77"/>
         <v>0.24509363334584758</v>
       </c>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C399" s="2">
-        <f>C387/C$394</f>
+        <f t="shared" si="77"/>
         <v>1</v>
       </c>
       <c r="D399" s="2">
-        <f>D387/D$394</f>
+        <f t="shared" si="77"/>
         <v>0.93331352650149302</v>
       </c>
       <c r="E399" s="2">
-        <f>E387/E$394</f>
+        <f t="shared" si="77"/>
         <v>1</v>
       </c>
       <c r="F399" s="2">
-        <f>F387/F$394</f>
+        <f t="shared" si="77"/>
         <v>0.7459036836904771</v>
       </c>
       <c r="G399" s="2">
-        <f>G387/G$394</f>
+        <f t="shared" si="77"/>
         <v>0.27586813623884487</v>
       </c>
     </row>

--- a/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/industrial sector (VDS_s) 0.xlsx
@@ -8943,6 +8943,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9246,6 +9247,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9906,6 +9908,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10209,6 +10212,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10314,6 +10318,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10617,6 +10622,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10723,6 +10729,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11026,6 +11033,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11132,6 +11140,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11435,6 +11444,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11541,6 +11551,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11844,6 +11855,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11950,6 +11962,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -12253,6 +12266,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -12359,6 +12373,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -12662,6 +12677,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -12768,6 +12784,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13071,6 +13088,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13177,6 +13195,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13480,6 +13499,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13586,6 +13606,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13889,6 +13910,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14961,6 +14983,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -15264,6 +15287,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
